--- a/research/traditional_assets/database/data/chile/chile_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_hotel_gaming.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="snse_enjoy" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.022</v>
+        <v>0.0255</v>
       </c>
       <c r="G2">
-        <v>0.1923738532110091</v>
+        <v>0.1534638994446068</v>
       </c>
       <c r="H2">
-        <v>0.1923738532110091</v>
+        <v>0.1534638994446068</v>
       </c>
       <c r="I2">
-        <v>-0.05676252711317821</v>
+        <v>0.002801490018429957</v>
       </c>
       <c r="J2">
-        <v>-0.05676252711317821</v>
+        <v>0.002801490018429957</v>
       </c>
       <c r="K2">
-        <v>-86</v>
+        <v>-139.4</v>
       </c>
       <c r="L2">
-        <v>-0.2465596330275229</v>
+        <v>-0.4074831920491084</v>
       </c>
       <c r="M2">
-        <v>0.8129999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="N2">
-        <v>0.02073979591836734</v>
+        <v>0.1096774193548387</v>
       </c>
       <c r="O2">
-        <v>-0.009453488372093023</v>
+        <v>-0.00975609756097561</v>
       </c>
       <c r="P2">
-        <v>0.8129999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="Q2">
-        <v>0.02073979591836734</v>
+        <v>0.1096774193548387</v>
       </c>
       <c r="R2">
-        <v>-0.009453488372093023</v>
+        <v>-0.00975609756097561</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>26.7</v>
+        <v>15.8</v>
       </c>
       <c r="V2">
-        <v>0.6811224489795917</v>
+        <v>1.274193548387097</v>
       </c>
       <c r="W2">
-        <v>-0.5043988269794721</v>
+        <v>-1.481402763018066</v>
       </c>
       <c r="X2">
-        <v>0.3397219802075209</v>
+        <v>0.9204619395787169</v>
       </c>
       <c r="Y2">
-        <v>-0.844120807186993</v>
+        <v>-2.401864702596783</v>
       </c>
       <c r="Z2">
-        <v>0.7951056373705288</v>
+        <v>0.898435429742054</v>
       </c>
       <c r="AA2">
-        <v>-0.04513220529908548</v>
+        <v>0.002516957888626193</v>
       </c>
       <c r="AB2">
-        <v>0.1345367583431664</v>
+        <v>0.2038860609043269</v>
       </c>
       <c r="AC2">
-        <v>-0.1796689636422518</v>
+        <v>-0.2013691030157007</v>
       </c>
       <c r="AD2">
-        <v>314.6</v>
+        <v>346.4</v>
       </c>
       <c r="AE2">
-        <v>1.743847285382802</v>
+        <v>0.2330513234755586</v>
       </c>
       <c r="AF2">
-        <v>316.3438472853828</v>
+        <v>346.6330513234755</v>
       </c>
       <c r="AG2">
-        <v>289.6438472853828</v>
+        <v>330.8330513234755</v>
       </c>
       <c r="AH2">
-        <v>0.889746369401984</v>
+        <v>0.9654627896950132</v>
       </c>
       <c r="AI2">
-        <v>0.7864479454944754</v>
+        <v>1.193504147492519</v>
       </c>
       <c r="AJ2">
-        <v>0.8807944855176786</v>
+        <v>0.963872943027524</v>
       </c>
       <c r="AK2">
-        <v>0.7712650583389188</v>
+        <v>1.204636695143459</v>
       </c>
       <c r="AL2">
-        <v>81.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="AM2">
-        <v>81.062</v>
+        <v>84.294</v>
       </c>
       <c r="AN2">
-        <v>9.293943870014772</v>
+        <v>7.236718407253432</v>
       </c>
       <c r="AO2">
-        <v>-0.2564734895191123</v>
+        <v>0.0110093896713615</v>
       </c>
       <c r="AP2">
-        <v>8.556686773571132</v>
+        <v>6.911505866744846</v>
       </c>
       <c r="AQ2">
-        <v>-0.2565937183883941</v>
+        <v>0.01112771964789902</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +721,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.022</v>
+        <v>0.0255</v>
       </c>
       <c r="G3">
-        <v>0.1923738532110091</v>
+        <v>0.1534638994446068</v>
       </c>
       <c r="H3">
-        <v>0.1923738532110091</v>
+        <v>0.1534638994446068</v>
       </c>
       <c r="I3">
-        <v>-0.05676252711317821</v>
+        <v>0.002801490018429957</v>
       </c>
       <c r="J3">
-        <v>-0.05676252711317821</v>
+        <v>0.002801490018429957</v>
       </c>
       <c r="K3">
-        <v>-86</v>
+        <v>-139.4</v>
       </c>
       <c r="L3">
-        <v>-0.2465596330275229</v>
+        <v>-0.4074831920491084</v>
       </c>
       <c r="M3">
-        <v>0.8129999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="N3">
-        <v>0.02073979591836734</v>
+        <v>0.1096774193548387</v>
       </c>
       <c r="O3">
-        <v>-0.009453488372093023</v>
+        <v>-0.00975609756097561</v>
       </c>
       <c r="P3">
-        <v>0.8129999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="Q3">
-        <v>0.02073979591836734</v>
+        <v>0.1096774193548387</v>
       </c>
       <c r="R3">
-        <v>-0.009453488372093023</v>
+        <v>-0.00975609756097561</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +766,8842 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>26.7</v>
+        <v>15.8</v>
       </c>
       <c r="V3">
-        <v>0.6811224489795917</v>
+        <v>1.274193548387097</v>
       </c>
       <c r="W3">
-        <v>-0.5043988269794721</v>
+        <v>-1.481402763018066</v>
       </c>
       <c r="X3">
-        <v>0.3397219802075209</v>
+        <v>0.9204619395787169</v>
       </c>
       <c r="Y3">
-        <v>-0.844120807186993</v>
+        <v>-2.401864702596783</v>
       </c>
       <c r="Z3">
-        <v>0.7951056373705288</v>
+        <v>0.898435429742054</v>
       </c>
       <c r="AA3">
-        <v>-0.04513220529908548</v>
+        <v>0.002516957888626193</v>
       </c>
       <c r="AB3">
-        <v>0.1345367583431664</v>
+        <v>0.2038860609043269</v>
       </c>
       <c r="AC3">
-        <v>-0.1796689636422518</v>
+        <v>-0.2013691030157007</v>
       </c>
       <c r="AD3">
-        <v>314.6</v>
+        <v>346.4</v>
       </c>
       <c r="AE3">
-        <v>1.743847285382802</v>
+        <v>0.2330513234755586</v>
       </c>
       <c r="AF3">
-        <v>316.3438472853828</v>
+        <v>346.6330513234755</v>
       </c>
       <c r="AG3">
-        <v>289.6438472853828</v>
+        <v>330.8330513234755</v>
       </c>
       <c r="AH3">
-        <v>0.889746369401984</v>
+        <v>0.9654627896950132</v>
       </c>
       <c r="AI3">
-        <v>0.7864479454944754</v>
+        <v>1.193504147492519</v>
       </c>
       <c r="AJ3">
-        <v>0.8807944855176786</v>
+        <v>0.963872943027524</v>
       </c>
       <c r="AK3">
-        <v>0.7712650583389188</v>
+        <v>1.204636695143459</v>
       </c>
       <c r="AL3">
-        <v>81.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="AM3">
-        <v>81.062</v>
+        <v>84.294</v>
       </c>
       <c r="AN3">
-        <v>9.293943870014772</v>
+        <v>7.236718407253432</v>
       </c>
       <c r="AO3">
-        <v>-0.2564734895191123</v>
+        <v>0.0110093896713615</v>
       </c>
       <c r="AP3">
-        <v>8.556686773571132</v>
+        <v>6.911505866744846</v>
       </c>
       <c r="AQ3">
-        <v>-0.2565937183883941</v>
+        <v>0.01112771964789902</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Enjoy S.A. (SNSE:ENJOY)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SNSE:ENJOY</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0117957746478874</v>
+      </c>
+      <c r="F2">
+        <v>4.56376656645041</v>
+      </c>
+      <c r="G2">
+        <v>7.24158713358839</v>
+      </c>
+      <c r="H2">
+        <v>3.37528721448104</v>
+      </c>
+      <c r="I2">
+        <v>0.965462789695013</v>
+      </c>
+      <c r="J2">
+        <v>0.45</v>
+      </c>
+      <c r="K2">
+        <v>12.4</v>
+      </c>
+      <c r="L2">
+        <v>1318.42299009129</v>
+      </c>
+      <c r="M2">
+        <v>343.233051323475</v>
+      </c>
+      <c r="N2">
+        <v>1464.18786318686</v>
+      </c>
+      <c r="O2">
+        <v>346.633051323476</v>
+      </c>
+      <c r="P2">
+        <v>161.564873095564</v>
+      </c>
+      <c r="Q2">
+        <v>0.203886060904327</v>
+      </c>
+      <c r="R2">
+        <v>0.0828583327591592</v>
+      </c>
+      <c r="S2">
+        <v>0.178252207289859</v>
+      </c>
+      <c r="T2">
+        <v>0.0483852072898587</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.920461939578717</v>
+      </c>
+      <c r="X2">
+        <v>0.111063617234041</v>
+      </c>
+      <c r="Y2">
+        <v>16.0131796181652</v>
+      </c>
+      <c r="Z2">
+        <v>1.1948365168413</v>
+      </c>
+      <c r="AA2">
+        <v>346.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.2441811058765187</v>
+      </c>
+      <c r="AC2">
+        <v>0.01179577464788735</v>
+      </c>
+      <c r="AD2">
+        <v>346.6330513234755</v>
+      </c>
+      <c r="AE2">
+        <v>85.2</v>
+      </c>
+      <c r="AF2">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="AG2">
+        <v>47.867</v>
+      </c>
+      <c r="AH2">
+        <v>0.008381105876518725</v>
+      </c>
+      <c r="AI2">
+        <v>0.0458</v>
+      </c>
+      <c r="AJ2">
+        <v>12.4</v>
+      </c>
+      <c r="AK2">
+        <v>0.05462137816692637</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.27</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>51.752</v>
+      </c>
+      <c r="AR2">
+        <v>85.2</v>
+      </c>
+      <c r="AT2">
+        <v>15.8</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08665940748858603</v>
+      </c>
+      <c r="C2">
+        <v>1343.777187898733</v>
+      </c>
+      <c r="D2">
+        <v>1327.977187898733</v>
+      </c>
+      <c r="E2">
+        <v>-346.6330513234755</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>15.8</v>
+      </c>
+      <c r="H2">
+        <v>12.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K2">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L2">
+        <v>48.872</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>48.872</v>
+      </c>
+      <c r="O2">
+        <v>13.19544</v>
+      </c>
+      <c r="P2">
+        <v>35.67655999999999</v>
+      </c>
+      <c r="Q2">
+        <v>82.53855999999999</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08665940748858603</v>
+      </c>
+      <c r="T2">
+        <v>0.7480479046815169</v>
+      </c>
+      <c r="U2">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V2">
+        <v>0.27</v>
+      </c>
+      <c r="W2">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08652967916126544</v>
+      </c>
+      <c r="C3">
+        <v>1344.416604902632</v>
+      </c>
+      <c r="D3">
+        <v>1332.206935415866</v>
+      </c>
+      <c r="E3">
+        <v>-343.0427208102408</v>
+      </c>
+      <c r="F3">
+        <v>3.590330513234755</v>
+      </c>
+      <c r="G3">
+        <v>15.8</v>
+      </c>
+      <c r="H3">
+        <v>12.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K3">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L3">
+        <v>48.872</v>
+      </c>
+      <c r="M3">
+        <v>0.2157110276973531</v>
+      </c>
+      <c r="N3">
+        <v>48.65628897230265</v>
+      </c>
+      <c r="O3">
+        <v>13.13719802252172</v>
+      </c>
+      <c r="P3">
+        <v>35.51909094978093</v>
+      </c>
+      <c r="Q3">
+        <v>82.38109094978093</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08696069402865339</v>
+      </c>
+      <c r="T3">
+        <v>0.753563813473613</v>
+      </c>
+      <c r="U3">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V3">
+        <v>0.27</v>
+      </c>
+      <c r="W3">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>226.5623622570117</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08639995083394483</v>
+      </c>
+      <c r="C4">
+        <v>1345.083052386082</v>
+      </c>
+      <c r="D4">
+        <v>1336.463713412551</v>
+      </c>
+      <c r="E4">
+        <v>-339.452390297006</v>
+      </c>
+      <c r="F4">
+        <v>7.18066102646951</v>
+      </c>
+      <c r="G4">
+        <v>15.8</v>
+      </c>
+      <c r="H4">
+        <v>12.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K4">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L4">
+        <v>48.872</v>
+      </c>
+      <c r="M4">
+        <v>0.4314220553947063</v>
+      </c>
+      <c r="N4">
+        <v>48.44057794460529</v>
+      </c>
+      <c r="O4">
+        <v>13.07895604504343</v>
+      </c>
+      <c r="P4">
+        <v>35.36162189956187</v>
+      </c>
+      <c r="Q4">
+        <v>82.22362189956186</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08726812927362007</v>
+      </c>
+      <c r="T4">
+        <v>0.7591922918328947</v>
+      </c>
+      <c r="U4">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V4">
+        <v>0.27</v>
+      </c>
+      <c r="W4">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>113.2811811285058</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08627022250662424</v>
+      </c>
+      <c r="C5">
+        <v>1345.77679028975</v>
+      </c>
+      <c r="D5">
+        <v>1340.747781829455</v>
+      </c>
+      <c r="E5">
+        <v>-335.8620597837713</v>
+      </c>
+      <c r="F5">
+        <v>10.77099153970426</v>
+      </c>
+      <c r="G5">
+        <v>15.8</v>
+      </c>
+      <c r="H5">
+        <v>12.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K5">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L5">
+        <v>48.872</v>
+      </c>
+      <c r="M5">
+        <v>0.6471330830920593</v>
+      </c>
+      <c r="N5">
+        <v>48.22486691690794</v>
+      </c>
+      <c r="O5">
+        <v>13.02071406756514</v>
+      </c>
+      <c r="P5">
+        <v>35.2041528493428</v>
+      </c>
+      <c r="Q5">
+        <v>82.06615284934279</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08758190338961699</v>
+      </c>
+      <c r="T5">
+        <v>0.7649368212923677</v>
+      </c>
+      <c r="U5">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V5">
+        <v>0.27</v>
+      </c>
+      <c r="W5">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>75.52078741900391</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08614049417930367</v>
+      </c>
+      <c r="C6">
+        <v>1346.49808189801</v>
+      </c>
+      <c r="D6">
+        <v>1345.059403950949</v>
+      </c>
+      <c r="E6">
+        <v>-332.2717292705365</v>
+      </c>
+      <c r="F6">
+        <v>14.36132205293902</v>
+      </c>
+      <c r="G6">
+        <v>15.8</v>
+      </c>
+      <c r="H6">
+        <v>12.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K6">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L6">
+        <v>48.872</v>
+      </c>
+      <c r="M6">
+        <v>0.8628441107894126</v>
+      </c>
+      <c r="N6">
+        <v>48.00915588921059</v>
+      </c>
+      <c r="O6">
+        <v>12.96247209008686</v>
+      </c>
+      <c r="P6">
+        <v>35.04668379912373</v>
+      </c>
+      <c r="Q6">
+        <v>81.90868379912372</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08790221446636387</v>
+      </c>
+      <c r="T6">
+        <v>0.7708010284489132</v>
+      </c>
+      <c r="U6">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V6">
+        <v>0.27</v>
+      </c>
+      <c r="W6">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>56.64059056425292</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08601076585198304</v>
+      </c>
+      <c r="C7">
+        <v>1347.247193892877</v>
+      </c>
+      <c r="D7">
+        <v>1349.398846459051</v>
+      </c>
+      <c r="E7">
+        <v>-328.6813987573017</v>
+      </c>
+      <c r="F7">
+        <v>17.95165256617377</v>
+      </c>
+      <c r="G7">
+        <v>15.8</v>
+      </c>
+      <c r="H7">
+        <v>12.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K7">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L7">
+        <v>48.872</v>
+      </c>
+      <c r="M7">
+        <v>1.078555138486766</v>
+      </c>
+      <c r="N7">
+        <v>47.79344486151324</v>
+      </c>
+      <c r="O7">
+        <v>12.90423011260857</v>
+      </c>
+      <c r="P7">
+        <v>34.88921474890466</v>
+      </c>
+      <c r="Q7">
+        <v>81.75121474890466</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08822926893420012</v>
+      </c>
+      <c r="T7">
+        <v>0.7767886925982278</v>
+      </c>
+      <c r="U7">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V7">
+        <v>0.27</v>
+      </c>
+      <c r="W7">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>45.31247245140234</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08588103752466246</v>
+      </c>
+      <c r="C8">
+        <v>1348.024396408989</v>
+      </c>
+      <c r="D8">
+        <v>1353.766379488398</v>
+      </c>
+      <c r="E8">
+        <v>-325.091068244067</v>
+      </c>
+      <c r="F8">
+        <v>21.54198307940853</v>
+      </c>
+      <c r="G8">
+        <v>15.8</v>
+      </c>
+      <c r="H8">
+        <v>12.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K8">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L8">
+        <v>48.872</v>
+      </c>
+      <c r="M8">
+        <v>1.294266166184119</v>
+      </c>
+      <c r="N8">
+        <v>47.57773383381588</v>
+      </c>
+      <c r="O8">
+        <v>12.84598813513029</v>
+      </c>
+      <c r="P8">
+        <v>34.73174569868559</v>
+      </c>
+      <c r="Q8">
+        <v>81.59374569868558</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08856328200773504</v>
+      </c>
+      <c r="T8">
+        <v>0.7829037538571025</v>
+      </c>
+      <c r="U8">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V8">
+        <v>0.27</v>
+      </c>
+      <c r="W8">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>37.76039370950195</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08575130919734186</v>
+      </c>
+      <c r="C9">
+        <v>1348.829963089671</v>
+      </c>
+      <c r="D9">
+        <v>1358.162276682314</v>
+      </c>
+      <c r="E9">
+        <v>-321.5007377308322</v>
+      </c>
+      <c r="F9">
+        <v>25.13231359264329</v>
+      </c>
+      <c r="G9">
+        <v>15.8</v>
+      </c>
+      <c r="H9">
+        <v>12.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K9">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L9">
+        <v>48.872</v>
+      </c>
+      <c r="M9">
+        <v>1.509977193881472</v>
+      </c>
+      <c r="N9">
+        <v>47.36202280611852</v>
+      </c>
+      <c r="O9">
+        <v>12.787746157652</v>
+      </c>
+      <c r="P9">
+        <v>34.57427664846652</v>
+      </c>
+      <c r="Q9">
+        <v>81.43627664846652</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08890447815812016</v>
+      </c>
+      <c r="T9">
+        <v>0.7891503218097164</v>
+      </c>
+      <c r="U9">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V9">
+        <v>0.27</v>
+      </c>
+      <c r="W9">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>32.36605175100166</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08562158087002127</v>
+      </c>
+      <c r="C10">
+        <v>1349.66417114408</v>
+      </c>
+      <c r="D10">
+        <v>1362.586815249958</v>
+      </c>
+      <c r="E10">
+        <v>-317.9104072175975</v>
+      </c>
+      <c r="F10">
+        <v>28.72264410587804</v>
+      </c>
+      <c r="G10">
+        <v>15.8</v>
+      </c>
+      <c r="H10">
+        <v>12.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K10">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L10">
+        <v>48.872</v>
+      </c>
+      <c r="M10">
+        <v>1.725688221578825</v>
+      </c>
+      <c r="N10">
+        <v>47.14631177842117</v>
+      </c>
+      <c r="O10">
+        <v>12.72950418017372</v>
+      </c>
+      <c r="P10">
+        <v>34.41680759824745</v>
+      </c>
+      <c r="Q10">
+        <v>81.27880759824745</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08925309161612235</v>
+      </c>
+      <c r="T10">
+        <v>0.7955326847178219</v>
+      </c>
+      <c r="U10">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V10">
+        <v>0.27</v>
+      </c>
+      <c r="W10">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>28.32029528212646</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08549185254270067</v>
+      </c>
+      <c r="C11">
+        <v>1350.527301405479</v>
+      </c>
+      <c r="D11">
+        <v>1367.040276024592</v>
+      </c>
+      <c r="E11">
+        <v>-314.3200767043627</v>
+      </c>
+      <c r="F11">
+        <v>32.31297461911279</v>
+      </c>
+      <c r="G11">
+        <v>15.8</v>
+      </c>
+      <c r="H11">
+        <v>12.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K11">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L11">
+        <v>48.872</v>
+      </c>
+      <c r="M11">
+        <v>1.941399249276178</v>
+      </c>
+      <c r="N11">
+        <v>46.93060075072382</v>
+      </c>
+      <c r="O11">
+        <v>12.67126220269543</v>
+      </c>
+      <c r="P11">
+        <v>34.25933854802839</v>
+      </c>
+      <c r="Q11">
+        <v>81.12133854802838</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08960936690836636</v>
+      </c>
+      <c r="T11">
+        <v>0.8020553193381935</v>
+      </c>
+      <c r="U11">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V11">
+        <v>0.27</v>
+      </c>
+      <c r="W11">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>25.17359580633463</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08536212421538009</v>
+      </c>
+      <c r="C12">
+        <v>1351.419638390659</v>
+      </c>
+      <c r="D12">
+        <v>1371.522943523007</v>
+      </c>
+      <c r="E12">
+        <v>-310.729746191128</v>
+      </c>
+      <c r="F12">
+        <v>35.90330513234755</v>
+      </c>
+      <c r="G12">
+        <v>15.8</v>
+      </c>
+      <c r="H12">
+        <v>12.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K12">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L12">
+        <v>48.872</v>
+      </c>
+      <c r="M12">
+        <v>2.157110276973531</v>
+      </c>
+      <c r="N12">
+        <v>46.71488972302647</v>
+      </c>
+      <c r="O12">
+        <v>12.61302022521715</v>
+      </c>
+      <c r="P12">
+        <v>34.10186949780932</v>
+      </c>
+      <c r="Q12">
+        <v>80.96386949780931</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.0899735594293269</v>
+      </c>
+      <c r="T12">
+        <v>0.8087229013945734</v>
+      </c>
+      <c r="U12">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V12">
+        <v>0.27</v>
+      </c>
+      <c r="W12">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>22.65623622570117</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08523239588805948</v>
+      </c>
+      <c r="C13">
+        <v>1352.34147036053</v>
+      </c>
+      <c r="D13">
+        <v>1376.035106006112</v>
+      </c>
+      <c r="E13">
+        <v>-307.1394156778932</v>
+      </c>
+      <c r="F13">
+        <v>39.4936356455823</v>
+      </c>
+      <c r="G13">
+        <v>15.8</v>
+      </c>
+      <c r="H13">
+        <v>12.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K13">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L13">
+        <v>48.872</v>
+      </c>
+      <c r="M13">
+        <v>2.372821304670884</v>
+      </c>
+      <c r="N13">
+        <v>46.49917869532911</v>
+      </c>
+      <c r="O13">
+        <v>12.55477824773886</v>
+      </c>
+      <c r="P13">
+        <v>33.94440044759025</v>
+      </c>
+      <c r="Q13">
+        <v>80.80640044759025</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09034593605188206</v>
+      </c>
+      <c r="T13">
+        <v>0.8155403167555909</v>
+      </c>
+      <c r="U13">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V13">
+        <v>0.27</v>
+      </c>
+      <c r="W13">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>20.59657838700106</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08510266756073889</v>
+      </c>
+      <c r="C14">
+        <v>1353.293089381909</v>
+      </c>
+      <c r="D14">
+        <v>1380.577055540726</v>
+      </c>
+      <c r="E14">
+        <v>-303.5490851646584</v>
+      </c>
+      <c r="F14">
+        <v>43.08396615881706</v>
+      </c>
+      <c r="G14">
+        <v>15.8</v>
+      </c>
+      <c r="H14">
+        <v>12.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K14">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L14">
+        <v>48.872</v>
+      </c>
+      <c r="M14">
+        <v>2.588532332368237</v>
+      </c>
+      <c r="N14">
+        <v>46.28346766763176</v>
+      </c>
+      <c r="O14">
+        <v>12.49653627026058</v>
+      </c>
+      <c r="P14">
+        <v>33.78693139737118</v>
+      </c>
+      <c r="Q14">
+        <v>80.64893139737117</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09072677577949528</v>
+      </c>
+      <c r="T14">
+        <v>0.8225126733748135</v>
+      </c>
+      <c r="U14">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V14">
+        <v>0.27</v>
+      </c>
+      <c r="W14">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>18.88019685475097</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08497293923341828</v>
+      </c>
+      <c r="C15">
+        <v>1354.274791390547</v>
+      </c>
+      <c r="D15">
+        <v>1385.149088062599</v>
+      </c>
+      <c r="E15">
+        <v>-299.9587546514237</v>
+      </c>
+      <c r="F15">
+        <v>46.67429667205182</v>
+      </c>
+      <c r="G15">
+        <v>15.8</v>
+      </c>
+      <c r="H15">
+        <v>12.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K15">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L15">
+        <v>48.872</v>
+      </c>
+      <c r="M15">
+        <v>2.804243360065591</v>
+      </c>
+      <c r="N15">
+        <v>46.06775663993441</v>
+      </c>
+      <c r="O15">
+        <v>12.43829429278229</v>
+      </c>
+      <c r="P15">
+        <v>33.62946234715211</v>
+      </c>
+      <c r="Q15">
+        <v>80.49146234715211</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09111637044337548</v>
+      </c>
+      <c r="T15">
+        <v>0.8296453140542479</v>
+      </c>
+      <c r="U15">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V15">
+        <v>0.27</v>
+      </c>
+      <c r="W15">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>17.42787401977013</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08484321090609769</v>
+      </c>
+      <c r="C16">
+        <v>1355.286876255396</v>
+      </c>
+      <c r="D16">
+        <v>1389.751503440683</v>
+      </c>
+      <c r="E16">
+        <v>-296.368424138189</v>
+      </c>
+      <c r="F16">
+        <v>50.26462718528657</v>
+      </c>
+      <c r="G16">
+        <v>15.8</v>
+      </c>
+      <c r="H16">
+        <v>12.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K16">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L16">
+        <v>48.872</v>
+      </c>
+      <c r="M16">
+        <v>3.019954387762944</v>
+      </c>
+      <c r="N16">
+        <v>45.85204561223706</v>
+      </c>
+      <c r="O16">
+        <v>12.38005231530401</v>
+      </c>
+      <c r="P16">
+        <v>33.47199329693305</v>
+      </c>
+      <c r="Q16">
+        <v>80.33399329693304</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09151502544827614</v>
+      </c>
+      <c r="T16">
+        <v>0.8369438300983204</v>
+      </c>
+      <c r="U16">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V16">
+        <v>0.27</v>
+      </c>
+      <c r="W16">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>16.18302587550083</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.0847134825787771</v>
+      </c>
+      <c r="C17">
+        <v>1356.329647844181</v>
+      </c>
+      <c r="D17">
+        <v>1394.384605542702</v>
+      </c>
+      <c r="E17">
+        <v>-292.7780936249542</v>
+      </c>
+      <c r="F17">
+        <v>53.85495769852132</v>
+      </c>
+      <c r="G17">
+        <v>15.8</v>
+      </c>
+      <c r="H17">
+        <v>12.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K17">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L17">
+        <v>48.872</v>
+      </c>
+      <c r="M17">
+        <v>3.235665415460297</v>
+      </c>
+      <c r="N17">
+        <v>45.6363345845397</v>
+      </c>
+      <c r="O17">
+        <v>12.32181033782572</v>
+      </c>
+      <c r="P17">
+        <v>33.31452424671399</v>
+      </c>
+      <c r="Q17">
+        <v>80.17652424671398</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09192306057093919</v>
+      </c>
+      <c r="T17">
+        <v>0.8444140759316654</v>
+      </c>
+      <c r="U17">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V17">
+        <v>0.27</v>
+      </c>
+      <c r="W17">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>15.10415748380078</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08458375425145651</v>
+      </c>
+      <c r="C18">
+        <v>1357.40341409027</v>
+      </c>
+      <c r="D18">
+        <v>1399.048702302026</v>
+      </c>
+      <c r="E18">
+        <v>-289.1877631117194</v>
+      </c>
+      <c r="F18">
+        <v>57.44528821175608</v>
+      </c>
+      <c r="G18">
+        <v>15.8</v>
+      </c>
+      <c r="H18">
+        <v>12.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K18">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L18">
+        <v>48.872</v>
+      </c>
+      <c r="M18">
+        <v>3.45137644315765</v>
+      </c>
+      <c r="N18">
+        <v>45.42062355684235</v>
+      </c>
+      <c r="O18">
+        <v>12.26356836034743</v>
+      </c>
+      <c r="P18">
+        <v>33.15705519649492</v>
+      </c>
+      <c r="Q18">
+        <v>80.01905519649492</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09234081081557038</v>
+      </c>
+      <c r="T18">
+        <v>0.8520621847610422</v>
+      </c>
+      <c r="U18">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V18">
+        <v>0.27</v>
+      </c>
+      <c r="W18">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>14.16014764106323</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08445402592413589</v>
+      </c>
+      <c r="C19">
+        <v>1358.508487060903</v>
+      </c>
+      <c r="D19">
+        <v>1403.744105785894</v>
+      </c>
+      <c r="E19">
+        <v>-285.5974325984847</v>
+      </c>
+      <c r="F19">
+        <v>61.03561872499084</v>
+      </c>
+      <c r="G19">
+        <v>15.8</v>
+      </c>
+      <c r="H19">
+        <v>12.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K19">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L19">
+        <v>48.872</v>
+      </c>
+      <c r="M19">
+        <v>3.667087470855004</v>
+      </c>
+      <c r="N19">
+        <v>45.204912529145</v>
+      </c>
+      <c r="O19">
+        <v>12.20532638286915</v>
+      </c>
+      <c r="P19">
+        <v>32.99958614627585</v>
+      </c>
+      <c r="Q19">
+        <v>79.86158614627584</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09276862733115654</v>
+      </c>
+      <c r="T19">
+        <v>0.8598945853694402</v>
+      </c>
+      <c r="U19">
+        <v>0.06008110587651873</v>
+      </c>
+      <c r="V19">
+        <v>0.27</v>
+      </c>
+      <c r="W19">
+        <v>0.04385920728985867</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>13.32719777982421</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08446883759681532</v>
+      </c>
+      <c r="C20">
+        <v>1354.380467816567</v>
+      </c>
+      <c r="D20">
+        <v>1403.206417054793</v>
+      </c>
+      <c r="E20">
+        <v>-282.0071020852499</v>
+      </c>
+      <c r="F20">
+        <v>64.62594923822559</v>
+      </c>
+      <c r="G20">
+        <v>15.8</v>
+      </c>
+      <c r="H20">
+        <v>12.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K20">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L20">
+        <v>48.872</v>
+      </c>
+      <c r="M20">
+        <v>3.953887042714404</v>
+      </c>
+      <c r="N20">
+        <v>44.91811295728559</v>
+      </c>
+      <c r="O20">
+        <v>12.12789049846711</v>
+      </c>
+      <c r="P20">
+        <v>32.79022245881848</v>
+      </c>
+      <c r="Q20">
+        <v>79.65222245881847</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09320687839590336</v>
+      </c>
+      <c r="T20">
+        <v>0.8679180201390185</v>
+      </c>
+      <c r="U20">
+        <v>0.06118110587651873</v>
+      </c>
+      <c r="V20">
+        <v>0.27</v>
+      </c>
+      <c r="W20">
+        <v>0.04466220728985867</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>12.36049474151103</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08434713926949471</v>
+      </c>
+      <c r="C21">
+        <v>1355.220242288485</v>
+      </c>
+      <c r="D21">
+        <v>1407.636522039945</v>
+      </c>
+      <c r="E21">
+        <v>-278.4167715720151</v>
+      </c>
+      <c r="F21">
+        <v>68.21627975146035</v>
+      </c>
+      <c r="G21">
+        <v>15.8</v>
+      </c>
+      <c r="H21">
+        <v>12.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K21">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L21">
+        <v>48.872</v>
+      </c>
+      <c r="M21">
+        <v>4.173547433976316</v>
+      </c>
+      <c r="N21">
+        <v>44.69845256602368</v>
+      </c>
+      <c r="O21">
+        <v>12.0685821928264</v>
+      </c>
+      <c r="P21">
+        <v>32.62987037319729</v>
+      </c>
+      <c r="Q21">
+        <v>79.49187037319729</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09365595047459452</v>
+      </c>
+      <c r="T21">
+        <v>0.8761395644090804</v>
+      </c>
+      <c r="U21">
+        <v>0.06118110587651873</v>
+      </c>
+      <c r="V21">
+        <v>0.27</v>
+      </c>
+      <c r="W21">
+        <v>0.04466220728985867</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>11.70994238669466</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08422544094217412</v>
+      </c>
+      <c r="C22">
+        <v>1356.088078188107</v>
+      </c>
+      <c r="D22">
+        <v>1412.094688452802</v>
+      </c>
+      <c r="E22">
+        <v>-274.8264410587804</v>
+      </c>
+      <c r="F22">
+        <v>71.8066102646951</v>
+      </c>
+      <c r="G22">
+        <v>15.8</v>
+      </c>
+      <c r="H22">
+        <v>12.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K22">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L22">
+        <v>48.872</v>
+      </c>
+      <c r="M22">
+        <v>4.393207825238227</v>
+      </c>
+      <c r="N22">
+        <v>44.47879217476177</v>
+      </c>
+      <c r="O22">
+        <v>12.00927388718568</v>
+      </c>
+      <c r="P22">
+        <v>32.46951828757609</v>
+      </c>
+      <c r="Q22">
+        <v>79.33151828757609</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09411624935525298</v>
+      </c>
+      <c r="T22">
+        <v>0.8845666472858938</v>
+      </c>
+      <c r="U22">
+        <v>0.06118110587651873</v>
+      </c>
+      <c r="V22">
+        <v>0.27</v>
+      </c>
+      <c r="W22">
+        <v>0.04466220728985867</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>11.12444526735993</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08410374261485354</v>
+      </c>
+      <c r="C23">
+        <v>1356.984242985029</v>
+      </c>
+      <c r="D23">
+        <v>1416.581183762959</v>
+      </c>
+      <c r="E23">
+        <v>-271.2361105455457</v>
+      </c>
+      <c r="F23">
+        <v>75.39694077792986</v>
+      </c>
+      <c r="G23">
+        <v>15.8</v>
+      </c>
+      <c r="H23">
+        <v>12.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K23">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L23">
+        <v>48.872</v>
+      </c>
+      <c r="M23">
+        <v>4.612868216500138</v>
+      </c>
+      <c r="N23">
+        <v>44.25913178349986</v>
+      </c>
+      <c r="O23">
+        <v>11.94996558154496</v>
+      </c>
+      <c r="P23">
+        <v>32.30916620195489</v>
+      </c>
+      <c r="Q23">
+        <v>79.17116620195489</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09458820137213064</v>
+      </c>
+      <c r="T23">
+        <v>0.8932070740330063</v>
+      </c>
+      <c r="U23">
+        <v>0.06118110587651873</v>
+      </c>
+      <c r="V23">
+        <v>0.27</v>
+      </c>
+      <c r="W23">
+        <v>0.04466220728985867</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>10.59470977843803</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08398204428753293</v>
+      </c>
+      <c r="C24">
+        <v>1357.909007558887</v>
+      </c>
+      <c r="D24">
+        <v>1421.096278850051</v>
+      </c>
+      <c r="E24">
+        <v>-267.6457800323109</v>
+      </c>
+      <c r="F24">
+        <v>78.9872712911646</v>
+      </c>
+      <c r="G24">
+        <v>15.8</v>
+      </c>
+      <c r="H24">
+        <v>12.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K24">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L24">
+        <v>48.872</v>
+      </c>
+      <c r="M24">
+        <v>4.83252860776205</v>
+      </c>
+      <c r="N24">
+        <v>44.03947139223795</v>
+      </c>
+      <c r="O24">
+        <v>11.89065727590425</v>
+      </c>
+      <c r="P24">
+        <v>32.1488141163337</v>
+      </c>
+      <c r="Q24">
+        <v>79.01081411633371</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09507225472277439</v>
+      </c>
+      <c r="T24">
+        <v>0.9020690501838908</v>
+      </c>
+      <c r="U24">
+        <v>0.06118110587651873</v>
+      </c>
+      <c r="V24">
+        <v>0.27</v>
+      </c>
+      <c r="W24">
+        <v>0.04466220728985867</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>10.1131320612363</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08422972596021233</v>
+      </c>
+      <c r="C25">
+        <v>1345.159634284107</v>
+      </c>
+      <c r="D25">
+        <v>1411.937236088506</v>
+      </c>
+      <c r="E25">
+        <v>-264.0554495190761</v>
+      </c>
+      <c r="F25">
+        <v>82.57760180439936</v>
+      </c>
+      <c r="G25">
+        <v>15.8</v>
+      </c>
+      <c r="H25">
+        <v>12.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K25">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L25">
+        <v>48.872</v>
+      </c>
+      <c r="M25">
+        <v>5.23385972299364</v>
+      </c>
+      <c r="N25">
+        <v>43.63814027700636</v>
+      </c>
+      <c r="O25">
+        <v>11.78229787479172</v>
+      </c>
+      <c r="P25">
+        <v>31.85584240221464</v>
+      </c>
+      <c r="Q25">
+        <v>78.71784240221464</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09556888088772056</v>
+      </c>
+      <c r="T25">
+        <v>0.9111612075334996</v>
+      </c>
+      <c r="U25">
+        <v>0.06338110587651873</v>
+      </c>
+      <c r="V25">
+        <v>0.27</v>
+      </c>
+      <c r="W25">
+        <v>0.04626820728985867</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>9.337659506863208</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08412408763289174</v>
+      </c>
+      <c r="C26">
+        <v>1345.461234332424</v>
+      </c>
+      <c r="D26">
+        <v>1415.829166650058</v>
+      </c>
+      <c r="E26">
+        <v>-260.4651190058414</v>
+      </c>
+      <c r="F26">
+        <v>86.16793231763411</v>
+      </c>
+      <c r="G26">
+        <v>15.8</v>
+      </c>
+      <c r="H26">
+        <v>12.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K26">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L26">
+        <v>48.872</v>
+      </c>
+      <c r="M26">
+        <v>5.461418841384667</v>
+      </c>
+      <c r="N26">
+        <v>43.41058115861533</v>
+      </c>
+      <c r="O26">
+        <v>11.72085691282614</v>
+      </c>
+      <c r="P26">
+        <v>31.68972424578919</v>
+      </c>
+      <c r="Q26">
+        <v>78.55172424578919</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.0960785761622706</v>
+      </c>
+      <c r="T26">
+        <v>0.9204926321817825</v>
+      </c>
+      <c r="U26">
+        <v>0.06338110587651873</v>
+      </c>
+      <c r="V26">
+        <v>0.27</v>
+      </c>
+      <c r="W26">
+        <v>0.04626820728985867</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>8.948590360743909</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08401844930557115</v>
+      </c>
+      <c r="C27">
+        <v>1345.784349488865</v>
+      </c>
+      <c r="D27">
+        <v>1419.742612319734</v>
+      </c>
+      <c r="E27">
+        <v>-256.8747884926066</v>
+      </c>
+      <c r="F27">
+        <v>89.75826283086887</v>
+      </c>
+      <c r="G27">
+        <v>15.8</v>
+      </c>
+      <c r="H27">
+        <v>12.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K27">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L27">
+        <v>48.872</v>
+      </c>
+      <c r="M27">
+        <v>5.688977959775696</v>
+      </c>
+      <c r="N27">
+        <v>43.1830220402243</v>
+      </c>
+      <c r="O27">
+        <v>11.65941595086056</v>
+      </c>
+      <c r="P27">
+        <v>31.52360608936374</v>
+      </c>
+      <c r="Q27">
+        <v>78.38560608936373</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09660186331080864</v>
+      </c>
+      <c r="T27">
+        <v>0.9300728948206861</v>
+      </c>
+      <c r="U27">
+        <v>0.06338110587651873</v>
+      </c>
+      <c r="V27">
+        <v>0.27</v>
+      </c>
+      <c r="W27">
+        <v>0.04626820728985867</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>8.59064674631415</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08391281097825054</v>
+      </c>
+      <c r="C28">
+        <v>1346.129158655483</v>
+      </c>
+      <c r="D28">
+        <v>1423.677751999587</v>
+      </c>
+      <c r="E28">
+        <v>-253.2844579793719</v>
+      </c>
+      <c r="F28">
+        <v>93.34859334410363</v>
+      </c>
+      <c r="G28">
+        <v>15.8</v>
+      </c>
+      <c r="H28">
+        <v>12.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K28">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L28">
+        <v>48.872</v>
+      </c>
+      <c r="M28">
+        <v>5.916537078166724</v>
+      </c>
+      <c r="N28">
+        <v>42.95546292183327</v>
+      </c>
+      <c r="O28">
+        <v>11.59797498889498</v>
+      </c>
+      <c r="P28">
+        <v>31.35748793293829</v>
+      </c>
+      <c r="Q28">
+        <v>78.21948793293828</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09713929335525309</v>
+      </c>
+      <c r="T28">
+        <v>0.9399120834768573</v>
+      </c>
+      <c r="U28">
+        <v>0.06338110587651873</v>
+      </c>
+      <c r="V28">
+        <v>0.27</v>
+      </c>
+      <c r="W28">
+        <v>0.04626820728985867</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>8.260237256071299</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08380717265092995</v>
+      </c>
+      <c r="C29">
+        <v>1346.495842723314</v>
+      </c>
+      <c r="D29">
+        <v>1427.634766580652</v>
+      </c>
+      <c r="E29">
+        <v>-249.6941274661371</v>
+      </c>
+      <c r="F29">
+        <v>96.93892385733839</v>
+      </c>
+      <c r="G29">
+        <v>15.8</v>
+      </c>
+      <c r="H29">
+        <v>12.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K29">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L29">
+        <v>48.872</v>
+      </c>
+      <c r="M29">
+        <v>6.144096196557752</v>
+      </c>
+      <c r="N29">
+        <v>42.72790380344225</v>
+      </c>
+      <c r="O29">
+        <v>11.53653402692941</v>
+      </c>
+      <c r="P29">
+        <v>31.19136977651284</v>
+      </c>
+      <c r="Q29">
+        <v>78.05336977651282</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09769144751050426</v>
+      </c>
+      <c r="T29">
+        <v>0.9500208389455266</v>
+      </c>
+      <c r="U29">
+        <v>0.06338110587651873</v>
+      </c>
+      <c r="V29">
+        <v>0.27</v>
+      </c>
+      <c r="W29">
+        <v>0.04626820728985867</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>7.954302542883473</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08400813432360935</v>
+      </c>
+      <c r="C30">
+        <v>1335.39664333317</v>
+      </c>
+      <c r="D30">
+        <v>1420.125897703743</v>
+      </c>
+      <c r="E30">
+        <v>-246.1037969529024</v>
+      </c>
+      <c r="F30">
+        <v>100.5292543705731</v>
+      </c>
+      <c r="G30">
+        <v>15.8</v>
+      </c>
+      <c r="H30">
+        <v>12.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K30">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L30">
+        <v>48.872</v>
+      </c>
+      <c r="M30">
+        <v>6.522449196504639</v>
+      </c>
+      <c r="N30">
+        <v>42.34955080349536</v>
+      </c>
+      <c r="O30">
+        <v>11.43437871694375</v>
+      </c>
+      <c r="P30">
+        <v>30.91517208655161</v>
+      </c>
+      <c r="Q30">
+        <v>77.77717208655162</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09825893928117907</v>
+      </c>
+      <c r="T30">
+        <v>0.9604103931772142</v>
+      </c>
+      <c r="U30">
+        <v>0.06488110587651873</v>
+      </c>
+      <c r="V30">
+        <v>0.27</v>
+      </c>
+      <c r="W30">
+        <v>0.04736320728985867</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>7.492890864706214</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08391344599628875</v>
+      </c>
+      <c r="C31">
+        <v>1335.334446850411</v>
+      </c>
+      <c r="D31">
+        <v>1423.654031734219</v>
+      </c>
+      <c r="E31">
+        <v>-242.5134664396676</v>
+      </c>
+      <c r="F31">
+        <v>104.1195848838079</v>
+      </c>
+      <c r="G31">
+        <v>15.8</v>
+      </c>
+      <c r="H31">
+        <v>12.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K31">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L31">
+        <v>48.872</v>
+      </c>
+      <c r="M31">
+        <v>6.755393810665518</v>
+      </c>
+      <c r="N31">
+        <v>42.11660618933448</v>
+      </c>
+      <c r="O31">
+        <v>11.37148367112031</v>
+      </c>
+      <c r="P31">
+        <v>30.74512251821417</v>
+      </c>
+      <c r="Q31">
+        <v>77.60712251821417</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09884241673553484</v>
+      </c>
+      <c r="T31">
+        <v>0.9710926109083862</v>
+      </c>
+      <c r="U31">
+        <v>0.06488110587651873</v>
+      </c>
+      <c r="V31">
+        <v>0.27</v>
+      </c>
+      <c r="W31">
+        <v>0.04736320728985867</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>7.23451531764738</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08381875766896815</v>
+      </c>
+      <c r="C32">
+        <v>1335.289824487924</v>
+      </c>
+      <c r="D32">
+        <v>1427.199739884966</v>
+      </c>
+      <c r="E32">
+        <v>-238.9231359264328</v>
+      </c>
+      <c r="F32">
+        <v>107.7099153970426</v>
+      </c>
+      <c r="G32">
+        <v>15.8</v>
+      </c>
+      <c r="H32">
+        <v>12.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K32">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L32">
+        <v>48.872</v>
+      </c>
+      <c r="M32">
+        <v>6.988338424826399</v>
+      </c>
+      <c r="N32">
+        <v>41.8836615751736</v>
+      </c>
+      <c r="O32">
+        <v>11.30858862529687</v>
+      </c>
+      <c r="P32">
+        <v>30.57507294987673</v>
+      </c>
+      <c r="Q32">
+        <v>77.43707294987672</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.0994425649743008</v>
+      </c>
+      <c r="T32">
+        <v>0.9820800348604487</v>
+      </c>
+      <c r="U32">
+        <v>0.06488110587651873</v>
+      </c>
+      <c r="V32">
+        <v>0.27</v>
+      </c>
+      <c r="W32">
+        <v>0.04736320728985867</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>6.993364807059135</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08372406934164757</v>
+      </c>
+      <c r="C33">
+        <v>1335.262907882216</v>
+      </c>
+      <c r="D33">
+        <v>1430.763153792494</v>
+      </c>
+      <c r="E33">
+        <v>-235.3328054131981</v>
+      </c>
+      <c r="F33">
+        <v>111.3002459102774</v>
+      </c>
+      <c r="G33">
+        <v>15.8</v>
+      </c>
+      <c r="H33">
+        <v>12.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K33">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L33">
+        <v>48.872</v>
+      </c>
+      <c r="M33">
+        <v>7.221283038987278</v>
+      </c>
+      <c r="N33">
+        <v>41.65071696101272</v>
+      </c>
+      <c r="O33">
+        <v>11.24569357947344</v>
+      </c>
+      <c r="P33">
+        <v>30.40502338153928</v>
+      </c>
+      <c r="Q33">
+        <v>77.26702338153927</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1000601088141904</v>
+      </c>
+      <c r="T33">
+        <v>0.9933859348690928</v>
+      </c>
+      <c r="U33">
+        <v>0.06488110587651873</v>
+      </c>
+      <c r="V33">
+        <v>0.27</v>
+      </c>
+      <c r="W33">
+        <v>0.04736320728985867</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>6.767772393928195</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08362938101432697</v>
+      </c>
+      <c r="C34">
+        <v>1335.253829987766</v>
+      </c>
+      <c r="D34">
+        <v>1434.344406411279</v>
+      </c>
+      <c r="E34">
+        <v>-231.7424748999634</v>
+      </c>
+      <c r="F34">
+        <v>114.8905764235122</v>
+      </c>
+      <c r="G34">
+        <v>15.8</v>
+      </c>
+      <c r="H34">
+        <v>12.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K34">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L34">
+        <v>48.872</v>
+      </c>
+      <c r="M34">
+        <v>7.454227653148158</v>
+      </c>
+      <c r="N34">
+        <v>41.41777234685184</v>
+      </c>
+      <c r="O34">
+        <v>11.18279853365</v>
+      </c>
+      <c r="P34">
+        <v>30.23497381320184</v>
+      </c>
+      <c r="Q34">
+        <v>77.09697381320184</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1006958157081944</v>
+      </c>
+      <c r="T34">
+        <v>1.005024361348579</v>
+      </c>
+      <c r="U34">
+        <v>0.06488110587651873</v>
+      </c>
+      <c r="V34">
+        <v>0.27</v>
+      </c>
+      <c r="W34">
+        <v>0.04736320728985867</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>6.556279506617939</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08353469268700636</v>
+      </c>
+      <c r="C35">
+        <v>1335.262725093547</v>
+      </c>
+      <c r="D35">
+        <v>1437.943632030294</v>
+      </c>
+      <c r="E35">
+        <v>-228.1521443867286</v>
+      </c>
+      <c r="F35">
+        <v>118.4809069367469</v>
+      </c>
+      <c r="G35">
+        <v>15.8</v>
+      </c>
+      <c r="H35">
+        <v>12.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K35">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L35">
+        <v>48.872</v>
+      </c>
+      <c r="M35">
+        <v>7.687172267309039</v>
+      </c>
+      <c r="N35">
+        <v>41.18482773269096</v>
+      </c>
+      <c r="O35">
+        <v>11.11990348782656</v>
+      </c>
+      <c r="P35">
+        <v>30.0649242448644</v>
+      </c>
+      <c r="Q35">
+        <v>76.9269242448644</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1013504989273926</v>
+      </c>
+      <c r="T35">
+        <v>1.017010203543871</v>
+      </c>
+      <c r="U35">
+        <v>0.06488110587651873</v>
+      </c>
+      <c r="V35">
+        <v>0.27</v>
+      </c>
+      <c r="W35">
+        <v>0.04736320728985867</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>6.357604370053758</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08344000435968578</v>
+      </c>
+      <c r="C36">
+        <v>1335.289728839818</v>
+      </c>
+      <c r="D36">
+        <v>1441.5609662898</v>
+      </c>
+      <c r="E36">
+        <v>-224.5618138734938</v>
+      </c>
+      <c r="F36">
+        <v>122.0712374499817</v>
+      </c>
+      <c r="G36">
+        <v>15.8</v>
+      </c>
+      <c r="H36">
+        <v>12.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K36">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L36">
+        <v>48.872</v>
+      </c>
+      <c r="M36">
+        <v>7.920116881469919</v>
+      </c>
+      <c r="N36">
+        <v>40.95188311853008</v>
+      </c>
+      <c r="O36">
+        <v>11.05700844200312</v>
+      </c>
+      <c r="P36">
+        <v>29.89487467652695</v>
+      </c>
+      <c r="Q36">
+        <v>76.75687467652695</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.102025021032021</v>
+      </c>
+      <c r="T36">
+        <v>1.029359253078415</v>
+      </c>
+      <c r="U36">
+        <v>0.06488110587651873</v>
+      </c>
+      <c r="V36">
+        <v>0.27</v>
+      </c>
+      <c r="W36">
+        <v>0.04736320728985867</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>6.170616006228647</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08370301603236519</v>
+      </c>
+      <c r="C37">
+        <v>1321.696306206171</v>
+      </c>
+      <c r="D37">
+        <v>1431.557874169387</v>
+      </c>
+      <c r="E37">
+        <v>-220.9714833602591</v>
+      </c>
+      <c r="F37">
+        <v>125.6615679632164</v>
+      </c>
+      <c r="G37">
+        <v>15.8</v>
+      </c>
+      <c r="H37">
+        <v>12.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K37">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L37">
+        <v>48.872</v>
+      </c>
+      <c r="M37">
+        <v>8.328987690779302</v>
+      </c>
+      <c r="N37">
+        <v>40.5430123092207</v>
+      </c>
+      <c r="O37">
+        <v>10.94661332348959</v>
+      </c>
+      <c r="P37">
+        <v>29.59639898573111</v>
+      </c>
+      <c r="Q37">
+        <v>76.45839898573111</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1027202976629456</v>
+      </c>
+      <c r="T37">
+        <v>1.042088273367867</v>
+      </c>
+      <c r="U37">
+        <v>0.06628110587651873</v>
+      </c>
+      <c r="V37">
+        <v>0.27</v>
+      </c>
+      <c r="W37">
+        <v>0.04838520728985867</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.867699871150523</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08361854770504459</v>
+      </c>
+      <c r="C38">
+        <v>1321.303382955552</v>
+      </c>
+      <c r="D38">
+        <v>1434.755281432004</v>
+      </c>
+      <c r="E38">
+        <v>-217.3811528470243</v>
+      </c>
+      <c r="F38">
+        <v>129.2518984764512</v>
+      </c>
+      <c r="G38">
+        <v>15.8</v>
+      </c>
+      <c r="H38">
+        <v>12.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K38">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L38">
+        <v>48.872</v>
+      </c>
+      <c r="M38">
+        <v>8.56695876765871</v>
+      </c>
+      <c r="N38">
+        <v>40.30504123234129</v>
+      </c>
+      <c r="O38">
+        <v>10.88236113273215</v>
+      </c>
+      <c r="P38">
+        <v>29.42268009960914</v>
+      </c>
+      <c r="Q38">
+        <v>76.28468009960913</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1034373016885867</v>
+      </c>
+      <c r="T38">
+        <v>1.055215075541365</v>
+      </c>
+      <c r="U38">
+        <v>0.06628110587651873</v>
+      </c>
+      <c r="V38">
+        <v>0.27</v>
+      </c>
+      <c r="W38">
+        <v>0.04838520728985867</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>5.704708208063009</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08353407937772399</v>
+      </c>
+      <c r="C39">
+        <v>1320.924774597344</v>
+      </c>
+      <c r="D39">
+        <v>1437.96700358703</v>
+      </c>
+      <c r="E39">
+        <v>-213.7908223337896</v>
+      </c>
+      <c r="F39">
+        <v>132.8422289896859</v>
+      </c>
+      <c r="G39">
+        <v>15.8</v>
+      </c>
+      <c r="H39">
+        <v>12.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K39">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L39">
+        <v>48.872</v>
+      </c>
+      <c r="M39">
+        <v>8.804929844538119</v>
+      </c>
+      <c r="N39">
+        <v>40.06707015546188</v>
+      </c>
+      <c r="O39">
+        <v>10.81810894197471</v>
+      </c>
+      <c r="P39">
+        <v>29.24896121348717</v>
+      </c>
+      <c r="Q39">
+        <v>76.11096121348717</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1041770677467878</v>
+      </c>
+      <c r="T39">
+        <v>1.068758601593386</v>
+      </c>
+      <c r="U39">
+        <v>0.06628110587651873</v>
+      </c>
+      <c r="V39">
+        <v>0.27</v>
+      </c>
+      <c r="W39">
+        <v>0.04838520728985867</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>5.550526905142386</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08344961105040338</v>
+      </c>
+      <c r="C40">
+        <v>1320.560577479554</v>
+      </c>
+      <c r="D40">
+        <v>1441.193136982475</v>
+      </c>
+      <c r="E40">
+        <v>-210.2004918205548</v>
+      </c>
+      <c r="F40">
+        <v>136.4325595029207</v>
+      </c>
+      <c r="G40">
+        <v>15.8</v>
+      </c>
+      <c r="H40">
+        <v>12.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K40">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L40">
+        <v>48.872</v>
+      </c>
+      <c r="M40">
+        <v>9.042900921417528</v>
+      </c>
+      <c r="N40">
+        <v>39.82909907858247</v>
+      </c>
+      <c r="O40">
+        <v>10.75385675121727</v>
+      </c>
+      <c r="P40">
+        <v>29.0752423273652</v>
+      </c>
+      <c r="Q40">
+        <v>75.9372423273652</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1049406972262211</v>
+      </c>
+      <c r="T40">
+        <v>1.08273901558257</v>
+      </c>
+      <c r="U40">
+        <v>0.06628110587651873</v>
+      </c>
+      <c r="V40">
+        <v>0.27</v>
+      </c>
+      <c r="W40">
+        <v>0.04838520728985867</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>5.40446040763864</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08336514272308281</v>
+      </c>
+      <c r="C41">
+        <v>1320.210888816776</v>
+      </c>
+      <c r="D41">
+        <v>1444.433778832932</v>
+      </c>
+      <c r="E41">
+        <v>-206.6101613073201</v>
+      </c>
+      <c r="F41">
+        <v>140.0228900161555</v>
+      </c>
+      <c r="G41">
+        <v>15.8</v>
+      </c>
+      <c r="H41">
+        <v>12.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K41">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L41">
+        <v>48.872</v>
+      </c>
+      <c r="M41">
+        <v>9.280871998296936</v>
+      </c>
+      <c r="N41">
+        <v>39.59112800170306</v>
+      </c>
+      <c r="O41">
+        <v>10.68960456045983</v>
+      </c>
+      <c r="P41">
+        <v>28.90152344124323</v>
+      </c>
+      <c r="Q41">
+        <v>75.76352344124322</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1057293637377671</v>
+      </c>
+      <c r="T41">
+        <v>1.097177803800907</v>
+      </c>
+      <c r="U41">
+        <v>0.06628110587651873</v>
+      </c>
+      <c r="V41">
+        <v>0.27</v>
+      </c>
+      <c r="W41">
+        <v>0.04838520728985867</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>5.265884499750469</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08328067439576221</v>
+      </c>
+      <c r="C42">
+        <v>1319.875806699957</v>
+      </c>
+      <c r="D42">
+        <v>1447.689027229348</v>
+      </c>
+      <c r="E42">
+        <v>-203.0198307940853</v>
+      </c>
+      <c r="F42">
+        <v>143.6132205293902</v>
+      </c>
+      <c r="G42">
+        <v>15.8</v>
+      </c>
+      <c r="H42">
+        <v>12.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K42">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L42">
+        <v>48.872</v>
+      </c>
+      <c r="M42">
+        <v>9.518843075176344</v>
+      </c>
+      <c r="N42">
+        <v>39.35315692482366</v>
+      </c>
+      <c r="O42">
+        <v>10.62535236970239</v>
+      </c>
+      <c r="P42">
+        <v>28.72780455512127</v>
+      </c>
+      <c r="Q42">
+        <v>75.58980455512126</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1065443191330312</v>
+      </c>
+      <c r="T42">
+        <v>1.112097884959855</v>
+      </c>
+      <c r="U42">
+        <v>0.06628110587651873</v>
+      </c>
+      <c r="V42">
+        <v>0.27</v>
+      </c>
+      <c r="W42">
+        <v>0.04838520728985867</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>5.134237387256708</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08319620606844161</v>
+      </c>
+      <c r="C43">
+        <v>1319.55543010629</v>
+      </c>
+      <c r="D43">
+        <v>1450.958981148915</v>
+      </c>
+      <c r="E43">
+        <v>-199.4295002808506</v>
+      </c>
+      <c r="F43">
+        <v>147.203551042625</v>
+      </c>
+      <c r="G43">
+        <v>15.8</v>
+      </c>
+      <c r="H43">
+        <v>12.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K43">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L43">
+        <v>48.872</v>
+      </c>
+      <c r="M43">
+        <v>9.756814152055753</v>
+      </c>
+      <c r="N43">
+        <v>39.11518584794425</v>
+      </c>
+      <c r="O43">
+        <v>10.56110017894495</v>
+      </c>
+      <c r="P43">
+        <v>28.5540856689993</v>
+      </c>
+      <c r="Q43">
+        <v>75.4160856689993</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1073869001349145</v>
+      </c>
+      <c r="T43">
+        <v>1.127523731581819</v>
+      </c>
+      <c r="U43">
+        <v>0.06628110587651873</v>
+      </c>
+      <c r="V43">
+        <v>0.27</v>
+      </c>
+      <c r="W43">
+        <v>0.04838520728985867</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>5.009012085128496</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.08311173774112102</v>
+      </c>
+      <c r="C44">
+        <v>1319.249858909247</v>
+      </c>
+      <c r="D44">
+        <v>1454.243740465107</v>
+      </c>
+      <c r="E44">
+        <v>-195.8391697676158</v>
+      </c>
+      <c r="F44">
+        <v>150.7938815558597</v>
+      </c>
+      <c r="G44">
+        <v>15.8</v>
+      </c>
+      <c r="H44">
+        <v>12.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K44">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L44">
+        <v>48.872</v>
+      </c>
+      <c r="M44">
+        <v>9.994785228935163</v>
+      </c>
+      <c r="N44">
+        <v>38.87721477106484</v>
+      </c>
+      <c r="O44">
+        <v>10.49684798818751</v>
+      </c>
+      <c r="P44">
+        <v>28.38036678287733</v>
+      </c>
+      <c r="Q44">
+        <v>75.24236678287733</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1082585356541041</v>
+      </c>
+      <c r="T44">
+        <v>1.143481503949367</v>
+      </c>
+      <c r="U44">
+        <v>0.06628110587651873</v>
+      </c>
+      <c r="V44">
+        <v>0.27</v>
+      </c>
+      <c r="W44">
+        <v>0.04838520728985867</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.889749892625435</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.08302726941380043</v>
+      </c>
+      <c r="C45">
+        <v>1318.959193888749</v>
+      </c>
+      <c r="D45">
+        <v>1457.543405957843</v>
+      </c>
+      <c r="E45">
+        <v>-192.2488392543811</v>
+      </c>
+      <c r="F45">
+        <v>154.3842120690944</v>
+      </c>
+      <c r="G45">
+        <v>15.8</v>
+      </c>
+      <c r="H45">
+        <v>12.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K45">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L45">
+        <v>48.872</v>
+      </c>
+      <c r="M45">
+        <v>10.23275630581457</v>
+      </c>
+      <c r="N45">
+        <v>38.63924369418543</v>
+      </c>
+      <c r="O45">
+        <v>10.43259579743007</v>
+      </c>
+      <c r="P45">
+        <v>28.20664789675536</v>
+      </c>
+      <c r="Q45">
+        <v>75.06864789675535</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1091607548757214</v>
+      </c>
+      <c r="T45">
+        <v>1.159999198154373</v>
+      </c>
+      <c r="U45">
+        <v>0.06628110587651873</v>
+      </c>
+      <c r="V45">
+        <v>0.27</v>
+      </c>
+      <c r="W45">
+        <v>0.04838520728985867</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>4.776034778843449</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08294280108647983</v>
+      </c>
+      <c r="C46">
+        <v>1318.683536741472</v>
+      </c>
+      <c r="D46">
+        <v>1460.858079323801</v>
+      </c>
+      <c r="E46">
+        <v>-188.6585087411463</v>
+      </c>
+      <c r="F46">
+        <v>157.9745425823292</v>
+      </c>
+      <c r="G46">
+        <v>15.8</v>
+      </c>
+      <c r="H46">
+        <v>12.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K46">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L46">
+        <v>48.872</v>
+      </c>
+      <c r="M46">
+        <v>10.47072738269398</v>
+      </c>
+      <c r="N46">
+        <v>38.40127261730602</v>
+      </c>
+      <c r="O46">
+        <v>10.36834360667263</v>
+      </c>
+      <c r="P46">
+        <v>28.0329290106334</v>
+      </c>
+      <c r="Q46">
+        <v>74.89492901063339</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1100951962123964</v>
+      </c>
+      <c r="T46">
+        <v>1.177106810009558</v>
+      </c>
+      <c r="U46">
+        <v>0.06628110587651873</v>
+      </c>
+      <c r="V46">
+        <v>0.27</v>
+      </c>
+      <c r="W46">
+        <v>0.04838520728985867</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>4.667488533869735</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08285833275915923</v>
+      </c>
+      <c r="C47">
+        <v>1318.422990091295</v>
+      </c>
+      <c r="D47">
+        <v>1464.187863186859</v>
+      </c>
+      <c r="E47">
+        <v>-185.0681782279115</v>
+      </c>
+      <c r="F47">
+        <v>161.564873095564</v>
+      </c>
+      <c r="G47">
+        <v>15.8</v>
+      </c>
+      <c r="H47">
+        <v>12.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K47">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L47">
+        <v>48.872</v>
+      </c>
+      <c r="M47">
+        <v>10.70869845957339</v>
+      </c>
+      <c r="N47">
+        <v>38.16330154042662</v>
+      </c>
+      <c r="O47">
+        <v>10.30409141591519</v>
+      </c>
+      <c r="P47">
+        <v>27.85921012451143</v>
+      </c>
+      <c r="Q47">
+        <v>74.72121012451143</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1110636172340415</v>
+      </c>
+      <c r="T47">
+        <v>1.194836516841296</v>
+      </c>
+      <c r="U47">
+        <v>0.06628110587651873</v>
+      </c>
+      <c r="V47">
+        <v>0.27</v>
+      </c>
+      <c r="W47">
+        <v>0.04838520728985867</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>4.563766566450408</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.08364694443183862</v>
+      </c>
+      <c r="C48">
+        <v>1284.323574703739</v>
+      </c>
+      <c r="D48">
+        <v>1433.678778312538</v>
+      </c>
+      <c r="E48">
+        <v>-181.4778477146768</v>
+      </c>
+      <c r="F48">
+        <v>165.1552036087987</v>
+      </c>
+      <c r="G48">
+        <v>15.8</v>
+      </c>
+      <c r="H48">
+        <v>12.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K48">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L48">
+        <v>48.872</v>
+      </c>
+      <c r="M48">
+        <v>11.37607306583567</v>
+      </c>
+      <c r="N48">
+        <v>37.49592693416433</v>
+      </c>
+      <c r="O48">
+        <v>10.12390027222437</v>
+      </c>
+      <c r="P48">
+        <v>27.37202666193996</v>
+      </c>
+      <c r="Q48">
+        <v>74.23402666193996</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1120679057009327</v>
+      </c>
+      <c r="T48">
+        <v>1.213222879481616</v>
+      </c>
+      <c r="U48">
+        <v>0.06888110587651872</v>
+      </c>
+      <c r="V48">
+        <v>0.27</v>
+      </c>
+      <c r="W48">
+        <v>0.05028320728985866</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>4.296034292076686</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.08358145610451805</v>
+      </c>
+      <c r="C49">
+        <v>1283.218305243921</v>
+      </c>
+      <c r="D49">
+        <v>1436.163839365955</v>
+      </c>
+      <c r="E49">
+        <v>-177.887517201442</v>
+      </c>
+      <c r="F49">
+        <v>168.7455341220335</v>
+      </c>
+      <c r="G49">
+        <v>15.8</v>
+      </c>
+      <c r="H49">
+        <v>12.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K49">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L49">
+        <v>48.872</v>
+      </c>
+      <c r="M49">
+        <v>11.62337900204949</v>
+      </c>
+      <c r="N49">
+        <v>37.24862099795051</v>
+      </c>
+      <c r="O49">
+        <v>10.05712766944664</v>
+      </c>
+      <c r="P49">
+        <v>27.19149332850387</v>
+      </c>
+      <c r="Q49">
+        <v>74.05349332850386</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1131100918458197</v>
+      </c>
+      <c r="T49">
+        <v>1.232303067127231</v>
+      </c>
+      <c r="U49">
+        <v>0.06888110587651872</v>
+      </c>
+      <c r="V49">
+        <v>0.27</v>
+      </c>
+      <c r="W49">
+        <v>0.05028320728985866</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>4.204629307138884</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.08351596777719744</v>
+      </c>
+      <c r="C50">
+        <v>1282.121665682858</v>
+      </c>
+      <c r="D50">
+        <v>1438.657530318127</v>
+      </c>
+      <c r="E50">
+        <v>-174.2971866882073</v>
+      </c>
+      <c r="F50">
+        <v>172.3358646352682</v>
+      </c>
+      <c r="G50">
+        <v>15.8</v>
+      </c>
+      <c r="H50">
+        <v>12.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K50">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L50">
+        <v>48.872</v>
+      </c>
+      <c r="M50">
+        <v>11.87068493826331</v>
+      </c>
+      <c r="N50">
+        <v>37.00131506173669</v>
+      </c>
+      <c r="O50">
+        <v>9.990355066668908</v>
+      </c>
+      <c r="P50">
+        <v>27.01095999506778</v>
+      </c>
+      <c r="Q50">
+        <v>73.87295999506777</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1141923620732025</v>
+      </c>
+      <c r="T50">
+        <v>1.252117108143831</v>
+      </c>
+      <c r="U50">
+        <v>0.06888110587651872</v>
+      </c>
+      <c r="V50">
+        <v>0.27</v>
+      </c>
+      <c r="W50">
+        <v>0.05028320728985866</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>4.117032863240158</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.08345047944987685</v>
+      </c>
+      <c r="C51">
+        <v>1281.033701052457</v>
+      </c>
+      <c r="D51">
+        <v>1441.15989620096</v>
+      </c>
+      <c r="E51">
+        <v>-170.7068561749725</v>
+      </c>
+      <c r="F51">
+        <v>175.926195148503</v>
+      </c>
+      <c r="G51">
+        <v>15.8</v>
+      </c>
+      <c r="H51">
+        <v>12.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K51">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L51">
+        <v>48.872</v>
+      </c>
+      <c r="M51">
+        <v>12.11799087447713</v>
+      </c>
+      <c r="N51">
+        <v>36.75400912552287</v>
+      </c>
+      <c r="O51">
+        <v>9.923582463891176</v>
+      </c>
+      <c r="P51">
+        <v>26.83042666163169</v>
+      </c>
+      <c r="Q51">
+        <v>73.69242666163169</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1153170742702865</v>
+      </c>
+      <c r="T51">
+        <v>1.272708170376769</v>
+      </c>
+      <c r="U51">
+        <v>0.06888110587651872</v>
+      </c>
+      <c r="V51">
+        <v>0.27</v>
+      </c>
+      <c r="W51">
+        <v>0.05028320728985866</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>4.033011784398521</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.08437049112255625</v>
+      </c>
+      <c r="C52">
+        <v>1243.067766596577</v>
+      </c>
+      <c r="D52">
+        <v>1406.784292258315</v>
+      </c>
+      <c r="E52">
+        <v>-167.1165256617378</v>
+      </c>
+      <c r="F52">
+        <v>179.5165256617377</v>
+      </c>
+      <c r="G52">
+        <v>15.8</v>
+      </c>
+      <c r="H52">
+        <v>12.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K52">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L52">
+        <v>48.872</v>
+      </c>
+      <c r="M52">
+        <v>12.84999142997764</v>
+      </c>
+      <c r="N52">
+        <v>36.02200857002236</v>
+      </c>
+      <c r="O52">
+        <v>9.725942313906037</v>
+      </c>
+      <c r="P52">
+        <v>26.29606625611632</v>
+      </c>
+      <c r="Q52">
+        <v>73.15806625611631</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1164867749552538</v>
+      </c>
+      <c r="T52">
+        <v>1.294122875099024</v>
+      </c>
+      <c r="U52">
+        <v>0.07158110587651872</v>
+      </c>
+      <c r="V52">
+        <v>0.27</v>
+      </c>
+      <c r="W52">
+        <v>0.05225420728985867</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>3.803271018997484</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.08432471279523567</v>
+      </c>
+      <c r="C53">
+        <v>1241.149096353537</v>
+      </c>
+      <c r="D53">
+        <v>1408.45595252851</v>
+      </c>
+      <c r="E53">
+        <v>-163.526195148503</v>
+      </c>
+      <c r="F53">
+        <v>183.1068561749725</v>
+      </c>
+      <c r="G53">
+        <v>15.8</v>
+      </c>
+      <c r="H53">
+        <v>12.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K53">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L53">
+        <v>48.872</v>
+      </c>
+      <c r="M53">
+        <v>13.10699125857719</v>
+      </c>
+      <c r="N53">
+        <v>35.7650087414228</v>
+      </c>
+      <c r="O53">
+        <v>9.656552360184158</v>
+      </c>
+      <c r="P53">
+        <v>26.10845638123865</v>
+      </c>
+      <c r="Q53">
+        <v>72.97045638123865</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1177042185253219</v>
+      </c>
+      <c r="T53">
+        <v>1.31641164940178</v>
+      </c>
+      <c r="U53">
+        <v>0.07158110587651872</v>
+      </c>
+      <c r="V53">
+        <v>0.27</v>
+      </c>
+      <c r="W53">
+        <v>0.05225420728985867</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>3.728697077448514</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.08427893446791507</v>
+      </c>
+      <c r="C54">
+        <v>1239.234403653643</v>
+      </c>
+      <c r="D54">
+        <v>1410.13159034185</v>
+      </c>
+      <c r="E54">
+        <v>-159.9358646352682</v>
+      </c>
+      <c r="F54">
+        <v>186.6971866882073</v>
+      </c>
+      <c r="G54">
+        <v>15.8</v>
+      </c>
+      <c r="H54">
+        <v>12.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K54">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L54">
+        <v>48.872</v>
+      </c>
+      <c r="M54">
+        <v>13.36399108717675</v>
+      </c>
+      <c r="N54">
+        <v>35.50800891282326</v>
+      </c>
+      <c r="O54">
+        <v>9.58716240646228</v>
+      </c>
+      <c r="P54">
+        <v>25.92084650636098</v>
+      </c>
+      <c r="Q54">
+        <v>72.78284650636097</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1189723889108095</v>
+      </c>
+      <c r="T54">
+        <v>1.339629122633817</v>
+      </c>
+      <c r="U54">
+        <v>0.07158110587651872</v>
+      </c>
+      <c r="V54">
+        <v>0.27</v>
+      </c>
+      <c r="W54">
+        <v>0.05225420728985867</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>3.656991364420658</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.08423315614059447</v>
+      </c>
+      <c r="C55">
+        <v>1237.323702710034</v>
+      </c>
+      <c r="D55">
+        <v>1411.811219911476</v>
+      </c>
+      <c r="E55">
+        <v>-156.3455341220335</v>
+      </c>
+      <c r="F55">
+        <v>190.287517201442</v>
+      </c>
+      <c r="G55">
+        <v>15.8</v>
+      </c>
+      <c r="H55">
+        <v>12.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K55">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L55">
+        <v>48.872</v>
+      </c>
+      <c r="M55">
+        <v>13.6209909157763</v>
+      </c>
+      <c r="N55">
+        <v>35.2510090842237</v>
+      </c>
+      <c r="O55">
+        <v>9.517772452740399</v>
+      </c>
+      <c r="P55">
+        <v>25.7332366314833</v>
+      </c>
+      <c r="Q55">
+        <v>72.59523663148329</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1202945239935519</v>
+      </c>
+      <c r="T55">
+        <v>1.363834573450196</v>
+      </c>
+      <c r="U55">
+        <v>0.07158110587651872</v>
+      </c>
+      <c r="V55">
+        <v>0.27</v>
+      </c>
+      <c r="W55">
+        <v>0.05225420728985867</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>3.587991527356117</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.08418737781327386</v>
+      </c>
+      <c r="C56">
+        <v>1235.417007803649</v>
+      </c>
+      <c r="D56">
+        <v>1413.494855518326</v>
+      </c>
+      <c r="E56">
+        <v>-152.7552036087987</v>
+      </c>
+      <c r="F56">
+        <v>193.8778477146768</v>
+      </c>
+      <c r="G56">
+        <v>15.8</v>
+      </c>
+      <c r="H56">
+        <v>12.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K56">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L56">
+        <v>48.872</v>
+      </c>
+      <c r="M56">
+        <v>13.87799074437585</v>
+      </c>
+      <c r="N56">
+        <v>34.99400925562415</v>
+      </c>
+      <c r="O56">
+        <v>9.448382499018521</v>
+      </c>
+      <c r="P56">
+        <v>25.54562675660563</v>
+      </c>
+      <c r="Q56">
+        <v>72.40762675660562</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1216741432103265</v>
+      </c>
+      <c r="T56">
+        <v>1.389092435171634</v>
+      </c>
+      <c r="U56">
+        <v>0.07158110587651872</v>
+      </c>
+      <c r="V56">
+        <v>0.27</v>
+      </c>
+      <c r="W56">
+        <v>0.05225420728985867</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>3.521547239812485</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.08602864948595329</v>
+      </c>
+      <c r="C57">
+        <v>1167.130793381789</v>
+      </c>
+      <c r="D57">
+        <v>1348.798971609701</v>
+      </c>
+      <c r="E57">
+        <v>-149.164873095564</v>
+      </c>
+      <c r="F57">
+        <v>197.4681782279115</v>
+      </c>
+      <c r="G57">
+        <v>15.8</v>
+      </c>
+      <c r="H57">
+        <v>12.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K57">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L57">
+        <v>48.872</v>
+      </c>
+      <c r="M57">
+        <v>15.06309101064659</v>
+      </c>
+      <c r="N57">
+        <v>33.80890898935341</v>
+      </c>
+      <c r="O57">
+        <v>9.128405427125422</v>
+      </c>
+      <c r="P57">
+        <v>24.68050356222799</v>
+      </c>
+      <c r="Q57">
+        <v>71.54250356222798</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1231150788367356</v>
+      </c>
+      <c r="T57">
+        <v>1.415472868525137</v>
+      </c>
+      <c r="U57">
+        <v>0.07628110587651873</v>
+      </c>
+      <c r="V57">
+        <v>0.27</v>
+      </c>
+      <c r="W57">
+        <v>0.05568520728985867</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>3.24448680323695</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.08601718115863267</v>
+      </c>
+      <c r="C58">
+        <v>1163.925086247183</v>
+      </c>
+      <c r="D58">
+        <v>1349.183594988329</v>
+      </c>
+      <c r="E58">
+        <v>-145.5745425823292</v>
+      </c>
+      <c r="F58">
+        <v>201.0585087411463</v>
+      </c>
+      <c r="G58">
+        <v>15.8</v>
+      </c>
+      <c r="H58">
+        <v>12.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K58">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L58">
+        <v>48.872</v>
+      </c>
+      <c r="M58">
+        <v>15.33696539265835</v>
+      </c>
+      <c r="N58">
+        <v>33.53503460734165</v>
+      </c>
+      <c r="O58">
+        <v>9.054459343982247</v>
+      </c>
+      <c r="P58">
+        <v>24.48057526335941</v>
+      </c>
+      <c r="Q58">
+        <v>71.34257526335941</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1246215115370723</v>
+      </c>
+      <c r="T58">
+        <v>1.443052412485617</v>
+      </c>
+      <c r="U58">
+        <v>0.07628110587651873</v>
+      </c>
+      <c r="V58">
+        <v>0.27</v>
+      </c>
+      <c r="W58">
+        <v>0.05568520728985867</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>3.186549538893433</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.08600571283131209</v>
+      </c>
+      <c r="C59">
+        <v>1160.719598533472</v>
+      </c>
+      <c r="D59">
+        <v>1349.568437787854</v>
+      </c>
+      <c r="E59">
+        <v>-141.9842120690945</v>
+      </c>
+      <c r="F59">
+        <v>204.648839254381</v>
+      </c>
+      <c r="G59">
+        <v>15.8</v>
+      </c>
+      <c r="H59">
+        <v>12.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K59">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L59">
+        <v>48.872</v>
+      </c>
+      <c r="M59">
+        <v>15.6108397746701</v>
+      </c>
+      <c r="N59">
+        <v>33.2611602253299</v>
+      </c>
+      <c r="O59">
+        <v>8.980513260839073</v>
+      </c>
+      <c r="P59">
+        <v>24.28064696449082</v>
+      </c>
+      <c r="Q59">
+        <v>71.14264696449081</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1261980108746341</v>
+      </c>
+      <c r="T59">
+        <v>1.471914725932632</v>
+      </c>
+      <c r="U59">
+        <v>0.07628110587651873</v>
+      </c>
+      <c r="V59">
+        <v>0.27</v>
+      </c>
+      <c r="W59">
+        <v>0.05568520728985867</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>3.13064516101811</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.08599424450399148</v>
+      </c>
+      <c r="C60">
+        <v>1157.514330428478</v>
+      </c>
+      <c r="D60">
+        <v>1349.953500196094</v>
+      </c>
+      <c r="E60">
+        <v>-138.3938815558597</v>
+      </c>
+      <c r="F60">
+        <v>208.2391697676158</v>
+      </c>
+      <c r="G60">
+        <v>15.8</v>
+      </c>
+      <c r="H60">
+        <v>12.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K60">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L60">
+        <v>48.872</v>
+      </c>
+      <c r="M60">
+        <v>15.88471415668186</v>
+      </c>
+      <c r="N60">
+        <v>32.98728584331814</v>
+      </c>
+      <c r="O60">
+        <v>8.906567177695898</v>
+      </c>
+      <c r="P60">
+        <v>24.08071866562224</v>
+      </c>
+      <c r="Q60">
+        <v>70.94271866562224</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1278495816092225</v>
+      </c>
+      <c r="T60">
+        <v>1.502151435258074</v>
+      </c>
+      <c r="U60">
+        <v>0.07628110587651873</v>
+      </c>
+      <c r="V60">
+        <v>0.27</v>
+      </c>
+      <c r="W60">
+        <v>0.05568520728985867</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>3.076668520310901</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.0859827761766709</v>
+      </c>
+      <c r="C61">
+        <v>1154.309282120229</v>
+      </c>
+      <c r="D61">
+        <v>1350.33878240108</v>
+      </c>
+      <c r="E61">
+        <v>-134.803551042625</v>
+      </c>
+      <c r="F61">
+        <v>211.8295002808505</v>
+      </c>
+      <c r="G61">
+        <v>15.8</v>
+      </c>
+      <c r="H61">
+        <v>12.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K61">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L61">
+        <v>48.872</v>
+      </c>
+      <c r="M61">
+        <v>16.15858853869361</v>
+      </c>
+      <c r="N61">
+        <v>32.71341146130639</v>
+      </c>
+      <c r="O61">
+        <v>8.832621094552724</v>
+      </c>
+      <c r="P61">
+        <v>23.88079036675366</v>
+      </c>
+      <c r="Q61">
+        <v>70.74279036675365</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1295817167698885</v>
+      </c>
+      <c r="T61">
+        <v>1.533863106014027</v>
+      </c>
+      <c r="U61">
+        <v>0.07628110587651873</v>
+      </c>
+      <c r="V61">
+        <v>0.27</v>
+      </c>
+      <c r="W61">
+        <v>0.05568520728985867</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>3.024521596237835</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.09004470784935029</v>
+      </c>
+      <c r="C62">
+        <v>1026.749687582059</v>
+      </c>
+      <c r="D62">
+        <v>1226.369518376144</v>
+      </c>
+      <c r="E62">
+        <v>-131.2132205293902</v>
+      </c>
+      <c r="F62">
+        <v>215.4198307940853</v>
+      </c>
+      <c r="G62">
+        <v>15.8</v>
+      </c>
+      <c r="H62">
+        <v>12.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K62">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L62">
+        <v>48.872</v>
+      </c>
+      <c r="M62">
+        <v>18.43586734709036</v>
+      </c>
+      <c r="N62">
+        <v>30.43613265290964</v>
+      </c>
+      <c r="O62">
+        <v>8.217755816285603</v>
+      </c>
+      <c r="P62">
+        <v>22.21837683662404</v>
+      </c>
+      <c r="Q62">
+        <v>69.08037683662403</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1314004586885877</v>
+      </c>
+      <c r="T62">
+        <v>1.567160360307778</v>
+      </c>
+      <c r="U62">
+        <v>0.08558110587651872</v>
+      </c>
+      <c r="V62">
+        <v>0.27</v>
+      </c>
+      <c r="W62">
+        <v>0.06247420728985867</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>2.650919486449506</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.0901011295220297</v>
+      </c>
+      <c r="C63">
+        <v>1021.597459656808</v>
+      </c>
+      <c r="D63">
+        <v>1224.807620964129</v>
+      </c>
+      <c r="E63">
+        <v>-127.6228900161555</v>
+      </c>
+      <c r="F63">
+        <v>219.01016130732</v>
+      </c>
+      <c r="G63">
+        <v>15.8</v>
+      </c>
+      <c r="H63">
+        <v>12.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K63">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L63">
+        <v>48.872</v>
+      </c>
+      <c r="M63">
+        <v>18.7431318028752</v>
+      </c>
+      <c r="N63">
+        <v>30.1288681971248</v>
+      </c>
+      <c r="O63">
+        <v>8.134794413223696</v>
+      </c>
+      <c r="P63">
+        <v>21.9940737839011</v>
+      </c>
+      <c r="Q63">
+        <v>68.8560737839011</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1333124694236305</v>
+      </c>
+      <c r="T63">
+        <v>1.602165166103772</v>
+      </c>
+      <c r="U63">
+        <v>0.08558110587651872</v>
+      </c>
+      <c r="V63">
+        <v>0.27</v>
+      </c>
+      <c r="W63">
+        <v>0.06247420728985867</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>2.607461789950334</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.0901575511947091</v>
+      </c>
+      <c r="C64">
+        <v>1016.449205118825</v>
+      </c>
+      <c r="D64">
+        <v>1223.249696939379</v>
+      </c>
+      <c r="E64">
+        <v>-124.0325595029207</v>
+      </c>
+      <c r="F64">
+        <v>222.6004918205548</v>
+      </c>
+      <c r="G64">
+        <v>15.8</v>
+      </c>
+      <c r="H64">
+        <v>12.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K64">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L64">
+        <v>48.872</v>
+      </c>
+      <c r="M64">
+        <v>19.05039625866004</v>
+      </c>
+      <c r="N64">
+        <v>29.82160374133996</v>
+      </c>
+      <c r="O64">
+        <v>8.05183301016179</v>
+      </c>
+      <c r="P64">
+        <v>21.76977073117817</v>
+      </c>
+      <c r="Q64">
+        <v>68.63177073117816</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.135325112302623</v>
+      </c>
+      <c r="T64">
+        <v>1.639012330099555</v>
+      </c>
+      <c r="U64">
+        <v>0.08558110587651872</v>
+      </c>
+      <c r="V64">
+        <v>0.27</v>
+      </c>
+      <c r="W64">
+        <v>0.06247420728985867</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>2.565405954628554</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.0902139728673885</v>
+      </c>
+      <c r="C65">
+        <v>1011.304908825227</v>
+      </c>
+      <c r="D65">
+        <v>1221.695731159017</v>
+      </c>
+      <c r="E65">
+        <v>-120.442228989686</v>
+      </c>
+      <c r="F65">
+        <v>226.1908223337896</v>
+      </c>
+      <c r="G65">
+        <v>15.8</v>
+      </c>
+      <c r="H65">
+        <v>12.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K65">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L65">
+        <v>48.872</v>
+      </c>
+      <c r="M65">
+        <v>19.35766071444488</v>
+      </c>
+      <c r="N65">
+        <v>29.51433928555512</v>
+      </c>
+      <c r="O65">
+        <v>7.968871607099883</v>
+      </c>
+      <c r="P65">
+        <v>21.54546767845524</v>
+      </c>
+      <c r="Q65">
+        <v>68.40746767845523</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.137446546688588</v>
+      </c>
+      <c r="T65">
+        <v>1.677851232689705</v>
+      </c>
+      <c r="U65">
+        <v>0.08558110587651872</v>
+      </c>
+      <c r="V65">
+        <v>0.27</v>
+      </c>
+      <c r="W65">
+        <v>0.06247420728985867</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>2.524685225190006</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.09246623454006792</v>
+      </c>
+      <c r="C66">
+        <v>948.7516365172564</v>
+      </c>
+      <c r="D66">
+        <v>1162.732789364281</v>
+      </c>
+      <c r="E66">
+        <v>-116.8518984764512</v>
+      </c>
+      <c r="F66">
+        <v>229.7811528470243</v>
+      </c>
+      <c r="G66">
+        <v>15.8</v>
+      </c>
+      <c r="H66">
+        <v>12.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K66">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L66">
+        <v>48.872</v>
+      </c>
+      <c r="M66">
+        <v>20.74489658861073</v>
+      </c>
+      <c r="N66">
+        <v>28.12710341138927</v>
+      </c>
+      <c r="O66">
+        <v>7.594317921075103</v>
+      </c>
+      <c r="P66">
+        <v>20.53278549031416</v>
+      </c>
+      <c r="Q66">
+        <v>67.39478549031416</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1396858385404399</v>
+      </c>
+      <c r="T66">
+        <v>1.718847852090419</v>
+      </c>
+      <c r="U66">
+        <v>0.09028110587651872</v>
+      </c>
+      <c r="V66">
+        <v>0.27</v>
+      </c>
+      <c r="W66">
+        <v>0.06590520728985866</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>2.355856525543322</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.09255696621274731</v>
+      </c>
+      <c r="C67">
+        <v>942.9050285035061</v>
+      </c>
+      <c r="D67">
+        <v>1160.476511863765</v>
+      </c>
+      <c r="E67">
+        <v>-113.2615679632164</v>
+      </c>
+      <c r="F67">
+        <v>233.3714833602591</v>
+      </c>
+      <c r="G67">
+        <v>15.8</v>
+      </c>
+      <c r="H67">
+        <v>12.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K67">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L67">
+        <v>48.872</v>
+      </c>
+      <c r="M67">
+        <v>21.06903559780778</v>
+      </c>
+      <c r="N67">
+        <v>27.80296440219222</v>
+      </c>
+      <c r="O67">
+        <v>7.506800388591901</v>
+      </c>
+      <c r="P67">
+        <v>20.29616401360032</v>
+      </c>
+      <c r="Q67">
+        <v>67.15816401360031</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1420530899266834</v>
+      </c>
+      <c r="T67">
+        <v>1.762187135456888</v>
+      </c>
+      <c r="U67">
+        <v>0.09028110587651872</v>
+      </c>
+      <c r="V67">
+        <v>0.27</v>
+      </c>
+      <c r="W67">
+        <v>0.06590520728985866</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>2.319612578996502</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.09264769788542671</v>
+      </c>
+      <c r="C68">
+        <v>937.0671601222621</v>
+      </c>
+      <c r="D68">
+        <v>1158.228973995756</v>
+      </c>
+      <c r="E68">
+        <v>-109.6712374499817</v>
+      </c>
+      <c r="F68">
+        <v>236.9618138734938</v>
+      </c>
+      <c r="G68">
+        <v>15.8</v>
+      </c>
+      <c r="H68">
+        <v>12.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K68">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L68">
+        <v>48.872</v>
+      </c>
+      <c r="M68">
+        <v>21.39317460700482</v>
+      </c>
+      <c r="N68">
+        <v>27.47882539299518</v>
+      </c>
+      <c r="O68">
+        <v>7.419282856108699</v>
+      </c>
+      <c r="P68">
+        <v>20.05954253688648</v>
+      </c>
+      <c r="Q68">
+        <v>66.92154253688648</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1445595913944706</v>
+      </c>
+      <c r="T68">
+        <v>1.808075788433149</v>
+      </c>
+      <c r="U68">
+        <v>0.09028110587651872</v>
+      </c>
+      <c r="V68">
+        <v>0.27</v>
+      </c>
+      <c r="W68">
+        <v>0.06590520728985866</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>2.284466933860191</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.09273842955810613</v>
+      </c>
+      <c r="C69">
+        <v>931.2379806925693</v>
+      </c>
+      <c r="D69">
+        <v>1155.990125079298</v>
+      </c>
+      <c r="E69">
+        <v>-106.0809069367469</v>
+      </c>
+      <c r="F69">
+        <v>240.5521443867286</v>
+      </c>
+      <c r="G69">
+        <v>15.8</v>
+      </c>
+      <c r="H69">
+        <v>12.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K69">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L69">
+        <v>48.872</v>
+      </c>
+      <c r="M69">
+        <v>21.71731361620186</v>
+      </c>
+      <c r="N69">
+        <v>27.15468638379814</v>
+      </c>
+      <c r="O69">
+        <v>7.331765323625497</v>
+      </c>
+      <c r="P69">
+        <v>19.82292106017264</v>
+      </c>
+      <c r="Q69">
+        <v>66.68492106017263</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1472180020421237</v>
+      </c>
+      <c r="T69">
+        <v>1.85674557189282</v>
+      </c>
+      <c r="U69">
+        <v>0.09028110587651872</v>
+      </c>
+      <c r="V69">
+        <v>0.27</v>
+      </c>
+      <c r="W69">
+        <v>0.06590520728985866</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>2.250370412459293</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.09282916123078552</v>
+      </c>
+      <c r="C70">
+        <v>925.4174399245819</v>
+      </c>
+      <c r="D70">
+        <v>1153.759914824545</v>
+      </c>
+      <c r="E70">
+        <v>-102.4905764235122</v>
+      </c>
+      <c r="F70">
+        <v>244.1424748999634</v>
+      </c>
+      <c r="G70">
+        <v>15.8</v>
+      </c>
+      <c r="H70">
+        <v>12.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K70">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L70">
+        <v>48.872</v>
+      </c>
+      <c r="M70">
+        <v>22.04145262539891</v>
+      </c>
+      <c r="N70">
+        <v>26.83054737460109</v>
+      </c>
+      <c r="O70">
+        <v>7.244247791142295</v>
+      </c>
+      <c r="P70">
+        <v>19.5862995834588</v>
+      </c>
+      <c r="Q70">
+        <v>66.44829958345879</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1500425633552551</v>
+      </c>
+      <c r="T70">
+        <v>1.90845721681872</v>
+      </c>
+      <c r="U70">
+        <v>0.09028110587651872</v>
+      </c>
+      <c r="V70">
+        <v>0.27</v>
+      </c>
+      <c r="W70">
+        <v>0.06590520728985866</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>2.217276729923126</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.09291989290346493</v>
+      </c>
+      <c r="C71">
+        <v>919.6054879157944</v>
+      </c>
+      <c r="D71">
+        <v>1151.538293328992</v>
+      </c>
+      <c r="E71">
+        <v>-98.90024591027739</v>
+      </c>
+      <c r="F71">
+        <v>247.7328054131981</v>
+      </c>
+      <c r="G71">
+        <v>15.8</v>
+      </c>
+      <c r="H71">
+        <v>12.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K71">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L71">
+        <v>48.872</v>
+      </c>
+      <c r="M71">
+        <v>22.36559163459595</v>
+      </c>
+      <c r="N71">
+        <v>26.50640836540405</v>
+      </c>
+      <c r="O71">
+        <v>7.156730258659095</v>
+      </c>
+      <c r="P71">
+        <v>19.34967810674496</v>
+      </c>
+      <c r="Q71">
+        <v>66.21167810674496</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1530493544305241</v>
+      </c>
+      <c r="T71">
+        <v>1.96350509690113</v>
+      </c>
+      <c r="U71">
+        <v>0.09028110587651872</v>
+      </c>
+      <c r="V71">
+        <v>0.27</v>
+      </c>
+      <c r="W71">
+        <v>0.06590520728985866</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>2.185142284561922</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.09301062457614433</v>
+      </c>
+      <c r="C72">
+        <v>913.8020751473226</v>
+      </c>
+      <c r="D72">
+        <v>1149.325211073756</v>
+      </c>
+      <c r="E72">
+        <v>-95.30991539704266</v>
+      </c>
+      <c r="F72">
+        <v>251.3231359264329</v>
+      </c>
+      <c r="G72">
+        <v>15.8</v>
+      </c>
+      <c r="H72">
+        <v>12.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K72">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L72">
+        <v>48.872</v>
+      </c>
+      <c r="M72">
+        <v>22.68973064379299</v>
+      </c>
+      <c r="N72">
+        <v>26.18226935620701</v>
+      </c>
+      <c r="O72">
+        <v>7.069212726175893</v>
+      </c>
+      <c r="P72">
+        <v>19.11305663003112</v>
+      </c>
+      <c r="Q72">
+        <v>65.9750566300311</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1562565982441443</v>
+      </c>
+      <c r="T72">
+        <v>2.022222835655701</v>
+      </c>
+      <c r="U72">
+        <v>0.09028110587651872</v>
+      </c>
+      <c r="V72">
+        <v>0.27</v>
+      </c>
+      <c r="W72">
+        <v>0.06590520728985866</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>2.153925966211037</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.09310135624882374</v>
+      </c>
+      <c r="C73">
+        <v>908.007152480223</v>
+      </c>
+      <c r="D73">
+        <v>1147.120618919891</v>
+      </c>
+      <c r="E73">
+        <v>-91.71958488380793</v>
+      </c>
+      <c r="F73">
+        <v>254.9134664396676</v>
+      </c>
+      <c r="G73">
+        <v>15.8</v>
+      </c>
+      <c r="H73">
+        <v>12.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K73">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L73">
+        <v>48.872</v>
+      </c>
+      <c r="M73">
+        <v>23.01386965299003</v>
+      </c>
+      <c r="N73">
+        <v>25.85813034700997</v>
+      </c>
+      <c r="O73">
+        <v>6.981695193692692</v>
+      </c>
+      <c r="P73">
+        <v>18.87643515331727</v>
+      </c>
+      <c r="Q73">
+        <v>65.73843515331727</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1596850312862899</v>
+      </c>
+      <c r="T73">
+        <v>2.084990073634724</v>
+      </c>
+      <c r="U73">
+        <v>0.09028110587651872</v>
+      </c>
+      <c r="V73">
+        <v>0.27</v>
+      </c>
+      <c r="W73">
+        <v>0.06590520728985866</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>2.123588980771445</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.09319208792150313</v>
+      </c>
+      <c r="C74">
+        <v>902.2206711518561</v>
+      </c>
+      <c r="D74">
+        <v>1144.924468104758</v>
+      </c>
+      <c r="E74">
+        <v>-88.12925437057316</v>
+      </c>
+      <c r="F74">
+        <v>258.5037969529023</v>
+      </c>
+      <c r="G74">
+        <v>15.8</v>
+      </c>
+      <c r="H74">
+        <v>12.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K74">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L74">
+        <v>48.872</v>
+      </c>
+      <c r="M74">
+        <v>23.33800866218708</v>
+      </c>
+      <c r="N74">
+        <v>25.53399133781292</v>
+      </c>
+      <c r="O74">
+        <v>6.89417766120949</v>
+      </c>
+      <c r="P74">
+        <v>18.63981367660343</v>
+      </c>
+      <c r="Q74">
+        <v>65.50181367660343</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1633583524028747</v>
+      </c>
+      <c r="T74">
+        <v>2.152240685755107</v>
+      </c>
+      <c r="U74">
+        <v>0.09028110587651872</v>
+      </c>
+      <c r="V74">
+        <v>0.27</v>
+      </c>
+      <c r="W74">
+        <v>0.06590520728985866</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>2.094094689371842</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.09328281959418255</v>
+      </c>
+      <c r="C75">
+        <v>896.4425827722903</v>
+      </c>
+      <c r="D75">
+        <v>1142.736710238427</v>
+      </c>
+      <c r="E75">
+        <v>-84.53892385733843</v>
+      </c>
+      <c r="F75">
+        <v>262.0941274661371</v>
+      </c>
+      <c r="G75">
+        <v>15.8</v>
+      </c>
+      <c r="H75">
+        <v>12.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K75">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L75">
+        <v>48.872</v>
+      </c>
+      <c r="M75">
+        <v>23.66214767138412</v>
+      </c>
+      <c r="N75">
+        <v>25.20985232861588</v>
+      </c>
+      <c r="O75">
+        <v>6.806660128726289</v>
+      </c>
+      <c r="P75">
+        <v>18.4031921998896</v>
+      </c>
+      <c r="Q75">
+        <v>65.26519219988958</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1673037713799471</v>
+      </c>
+      <c r="T75">
+        <v>2.224472824699222</v>
+      </c>
+      <c r="U75">
+        <v>0.09028110587651872</v>
+      </c>
+      <c r="V75">
+        <v>0.27</v>
+      </c>
+      <c r="W75">
+        <v>0.06590520728985866</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>2.06540846075031</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.09337355126686195</v>
+      </c>
+      <c r="C76">
+        <v>890.6728393207511</v>
+      </c>
+      <c r="D76">
+        <v>1140.557297300123</v>
+      </c>
+      <c r="E76">
+        <v>-80.94859334410364</v>
+      </c>
+      <c r="F76">
+        <v>265.6844579793719</v>
+      </c>
+      <c r="G76">
+        <v>15.8</v>
+      </c>
+      <c r="H76">
+        <v>12.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K76">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L76">
+        <v>48.872</v>
+      </c>
+      <c r="M76">
+        <v>23.98628668058116</v>
+      </c>
+      <c r="N76">
+        <v>24.88571331941884</v>
+      </c>
+      <c r="O76">
+        <v>6.719142596243088</v>
+      </c>
+      <c r="P76">
+        <v>18.16657072317575</v>
+      </c>
+      <c r="Q76">
+        <v>65.02857072317575</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1715526841244867</v>
+      </c>
+      <c r="T76">
+        <v>2.302261282023653</v>
+      </c>
+      <c r="U76">
+        <v>0.09028110587651872</v>
+      </c>
+      <c r="V76">
+        <v>0.27</v>
+      </c>
+      <c r="W76">
+        <v>0.06590520728985866</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>2.037497535605036</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.09346428293954134</v>
+      </c>
+      <c r="C77">
+        <v>884.9113931421032</v>
+      </c>
+      <c r="D77">
+        <v>1138.38618163471</v>
+      </c>
+      <c r="E77">
+        <v>-77.35826283086891</v>
+      </c>
+      <c r="F77">
+        <v>269.2747884926066</v>
+      </c>
+      <c r="G77">
+        <v>15.8</v>
+      </c>
+      <c r="H77">
+        <v>12.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K77">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L77">
+        <v>48.872</v>
+      </c>
+      <c r="M77">
+        <v>24.3104256897782</v>
+      </c>
+      <c r="N77">
+        <v>24.5615743102218</v>
+      </c>
+      <c r="O77">
+        <v>6.631625063759886</v>
+      </c>
+      <c r="P77">
+        <v>17.92994924646191</v>
+      </c>
+      <c r="Q77">
+        <v>64.79194924646191</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1761415098885894</v>
+      </c>
+      <c r="T77">
+        <v>2.386272815934039</v>
+      </c>
+      <c r="U77">
+        <v>0.09028110587651872</v>
+      </c>
+      <c r="V77">
+        <v>0.27</v>
+      </c>
+      <c r="W77">
+        <v>0.06590520728985866</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>2.010330901796968</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1025982546122208</v>
+      </c>
+      <c r="C78">
+        <v>698.2522833747979</v>
+      </c>
+      <c r="D78">
+        <v>955.3174023806394</v>
+      </c>
+      <c r="E78">
+        <v>-73.76793231763412</v>
+      </c>
+      <c r="F78">
+        <v>272.8651190058414</v>
+      </c>
+      <c r="G78">
+        <v>15.8</v>
+      </c>
+      <c r="H78">
+        <v>12.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K78">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L78">
+        <v>48.872</v>
+      </c>
+      <c r="M78">
+        <v>29.08226613877046</v>
+      </c>
+      <c r="N78">
+        <v>19.78973386122954</v>
+      </c>
+      <c r="O78">
+        <v>5.343228142531975</v>
+      </c>
+      <c r="P78">
+        <v>14.44650571869756</v>
+      </c>
+      <c r="Q78">
+        <v>61.30850571869755</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1811127377997008</v>
+      </c>
+      <c r="T78">
+        <v>2.477285311003624</v>
+      </c>
+      <c r="U78">
+        <v>0.1065811058765187</v>
+      </c>
+      <c r="V78">
+        <v>0.27</v>
+      </c>
+      <c r="W78">
+        <v>0.07780420728985867</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>1.680474271392738</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1028079762849002</v>
+      </c>
+      <c r="C79">
+        <v>691.147518976632</v>
+      </c>
+      <c r="D79">
+        <v>951.8029684957082</v>
+      </c>
+      <c r="E79">
+        <v>-70.17760180439939</v>
+      </c>
+      <c r="F79">
+        <v>276.4554495190761</v>
+      </c>
+      <c r="G79">
+        <v>15.8</v>
+      </c>
+      <c r="H79">
+        <v>12.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K79">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L79">
+        <v>48.872</v>
+      </c>
+      <c r="M79">
+        <v>29.46492753533323</v>
+      </c>
+      <c r="N79">
+        <v>19.40707246466677</v>
+      </c>
+      <c r="O79">
+        <v>5.239909565460028</v>
+      </c>
+      <c r="P79">
+        <v>14.16716289920674</v>
+      </c>
+      <c r="Q79">
+        <v>61.02916289920674</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1865162463987348</v>
+      </c>
+      <c r="T79">
+        <v>2.576211936079259</v>
+      </c>
+      <c r="U79">
+        <v>0.1065811058765187</v>
+      </c>
+      <c r="V79">
+        <v>0.27</v>
+      </c>
+      <c r="W79">
+        <v>0.07780420728985867</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>1.65864993020582</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1030176979575796</v>
+      </c>
+      <c r="C80">
+        <v>684.0685176895026</v>
+      </c>
+      <c r="D80">
+        <v>948.3142977218135</v>
+      </c>
+      <c r="E80">
+        <v>-66.5872712911646</v>
+      </c>
+      <c r="F80">
+        <v>280.0457800323109</v>
+      </c>
+      <c r="G80">
+        <v>15.8</v>
+      </c>
+      <c r="H80">
+        <v>12.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K80">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L80">
+        <v>48.872</v>
+      </c>
+      <c r="M80">
+        <v>29.84758893189601</v>
+      </c>
+      <c r="N80">
+        <v>19.02441106810399</v>
+      </c>
+      <c r="O80">
+        <v>5.136590988388079</v>
+      </c>
+      <c r="P80">
+        <v>13.88782007971592</v>
+      </c>
+      <c r="Q80">
+        <v>60.74982007971591</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.1924109830522265</v>
+      </c>
+      <c r="T80">
+        <v>2.684131890707225</v>
+      </c>
+      <c r="U80">
+        <v>0.1065811058765187</v>
+      </c>
+      <c r="V80">
+        <v>0.27</v>
+      </c>
+      <c r="W80">
+        <v>0.07780420728985867</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>1.637385187510873</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.103227419630259</v>
+      </c>
+      <c r="C81">
+        <v>677.0149972571579</v>
+      </c>
+      <c r="D81">
+        <v>944.8511078027036</v>
+      </c>
+      <c r="E81">
+        <v>-62.99694077792986</v>
+      </c>
+      <c r="F81">
+        <v>283.6361105455456</v>
+      </c>
+      <c r="G81">
+        <v>15.8</v>
+      </c>
+      <c r="H81">
+        <v>12.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K81">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L81">
+        <v>48.872</v>
+      </c>
+      <c r="M81">
+        <v>30.23025032845877</v>
+      </c>
+      <c r="N81">
+        <v>18.64174967154123</v>
+      </c>
+      <c r="O81">
+        <v>5.033272411316132</v>
+      </c>
+      <c r="P81">
+        <v>13.6084772602251</v>
+      </c>
+      <c r="Q81">
+        <v>60.4704772602251</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.1988671231965268</v>
+      </c>
+      <c r="T81">
+        <v>2.80232993625214</v>
+      </c>
+      <c r="U81">
+        <v>0.1065811058765187</v>
+      </c>
+      <c r="V81">
+        <v>0.27</v>
+      </c>
+      <c r="W81">
+        <v>0.07780420728985867</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>1.616658792732255</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1034371413029384</v>
+      </c>
+      <c r="C82">
+        <v>669.9866795314783</v>
+      </c>
+      <c r="D82">
+        <v>941.4131205902587</v>
+      </c>
+      <c r="E82">
+        <v>-59.40661026469513</v>
+      </c>
+      <c r="F82">
+        <v>287.2264410587804</v>
+      </c>
+      <c r="G82">
+        <v>15.8</v>
+      </c>
+      <c r="H82">
+        <v>12.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K82">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L82">
+        <v>48.872</v>
+      </c>
+      <c r="M82">
+        <v>30.61291172502154</v>
+      </c>
+      <c r="N82">
+        <v>18.25908827497846</v>
+      </c>
+      <c r="O82">
+        <v>4.929953834244185</v>
+      </c>
+      <c r="P82">
+        <v>13.32913444073428</v>
+      </c>
+      <c r="Q82">
+        <v>60.19113444073427</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2059688773552573</v>
+      </c>
+      <c r="T82">
+        <v>2.932347786351547</v>
+      </c>
+      <c r="U82">
+        <v>0.1065811058765187</v>
+      </c>
+      <c r="V82">
+        <v>0.27</v>
+      </c>
+      <c r="W82">
+        <v>0.07780420728985867</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>1.596450557823102</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1036468629756178</v>
+      </c>
+      <c r="C83">
+        <v>662.983290398008</v>
+      </c>
+      <c r="D83">
+        <v>938.0000619700231</v>
+      </c>
+      <c r="E83">
+        <v>-55.81627975146034</v>
+      </c>
+      <c r="F83">
+        <v>290.8167715720152</v>
+      </c>
+      <c r="G83">
+        <v>15.8</v>
+      </c>
+      <c r="H83">
+        <v>12.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K83">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L83">
+        <v>48.872</v>
+      </c>
+      <c r="M83">
+        <v>30.99557312158431</v>
+      </c>
+      <c r="N83">
+        <v>17.87642687841569</v>
+      </c>
+      <c r="O83">
+        <v>4.826635257172236</v>
+      </c>
+      <c r="P83">
+        <v>13.04979162124345</v>
+      </c>
+      <c r="Q83">
+        <v>59.91179162124345</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2138181845833277</v>
+      </c>
+      <c r="T83">
+        <v>3.076051725935101</v>
+      </c>
+      <c r="U83">
+        <v>0.1065811058765187</v>
+      </c>
+      <c r="V83">
+        <v>0.27</v>
+      </c>
+      <c r="W83">
+        <v>0.07780420728985867</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>1.576741291677137</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1038565846482972</v>
+      </c>
+      <c r="C84">
+        <v>656.0045597030977</v>
+      </c>
+      <c r="D84">
+        <v>934.6116617883476</v>
+      </c>
+      <c r="E84">
+        <v>-52.22594923822561</v>
+      </c>
+      <c r="F84">
+        <v>294.4071020852499</v>
+      </c>
+      <c r="G84">
+        <v>15.8</v>
+      </c>
+      <c r="H84">
+        <v>12.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K84">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L84">
+        <v>48.872</v>
+      </c>
+      <c r="M84">
+        <v>31.37823451814708</v>
+      </c>
+      <c r="N84">
+        <v>17.49376548185292</v>
+      </c>
+      <c r="O84">
+        <v>4.723316680100289</v>
+      </c>
+      <c r="P84">
+        <v>12.77044880175263</v>
+      </c>
+      <c r="Q84">
+        <v>59.63244880175263</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2225396370589616</v>
+      </c>
+      <c r="T84">
+        <v>3.235722769916829</v>
+      </c>
+      <c r="U84">
+        <v>0.1065811058765187</v>
+      </c>
+      <c r="V84">
+        <v>0.27</v>
+      </c>
+      <c r="W84">
+        <v>0.07780420728985867</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>1.557512739339611</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1040663063209766</v>
+      </c>
+      <c r="C85">
+        <v>649.0502211826254</v>
+      </c>
+      <c r="D85">
+        <v>931.2476537811101</v>
+      </c>
+      <c r="E85">
+        <v>-48.63561872499082</v>
+      </c>
+      <c r="F85">
+        <v>297.9974325984847</v>
+      </c>
+      <c r="G85">
+        <v>15.8</v>
+      </c>
+      <c r="H85">
+        <v>12.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K85">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L85">
+        <v>48.872</v>
+      </c>
+      <c r="M85">
+        <v>31.76089591470985</v>
+      </c>
+      <c r="N85">
+        <v>17.11110408529015</v>
+      </c>
+      <c r="O85">
+        <v>4.619998103028341</v>
+      </c>
+      <c r="P85">
+        <v>12.49110598226181</v>
+      </c>
+      <c r="Q85">
+        <v>59.35310598226181</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.232287142767023</v>
+      </c>
+      <c r="T85">
+        <v>3.41417864260229</v>
+      </c>
+      <c r="U85">
+        <v>0.1065811058765187</v>
+      </c>
+      <c r="V85">
+        <v>0.27</v>
+      </c>
+      <c r="W85">
+        <v>0.07780420728985867</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>1.538747525612628</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.104276027993656</v>
+      </c>
+      <c r="C86">
+        <v>642.1200123922454</v>
+      </c>
+      <c r="D86">
+        <v>927.9077755039649</v>
+      </c>
+      <c r="E86">
+        <v>-45.04528821175609</v>
+      </c>
+      <c r="F86">
+        <v>301.5877631117194</v>
+      </c>
+      <c r="G86">
+        <v>15.8</v>
+      </c>
+      <c r="H86">
+        <v>12.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K86">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L86">
+        <v>48.872</v>
+      </c>
+      <c r="M86">
+        <v>32.14355731127262</v>
+      </c>
+      <c r="N86">
+        <v>16.72844268872738</v>
+      </c>
+      <c r="O86">
+        <v>4.516679525956394</v>
+      </c>
+      <c r="P86">
+        <v>12.21176316277099</v>
+      </c>
+      <c r="Q86">
+        <v>59.07376316277099</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.243253086688592</v>
+      </c>
+      <c r="T86">
+        <v>3.61494149937343</v>
+      </c>
+      <c r="U86">
+        <v>0.1065811058765187</v>
+      </c>
+      <c r="V86">
+        <v>0.27</v>
+      </c>
+      <c r="W86">
+        <v>0.07780420728985867</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>1.520429102688668</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1044857496663354</v>
+      </c>
+      <c r="C87">
+        <v>635.2136746391382</v>
+      </c>
+      <c r="D87">
+        <v>924.5917682640924</v>
+      </c>
+      <c r="E87">
+        <v>-41.45495769852135</v>
+      </c>
+      <c r="F87">
+        <v>305.1780936249542</v>
+      </c>
+      <c r="G87">
+        <v>15.8</v>
+      </c>
+      <c r="H87">
+        <v>12.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K87">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L87">
+        <v>48.872</v>
+      </c>
+      <c r="M87">
+        <v>32.52621870783538</v>
+      </c>
+      <c r="N87">
+        <v>16.34578129216462</v>
+      </c>
+      <c r="O87">
+        <v>4.413360948884447</v>
+      </c>
+      <c r="P87">
+        <v>11.93242034328017</v>
+      </c>
+      <c r="Q87">
+        <v>58.79442034328017</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2556811564663702</v>
+      </c>
+      <c r="T87">
+        <v>3.842472737047391</v>
+      </c>
+      <c r="U87">
+        <v>0.1065811058765187</v>
+      </c>
+      <c r="V87">
+        <v>0.27</v>
+      </c>
+      <c r="W87">
+        <v>0.07780420728985867</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>1.502541701480566</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1496907023427542</v>
+      </c>
+      <c r="C88">
+        <v>229.3147044991188</v>
+      </c>
+      <c r="D88">
+        <v>522.2831286373078</v>
+      </c>
+      <c r="E88">
+        <v>-37.86462718528662</v>
+      </c>
+      <c r="F88">
+        <v>308.7684241381889</v>
+      </c>
+      <c r="G88">
+        <v>15.8</v>
+      </c>
+      <c r="H88">
+        <v>12.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K88">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L88">
+        <v>48.872</v>
+      </c>
+      <c r="M88">
+        <v>53.10233504303571</v>
+      </c>
+      <c r="N88">
+        <v>-4.230335043035709</v>
+      </c>
+      <c r="O88">
+        <v>-1.142190461619641</v>
+      </c>
+      <c r="P88">
+        <v>-3.088144581416067</v>
+      </c>
+      <c r="Q88">
+        <v>43.77385541858393</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.2752833423558707</v>
+      </c>
+      <c r="T88">
+        <v>4.201346616604128</v>
+      </c>
+      <c r="U88">
+        <v>0.1719811058765187</v>
+      </c>
+      <c r="V88">
+        <v>0.2484907676716292</v>
+      </c>
+      <c r="W88">
+        <v>0.1292453888522468</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.9203361765615896</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1509525134015194</v>
+      </c>
+      <c r="C89">
+        <v>219.457071320425</v>
+      </c>
+      <c r="D89">
+        <v>516.0158259718487</v>
+      </c>
+      <c r="E89">
+        <v>-34.27429667205183</v>
+      </c>
+      <c r="F89">
+        <v>312.3587546514237</v>
+      </c>
+      <c r="G89">
+        <v>15.8</v>
+      </c>
+      <c r="H89">
+        <v>12.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K89">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L89">
+        <v>48.872</v>
+      </c>
+      <c r="M89">
+        <v>53.71980405516404</v>
+      </c>
+      <c r="N89">
+        <v>-4.84780405516404</v>
+      </c>
+      <c r="O89">
+        <v>-1.308907094894291</v>
+      </c>
+      <c r="P89">
+        <v>-3.538896960269749</v>
+      </c>
+      <c r="Q89">
+        <v>43.32310303973024</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.2929359071524761</v>
+      </c>
+      <c r="T89">
+        <v>4.524527125573677</v>
+      </c>
+      <c r="U89">
+        <v>0.1719811058765187</v>
+      </c>
+      <c r="V89">
+        <v>0.2456345519512656</v>
+      </c>
+      <c r="W89">
+        <v>0.1297366039904569</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.9097575998195022</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1522143244602846</v>
+      </c>
+      <c r="C90">
+        <v>209.7480676021357</v>
+      </c>
+      <c r="D90">
+        <v>509.8971527667941</v>
+      </c>
+      <c r="E90">
+        <v>-30.6839661588171</v>
+      </c>
+      <c r="F90">
+        <v>315.9490851646584</v>
+      </c>
+      <c r="G90">
+        <v>15.8</v>
+      </c>
+      <c r="H90">
+        <v>12.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K90">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L90">
+        <v>48.872</v>
+      </c>
+      <c r="M90">
+        <v>54.33727306729236</v>
+      </c>
+      <c r="N90">
+        <v>-5.465273067292358</v>
+      </c>
+      <c r="O90">
+        <v>-1.475623728168937</v>
+      </c>
+      <c r="P90">
+        <v>-3.989649339123421</v>
+      </c>
+      <c r="Q90">
+        <v>42.87235066087657</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3135305660818493</v>
+      </c>
+      <c r="T90">
+        <v>4.901571052704818</v>
+      </c>
+      <c r="U90">
+        <v>0.1719811058765187</v>
+      </c>
+      <c r="V90">
+        <v>0.2428432502245467</v>
+      </c>
+      <c r="W90">
+        <v>0.130216655148253</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.8994194452760989</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1534761355190498</v>
+      </c>
+      <c r="C91">
+        <v>200.1824681670311</v>
+      </c>
+      <c r="D91">
+        <v>503.9218838449243</v>
+      </c>
+      <c r="E91">
+        <v>-27.09363564558231</v>
+      </c>
+      <c r="F91">
+        <v>319.5394156778932</v>
+      </c>
+      <c r="G91">
+        <v>15.8</v>
+      </c>
+      <c r="H91">
+        <v>12.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K91">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L91">
+        <v>48.872</v>
+      </c>
+      <c r="M91">
+        <v>54.95474207942068</v>
+      </c>
+      <c r="N91">
+        <v>-6.082742079420683</v>
+      </c>
+      <c r="O91">
+        <v>-1.642340361443585</v>
+      </c>
+      <c r="P91">
+        <v>-4.440401717977099</v>
+      </c>
+      <c r="Q91">
+        <v>42.4215982820229</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3378697084529264</v>
+      </c>
+      <c r="T91">
+        <v>5.347168421132528</v>
+      </c>
+      <c r="U91">
+        <v>0.1719811058765187</v>
+      </c>
+      <c r="V91">
+        <v>0.2401146743793271</v>
+      </c>
+      <c r="W91">
+        <v>0.1306859186395819</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.8893136088123225</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1547379465778149</v>
+      </c>
+      <c r="C92">
+        <v>190.7552899275072</v>
+      </c>
+      <c r="D92">
+        <v>498.0850361186352</v>
+      </c>
+      <c r="E92">
+        <v>-23.50330513234758</v>
+      </c>
+      <c r="F92">
+        <v>323.1297461911279</v>
+      </c>
+      <c r="G92">
+        <v>15.8</v>
+      </c>
+      <c r="H92">
+        <v>12.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K92">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L92">
+        <v>48.872</v>
+      </c>
+      <c r="M92">
+        <v>55.572211091549</v>
+      </c>
+      <c r="N92">
+        <v>-6.700211091549001</v>
+      </c>
+      <c r="O92">
+        <v>-1.80905699471823</v>
+      </c>
+      <c r="P92">
+        <v>-4.89115409683077</v>
+      </c>
+      <c r="Q92">
+        <v>41.97084590316923</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.3670766792982191</v>
+      </c>
+      <c r="T92">
+        <v>5.881885263245781</v>
+      </c>
+      <c r="U92">
+        <v>0.1719811058765187</v>
+      </c>
+      <c r="V92">
+        <v>0.2374467335528901</v>
+      </c>
+      <c r="W92">
+        <v>0.1311447540533256</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.8794323464921856</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1559997576365802</v>
+      </c>
+      <c r="C93">
+        <v>181.4617780256835</v>
+      </c>
+      <c r="D93">
+        <v>492.3818547300462</v>
+      </c>
+      <c r="E93">
+        <v>-19.91297461911279</v>
+      </c>
+      <c r="F93">
+        <v>326.7200767043627</v>
+      </c>
+      <c r="G93">
+        <v>15.8</v>
+      </c>
+      <c r="H93">
+        <v>12.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K93">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L93">
+        <v>48.872</v>
+      </c>
+      <c r="M93">
+        <v>56.18968010367733</v>
+      </c>
+      <c r="N93">
+        <v>-7.317680103677333</v>
+      </c>
+      <c r="O93">
+        <v>-1.97577362799288</v>
+      </c>
+      <c r="P93">
+        <v>-5.341906475684453</v>
+      </c>
+      <c r="Q93">
+        <v>41.52009352431554</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4027740881091324</v>
+      </c>
+      <c r="T93">
+        <v>6.535428070273091</v>
+      </c>
+      <c r="U93">
+        <v>0.1719811058765187</v>
+      </c>
+      <c r="V93">
+        <v>0.2348374287885726</v>
+      </c>
+      <c r="W93">
+        <v>0.1315935051722618</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.8697682547724911</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1572615686953453</v>
+      </c>
+      <c r="C94">
+        <v>172.2973929149234</v>
+      </c>
+      <c r="D94">
+        <v>486.8078001325209</v>
+      </c>
+      <c r="E94">
+        <v>-16.32264410587806</v>
+      </c>
+      <c r="F94">
+        <v>330.3104072175975</v>
+      </c>
+      <c r="G94">
+        <v>15.8</v>
+      </c>
+      <c r="H94">
+        <v>12.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K94">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L94">
+        <v>48.872</v>
+      </c>
+      <c r="M94">
+        <v>56.80714911580565</v>
+      </c>
+      <c r="N94">
+        <v>-7.93514911580565</v>
+      </c>
+      <c r="O94">
+        <v>-2.142490261267526</v>
+      </c>
+      <c r="P94">
+        <v>-5.792658854538125</v>
+      </c>
+      <c r="Q94">
+        <v>41.06934114546187</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.447395849122774</v>
+      </c>
+      <c r="T94">
+        <v>7.352356579057228</v>
+      </c>
+      <c r="U94">
+        <v>0.1719811058765187</v>
+      </c>
+      <c r="V94">
+        <v>0.2322848480408708</v>
+      </c>
+      <c r="W94">
+        <v>0.1320325008320907</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.860314252003225</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1585233797541105</v>
+      </c>
+      <c r="C95">
+        <v>163.2577983090019</v>
+      </c>
+      <c r="D95">
+        <v>481.3585360398342</v>
+      </c>
+      <c r="E95">
+        <v>-12.73231359264327</v>
+      </c>
+      <c r="F95">
+        <v>333.9007377308322</v>
+      </c>
+      <c r="G95">
+        <v>15.8</v>
+      </c>
+      <c r="H95">
+        <v>12.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K95">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L95">
+        <v>48.872</v>
+      </c>
+      <c r="M95">
+        <v>57.42461812793398</v>
+      </c>
+      <c r="N95">
+        <v>-8.552618127933975</v>
+      </c>
+      <c r="O95">
+        <v>-2.309206894542173</v>
+      </c>
+      <c r="P95">
+        <v>-6.243411233391802</v>
+      </c>
+      <c r="Q95">
+        <v>40.61858876660819</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.5047666847117418</v>
+      </c>
+      <c r="T95">
+        <v>8.402693233208263</v>
+      </c>
+      <c r="U95">
+        <v>0.1719811058765187</v>
+      </c>
+      <c r="V95">
+        <v>0.2297871615027969</v>
+      </c>
+      <c r="W95">
+        <v>0.1324620557250415</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.8510635611214699</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1597851908128757</v>
+      </c>
+      <c r="C96">
+        <v>154.3388499316868</v>
+      </c>
+      <c r="D96">
+        <v>476.0299181757538</v>
+      </c>
+      <c r="E96">
+        <v>-9.141983079408533</v>
+      </c>
+      <c r="F96">
+        <v>337.491068244067</v>
+      </c>
+      <c r="G96">
+        <v>15.8</v>
+      </c>
+      <c r="H96">
+        <v>12.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K96">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L96">
+        <v>48.872</v>
+      </c>
+      <c r="M96">
+        <v>58.04208714006229</v>
+      </c>
+      <c r="N96">
+        <v>-9.170087140062293</v>
+      </c>
+      <c r="O96">
+        <v>-2.475923527816819</v>
+      </c>
+      <c r="P96">
+        <v>-6.694163612245474</v>
+      </c>
+      <c r="Q96">
+        <v>40.16783638775452</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.5812611321636989</v>
+      </c>
+      <c r="T96">
+        <v>9.803142105409643</v>
+      </c>
+      <c r="U96">
+        <v>0.1719811058765187</v>
+      </c>
+      <c r="V96">
+        <v>0.2273426172314905</v>
+      </c>
+      <c r="W96">
+        <v>0.1328824711521849</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.8420096934499649</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1610470018716409</v>
+      </c>
+      <c r="C97">
+        <v>145.5365850053882</v>
+      </c>
+      <c r="D97">
+        <v>470.8179837626899</v>
+      </c>
+      <c r="E97">
+        <v>-5.5516525661738</v>
+      </c>
+      <c r="F97">
+        <v>341.0813987573017</v>
+      </c>
+      <c r="G97">
+        <v>15.8</v>
+      </c>
+      <c r="H97">
+        <v>12.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K97">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L97">
+        <v>48.872</v>
+      </c>
+      <c r="M97">
+        <v>58.65955615219061</v>
+      </c>
+      <c r="N97">
+        <v>-9.787556152190611</v>
+      </c>
+      <c r="O97">
+        <v>-2.642640161091465</v>
+      </c>
+      <c r="P97">
+        <v>-7.144915991099145</v>
+      </c>
+      <c r="Q97">
+        <v>39.71708400890085</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.688353358596439</v>
+      </c>
+      <c r="T97">
+        <v>11.76377052649158</v>
+      </c>
+      <c r="U97">
+        <v>0.1719811058765187</v>
+      </c>
+      <c r="V97">
+        <v>0.2249495370501065</v>
+      </c>
+      <c r="W97">
+        <v>0.1332940357282305</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.8331464335189127</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1623088129304061</v>
+      </c>
+      <c r="C98">
+        <v>136.8472124228454</v>
+      </c>
+      <c r="D98">
+        <v>465.7189416933818</v>
+      </c>
+      <c r="E98">
+        <v>-1.961322052939067</v>
+      </c>
+      <c r="F98">
+        <v>344.6717292705364</v>
+      </c>
+      <c r="G98">
+        <v>15.8</v>
+      </c>
+      <c r="H98">
+        <v>12.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K98">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L98">
+        <v>48.872</v>
+      </c>
+      <c r="M98">
+        <v>59.27702516431894</v>
+      </c>
+      <c r="N98">
+        <v>-10.40502516431894</v>
+      </c>
+      <c r="O98">
+        <v>-2.809356794366113</v>
+      </c>
+      <c r="P98">
+        <v>-7.595668369952823</v>
+      </c>
+      <c r="Q98">
+        <v>39.26633163004717</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.8489916982455469</v>
+      </c>
+      <c r="T98">
+        <v>14.70471315811444</v>
+      </c>
+      <c r="U98">
+        <v>0.1719811058765187</v>
+      </c>
+      <c r="V98">
+        <v>0.2226063127058345</v>
+      </c>
+      <c r="W98">
+        <v>0.1336970260422752</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.824467824836424</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1635706239891713</v>
+      </c>
+      <c r="C99">
+        <v>128.2671035506273</v>
+      </c>
+      <c r="D99">
+        <v>460.7291633343985</v>
+      </c>
+      <c r="E99">
+        <v>1.629008460295722</v>
+      </c>
+      <c r="F99">
+        <v>348.2620597837712</v>
+      </c>
+      <c r="G99">
+        <v>15.8</v>
+      </c>
+      <c r="H99">
+        <v>12.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K99">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L99">
+        <v>48.872</v>
+      </c>
+      <c r="M99">
+        <v>59.89449417644726</v>
+      </c>
+      <c r="N99">
+        <v>-11.02249417644726</v>
+      </c>
+      <c r="O99">
+        <v>-2.976073427640761</v>
+      </c>
+      <c r="P99">
+        <v>-8.046420748806501</v>
+      </c>
+      <c r="Q99">
+        <v>38.8155792511935</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.116722264327396</v>
+      </c>
+      <c r="T99">
+        <v>19.60628421081925</v>
+      </c>
+      <c r="U99">
+        <v>0.1719811058765187</v>
+      </c>
+      <c r="V99">
+        <v>0.2203114022655681</v>
+      </c>
+      <c r="W99">
+        <v>0.1340917072776798</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.8159681565391412</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1648324350479365</v>
+      </c>
+      <c r="C100">
+        <v>119.7927836175604</v>
+      </c>
+      <c r="D100">
+        <v>455.8451739145663</v>
+      </c>
+      <c r="E100">
+        <v>5.219338973530455</v>
+      </c>
+      <c r="F100">
+        <v>351.852390297006</v>
+      </c>
+      <c r="G100">
+        <v>15.8</v>
+      </c>
+      <c r="H100">
+        <v>12.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K100">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L100">
+        <v>48.872</v>
+      </c>
+      <c r="M100">
+        <v>60.51196318857558</v>
+      </c>
+      <c r="N100">
+        <v>-11.63996318857558</v>
+      </c>
+      <c r="O100">
+        <v>-3.142790060915406</v>
+      </c>
+      <c r="P100">
+        <v>-8.497173127660172</v>
+      </c>
+      <c r="Q100">
+        <v>38.36482687233982</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.652183396491094</v>
+      </c>
+      <c r="T100">
+        <v>29.40942631622888</v>
+      </c>
+      <c r="U100">
+        <v>0.1719811058765187</v>
+      </c>
+      <c r="V100">
+        <v>0.218063326732246</v>
+      </c>
+      <c r="W100">
+        <v>0.1344783337939944</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.8076419508601704</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2198054094421459</v>
+      </c>
+      <c r="C101">
+        <v>-27.81125976625725</v>
+      </c>
+      <c r="D101">
+        <v>311.8314610439835</v>
+      </c>
+      <c r="E101">
+        <v>8.809669486765245</v>
+      </c>
+      <c r="F101">
+        <v>355.4427208102408</v>
+      </c>
+      <c r="G101">
+        <v>15.8</v>
+      </c>
+      <c r="H101">
+        <v>12.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>95.73399999999999</v>
+      </c>
+      <c r="K101">
+        <v>46.86199999999999</v>
+      </c>
+      <c r="L101">
+        <v>48.872</v>
+      </c>
+      <c r="M101">
+        <v>79.68354222699847</v>
+      </c>
+      <c r="N101">
+        <v>-30.81154222699847</v>
+      </c>
+      <c r="O101">
+        <v>-8.319116401289588</v>
+      </c>
+      <c r="P101">
+        <v>-22.49242582570888</v>
+      </c>
+      <c r="Q101">
+        <v>24.36957417429111</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.461883126526614</v>
+      </c>
+      <c r="T101">
+        <v>62.54113757596611</v>
+      </c>
+      <c r="U101">
+        <v>0.2241811058765187</v>
+      </c>
+      <c r="V101">
+        <v>0.1655980599156786</v>
+      </c>
+      <c r="W101">
+        <v>0.1870571496736159</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.6133261478358467</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/chile/chile_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_hotel_gaming.xlsx
@@ -644,10 +644,10 @@
         <v>-1.481402763018066</v>
       </c>
       <c r="X2">
-        <v>0.9204619395787169</v>
+        <v>0.9201037169195851</v>
       </c>
       <c r="Y2">
-        <v>-2.401864702596783</v>
+        <v>-2.401506479937651</v>
       </c>
       <c r="Z2">
         <v>0.898435429742054</v>
@@ -656,10 +656,10 @@
         <v>0.002516957888626193</v>
       </c>
       <c r="AB2">
-        <v>0.2038860609043269</v>
+        <v>0.2038736888930125</v>
       </c>
       <c r="AC2">
-        <v>-0.2013691030157007</v>
+        <v>-0.2013567310043863</v>
       </c>
       <c r="AD2">
         <v>346.4</v>
@@ -775,10 +775,10 @@
         <v>-1.481402763018066</v>
       </c>
       <c r="X3">
-        <v>0.9204619395787169</v>
+        <v>0.9201037169195851</v>
       </c>
       <c r="Y3">
-        <v>-2.401864702596783</v>
+        <v>-2.401506479937651</v>
       </c>
       <c r="Z3">
         <v>0.898435429742054</v>
@@ -787,10 +787,10 @@
         <v>0.002516957888626193</v>
       </c>
       <c r="AB3">
-        <v>0.2038860609043269</v>
+        <v>0.2038736888930125</v>
       </c>
       <c r="AC3">
-        <v>-0.2013691030157007</v>
+        <v>-0.2013567310043863</v>
       </c>
       <c r="AD3">
         <v>346.4</v>
@@ -1127,49 +1127,49 @@
         <v>0.0117957746478874</v>
       </c>
       <c r="F2">
-        <v>4.56376656645041</v>
+        <v>4.5479661901308</v>
       </c>
       <c r="G2">
         <v>7.24158713358839</v>
       </c>
       <c r="H2">
-        <v>3.37528721448104</v>
+        <v>3.52529997956909</v>
       </c>
       <c r="I2">
         <v>0.965462789695013</v>
       </c>
       <c r="J2">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="K2">
         <v>12.4</v>
       </c>
       <c r="L2">
-        <v>1318.42299009129</v>
+        <v>1354.89229233182</v>
       </c>
       <c r="M2">
         <v>343.233051323475</v>
       </c>
       <c r="N2">
-        <v>1464.18786318686</v>
+        <v>1507.83782645385</v>
       </c>
       <c r="O2">
         <v>346.633051323476</v>
       </c>
       <c r="P2">
-        <v>161.564873095564</v>
+        <v>168.745534122033</v>
       </c>
       <c r="Q2">
-        <v>0.203886060904327</v>
+        <v>0.203873688893012</v>
       </c>
       <c r="R2">
-        <v>0.0828583327591592</v>
+        <v>0.0817827254767222</v>
       </c>
       <c r="S2">
         <v>0.178252207289859</v>
       </c>
       <c r="T2">
-        <v>0.0483852072898587</v>
+        <v>0.0464872072898587</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.920461939578717</v>
+        <v>0.920103716919585</v>
       </c>
       <c r="X2">
-        <v>0.111063617234041</v>
+        <v>0.113082524623564</v>
       </c>
       <c r="Y2">
         <v>16.0131796181652</v>
       </c>
       <c r="Z2">
-        <v>1.1948365168413</v>
+        <v>1.23230306712723</v>
       </c>
       <c r="AA2">
         <v>346.4</v>
@@ -1224,7 +1224,7 @@
         <v>12.4</v>
       </c>
       <c r="AK2">
-        <v>0.05462137816692637</v>
+        <v>0.05459900767788712</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1409,13 +1409,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08665940748858603</v>
+        <v>0.08664267329113351</v>
       </c>
       <c r="C2">
-        <v>1343.777187898733</v>
+        <v>1344.217319453104</v>
       </c>
       <c r="D2">
-        <v>1327.977187898733</v>
+        <v>1328.417319453104</v>
       </c>
       <c r="E2">
         <v>-346.6330513234755</v>
@@ -1460,19 +1460,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08665940748858603</v>
+        <v>0.08664267329113351</v>
       </c>
       <c r="T2">
         <v>0.7480479046815169</v>
       </c>
       <c r="U2">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V2">
         <v>0.27</v>
       </c>
       <c r="W2">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1491,13 +1491,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08652967916126544</v>
+        <v>0.08650277014614603</v>
       </c>
       <c r="C3">
-        <v>1344.416604902632</v>
+        <v>1345.193011355051</v>
       </c>
       <c r="D3">
-        <v>1332.206935415866</v>
+        <v>1332.983341868286</v>
       </c>
       <c r="E3">
         <v>-343.0427208102408</v>
@@ -1524,37 +1524,37 @@
         <v>48.872</v>
       </c>
       <c r="M3">
-        <v>0.2157110276973531</v>
+        <v>0.2106845649788245</v>
       </c>
       <c r="N3">
-        <v>48.65628897230265</v>
+        <v>48.66131543502117</v>
       </c>
       <c r="O3">
-        <v>13.13719802252172</v>
+        <v>13.13855516745572</v>
       </c>
       <c r="P3">
-        <v>35.51909094978093</v>
+        <v>35.52276026756546</v>
       </c>
       <c r="Q3">
-        <v>82.38109094978093</v>
+        <v>82.38476026756545</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08696069402865339</v>
+        <v>0.08694383643762368</v>
       </c>
       <c r="T3">
         <v>0.753563813473613</v>
       </c>
       <c r="U3">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V3">
         <v>0.27</v>
       </c>
       <c r="W3">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>226.5623622570117</v>
+        <v>231.967633722537</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,13 +1573,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08639995083394483</v>
+        <v>0.08636286700115858</v>
       </c>
       <c r="C4">
-        <v>1345.083052386082</v>
+        <v>1346.200200088617</v>
       </c>
       <c r="D4">
-        <v>1336.463713412551</v>
+        <v>1337.580861115087</v>
       </c>
       <c r="E4">
         <v>-339.452390297006</v>
@@ -1606,37 +1606,37 @@
         <v>48.872</v>
       </c>
       <c r="M4">
-        <v>0.4314220553947063</v>
+        <v>0.421369129957649</v>
       </c>
       <c r="N4">
-        <v>48.44057794460529</v>
+        <v>48.45063087004235</v>
       </c>
       <c r="O4">
-        <v>13.07895604504343</v>
+        <v>13.08167033491144</v>
       </c>
       <c r="P4">
-        <v>35.36162189956187</v>
+        <v>35.36896053513092</v>
       </c>
       <c r="Q4">
-        <v>82.22362189956186</v>
+        <v>82.23096053513092</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08726812927362007</v>
+        <v>0.08725114577077694</v>
       </c>
       <c r="T4">
         <v>0.7591922918328947</v>
       </c>
       <c r="U4">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V4">
         <v>0.27</v>
       </c>
       <c r="W4">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>113.2811811285058</v>
+        <v>115.9838168612685</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,13 +1655,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08627022250662424</v>
+        <v>0.08622296385617109</v>
       </c>
       <c r="C5">
-        <v>1345.77679028975</v>
+        <v>1347.239212683694</v>
       </c>
       <c r="D5">
-        <v>1340.747781829455</v>
+        <v>1342.210204223398</v>
       </c>
       <c r="E5">
         <v>-335.8620597837713</v>
@@ -1688,37 +1688,37 @@
         <v>48.872</v>
       </c>
       <c r="M5">
-        <v>0.6471330830920593</v>
+        <v>0.6320536949364735</v>
       </c>
       <c r="N5">
-        <v>48.22486691690794</v>
+        <v>48.23994630506353</v>
       </c>
       <c r="O5">
-        <v>13.02071406756514</v>
+        <v>13.02478550236715</v>
       </c>
       <c r="P5">
-        <v>35.2041528493428</v>
+        <v>35.21516080269637</v>
       </c>
       <c r="Q5">
-        <v>82.06615284934279</v>
+        <v>82.07716080269637</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08758190338961699</v>
+        <v>0.08756479137884055</v>
       </c>
       <c r="T5">
         <v>0.7649368212923677</v>
       </c>
       <c r="U5">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V5">
         <v>0.27</v>
       </c>
       <c r="W5">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.52078741900391</v>
+        <v>77.32254457417899</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,13 +1737,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08614049417930367</v>
+        <v>0.08608306071118363</v>
       </c>
       <c r="C6">
-        <v>1346.49808189801</v>
+        <v>1348.310380713269</v>
       </c>
       <c r="D6">
-        <v>1345.059403950949</v>
+        <v>1346.871702766208</v>
       </c>
       <c r="E6">
         <v>-332.2717292705365</v>
@@ -1770,37 +1770,37 @@
         <v>48.872</v>
       </c>
       <c r="M6">
-        <v>0.8628441107894126</v>
+        <v>0.8427382599152979</v>
       </c>
       <c r="N6">
-        <v>48.00915588921059</v>
+        <v>48.0292617400847</v>
       </c>
       <c r="O6">
-        <v>12.96247209008686</v>
+        <v>12.96790066982287</v>
       </c>
       <c r="P6">
-        <v>35.04668379912373</v>
+        <v>35.06136107026183</v>
       </c>
       <c r="Q6">
-        <v>81.90868379912372</v>
+        <v>81.92336107026182</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08790221446636387</v>
+        <v>0.08788497127040551</v>
       </c>
       <c r="T6">
         <v>0.7708010284489132</v>
       </c>
       <c r="U6">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V6">
         <v>0.27</v>
       </c>
       <c r="W6">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.64059056425292</v>
+        <v>57.99190843063424</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,13 +1819,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08601076585198304</v>
+        <v>0.08594315756619614</v>
       </c>
       <c r="C7">
-        <v>1347.247193892877</v>
+        <v>1349.414040372604</v>
       </c>
       <c r="D7">
-        <v>1349.398846459051</v>
+        <v>1351.565692938778</v>
       </c>
       <c r="E7">
         <v>-328.6813987573017</v>
@@ -1852,37 +1852,37 @@
         <v>48.872</v>
       </c>
       <c r="M7">
-        <v>1.078555138486766</v>
+        <v>1.053422824894122</v>
       </c>
       <c r="N7">
-        <v>47.79344486151324</v>
+        <v>47.81857717510588</v>
       </c>
       <c r="O7">
-        <v>12.90423011260857</v>
+        <v>12.91101583727859</v>
       </c>
       <c r="P7">
-        <v>34.88921474890466</v>
+        <v>34.90756133782729</v>
       </c>
       <c r="Q7">
-        <v>81.75121474890466</v>
+        <v>81.76956133782728</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08822926893420012</v>
+        <v>0.08821189179126654</v>
       </c>
       <c r="T7">
         <v>0.7767886925982278</v>
       </c>
       <c r="U7">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V7">
         <v>0.27</v>
       </c>
       <c r="W7">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.31247245140234</v>
+        <v>46.3935267445074</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,13 +1901,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08588103752466246</v>
+        <v>0.08580325442120866</v>
       </c>
       <c r="C8">
-        <v>1348.024396408989</v>
+        <v>1350.550532560052</v>
       </c>
       <c r="D8">
-        <v>1353.766379488398</v>
+        <v>1356.29251563946</v>
       </c>
       <c r="E8">
         <v>-325.091068244067</v>
@@ -1934,37 +1934,37 @@
         <v>48.872</v>
       </c>
       <c r="M8">
-        <v>1.294266166184119</v>
+        <v>1.264107389872947</v>
       </c>
       <c r="N8">
-        <v>47.57773383381588</v>
+        <v>47.60789261012705</v>
       </c>
       <c r="O8">
-        <v>12.84598813513029</v>
+        <v>12.8541310047343</v>
       </c>
       <c r="P8">
-        <v>34.73174569868559</v>
+        <v>34.75376160539275</v>
       </c>
       <c r="Q8">
-        <v>81.59374569868558</v>
+        <v>81.61576160539275</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08856328200773504</v>
+        <v>0.08854576806789058</v>
       </c>
       <c r="T8">
         <v>0.7829037538571025</v>
       </c>
       <c r="U8">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V8">
         <v>0.27</v>
       </c>
       <c r="W8">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.76039370950195</v>
+        <v>38.6612722870895</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08575130919734186</v>
+        <v>0.0856633512762212</v>
       </c>
       <c r="C9">
-        <v>1348.829963089671</v>
+        <v>1351.720202959588</v>
       </c>
       <c r="D9">
-        <v>1358.162276682314</v>
+        <v>1361.052516552231</v>
       </c>
       <c r="E9">
         <v>-321.5007377308322</v>
@@ -2016,37 +2016,37 @@
         <v>48.872</v>
       </c>
       <c r="M9">
-        <v>1.509977193881472</v>
+        <v>1.474791954851771</v>
       </c>
       <c r="N9">
-        <v>47.36202280611852</v>
+        <v>47.39720804514823</v>
       </c>
       <c r="O9">
-        <v>12.787746157652</v>
+        <v>12.79724617219002</v>
       </c>
       <c r="P9">
-        <v>34.57427664846652</v>
+        <v>34.5999618729582</v>
       </c>
       <c r="Q9">
-        <v>81.43627664846652</v>
+        <v>81.4619618729582</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08890447815812016</v>
+        <v>0.08888682447949581</v>
       </c>
       <c r="T9">
         <v>0.7891503218097164</v>
       </c>
       <c r="U9">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V9">
         <v>0.27</v>
       </c>
       <c r="W9">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.36605175100166</v>
+        <v>33.13823338893386</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,13 +2065,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08562158087002127</v>
+        <v>0.08552344813123373</v>
       </c>
       <c r="C10">
-        <v>1349.66417114408</v>
+        <v>1352.923402125088</v>
       </c>
       <c r="D10">
-        <v>1362.586815249958</v>
+        <v>1365.846046230966</v>
       </c>
       <c r="E10">
         <v>-317.9104072175975</v>
@@ -2098,37 +2098,37 @@
         <v>48.872</v>
       </c>
       <c r="M10">
-        <v>1.725688221578825</v>
+        <v>1.685476519830596</v>
       </c>
       <c r="N10">
-        <v>47.14631177842117</v>
+        <v>47.18652348016941</v>
       </c>
       <c r="O10">
-        <v>12.72950418017372</v>
+        <v>12.74036133964574</v>
       </c>
       <c r="P10">
-        <v>34.41680759824745</v>
+        <v>34.44616214052367</v>
       </c>
       <c r="Q10">
-        <v>81.27880759824745</v>
+        <v>81.30816214052366</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08925309161612235</v>
+        <v>0.08923529516091852</v>
       </c>
       <c r="T10">
         <v>0.7955326847178219</v>
       </c>
       <c r="U10">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V10">
         <v>0.27</v>
       </c>
       <c r="W10">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.32029528212646</v>
+        <v>28.99595421531712</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,13 +2147,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08549185254270067</v>
+        <v>0.08538354498624626</v>
       </c>
       <c r="C11">
-        <v>1350.527301405479</v>
+        <v>1354.160485566385</v>
       </c>
       <c r="D11">
-        <v>1367.040276024592</v>
+        <v>1370.673460185497</v>
       </c>
       <c r="E11">
         <v>-314.3200767043627</v>
@@ -2180,37 +2180,37 @@
         <v>48.872</v>
       </c>
       <c r="M11">
-        <v>1.941399249276178</v>
+        <v>1.89616108480942</v>
       </c>
       <c r="N11">
-        <v>46.93060075072382</v>
+        <v>46.97583891519058</v>
       </c>
       <c r="O11">
-        <v>12.67126220269543</v>
+        <v>12.68347650710146</v>
       </c>
       <c r="P11">
-        <v>34.25933854802839</v>
+        <v>34.29236240808912</v>
       </c>
       <c r="Q11">
-        <v>81.12133854802838</v>
+        <v>81.15436240808911</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08960936690836636</v>
+        <v>0.08959142453863624</v>
       </c>
       <c r="T11">
         <v>0.8020553193381935</v>
       </c>
       <c r="U11">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V11">
         <v>0.27</v>
       </c>
       <c r="W11">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.17359580633463</v>
+        <v>25.77418152472633</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,13 +2229,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08536212421538009</v>
+        <v>0.08524364184125878</v>
       </c>
       <c r="C12">
-        <v>1351.419638390659</v>
+        <v>1355.431813837158</v>
       </c>
       <c r="D12">
-        <v>1371.522943523007</v>
+        <v>1375.535118969505</v>
       </c>
       <c r="E12">
         <v>-310.729746191128</v>
@@ -2262,37 +2262,37 @@
         <v>48.872</v>
       </c>
       <c r="M12">
-        <v>2.157110276973531</v>
+        <v>2.106845649788245</v>
       </c>
       <c r="N12">
-        <v>46.71488972302647</v>
+        <v>46.76515435021175</v>
       </c>
       <c r="O12">
-        <v>12.61302022521715</v>
+        <v>12.62659167455717</v>
       </c>
       <c r="P12">
-        <v>34.10186949780932</v>
+        <v>34.13856267565458</v>
       </c>
       <c r="Q12">
-        <v>80.96386949780931</v>
+        <v>81.00056267565458</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.0899735594293269</v>
+        <v>0.08995546790252545</v>
       </c>
       <c r="T12">
         <v>0.8087229013945734</v>
       </c>
       <c r="U12">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V12">
         <v>0.27</v>
       </c>
       <c r="W12">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.65623622570117</v>
+        <v>23.1967633722537</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08523239588805948</v>
+        <v>0.0851037386962713</v>
       </c>
       <c r="C13">
-        <v>1352.34147036053</v>
+        <v>1356.737752624706</v>
       </c>
       <c r="D13">
-        <v>1376.035106006112</v>
+        <v>1380.431388270288</v>
       </c>
       <c r="E13">
         <v>-307.1394156778932</v>
@@ -2344,37 +2344,37 @@
         <v>48.872</v>
       </c>
       <c r="M13">
-        <v>2.372821304670884</v>
+        <v>2.317530214767069</v>
       </c>
       <c r="N13">
-        <v>46.49917869532911</v>
+        <v>46.55446978523293</v>
       </c>
       <c r="O13">
-        <v>12.55477824773886</v>
+        <v>12.56970684201289</v>
       </c>
       <c r="P13">
-        <v>33.94440044759025</v>
+        <v>33.98476294322004</v>
       </c>
       <c r="Q13">
-        <v>80.80640044759025</v>
+        <v>80.84676294322003</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09034593605188206</v>
+        <v>0.090327692016165</v>
       </c>
       <c r="T13">
         <v>0.8155403167555909</v>
       </c>
       <c r="U13">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V13">
         <v>0.27</v>
       </c>
       <c r="W13">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.59657838700106</v>
+        <v>21.08796670204882</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,13 +2393,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08510266756073889</v>
+        <v>0.08496383555128383</v>
       </c>
       <c r="C14">
-        <v>1353.293089381909</v>
+        <v>1358.078672841639</v>
       </c>
       <c r="D14">
-        <v>1380.577055540726</v>
+        <v>1385.362639000456</v>
       </c>
       <c r="E14">
         <v>-303.5490851646584</v>
@@ -2426,37 +2426,37 @@
         <v>48.872</v>
       </c>
       <c r="M14">
-        <v>2.588532332368237</v>
+        <v>2.528214779745894</v>
       </c>
       <c r="N14">
-        <v>46.28346766763176</v>
+        <v>46.34378522025411</v>
       </c>
       <c r="O14">
-        <v>12.49653627026058</v>
+        <v>12.51282200946861</v>
       </c>
       <c r="P14">
-        <v>33.78693139737118</v>
+        <v>33.8309632107855</v>
       </c>
       <c r="Q14">
-        <v>80.64893139737117</v>
+        <v>80.69296321078549</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09072677577949528</v>
+        <v>0.0907083757687509</v>
       </c>
       <c r="T14">
         <v>0.8225126733748135</v>
       </c>
       <c r="U14">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V14">
         <v>0.27</v>
       </c>
       <c r="W14">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.88019685475097</v>
+        <v>19.33063614354475</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,13 +2475,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08497293923341828</v>
+        <v>0.08482393240629635</v>
       </c>
       <c r="C15">
-        <v>1354.274791390547</v>
+        <v>1359.454950719542</v>
       </c>
       <c r="D15">
-        <v>1385.149088062599</v>
+        <v>1390.329247391594</v>
       </c>
       <c r="E15">
         <v>-299.9587546514237</v>
@@ -2508,37 +2508,37 @@
         <v>48.872</v>
       </c>
       <c r="M15">
-        <v>2.804243360065591</v>
+        <v>2.738899344724719</v>
       </c>
       <c r="N15">
-        <v>46.06775663993441</v>
+        <v>46.13310065527528</v>
       </c>
       <c r="O15">
-        <v>12.43829429278229</v>
+        <v>12.45593717692433</v>
       </c>
       <c r="P15">
-        <v>33.62946234715211</v>
+        <v>33.67716347835095</v>
       </c>
       <c r="Q15">
-        <v>80.49146234715211</v>
+        <v>80.53916347835094</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09111637044337548</v>
+        <v>0.09109781087197096</v>
       </c>
       <c r="T15">
         <v>0.8296453140542479</v>
       </c>
       <c r="U15">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V15">
         <v>0.27</v>
       </c>
       <c r="W15">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.42787401977013</v>
+        <v>17.84366413250284</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,13 +2557,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08484321090609769</v>
+        <v>0.08468402926130889</v>
       </c>
       <c r="C16">
-        <v>1355.286876255396</v>
+        <v>1360.866967904664</v>
       </c>
       <c r="D16">
-        <v>1389.751503440683</v>
+        <v>1395.331595089951</v>
       </c>
       <c r="E16">
         <v>-296.368424138189</v>
@@ -2590,37 +2590,37 @@
         <v>48.872</v>
       </c>
       <c r="M16">
-        <v>3.019954387762944</v>
+        <v>2.949583909703543</v>
       </c>
       <c r="N16">
-        <v>45.85204561223706</v>
+        <v>45.92241609029646</v>
       </c>
       <c r="O16">
-        <v>12.38005231530401</v>
+        <v>12.39905234438004</v>
       </c>
       <c r="P16">
-        <v>33.47199329693305</v>
+        <v>33.52336374591641</v>
       </c>
       <c r="Q16">
-        <v>80.33399329693304</v>
+        <v>80.38536374591641</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09151502544827614</v>
+        <v>0.09149630260549846</v>
       </c>
       <c r="T16">
         <v>0.8369438300983204</v>
       </c>
       <c r="U16">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V16">
         <v>0.27</v>
       </c>
       <c r="W16">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.18302587550083</v>
+        <v>16.56911669446693</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,13 +2639,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.0847134825787771</v>
+        <v>0.08454412611632142</v>
       </c>
       <c r="C17">
-        <v>1356.329647844181</v>
+        <v>1362.315111555678</v>
       </c>
       <c r="D17">
-        <v>1394.384605542702</v>
+        <v>1400.370069254199</v>
       </c>
       <c r="E17">
         <v>-292.7780936249542</v>
@@ -2672,37 +2672,37 @@
         <v>48.872</v>
       </c>
       <c r="M17">
-        <v>3.235665415460297</v>
+        <v>3.160268474682367</v>
       </c>
       <c r="N17">
-        <v>45.6363345845397</v>
+        <v>45.71173152531763</v>
       </c>
       <c r="O17">
-        <v>12.32181033782572</v>
+        <v>12.34216751183576</v>
       </c>
       <c r="P17">
-        <v>33.31452424671399</v>
+        <v>33.36956401348187</v>
       </c>
       <c r="Q17">
-        <v>80.17652424671398</v>
+        <v>80.23156401348186</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09192306057093919</v>
+        <v>0.09190417061510896</v>
       </c>
       <c r="T17">
         <v>0.8444140759316654</v>
       </c>
       <c r="U17">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V17">
         <v>0.27</v>
       </c>
       <c r="W17">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.10415748380078</v>
+        <v>15.4645089148358</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,13 +2721,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08458375425145651</v>
+        <v>0.08440422297133393</v>
       </c>
       <c r="C18">
-        <v>1357.40341409027</v>
+        <v>1363.799774443566</v>
       </c>
       <c r="D18">
-        <v>1399.048702302026</v>
+        <v>1405.445062655322</v>
       </c>
       <c r="E18">
         <v>-289.1877631117194</v>
@@ -2754,37 +2754,37 @@
         <v>48.872</v>
       </c>
       <c r="M18">
-        <v>3.45137644315765</v>
+        <v>3.370953039661192</v>
       </c>
       <c r="N18">
-        <v>45.42062355684235</v>
+        <v>45.50104696033881</v>
       </c>
       <c r="O18">
-        <v>12.26356836034743</v>
+        <v>12.28528267929148</v>
       </c>
       <c r="P18">
-        <v>33.15705519649492</v>
+        <v>33.21576428104733</v>
       </c>
       <c r="Q18">
-        <v>80.01905519649492</v>
+        <v>80.07776428104732</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09234081081557038</v>
+        <v>0.09232174976780541</v>
       </c>
       <c r="T18">
         <v>0.8520621847610422</v>
       </c>
       <c r="U18">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V18">
         <v>0.27</v>
       </c>
       <c r="W18">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.16014764106323</v>
+        <v>14.49797710765856</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,13 +2803,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08445402592413589</v>
+        <v>0.08426431982634647</v>
       </c>
       <c r="C19">
-        <v>1358.508487060903</v>
+        <v>1365.321355053686</v>
       </c>
       <c r="D19">
-        <v>1403.744105785894</v>
+        <v>1410.556973778677</v>
       </c>
       <c r="E19">
         <v>-285.5974325984847</v>
@@ -2836,37 +2836,37 @@
         <v>48.872</v>
       </c>
       <c r="M19">
-        <v>3.667087470855004</v>
+        <v>3.581637604640016</v>
       </c>
       <c r="N19">
-        <v>45.204912529145</v>
+        <v>45.29036239535998</v>
       </c>
       <c r="O19">
-        <v>12.20532638286915</v>
+        <v>12.2283978467472</v>
       </c>
       <c r="P19">
-        <v>32.99958614627585</v>
+        <v>33.06196454861279</v>
       </c>
       <c r="Q19">
-        <v>79.86158614627584</v>
+        <v>79.92396454861279</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09276862733115654</v>
+        <v>0.09274939106875962</v>
       </c>
       <c r="T19">
         <v>0.8598945853694402</v>
       </c>
       <c r="U19">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V19">
         <v>0.27</v>
       </c>
       <c r="W19">
-        <v>0.04385920728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.32719777982421</v>
+        <v>13.64515492485512</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,13 +2885,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08446883759681532</v>
+        <v>0.08412441668135899</v>
       </c>
       <c r="C20">
-        <v>1354.380467816567</v>
+        <v>1366.880257690076</v>
       </c>
       <c r="D20">
-        <v>1403.206417054793</v>
+        <v>1415.706206928301</v>
       </c>
       <c r="E20">
         <v>-282.0071020852499</v>
@@ -2918,45 +2918,45 @@
         <v>48.872</v>
       </c>
       <c r="M20">
-        <v>3.953887042714404</v>
+        <v>3.792322169618841</v>
       </c>
       <c r="N20">
-        <v>44.91811295728559</v>
+        <v>45.07967783038116</v>
       </c>
       <c r="O20">
-        <v>12.12789049846711</v>
+        <v>12.17151301420291</v>
       </c>
       <c r="P20">
-        <v>32.79022245881848</v>
+        <v>32.90816481617824</v>
       </c>
       <c r="Q20">
-        <v>79.65222245881847</v>
+        <v>79.77016481617824</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09320687839590336</v>
+        <v>0.09318746264534686</v>
       </c>
       <c r="T20">
         <v>0.8679180201390185</v>
       </c>
       <c r="U20">
-        <v>0.06118110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V20">
         <v>0.27</v>
       </c>
       <c r="W20">
-        <v>0.04466220728985867</v>
+        <v>0.04283720728985867</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>12.36049474151103</v>
+        <v>12.88709076236317</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,13 +2967,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08434713926949471</v>
+        <v>0.0841925635363715</v>
       </c>
       <c r="C21">
-        <v>1355.220242288485</v>
+        <v>1360.777046641201</v>
       </c>
       <c r="D21">
-        <v>1407.636522039945</v>
+        <v>1413.193326392661</v>
       </c>
       <c r="E21">
         <v>-278.4167715720151</v>
@@ -3000,37 +3000,37 @@
         <v>48.872</v>
       </c>
       <c r="M21">
-        <v>4.173547433976316</v>
+        <v>4.105331154224856</v>
       </c>
       <c r="N21">
-        <v>44.69845256602368</v>
+        <v>44.76666884577514</v>
       </c>
       <c r="O21">
-        <v>12.0685821928264</v>
+        <v>12.08700058835929</v>
       </c>
       <c r="P21">
-        <v>32.62987037319729</v>
+        <v>32.67966825741586</v>
       </c>
       <c r="Q21">
-        <v>79.49187037319729</v>
+        <v>79.54166825741585</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09365595047459452</v>
+        <v>0.09363635080407205</v>
       </c>
       <c r="T21">
         <v>0.8761395644090804</v>
       </c>
       <c r="U21">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V21">
         <v>0.27</v>
       </c>
       <c r="W21">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.70994238669466</v>
+        <v>11.9045207716569</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,13 +3049,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08422544094217412</v>
+        <v>0.08406361039138405</v>
       </c>
       <c r="C22">
-        <v>1356.088078188107</v>
+        <v>1361.949354103045</v>
       </c>
       <c r="D22">
-        <v>1412.094688452802</v>
+        <v>1417.95596436774</v>
       </c>
       <c r="E22">
         <v>-274.8264410587804</v>
@@ -3082,37 +3082,37 @@
         <v>48.872</v>
       </c>
       <c r="M22">
-        <v>4.393207825238227</v>
+        <v>4.321401214973532</v>
       </c>
       <c r="N22">
-        <v>44.47879217476177</v>
+        <v>44.55059878502647</v>
       </c>
       <c r="O22">
-        <v>12.00927388718568</v>
+        <v>12.02866167195715</v>
       </c>
       <c r="P22">
-        <v>32.46951828757609</v>
+        <v>32.52193711306932</v>
       </c>
       <c r="Q22">
-        <v>79.33151828757609</v>
+        <v>79.38393711306932</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09411624935525298</v>
+        <v>0.09409646116676539</v>
       </c>
       <c r="T22">
         <v>0.8845666472858938</v>
       </c>
       <c r="U22">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V22">
         <v>0.27</v>
       </c>
       <c r="W22">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.12444526735993</v>
+        <v>11.30929473307406</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,13 +3131,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08410374261485354</v>
+        <v>0.08393465724639657</v>
       </c>
       <c r="C23">
-        <v>1356.984242985029</v>
+        <v>1363.153871485716</v>
       </c>
       <c r="D23">
-        <v>1416.581183762959</v>
+        <v>1422.750812263646</v>
       </c>
       <c r="E23">
         <v>-271.2361105455457</v>
@@ -3164,37 +3164,37 @@
         <v>48.872</v>
       </c>
       <c r="M23">
-        <v>4.612868216500138</v>
+        <v>4.537471275722209</v>
       </c>
       <c r="N23">
-        <v>44.25913178349986</v>
+        <v>44.33452872427779</v>
       </c>
       <c r="O23">
-        <v>11.94996558154496</v>
+        <v>11.970322755555</v>
       </c>
       <c r="P23">
-        <v>32.30916620195489</v>
+        <v>32.36420596872279</v>
       </c>
       <c r="Q23">
-        <v>79.17116620195489</v>
+        <v>79.22620596872278</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09458820137213064</v>
+        <v>0.0945682198930712</v>
       </c>
       <c r="T23">
         <v>0.8932070740330063</v>
       </c>
       <c r="U23">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V23">
         <v>0.27</v>
       </c>
       <c r="W23">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.59470977843803</v>
+        <v>10.77075688864196</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,13 +3213,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08398204428753293</v>
+        <v>0.08380570410140908</v>
       </c>
       <c r="C24">
-        <v>1357.909007558887</v>
+        <v>1364.390926653466</v>
       </c>
       <c r="D24">
-        <v>1421.096278850051</v>
+        <v>1427.578197944631</v>
       </c>
       <c r="E24">
         <v>-267.6457800323109</v>
@@ -3246,37 +3246,37 @@
         <v>48.872</v>
       </c>
       <c r="M24">
-        <v>4.83252860776205</v>
+        <v>4.753541336470885</v>
       </c>
       <c r="N24">
-        <v>44.03947139223795</v>
+        <v>44.11845866352911</v>
       </c>
       <c r="O24">
-        <v>11.89065727590425</v>
+        <v>11.91198383915286</v>
       </c>
       <c r="P24">
-        <v>32.1488141163337</v>
+        <v>32.20647482437625</v>
       </c>
       <c r="Q24">
-        <v>79.01081411633371</v>
+        <v>79.06847482437624</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09507225472277439</v>
+        <v>0.0950520749969746</v>
       </c>
       <c r="T24">
         <v>0.9020690501838908</v>
       </c>
       <c r="U24">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V24">
         <v>0.27</v>
       </c>
       <c r="W24">
-        <v>0.04466220728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.1131320612363</v>
+        <v>10.28117703006732</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,13 +3295,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08422972596021233</v>
+        <v>0.08367675095642163</v>
       </c>
       <c r="C25">
-        <v>1345.159634284107</v>
+        <v>1365.660851935463</v>
       </c>
       <c r="D25">
-        <v>1411.937236088506</v>
+        <v>1432.438453739862</v>
       </c>
       <c r="E25">
         <v>-264.0554495190761</v>
@@ -3328,45 +3328,45 @@
         <v>48.872</v>
       </c>
       <c r="M25">
-        <v>5.23385972299364</v>
+        <v>4.969611397219562</v>
       </c>
       <c r="N25">
-        <v>43.63814027700636</v>
+        <v>43.90238860278044</v>
       </c>
       <c r="O25">
-        <v>11.78229787479172</v>
+        <v>11.85364492275072</v>
       </c>
       <c r="P25">
-        <v>31.85584240221464</v>
+        <v>32.04874368002972</v>
       </c>
       <c r="Q25">
-        <v>78.71784240221464</v>
+        <v>78.91074368002973</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09556888088772056</v>
+        <v>0.09554849776591445</v>
       </c>
       <c r="T25">
         <v>0.9111612075334996</v>
       </c>
       <c r="U25">
-        <v>0.06338110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V25">
         <v>0.27</v>
       </c>
       <c r="W25">
-        <v>0.04626820728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>9.337659506863208</v>
+        <v>9.834169333107877</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,13 +3377,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08412408763289174</v>
+        <v>0.08384563781143414</v>
       </c>
       <c r="C26">
-        <v>1345.461234332424</v>
+        <v>1355.711841705774</v>
       </c>
       <c r="D26">
-        <v>1415.829166650058</v>
+        <v>1426.079774023408</v>
       </c>
       <c r="E26">
         <v>-260.4651190058414</v>
@@ -3410,37 +3410,37 @@
         <v>48.872</v>
       </c>
       <c r="M26">
-        <v>5.461418841384667</v>
+        <v>5.332166942908216</v>
       </c>
       <c r="N26">
-        <v>43.41058115861533</v>
+        <v>43.53983305709178</v>
       </c>
       <c r="O26">
-        <v>11.72085691282614</v>
+        <v>11.75575492541478</v>
       </c>
       <c r="P26">
-        <v>31.68972424578919</v>
+        <v>31.784078131677</v>
       </c>
       <c r="Q26">
-        <v>78.55172424578919</v>
+        <v>78.646078131677</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.0960785761622706</v>
+        <v>0.09605798429193166</v>
       </c>
       <c r="T26">
         <v>0.9204926321817825</v>
       </c>
       <c r="U26">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V26">
         <v>0.27</v>
       </c>
       <c r="W26">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.948590360743909</v>
+        <v>9.165504479374896</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,13 +3459,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08401844930557115</v>
+        <v>0.08372909466644668</v>
       </c>
       <c r="C27">
-        <v>1345.784349488865</v>
+        <v>1356.503366950745</v>
       </c>
       <c r="D27">
-        <v>1419.742612319734</v>
+        <v>1430.461629781614</v>
       </c>
       <c r="E27">
         <v>-256.8747884926066</v>
@@ -3492,37 +3492,37 @@
         <v>48.872</v>
       </c>
       <c r="M27">
-        <v>5.688977959775696</v>
+        <v>5.554340565529392</v>
       </c>
       <c r="N27">
-        <v>43.1830220402243</v>
+        <v>43.31765943447061</v>
       </c>
       <c r="O27">
-        <v>11.65941595086056</v>
+        <v>11.69576804730706</v>
       </c>
       <c r="P27">
-        <v>31.52360608936374</v>
+        <v>31.62189138716354</v>
       </c>
       <c r="Q27">
-        <v>78.38560608936373</v>
+        <v>78.48389138716354</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09660186331080864</v>
+        <v>0.09658105712530934</v>
       </c>
       <c r="T27">
         <v>0.9300728948206861</v>
       </c>
       <c r="U27">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V27">
         <v>0.27</v>
       </c>
       <c r="W27">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.59064674631415</v>
+        <v>8.7988843001999</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,13 +3541,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08391281097825054</v>
+        <v>0.0836125515214592</v>
       </c>
       <c r="C28">
-        <v>1346.129158655483</v>
+        <v>1357.321903081277</v>
       </c>
       <c r="D28">
-        <v>1423.677751999587</v>
+        <v>1434.870496425381</v>
       </c>
       <c r="E28">
         <v>-253.2844579793719</v>
@@ -3574,37 +3574,37 @@
         <v>48.872</v>
       </c>
       <c r="M28">
-        <v>5.916537078166724</v>
+        <v>5.776514188150568</v>
       </c>
       <c r="N28">
-        <v>42.95546292183327</v>
+        <v>43.09548581184943</v>
       </c>
       <c r="O28">
-        <v>11.59797498889498</v>
+        <v>11.63578116919935</v>
       </c>
       <c r="P28">
-        <v>31.35748793293829</v>
+        <v>31.45970464265008</v>
       </c>
       <c r="Q28">
-        <v>78.21948793293828</v>
+        <v>78.32170464265008</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09713929335525309</v>
+        <v>0.09711826706229182</v>
       </c>
       <c r="T28">
         <v>0.9399120834768573</v>
       </c>
       <c r="U28">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V28">
         <v>0.27</v>
       </c>
       <c r="W28">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.260237256071299</v>
+        <v>8.460465673269134</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,13 +3623,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08380717265092995</v>
+        <v>0.08349600837647173</v>
       </c>
       <c r="C29">
-        <v>1346.495842723314</v>
+        <v>1358.167700622585</v>
       </c>
       <c r="D29">
-        <v>1427.634766580652</v>
+        <v>1439.306624479923</v>
       </c>
       <c r="E29">
         <v>-249.6941274661371</v>
@@ -3656,37 +3656,37 @@
         <v>48.872</v>
       </c>
       <c r="M29">
-        <v>6.144096196557752</v>
+        <v>5.998687810771744</v>
       </c>
       <c r="N29">
-        <v>42.72790380344225</v>
+        <v>42.87331218922826</v>
       </c>
       <c r="O29">
-        <v>11.53653402692941</v>
+        <v>11.57579429109163</v>
       </c>
       <c r="P29">
-        <v>31.19136977651284</v>
+        <v>31.29751789813663</v>
       </c>
       <c r="Q29">
-        <v>78.05336977651282</v>
+        <v>78.15951789813661</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09769144751050426</v>
+        <v>0.09767019507973956</v>
       </c>
       <c r="T29">
         <v>0.9500208389455266</v>
       </c>
       <c r="U29">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V29">
         <v>0.27</v>
       </c>
       <c r="W29">
-        <v>0.04626820728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.954302542883473</v>
+        <v>8.147115092777685</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,13 +3705,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08400813432360935</v>
+        <v>0.08337946523148426</v>
       </c>
       <c r="C30">
-        <v>1335.39664333317</v>
+        <v>1359.041013207647</v>
       </c>
       <c r="D30">
-        <v>1420.125897703743</v>
+        <v>1443.77026757822</v>
       </c>
       <c r="E30">
         <v>-246.1037969529024</v>
@@ -3738,45 +3738,45 @@
         <v>48.872</v>
       </c>
       <c r="M30">
-        <v>6.522449196504639</v>
+        <v>6.220861433392919</v>
       </c>
       <c r="N30">
-        <v>42.34955080349536</v>
+        <v>42.65113856660708</v>
       </c>
       <c r="O30">
-        <v>11.43437871694375</v>
+        <v>11.51580741298391</v>
       </c>
       <c r="P30">
-        <v>30.91517208655161</v>
+        <v>31.13533115362317</v>
       </c>
       <c r="Q30">
-        <v>77.77717208655162</v>
+        <v>77.99733115362316</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09825893928117907</v>
+        <v>0.09823745443100532</v>
       </c>
       <c r="T30">
         <v>0.9604103931772142</v>
       </c>
       <c r="U30">
-        <v>0.06488110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.04736320728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.492890864706214</v>
+        <v>7.856146696607054</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,13 +3787,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08391344599628875</v>
+        <v>0.08343228208649676</v>
       </c>
       <c r="C31">
-        <v>1335.334446850411</v>
+        <v>1353.424353153228</v>
       </c>
       <c r="D31">
-        <v>1423.654031734219</v>
+        <v>1441.743938037036</v>
       </c>
       <c r="E31">
         <v>-242.5134664396676</v>
@@ -3820,37 +3820,37 @@
         <v>48.872</v>
       </c>
       <c r="M31">
-        <v>6.755393810665518</v>
+        <v>6.526330723921141</v>
       </c>
       <c r="N31">
-        <v>42.11660618933448</v>
+        <v>42.34566927607886</v>
       </c>
       <c r="O31">
-        <v>11.37148367112031</v>
+        <v>11.43333070454129</v>
       </c>
       <c r="P31">
-        <v>30.74512251821417</v>
+        <v>30.91233857153757</v>
       </c>
       <c r="Q31">
-        <v>77.60712251821417</v>
+        <v>77.77433857153756</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09884241673553484</v>
+        <v>0.09882069291892642</v>
       </c>
       <c r="T31">
         <v>0.9710926109083862</v>
       </c>
       <c r="U31">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V31">
         <v>0.27</v>
       </c>
       <c r="W31">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.23451531764738</v>
+        <v>7.488434476798441</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,13 +3869,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08381875766896815</v>
+        <v>0.08332157894150929</v>
       </c>
       <c r="C32">
-        <v>1335.289824487924</v>
+        <v>1354.087723915628</v>
       </c>
       <c r="D32">
-        <v>1427.199739884966</v>
+        <v>1445.99763931267</v>
       </c>
       <c r="E32">
         <v>-238.9231359264328</v>
@@ -3902,37 +3902,37 @@
         <v>48.872</v>
       </c>
       <c r="M32">
-        <v>6.988338424826399</v>
+        <v>6.751376610952906</v>
       </c>
       <c r="N32">
-        <v>41.8836615751736</v>
+        <v>42.1206233890471</v>
       </c>
       <c r="O32">
-        <v>11.30858862529687</v>
+        <v>11.37256831504272</v>
       </c>
       <c r="P32">
-        <v>30.57507294987673</v>
+        <v>30.74805507400438</v>
       </c>
       <c r="Q32">
-        <v>77.43707294987672</v>
+        <v>77.61005507400438</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.0994425649743008</v>
+        <v>0.09942059536364528</v>
       </c>
       <c r="T32">
         <v>0.9820800348604487</v>
       </c>
       <c r="U32">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V32">
         <v>0.27</v>
       </c>
       <c r="W32">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.993364807059135</v>
+        <v>7.238819994238492</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,13 +3951,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08372406934164757</v>
+        <v>0.08321087579652181</v>
       </c>
       <c r="C33">
-        <v>1335.262907882216</v>
+        <v>1354.776269074458</v>
       </c>
       <c r="D33">
-        <v>1430.763153792494</v>
+        <v>1450.276514984735</v>
       </c>
       <c r="E33">
         <v>-235.3328054131981</v>
@@ -3984,37 +3984,37 @@
         <v>48.872</v>
       </c>
       <c r="M33">
-        <v>7.221283038987278</v>
+        <v>6.976422497984669</v>
       </c>
       <c r="N33">
-        <v>41.65071696101272</v>
+        <v>41.89557750201533</v>
       </c>
       <c r="O33">
-        <v>11.24569357947344</v>
+        <v>11.31180592554414</v>
       </c>
       <c r="P33">
-        <v>30.40502338153928</v>
+        <v>30.58377157647119</v>
       </c>
       <c r="Q33">
-        <v>77.26702338153927</v>
+        <v>77.44577157647119</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1000601088141904</v>
+        <v>0.1000378862850227</v>
       </c>
       <c r="T33">
         <v>0.9933859348690928</v>
       </c>
       <c r="U33">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.767772393928195</v>
+        <v>7.005309671843701</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,13 +4033,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08362938101432697</v>
+        <v>0.08310017265153435</v>
       </c>
       <c r="C34">
-        <v>1335.253829987766</v>
+        <v>1355.490212774915</v>
       </c>
       <c r="D34">
-        <v>1434.344406411279</v>
+        <v>1454.580789198428</v>
       </c>
       <c r="E34">
         <v>-231.7424748999634</v>
@@ -4066,37 +4066,37 @@
         <v>48.872</v>
       </c>
       <c r="M34">
-        <v>7.454227653148158</v>
+        <v>7.201468385016432</v>
       </c>
       <c r="N34">
-        <v>41.41777234685184</v>
+        <v>41.67053161498357</v>
       </c>
       <c r="O34">
-        <v>11.18279853365</v>
+        <v>11.25104353604556</v>
       </c>
       <c r="P34">
-        <v>30.23497381320184</v>
+        <v>30.419488078938</v>
       </c>
       <c r="Q34">
-        <v>77.09697381320184</v>
+        <v>77.281488078938</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1006958157081944</v>
+        <v>0.1006733328217347</v>
       </c>
       <c r="T34">
         <v>1.005024361348579</v>
       </c>
       <c r="U34">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V34">
         <v>0.27</v>
       </c>
       <c r="W34">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.556279506617939</v>
+        <v>6.786393744598586</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,13 +4115,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08353469268700636</v>
+        <v>0.08298946950654687</v>
       </c>
       <c r="C35">
-        <v>1335.262725093547</v>
+        <v>1356.229781831081</v>
       </c>
       <c r="D35">
-        <v>1437.943632030294</v>
+        <v>1458.910688767828</v>
       </c>
       <c r="E35">
         <v>-228.1521443867286</v>
@@ -4148,37 +4148,37 @@
         <v>48.872</v>
       </c>
       <c r="M35">
-        <v>7.687172267309039</v>
+        <v>7.426514272048196</v>
       </c>
       <c r="N35">
-        <v>41.18482773269096</v>
+        <v>41.44548572795181</v>
       </c>
       <c r="O35">
-        <v>11.11990348782656</v>
+        <v>11.19028114654699</v>
       </c>
       <c r="P35">
-        <v>30.0649242448644</v>
+        <v>30.25520458140482</v>
       </c>
       <c r="Q35">
-        <v>76.9269242448644</v>
+        <v>77.11720458140482</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1013504989273926</v>
+        <v>0.1013277479117814</v>
       </c>
       <c r="T35">
         <v>1.017010203543871</v>
       </c>
       <c r="U35">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V35">
         <v>0.27</v>
       </c>
       <c r="W35">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.357604370053758</v>
+        <v>6.580745449307719</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,13 +4197,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08344000435968578</v>
+        <v>0.0828787663615594</v>
       </c>
       <c r="C36">
-        <v>1335.289728839818</v>
+        <v>1356.995205765758</v>
       </c>
       <c r="D36">
-        <v>1441.5609662898</v>
+        <v>1463.26644321574</v>
       </c>
       <c r="E36">
         <v>-224.5618138734938</v>
@@ -4230,37 +4230,37 @@
         <v>48.872</v>
       </c>
       <c r="M36">
-        <v>7.920116881469919</v>
+        <v>7.651560159079961</v>
       </c>
       <c r="N36">
-        <v>40.95188311853008</v>
+        <v>41.22043984092004</v>
       </c>
       <c r="O36">
-        <v>11.05700844200312</v>
+        <v>11.12951875704841</v>
       </c>
       <c r="P36">
-        <v>29.89487467652695</v>
+        <v>30.09092108387163</v>
       </c>
       <c r="Q36">
-        <v>76.75687467652695</v>
+        <v>76.95292108387162</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.102025021032021</v>
+        <v>0.1020019937621325</v>
       </c>
       <c r="T36">
         <v>1.029359253078415</v>
       </c>
       <c r="U36">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V36">
         <v>0.27</v>
       </c>
       <c r="W36">
-        <v>0.04736320728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.170616006228647</v>
+        <v>6.387194112563374</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,13 +4279,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08370301603236519</v>
+        <v>0.08276806321657194</v>
       </c>
       <c r="C37">
-        <v>1321.696306206171</v>
+        <v>1357.78671685103</v>
       </c>
       <c r="D37">
-        <v>1431.557874169387</v>
+        <v>1467.648284814246</v>
       </c>
       <c r="E37">
         <v>-220.9714833602591</v>
@@ -4312,45 +4312,45 @@
         <v>48.872</v>
       </c>
       <c r="M37">
-        <v>8.328987690779302</v>
+        <v>7.876606046111723</v>
       </c>
       <c r="N37">
-        <v>40.5430123092207</v>
+        <v>40.99539395388828</v>
       </c>
       <c r="O37">
-        <v>10.94661332348959</v>
+        <v>11.06875636754983</v>
       </c>
       <c r="P37">
-        <v>29.59639898573111</v>
+        <v>29.92663758633844</v>
       </c>
       <c r="Q37">
-        <v>76.45839898573111</v>
+        <v>76.78863758633844</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1027202976629456</v>
+        <v>0.1026969856386483</v>
       </c>
       <c r="T37">
         <v>1.042088273367867</v>
       </c>
       <c r="U37">
-        <v>0.06628110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.04838520728985867</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>5.867699871150523</v>
+        <v>6.204702852204421</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,13 +4361,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08361854770504459</v>
+        <v>0.08292016007158445</v>
       </c>
       <c r="C38">
-        <v>1321.303382955552</v>
+        <v>1348.182816138898</v>
       </c>
       <c r="D38">
-        <v>1434.755281432004</v>
+        <v>1461.63471461535</v>
       </c>
       <c r="E38">
         <v>-217.3811528470243</v>
@@ -4394,37 +4394,37 @@
         <v>48.872</v>
       </c>
       <c r="M38">
-        <v>8.56695876765871</v>
+        <v>8.230903831619937</v>
       </c>
       <c r="N38">
-        <v>40.30504123234129</v>
+        <v>40.64109616838006</v>
       </c>
       <c r="O38">
-        <v>10.88236113273215</v>
+        <v>10.97309596546262</v>
       </c>
       <c r="P38">
-        <v>29.42268009960914</v>
+        <v>29.66800020291744</v>
       </c>
       <c r="Q38">
-        <v>76.28468009960913</v>
+        <v>76.53000020291744</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1034373016885867</v>
+        <v>0.1034136960113052</v>
       </c>
       <c r="T38">
         <v>1.055215075541365</v>
       </c>
       <c r="U38">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V38">
         <v>0.27</v>
       </c>
       <c r="W38">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.704708208063009</v>
+        <v>5.9376225260041</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,13 +4443,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08353407937772399</v>
+        <v>0.08281675692659698</v>
       </c>
       <c r="C39">
-        <v>1320.924774597344</v>
+        <v>1348.675437209288</v>
       </c>
       <c r="D39">
-        <v>1437.96700358703</v>
+        <v>1465.717666198974</v>
       </c>
       <c r="E39">
         <v>-213.7908223337896</v>
@@ -4476,37 +4476,37 @@
         <v>48.872</v>
       </c>
       <c r="M39">
-        <v>8.804929844538119</v>
+        <v>8.459540049164936</v>
       </c>
       <c r="N39">
-        <v>40.06707015546188</v>
+        <v>40.41245995083506</v>
       </c>
       <c r="O39">
-        <v>10.81810894197471</v>
+        <v>10.91136418672547</v>
       </c>
       <c r="P39">
-        <v>29.24896121348717</v>
+        <v>29.5010957641096</v>
       </c>
       <c r="Q39">
-        <v>76.11096121348717</v>
+        <v>76.36309576410959</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1041770677467878</v>
+        <v>0.1041531590942052</v>
       </c>
       <c r="T39">
         <v>1.068758601593386</v>
       </c>
       <c r="U39">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V39">
         <v>0.27</v>
       </c>
       <c r="W39">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.550526905142386</v>
+        <v>5.777146241517503</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,13 +4525,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08344961105040338</v>
+        <v>0.08271335378160952</v>
       </c>
       <c r="C40">
-        <v>1320.560577479554</v>
+        <v>1349.190932930249</v>
       </c>
       <c r="D40">
-        <v>1441.193136982475</v>
+        <v>1469.823492433169</v>
       </c>
       <c r="E40">
         <v>-210.2004918205548</v>
@@ -4558,37 +4558,37 @@
         <v>48.872</v>
       </c>
       <c r="M40">
-        <v>9.042900921417528</v>
+        <v>8.688176266709934</v>
       </c>
       <c r="N40">
-        <v>39.82909907858247</v>
+        <v>40.18382373329007</v>
       </c>
       <c r="O40">
-        <v>10.75385675121727</v>
+        <v>10.84963240798832</v>
       </c>
       <c r="P40">
-        <v>29.0752423273652</v>
+        <v>29.33419132530175</v>
       </c>
       <c r="Q40">
-        <v>75.9372423273652</v>
+        <v>76.19619132530174</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1049406972262211</v>
+        <v>0.1049164758249407</v>
       </c>
       <c r="T40">
         <v>1.08273901558257</v>
       </c>
       <c r="U40">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V40">
         <v>0.27</v>
       </c>
       <c r="W40">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.40446040763864</v>
+        <v>5.625116077267043</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,13 +4607,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08336514272308281</v>
+        <v>0.08260995063662205</v>
       </c>
       <c r="C41">
-        <v>1320.210888816776</v>
+        <v>1349.729496073906</v>
       </c>
       <c r="D41">
-        <v>1444.433778832932</v>
+        <v>1473.952386090062</v>
       </c>
       <c r="E41">
         <v>-206.6101613073201</v>
@@ -4640,37 +4640,37 @@
         <v>48.872</v>
       </c>
       <c r="M41">
-        <v>9.280871998296936</v>
+        <v>8.916812484254933</v>
       </c>
       <c r="N41">
-        <v>39.59112800170306</v>
+        <v>39.95518751574507</v>
       </c>
       <c r="O41">
-        <v>10.68960456045983</v>
+        <v>10.78790062925117</v>
       </c>
       <c r="P41">
-        <v>28.90152344124323</v>
+        <v>29.1672868864939</v>
       </c>
       <c r="Q41">
-        <v>75.76352344124322</v>
+        <v>76.02928688649389</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1057293637377671</v>
+        <v>0.105704819333733</v>
       </c>
       <c r="T41">
         <v>1.097177803800907</v>
       </c>
       <c r="U41">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V41">
         <v>0.27</v>
       </c>
       <c r="W41">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.265884499750469</v>
+        <v>5.480882331696092</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,13 +4689,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08328067439576221</v>
+        <v>0.08250654749163457</v>
       </c>
       <c r="C42">
-        <v>1319.875806699957</v>
+        <v>1350.291321584559</v>
       </c>
       <c r="D42">
-        <v>1447.689027229348</v>
+        <v>1478.104542113949</v>
       </c>
       <c r="E42">
         <v>-203.0198307940853</v>
@@ -4722,37 +4722,37 @@
         <v>48.872</v>
       </c>
       <c r="M42">
-        <v>9.518843075176344</v>
+        <v>9.14544870179993</v>
       </c>
       <c r="N42">
-        <v>39.35315692482366</v>
+        <v>39.72655129820007</v>
       </c>
       <c r="O42">
-        <v>10.62535236970239</v>
+        <v>10.72616885051402</v>
       </c>
       <c r="P42">
-        <v>28.72780455512127</v>
+        <v>29.00038244768605</v>
       </c>
       <c r="Q42">
-        <v>75.58980455512126</v>
+        <v>75.86238244768604</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1065443191330312</v>
+        <v>0.1065194409594852</v>
       </c>
       <c r="T42">
         <v>1.112097884959855</v>
       </c>
       <c r="U42">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V42">
         <v>0.27</v>
       </c>
       <c r="W42">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.134237387256708</v>
+        <v>5.34386027340369</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,13 +4771,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08319620606844161</v>
+        <v>0.0824031443466471</v>
       </c>
       <c r="C43">
-        <v>1319.55543010629</v>
+        <v>1350.876606609361</v>
       </c>
       <c r="D43">
-        <v>1450.958981148915</v>
+        <v>1482.280157651986</v>
       </c>
       <c r="E43">
         <v>-199.4295002808506</v>
@@ -4804,37 +4804,37 @@
         <v>48.872</v>
       </c>
       <c r="M43">
-        <v>9.756814152055753</v>
+        <v>9.374084919344929</v>
       </c>
       <c r="N43">
-        <v>39.11518584794425</v>
+        <v>39.49791508065507</v>
       </c>
       <c r="O43">
-        <v>10.56110017894495</v>
+        <v>10.66443707177687</v>
       </c>
       <c r="P43">
-        <v>28.5540856689993</v>
+        <v>28.8334780088782</v>
       </c>
       <c r="Q43">
-        <v>75.4160856689993</v>
+        <v>75.6954780088782</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1073869001349145</v>
+        <v>0.1073616768776356</v>
       </c>
       <c r="T43">
         <v>1.127523731581819</v>
       </c>
       <c r="U43">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V43">
         <v>0.27</v>
       </c>
       <c r="W43">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.009012085128496</v>
+        <v>5.21352221795482</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,13 +4853,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08311173774112102</v>
+        <v>0.08229974120165962</v>
       </c>
       <c r="C44">
-        <v>1319.249858909247</v>
+        <v>1351.485550529523</v>
       </c>
       <c r="D44">
-        <v>1454.243740465107</v>
+        <v>1486.479432085383</v>
       </c>
       <c r="E44">
         <v>-195.8391697676158</v>
@@ -4886,37 +4886,37 @@
         <v>48.872</v>
       </c>
       <c r="M44">
-        <v>9.994785228935163</v>
+        <v>9.602721136889928</v>
       </c>
       <c r="N44">
-        <v>38.87721477106484</v>
+        <v>39.26927886311007</v>
       </c>
       <c r="O44">
-        <v>10.49684798818751</v>
+        <v>10.60270529303972</v>
       </c>
       <c r="P44">
-        <v>28.38036678287733</v>
+        <v>28.66657357007036</v>
       </c>
       <c r="Q44">
-        <v>75.24236678287733</v>
+        <v>75.52857357007035</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1082585356541041</v>
+        <v>0.1082329554136534</v>
       </c>
       <c r="T44">
         <v>1.143481503949367</v>
       </c>
       <c r="U44">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V44">
         <v>0.27</v>
       </c>
       <c r="W44">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.889749892625435</v>
+        <v>5.089390736574943</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,13 +4935,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08302726941380043</v>
+        <v>0.08219633805667215</v>
       </c>
       <c r="C45">
-        <v>1318.959193888749</v>
+        <v>1352.118354992051</v>
       </c>
       <c r="D45">
-        <v>1457.543405957843</v>
+        <v>1490.702567061146</v>
       </c>
       <c r="E45">
         <v>-192.2488392543811</v>
@@ -4968,37 +4968,37 @@
         <v>48.872</v>
       </c>
       <c r="M45">
-        <v>10.23275630581457</v>
+        <v>9.831357354434925</v>
       </c>
       <c r="N45">
-        <v>38.63924369418543</v>
+        <v>39.04064264556507</v>
       </c>
       <c r="O45">
-        <v>10.43259579743007</v>
+        <v>10.54097351430257</v>
       </c>
       <c r="P45">
-        <v>28.20664789675536</v>
+        <v>28.4996691312625</v>
       </c>
       <c r="Q45">
-        <v>75.06864789675535</v>
+        <v>75.36166913126249</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1091607548757214</v>
+        <v>0.1091348051263735</v>
       </c>
       <c r="T45">
         <v>1.159999198154373</v>
       </c>
       <c r="U45">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V45">
         <v>0.27</v>
       </c>
       <c r="W45">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.776034778843449</v>
+        <v>4.971032812468549</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,13 +5017,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08294280108647983</v>
+        <v>0.08209293491168468</v>
       </c>
       <c r="C46">
-        <v>1318.683536741472</v>
+        <v>1352.775223942021</v>
       </c>
       <c r="D46">
-        <v>1460.858079323801</v>
+        <v>1494.94976652435</v>
       </c>
       <c r="E46">
         <v>-188.6585087411463</v>
@@ -5050,37 +5050,37 @@
         <v>48.872</v>
       </c>
       <c r="M46">
-        <v>10.47072738269398</v>
+        <v>10.05999357197992</v>
       </c>
       <c r="N46">
-        <v>38.40127261730602</v>
+        <v>38.81200642802008</v>
       </c>
       <c r="O46">
-        <v>10.36834360667263</v>
+        <v>10.47924173556542</v>
       </c>
       <c r="P46">
-        <v>28.0329290106334</v>
+        <v>28.33276469245465</v>
       </c>
       <c r="Q46">
-        <v>74.89492901063339</v>
+        <v>75.19476469245464</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1100951962123964</v>
+        <v>0.1100688637574051</v>
       </c>
       <c r="T46">
         <v>1.177106810009558</v>
       </c>
       <c r="U46">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V46">
         <v>0.27</v>
       </c>
       <c r="W46">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.667488533869735</v>
+        <v>4.858054794003355</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,13 +5099,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08285833275915923</v>
+        <v>0.0819895317666972</v>
       </c>
       <c r="C47">
-        <v>1318.422990091295</v>
+        <v>1353.45636365541</v>
       </c>
       <c r="D47">
-        <v>1464.187863186859</v>
+        <v>1499.221236750974</v>
       </c>
       <c r="E47">
         <v>-185.0681782279115</v>
@@ -5132,37 +5132,37 @@
         <v>48.872</v>
       </c>
       <c r="M47">
-        <v>10.70869845957339</v>
+        <v>10.28862978952492</v>
       </c>
       <c r="N47">
-        <v>38.16330154042662</v>
+        <v>38.58337021047508</v>
       </c>
       <c r="O47">
-        <v>10.30409141591519</v>
+        <v>10.41750995682827</v>
       </c>
       <c r="P47">
-        <v>27.85921012451143</v>
+        <v>28.16586025364681</v>
       </c>
       <c r="Q47">
-        <v>74.72121012451143</v>
+        <v>75.02786025364681</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1110636172340415</v>
+        <v>0.1110368881568378</v>
       </c>
       <c r="T47">
         <v>1.194836516841296</v>
       </c>
       <c r="U47">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V47">
         <v>0.27</v>
       </c>
       <c r="W47">
-        <v>0.04838520728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.563766566450408</v>
+        <v>4.75009802080328</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,13 +5181,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08364694443183862</v>
+        <v>0.08188612862170973</v>
       </c>
       <c r="C48">
-        <v>1284.323574703739</v>
+        <v>1354.161982772494</v>
       </c>
       <c r="D48">
-        <v>1433.678778312538</v>
+        <v>1503.517186381293</v>
       </c>
       <c r="E48">
         <v>-181.4778477146768</v>
@@ -5214,45 +5214,45 @@
         <v>48.872</v>
       </c>
       <c r="M48">
-        <v>11.37607306583567</v>
+        <v>10.51726600706992</v>
       </c>
       <c r="N48">
-        <v>37.49592693416433</v>
+        <v>38.35473399293008</v>
       </c>
       <c r="O48">
-        <v>10.12390027222437</v>
+        <v>10.35577817809112</v>
       </c>
       <c r="P48">
-        <v>27.37202666193996</v>
+        <v>27.99895581483896</v>
       </c>
       <c r="Q48">
-        <v>74.23402666193996</v>
+        <v>74.86095581483895</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1120679057009327</v>
+        <v>0.1120407653118051</v>
       </c>
       <c r="T48">
         <v>1.213222879481616</v>
       </c>
       <c r="U48">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V48">
         <v>0.27</v>
       </c>
       <c r="W48">
-        <v>0.05028320728985866</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.296034292076686</v>
+        <v>4.646835020351034</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,13 +5263,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08358145610451805</v>
+        <v>0.08178272547672225</v>
       </c>
       <c r="C49">
-        <v>1283.218305243921</v>
+        <v>1354.892292331816</v>
       </c>
       <c r="D49">
-        <v>1436.163839365955</v>
+        <v>1507.83782645385</v>
       </c>
       <c r="E49">
         <v>-177.887517201442</v>
@@ -5296,45 +5296,45 @@
         <v>48.872</v>
       </c>
       <c r="M49">
-        <v>11.62337900204949</v>
+        <v>10.74590222461492</v>
       </c>
       <c r="N49">
-        <v>37.24862099795051</v>
+        <v>38.12609777538508</v>
       </c>
       <c r="O49">
-        <v>10.05712766944664</v>
+        <v>10.29404639935397</v>
       </c>
       <c r="P49">
-        <v>27.19149332850387</v>
+        <v>27.8320513760311</v>
       </c>
       <c r="Q49">
-        <v>74.05349332850386</v>
+        <v>74.6940513760311</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1131100918458197</v>
+        <v>0.1130825246235635</v>
       </c>
       <c r="T49">
         <v>1.232303067127231</v>
       </c>
       <c r="U49">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V49">
         <v>0.27</v>
       </c>
       <c r="W49">
-        <v>0.05028320728985866</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.204629307138884</v>
+        <v>4.547966190130799</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,13 +5345,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08351596777719744</v>
+        <v>0.08255532233173477</v>
       </c>
       <c r="C50">
-        <v>1282.121665682858</v>
+        <v>1319.607211543427</v>
       </c>
       <c r="D50">
-        <v>1438.657530318127</v>
+        <v>1476.143076178695</v>
       </c>
       <c r="E50">
         <v>-174.2971866882073</v>
@@ -5378,37 +5378,37 @@
         <v>48.872</v>
       </c>
       <c r="M50">
-        <v>11.87068493826331</v>
+        <v>11.40537810374808</v>
       </c>
       <c r="N50">
-        <v>37.00131506173669</v>
+        <v>37.46662189625192</v>
       </c>
       <c r="O50">
-        <v>9.990355066668908</v>
+        <v>10.11598791198802</v>
       </c>
       <c r="P50">
-        <v>27.01095999506778</v>
+        <v>27.3506339842639</v>
       </c>
       <c r="Q50">
-        <v>73.87295999506777</v>
+        <v>74.21263398426389</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1141923620732025</v>
+        <v>0.1141643516011589</v>
       </c>
       <c r="T50">
         <v>1.252117108143831</v>
       </c>
       <c r="U50">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V50">
         <v>0.27</v>
       </c>
       <c r="W50">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.117032863240158</v>
+        <v>4.284996039187817</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,13 +5427,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08345047944987685</v>
+        <v>0.08247016918674731</v>
       </c>
       <c r="C51">
-        <v>1281.033701052457</v>
+        <v>1319.444687014613</v>
       </c>
       <c r="D51">
-        <v>1441.15989620096</v>
+        <v>1479.570882163116</v>
       </c>
       <c r="E51">
         <v>-170.7068561749725</v>
@@ -5460,37 +5460,37 @@
         <v>48.872</v>
       </c>
       <c r="M51">
-        <v>12.11799087447713</v>
+        <v>11.64299014757617</v>
       </c>
       <c r="N51">
-        <v>36.75400912552287</v>
+        <v>37.22900985242383</v>
       </c>
       <c r="O51">
-        <v>9.923582463891176</v>
+        <v>10.05183266015444</v>
       </c>
       <c r="P51">
-        <v>26.83042666163169</v>
+        <v>27.17717719226939</v>
       </c>
       <c r="Q51">
-        <v>73.69242666163169</v>
+        <v>74.03917719226939</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1153170742702865</v>
+        <v>0.1152886031661109</v>
       </c>
       <c r="T51">
         <v>1.272708170376769</v>
       </c>
       <c r="U51">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V51">
         <v>0.27</v>
       </c>
       <c r="W51">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.033011784398521</v>
+        <v>4.197547140428881</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,13 +5509,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08437049112255625</v>
+        <v>0.08238501604175982</v>
       </c>
       <c r="C52">
-        <v>1243.067766596577</v>
+        <v>1319.298119207517</v>
       </c>
       <c r="D52">
-        <v>1406.784292258315</v>
+        <v>1483.014644869255</v>
       </c>
       <c r="E52">
         <v>-167.1165256617378</v>
@@ -5542,45 +5542,45 @@
         <v>48.872</v>
       </c>
       <c r="M52">
-        <v>12.84999142997764</v>
+        <v>11.88060219140426</v>
       </c>
       <c r="N52">
-        <v>36.02200857002236</v>
+        <v>36.99139780859574</v>
       </c>
       <c r="O52">
-        <v>9.725942313906037</v>
+        <v>9.987677408320851</v>
       </c>
       <c r="P52">
-        <v>26.29606625611632</v>
+        <v>27.00372040027489</v>
       </c>
       <c r="Q52">
-        <v>73.15806625611631</v>
+        <v>73.86572040027488</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1164867749552538</v>
+        <v>0.116457824793661</v>
       </c>
       <c r="T52">
         <v>1.294122875099024</v>
       </c>
       <c r="U52">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V52">
         <v>0.27</v>
       </c>
       <c r="W52">
-        <v>0.05225420728985867</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.803271018997484</v>
+        <v>4.113596197620303</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,13 +5591,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08432471279523567</v>
+        <v>0.08229986289677235</v>
       </c>
       <c r="C53">
-        <v>1241.149096353537</v>
+        <v>1319.167619801874</v>
       </c>
       <c r="D53">
-        <v>1408.45595252851</v>
+        <v>1486.474475976847</v>
       </c>
       <c r="E53">
         <v>-163.526195148503</v>
@@ -5624,45 +5624,45 @@
         <v>48.872</v>
       </c>
       <c r="M53">
-        <v>13.10699125857719</v>
+        <v>12.11821423523234</v>
       </c>
       <c r="N53">
-        <v>35.7650087414228</v>
+        <v>36.75378576476766</v>
       </c>
       <c r="O53">
-        <v>9.656552360184158</v>
+        <v>9.923522156487268</v>
       </c>
       <c r="P53">
-        <v>26.10845638123865</v>
+        <v>26.83026360828039</v>
       </c>
       <c r="Q53">
-        <v>72.97045638123865</v>
+        <v>73.69226360828038</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1177042185253219</v>
+        <v>0.1176747697529478</v>
       </c>
       <c r="T53">
         <v>1.31641164940178</v>
       </c>
       <c r="U53">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V53">
         <v>0.27</v>
       </c>
       <c r="W53">
-        <v>0.05225420728985867</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.728697077448514</v>
+        <v>4.032937448647356</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,13 +5673,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08427893446791507</v>
+        <v>0.08354330975178487</v>
       </c>
       <c r="C54">
-        <v>1239.234403653643</v>
+        <v>1266.605643071991</v>
       </c>
       <c r="D54">
-        <v>1410.13159034185</v>
+        <v>1437.502829760198</v>
       </c>
       <c r="E54">
         <v>-159.9358646352682</v>
@@ -5706,37 +5706,37 @@
         <v>48.872</v>
       </c>
       <c r="M54">
-        <v>13.36399108717675</v>
+        <v>13.00926643246915</v>
       </c>
       <c r="N54">
-        <v>35.50800891282326</v>
+        <v>35.86273356753085</v>
       </c>
       <c r="O54">
-        <v>9.58716240646228</v>
+        <v>9.68293806323333</v>
       </c>
       <c r="P54">
-        <v>25.92084650636098</v>
+        <v>26.17979550429752</v>
       </c>
       <c r="Q54">
-        <v>72.78284650636097</v>
+        <v>73.04179550429751</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1189723889108095</v>
+        <v>0.1189424207522049</v>
       </c>
       <c r="T54">
         <v>1.339629122633817</v>
       </c>
       <c r="U54">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V54">
         <v>0.27</v>
       </c>
       <c r="W54">
-        <v>0.05225420728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.656991364420658</v>
+        <v>3.756706825376634</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,13 +5755,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08423315614059447</v>
+        <v>0.08348370660679739</v>
       </c>
       <c r="C55">
-        <v>1237.323702710034</v>
+        <v>1265.288966009998</v>
       </c>
       <c r="D55">
-        <v>1411.811219911476</v>
+        <v>1439.77648321144</v>
       </c>
       <c r="E55">
         <v>-156.3455341220335</v>
@@ -5788,37 +5788,37 @@
         <v>48.872</v>
       </c>
       <c r="M55">
-        <v>13.6209909157763</v>
+        <v>13.25944463309356</v>
       </c>
       <c r="N55">
-        <v>35.2510090842237</v>
+        <v>35.61255536690644</v>
       </c>
       <c r="O55">
-        <v>9.517772452740399</v>
+        <v>9.61538994906474</v>
       </c>
       <c r="P55">
-        <v>25.7332366314833</v>
+        <v>25.9971654178417</v>
       </c>
       <c r="Q55">
-        <v>72.59523663148329</v>
+        <v>72.85916541784169</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1202945239935519</v>
+        <v>0.1202640143471751</v>
       </c>
       <c r="T55">
         <v>1.363834573450196</v>
       </c>
       <c r="U55">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V55">
         <v>0.27</v>
       </c>
       <c r="W55">
-        <v>0.05225420728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.587991527356117</v>
+        <v>3.685825564520471</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,13 +5837,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08418737781327386</v>
+        <v>0.08342410346180992</v>
       </c>
       <c r="C56">
-        <v>1235.417007803649</v>
+        <v>1263.979492675606</v>
       </c>
       <c r="D56">
-        <v>1413.494855518326</v>
+        <v>1442.057340390283</v>
       </c>
       <c r="E56">
         <v>-152.7552036087987</v>
@@ -5870,37 +5870,37 @@
         <v>48.872</v>
       </c>
       <c r="M56">
-        <v>13.87799074437585</v>
+        <v>13.50962283371797</v>
       </c>
       <c r="N56">
-        <v>34.99400925562415</v>
+        <v>35.36237716628203</v>
       </c>
       <c r="O56">
-        <v>9.448382499018521</v>
+        <v>9.547841834896149</v>
       </c>
       <c r="P56">
-        <v>25.54562675660563</v>
+        <v>25.81453533138588</v>
       </c>
       <c r="Q56">
-        <v>72.40762675660562</v>
+        <v>72.67653533138588</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1216741432103265</v>
+        <v>0.121643068533231</v>
       </c>
       <c r="T56">
         <v>1.389092435171634</v>
       </c>
       <c r="U56">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V56">
         <v>0.27</v>
       </c>
       <c r="W56">
-        <v>0.05225420728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.521547239812485</v>
+        <v>3.617569535547869</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,13 +5919,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08602864948595329</v>
+        <v>0.08336450031682247</v>
       </c>
       <c r="C57">
-        <v>1167.130793381789</v>
+        <v>1262.677257359022</v>
       </c>
       <c r="D57">
-        <v>1348.798971609701</v>
+        <v>1444.345435586934</v>
       </c>
       <c r="E57">
         <v>-149.164873095564</v>
@@ -5952,45 +5952,45 @@
         <v>48.872</v>
       </c>
       <c r="M57">
-        <v>15.06309101064659</v>
+        <v>13.75980103434237</v>
       </c>
       <c r="N57">
-        <v>33.80890898935341</v>
+        <v>35.11219896565763</v>
       </c>
       <c r="O57">
-        <v>9.128405427125422</v>
+        <v>9.480293720727559</v>
       </c>
       <c r="P57">
-        <v>24.68050356222799</v>
+        <v>25.63190524493007</v>
       </c>
       <c r="Q57">
-        <v>71.54250356222798</v>
+        <v>72.49390524493006</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1231150788367356</v>
+        <v>0.1230834140164449</v>
       </c>
       <c r="T57">
         <v>1.415472868525137</v>
       </c>
       <c r="U57">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V57">
         <v>0.27</v>
       </c>
       <c r="W57">
-        <v>0.05568520728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.24448680323695</v>
+        <v>3.551795543992454</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,13 +6001,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08601718115863267</v>
+        <v>0.08444953717183498</v>
       </c>
       <c r="C58">
-        <v>1163.925086247183</v>
+        <v>1218.538756190772</v>
       </c>
       <c r="D58">
-        <v>1349.183594988329</v>
+        <v>1403.797264931918</v>
       </c>
       <c r="E58">
         <v>-145.5745425823292</v>
@@ -6034,37 +6034,37 @@
         <v>48.872</v>
       </c>
       <c r="M58">
-        <v>15.33696539265835</v>
+        <v>14.57294305944199</v>
       </c>
       <c r="N58">
-        <v>33.53503460734165</v>
+        <v>34.29905694055801</v>
       </c>
       <c r="O58">
-        <v>9.054459343982247</v>
+        <v>9.260745373950664</v>
       </c>
       <c r="P58">
-        <v>24.48057526335941</v>
+        <v>25.03831156660735</v>
       </c>
       <c r="Q58">
-        <v>71.34257526335941</v>
+        <v>71.90031156660734</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1246215115370723</v>
+        <v>0.1245892297488957</v>
       </c>
       <c r="T58">
         <v>1.443052412485617</v>
       </c>
       <c r="U58">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V58">
         <v>0.27</v>
       </c>
       <c r="W58">
-        <v>0.05568520728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.186549538893433</v>
+        <v>3.353612225111607</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,13 +6083,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08600571283131209</v>
+        <v>0.08441037402684751</v>
       </c>
       <c r="C59">
-        <v>1160.719598533472</v>
+        <v>1216.372320607468</v>
       </c>
       <c r="D59">
-        <v>1349.568437787854</v>
+        <v>1405.221159861849</v>
       </c>
       <c r="E59">
         <v>-141.9842120690945</v>
@@ -6116,37 +6116,37 @@
         <v>48.872</v>
       </c>
       <c r="M59">
-        <v>15.6108397746701</v>
+        <v>14.83317418550345</v>
       </c>
       <c r="N59">
-        <v>33.2611602253299</v>
+        <v>34.03882581449655</v>
       </c>
       <c r="O59">
-        <v>8.980513260839073</v>
+        <v>9.190482969914068</v>
       </c>
       <c r="P59">
-        <v>24.28064696449082</v>
+        <v>24.84834284458248</v>
       </c>
       <c r="Q59">
-        <v>71.14264696449081</v>
+        <v>71.71034284458247</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1261980108746341</v>
+        <v>0.1261650834223909</v>
       </c>
       <c r="T59">
         <v>1.471914725932632</v>
       </c>
       <c r="U59">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V59">
         <v>0.27</v>
       </c>
       <c r="W59">
-        <v>0.05568520728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.13064516101811</v>
+        <v>3.294776922916666</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,13 +6165,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08599424450399148</v>
+        <v>0.08437121088186003</v>
       </c>
       <c r="C60">
-        <v>1157.514330428478</v>
+        <v>1214.208776517705</v>
       </c>
       <c r="D60">
-        <v>1349.953500196094</v>
+        <v>1406.647946285321</v>
       </c>
       <c r="E60">
         <v>-138.3938815558597</v>
@@ -6198,37 +6198,37 @@
         <v>48.872</v>
       </c>
       <c r="M60">
-        <v>15.88471415668186</v>
+        <v>15.09340531156492</v>
       </c>
       <c r="N60">
-        <v>32.98728584331814</v>
+        <v>33.77859468843508</v>
       </c>
       <c r="O60">
-        <v>8.906567177695898</v>
+        <v>9.120220565877473</v>
       </c>
       <c r="P60">
-        <v>24.08071866562224</v>
+        <v>24.65837412255761</v>
       </c>
       <c r="Q60">
-        <v>70.94271866562224</v>
+        <v>71.5203741225576</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1278495816092225</v>
+        <v>0.1278159777470048</v>
       </c>
       <c r="T60">
         <v>1.502151435258074</v>
       </c>
       <c r="U60">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V60">
         <v>0.27</v>
       </c>
       <c r="W60">
-        <v>0.05568520728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.076668520310901</v>
+        <v>3.23797042424569</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,13 +6247,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.0859827761766709</v>
+        <v>0.08433204773687256</v>
       </c>
       <c r="C61">
-        <v>1154.309282120229</v>
+        <v>1212.048132738041</v>
       </c>
       <c r="D61">
-        <v>1350.33878240108</v>
+        <v>1408.077633018891</v>
       </c>
       <c r="E61">
         <v>-134.803551042625</v>
@@ -6280,37 +6280,37 @@
         <v>48.872</v>
       </c>
       <c r="M61">
-        <v>16.15858853869361</v>
+        <v>15.35363643762638</v>
       </c>
       <c r="N61">
-        <v>32.71341146130639</v>
+        <v>33.51836356237362</v>
       </c>
       <c r="O61">
-        <v>8.832621094552724</v>
+        <v>9.049958161840879</v>
       </c>
       <c r="P61">
-        <v>23.88079036675366</v>
+        <v>24.46840540053275</v>
       </c>
       <c r="Q61">
-        <v>70.74279036675365</v>
+        <v>71.33040540053274</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1295817167698885</v>
+        <v>0.1295474035020877</v>
       </c>
       <c r="T61">
         <v>1.533863106014027</v>
       </c>
       <c r="U61">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V61">
         <v>0.27</v>
       </c>
       <c r="W61">
-        <v>0.05568520728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.024521596237835</v>
+        <v>3.183089569597458</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,13 +6329,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.09004470784935029</v>
+        <v>0.08429288459188508</v>
       </c>
       <c r="C62">
-        <v>1026.749687582059</v>
+        <v>1209.89039812091</v>
       </c>
       <c r="D62">
-        <v>1226.369518376144</v>
+        <v>1409.510228914995</v>
       </c>
       <c r="E62">
         <v>-131.2132205293902</v>
@@ -6362,45 +6362,45 @@
         <v>48.872</v>
       </c>
       <c r="M62">
-        <v>18.43586734709036</v>
+        <v>15.61386756368785</v>
       </c>
       <c r="N62">
-        <v>30.43613265290964</v>
+        <v>33.25813243631215</v>
       </c>
       <c r="O62">
-        <v>8.217755816285603</v>
+        <v>8.979695757804281</v>
       </c>
       <c r="P62">
-        <v>22.21837683662404</v>
+        <v>24.27843667850787</v>
       </c>
       <c r="Q62">
-        <v>69.08037683662403</v>
+        <v>71.14043667850787</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1314004586885877</v>
+        <v>0.1313654005449247</v>
       </c>
       <c r="T62">
         <v>1.567160360307778</v>
       </c>
       <c r="U62">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V62">
         <v>0.27</v>
       </c>
       <c r="W62">
-        <v>0.06247420728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.650919486449506</v>
+        <v>3.130038076770833</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,13 +6411,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.0901011295220297</v>
+        <v>0.08425372144689761</v>
       </c>
       <c r="C63">
-        <v>1021.597459656808</v>
+        <v>1207.735581554812</v>
       </c>
       <c r="D63">
-        <v>1224.807620964129</v>
+        <v>1410.945742862132</v>
       </c>
       <c r="E63">
         <v>-127.6228900161555</v>
@@ -6444,45 +6444,45 @@
         <v>48.872</v>
       </c>
       <c r="M63">
-        <v>18.7431318028752</v>
+        <v>15.87409868974931</v>
       </c>
       <c r="N63">
-        <v>30.1288681971248</v>
+        <v>32.9979013102507</v>
       </c>
       <c r="O63">
-        <v>8.134794413223696</v>
+        <v>8.909433353767689</v>
       </c>
       <c r="P63">
-        <v>21.9940737839011</v>
+        <v>24.08846795648301</v>
       </c>
       <c r="Q63">
-        <v>68.8560737839011</v>
+        <v>70.95046795648301</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1333124694236305</v>
+        <v>0.1332766282053431</v>
       </c>
       <c r="T63">
         <v>1.602165166103772</v>
       </c>
       <c r="U63">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V63">
         <v>0.27</v>
       </c>
       <c r="W63">
-        <v>0.06247420728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.607461789950334</v>
+        <v>3.07872597715164</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,13 +6493,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.0901575511947091</v>
+        <v>0.08421455830191013</v>
       </c>
       <c r="C64">
-        <v>1016.449205118825</v>
+        <v>1205.583691964492</v>
       </c>
       <c r="D64">
-        <v>1223.249696939379</v>
+        <v>1412.384183785047</v>
       </c>
       <c r="E64">
         <v>-124.0325595029207</v>
@@ -6526,45 +6526,45 @@
         <v>48.872</v>
       </c>
       <c r="M64">
-        <v>19.05039625866004</v>
+        <v>16.13432981581077</v>
       </c>
       <c r="N64">
-        <v>29.82160374133996</v>
+        <v>32.73767018418923</v>
       </c>
       <c r="O64">
-        <v>8.05183301016179</v>
+        <v>8.839170949731091</v>
       </c>
       <c r="P64">
-        <v>21.76977073117817</v>
+        <v>23.89849923445814</v>
       </c>
       <c r="Q64">
-        <v>68.63177073117816</v>
+        <v>70.76049923445814</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.135325112302623</v>
+        <v>0.1352884467952573</v>
       </c>
       <c r="T64">
         <v>1.639012330099555</v>
       </c>
       <c r="U64">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V64">
         <v>0.27</v>
       </c>
       <c r="W64">
-        <v>0.06247420728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.565405954628554</v>
+        <v>3.02906910655242</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,13 +6575,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.0902139728673885</v>
+        <v>0.08776261515692267</v>
       </c>
       <c r="C65">
-        <v>1011.304908825227</v>
+        <v>1082.572315683496</v>
       </c>
       <c r="D65">
-        <v>1221.695731159017</v>
+        <v>1292.963138017285</v>
       </c>
       <c r="E65">
         <v>-120.442228989686</v>
@@ -6608,37 +6608,37 @@
         <v>48.872</v>
       </c>
       <c r="M65">
-        <v>19.35766071444488</v>
+        <v>18.1588493560758</v>
       </c>
       <c r="N65">
-        <v>29.51433928555512</v>
+        <v>30.7131506439242</v>
       </c>
       <c r="O65">
-        <v>7.968871607099883</v>
+        <v>8.292550673859536</v>
       </c>
       <c r="P65">
-        <v>21.54546767845524</v>
+        <v>22.42059997006466</v>
       </c>
       <c r="Q65">
-        <v>68.40746767845523</v>
+        <v>69.28259997006467</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.137446546688588</v>
+        <v>0.1374090123359776</v>
       </c>
       <c r="T65">
         <v>1.677851232689705</v>
       </c>
       <c r="U65">
-        <v>0.08558110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V65">
         <v>0.27</v>
       </c>
       <c r="W65">
-        <v>0.06247420728985867</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.524685225190006</v>
+        <v>2.69135995578089</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,13 +6657,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.09246623454006792</v>
+        <v>0.0877803920119352</v>
       </c>
       <c r="C66">
-        <v>948.7516365172564</v>
+        <v>1078.434471982806</v>
       </c>
       <c r="D66">
-        <v>1162.732789364281</v>
+        <v>1292.41562482983</v>
       </c>
       <c r="E66">
         <v>-116.8518984764512</v>
@@ -6690,45 +6690,45 @@
         <v>48.872</v>
       </c>
       <c r="M66">
-        <v>20.74489658861073</v>
+        <v>18.44708506014049</v>
       </c>
       <c r="N66">
-        <v>28.12710341138927</v>
+        <v>30.42491493985951</v>
       </c>
       <c r="O66">
-        <v>7.594317921075103</v>
+        <v>8.214727033762067</v>
       </c>
       <c r="P66">
-        <v>20.53278549031416</v>
+        <v>22.21018790609744</v>
       </c>
       <c r="Q66">
-        <v>67.39478549031416</v>
+        <v>69.07218790609744</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1396858385404399</v>
+        <v>0.1396473870734046</v>
       </c>
       <c r="T66">
         <v>1.718847852090419</v>
       </c>
       <c r="U66">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V66">
         <v>0.27</v>
       </c>
       <c r="W66">
-        <v>0.06590520728985866</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.355856525543322</v>
+        <v>2.649307456471814</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,13 +6739,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.09255696621274731</v>
+        <v>0.08779816886694772</v>
       </c>
       <c r="C67">
-        <v>942.9050285035061</v>
+        <v>1074.297091781493</v>
       </c>
       <c r="D67">
-        <v>1160.476511863765</v>
+        <v>1291.868575141752</v>
       </c>
       <c r="E67">
         <v>-113.2615679632164</v>
@@ -6772,45 +6772,45 @@
         <v>48.872</v>
       </c>
       <c r="M67">
-        <v>21.06903559780778</v>
+        <v>18.73532076420519</v>
       </c>
       <c r="N67">
-        <v>27.80296440219222</v>
+        <v>30.13667923579481</v>
       </c>
       <c r="O67">
-        <v>7.506800388591901</v>
+        <v>8.136903393664598</v>
       </c>
       <c r="P67">
-        <v>20.29616401360032</v>
+        <v>21.99977584213021</v>
       </c>
       <c r="Q67">
-        <v>67.15816401360031</v>
+        <v>68.86177584213021</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1420530899266834</v>
+        <v>0.1420136689386845</v>
       </c>
       <c r="T67">
         <v>1.762187135456888</v>
       </c>
       <c r="U67">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V67">
         <v>0.27</v>
       </c>
       <c r="W67">
-        <v>0.06590520728985866</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.319612578996502</v>
+        <v>2.6085488802184</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.09264769788542671</v>
+        <v>0.08781594572196025</v>
       </c>
       <c r="C68">
-        <v>937.0671601222621</v>
+        <v>1070.16017449124</v>
       </c>
       <c r="D68">
-        <v>1158.228973995756</v>
+        <v>1291.321988364734</v>
       </c>
       <c r="E68">
         <v>-109.6712374499817</v>
@@ -6854,45 +6854,45 @@
         <v>48.872</v>
       </c>
       <c r="M68">
-        <v>21.39317460700482</v>
+        <v>19.02355646826988</v>
       </c>
       <c r="N68">
-        <v>27.47882539299518</v>
+        <v>29.84844353173012</v>
       </c>
       <c r="O68">
-        <v>7.419282856108699</v>
+        <v>8.059079753567131</v>
       </c>
       <c r="P68">
-        <v>20.05954253688648</v>
+        <v>21.78936377816299</v>
       </c>
       <c r="Q68">
-        <v>66.92154253688648</v>
+        <v>68.65136377816299</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1445595913944706</v>
+        <v>0.1445191438548633</v>
       </c>
       <c r="T68">
         <v>1.808075788433149</v>
       </c>
       <c r="U68">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V68">
         <v>0.27</v>
       </c>
       <c r="W68">
-        <v>0.06590520728985866</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.284466933860191</v>
+        <v>2.569025412336304</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,13 +6903,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.09273842955810613</v>
+        <v>0.08783372257697278</v>
       </c>
       <c r="C69">
-        <v>931.2379806925693</v>
+        <v>1066.023719524726</v>
       </c>
       <c r="D69">
-        <v>1155.990125079298</v>
+        <v>1290.775863911455</v>
       </c>
       <c r="E69">
         <v>-106.0809069367469</v>
@@ -6936,45 +6936,45 @@
         <v>48.872</v>
       </c>
       <c r="M69">
-        <v>21.71731361620186</v>
+        <v>19.31179217233458</v>
       </c>
       <c r="N69">
-        <v>27.15468638379814</v>
+        <v>29.56020782766542</v>
       </c>
       <c r="O69">
-        <v>7.331765323625497</v>
+        <v>7.981256113469664</v>
       </c>
       <c r="P69">
-        <v>19.82292106017264</v>
+        <v>21.57895171419575</v>
       </c>
       <c r="Q69">
-        <v>66.68492106017263</v>
+        <v>68.44095171419575</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1472180020421237</v>
+        <v>0.147176465735659</v>
       </c>
       <c r="T69">
         <v>1.85674557189282</v>
       </c>
       <c r="U69">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V69">
         <v>0.27</v>
       </c>
       <c r="W69">
-        <v>0.06590520728985866</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.250370412459293</v>
+        <v>2.530681749465613</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,13 +6985,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.09282916123078552</v>
+        <v>0.08978745943198529</v>
       </c>
       <c r="C70">
-        <v>925.4174399245819</v>
+        <v>1005.102585881481</v>
       </c>
       <c r="D70">
-        <v>1153.759914824545</v>
+        <v>1233.445060781445</v>
       </c>
       <c r="E70">
         <v>-102.4905764235122</v>
@@ -7018,37 +7018,37 @@
         <v>48.872</v>
       </c>
       <c r="M70">
-        <v>22.04145262539891</v>
+        <v>20.55218352850913</v>
       </c>
       <c r="N70">
-        <v>26.83054737460109</v>
+        <v>28.31981647149087</v>
       </c>
       <c r="O70">
-        <v>7.244247791142295</v>
+        <v>7.646350447302535</v>
       </c>
       <c r="P70">
-        <v>19.5862995834588</v>
+        <v>20.67346602418834</v>
       </c>
       <c r="Q70">
-        <v>66.44829958345879</v>
+        <v>67.53546602418834</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1500425633552551</v>
+        <v>0.1499998702340044</v>
       </c>
       <c r="T70">
         <v>1.90845721681872</v>
       </c>
       <c r="U70">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V70">
         <v>0.27</v>
       </c>
       <c r="W70">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.217276729923126</v>
+        <v>2.377946845998471</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,13 +7067,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09291989290346493</v>
+        <v>0.08983370628699783</v>
       </c>
       <c r="C71">
-        <v>919.6054879157944</v>
+        <v>1000.216816948412</v>
       </c>
       <c r="D71">
-        <v>1151.538293328992</v>
+        <v>1232.14962236161</v>
       </c>
       <c r="E71">
         <v>-98.90024591027739</v>
@@ -7100,37 +7100,37 @@
         <v>48.872</v>
       </c>
       <c r="M71">
-        <v>22.36559163459595</v>
+        <v>20.85442152157544</v>
       </c>
       <c r="N71">
-        <v>26.50640836540405</v>
+        <v>28.01757847842456</v>
       </c>
       <c r="O71">
-        <v>7.156730258659095</v>
+        <v>7.564746189174631</v>
       </c>
       <c r="P71">
-        <v>19.34967810674496</v>
+        <v>20.45283228924993</v>
       </c>
       <c r="Q71">
-        <v>66.21167810674496</v>
+        <v>67.31483228924992</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1530493544305241</v>
+        <v>0.1530054298612753</v>
       </c>
       <c r="T71">
         <v>1.96350509690113</v>
       </c>
       <c r="U71">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V71">
         <v>0.27</v>
       </c>
       <c r="W71">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.185142284561922</v>
+        <v>2.343483848230377</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,13 +7149,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09301062457614433</v>
+        <v>0.08987995314201036</v>
       </c>
       <c r="C72">
-        <v>913.8020751473226</v>
+        <v>995.3337662556545</v>
       </c>
       <c r="D72">
-        <v>1149.325211073756</v>
+        <v>1230.856902182087</v>
       </c>
       <c r="E72">
         <v>-95.30991539704266</v>
@@ -7182,37 +7182,37 @@
         <v>48.872</v>
       </c>
       <c r="M72">
-        <v>22.68973064379299</v>
+        <v>21.15665951464175</v>
       </c>
       <c r="N72">
-        <v>26.18226935620701</v>
+        <v>27.71534048535825</v>
       </c>
       <c r="O72">
-        <v>7.069212726175893</v>
+        <v>7.483141931046728</v>
       </c>
       <c r="P72">
-        <v>19.11305663003112</v>
+        <v>20.23219855431152</v>
       </c>
       <c r="Q72">
-        <v>65.9750566300311</v>
+        <v>67.09419855431152</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1562565982441443</v>
+        <v>0.1562113601303643</v>
       </c>
       <c r="T72">
         <v>2.022222835655701</v>
       </c>
       <c r="U72">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V72">
         <v>0.27</v>
       </c>
       <c r="W72">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.153925966211037</v>
+        <v>2.310005507541371</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,13 +7231,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.09310135624882374</v>
+        <v>0.08992619999702287</v>
       </c>
       <c r="C73">
-        <v>908.007152480223</v>
+        <v>990.4534252565815</v>
       </c>
       <c r="D73">
-        <v>1147.120618919891</v>
+        <v>1229.566891696249</v>
       </c>
       <c r="E73">
         <v>-91.71958488380793</v>
@@ -7264,37 +7264,37 @@
         <v>48.872</v>
       </c>
       <c r="M73">
-        <v>23.01386965299003</v>
+        <v>21.45889750770806</v>
       </c>
       <c r="N73">
-        <v>25.85813034700997</v>
+        <v>27.41310249229194</v>
       </c>
       <c r="O73">
-        <v>6.981695193692692</v>
+        <v>7.401537672918825</v>
       </c>
       <c r="P73">
-        <v>18.87643515331727</v>
+        <v>20.01156481937312</v>
       </c>
       <c r="Q73">
-        <v>65.73843515331727</v>
+        <v>66.87356481937312</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1596850312862899</v>
+        <v>0.1596383890387008</v>
       </c>
       <c r="T73">
         <v>2.084990073634724</v>
       </c>
       <c r="U73">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V73">
         <v>0.27</v>
       </c>
       <c r="W73">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.123588980771445</v>
+        <v>2.277470218702761</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,13 +7313,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.09319208792150313</v>
+        <v>0.0899724468520354</v>
       </c>
       <c r="C74">
-        <v>902.2206711518561</v>
+        <v>985.5757854403562</v>
       </c>
       <c r="D74">
-        <v>1144.924468104758</v>
+        <v>1228.279582393259</v>
       </c>
       <c r="E74">
         <v>-88.12925437057316</v>
@@ -7346,37 +7346,37 @@
         <v>48.872</v>
       </c>
       <c r="M74">
-        <v>23.33800866218708</v>
+        <v>21.76113550077437</v>
       </c>
       <c r="N74">
-        <v>25.53399133781292</v>
+        <v>27.11086449922563</v>
       </c>
       <c r="O74">
-        <v>6.89417766120949</v>
+        <v>7.31993341479092</v>
       </c>
       <c r="P74">
-        <v>18.63981367660343</v>
+        <v>19.79093108443471</v>
       </c>
       <c r="Q74">
-        <v>65.50181367660343</v>
+        <v>66.6529310844347</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1633583524028747</v>
+        <v>0.1633102057262041</v>
       </c>
       <c r="T74">
         <v>2.152240685755107</v>
       </c>
       <c r="U74">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V74">
         <v>0.27</v>
       </c>
       <c r="W74">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.094094689371842</v>
+        <v>2.245838687887444</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,13 +7395,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.09328281959418255</v>
+        <v>0.09001869370704793</v>
       </c>
       <c r="C75">
-        <v>896.4425827722903</v>
+        <v>980.7008383317482</v>
       </c>
       <c r="D75">
-        <v>1142.736710238427</v>
+        <v>1226.994965797885</v>
       </c>
       <c r="E75">
         <v>-84.53892385733843</v>
@@ -7428,37 +7428,37 @@
         <v>48.872</v>
       </c>
       <c r="M75">
-        <v>23.66214767138412</v>
+        <v>22.06337349384068</v>
       </c>
       <c r="N75">
-        <v>25.20985232861588</v>
+        <v>26.80862650615932</v>
       </c>
       <c r="O75">
-        <v>6.806660128726289</v>
+        <v>7.238329156663017</v>
       </c>
       <c r="P75">
-        <v>18.4031921998896</v>
+        <v>19.5702973494963</v>
       </c>
       <c r="Q75">
-        <v>65.26519219988958</v>
+        <v>66.4322973494963</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1673037713799471</v>
+        <v>0.167254008835004</v>
       </c>
       <c r="T75">
         <v>2.224472824699222</v>
       </c>
       <c r="U75">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V75">
         <v>0.27</v>
       </c>
       <c r="W75">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.06540846075031</v>
+        <v>2.21507377435474</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,13 +7477,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.09337355126686195</v>
+        <v>0.09006494056206046</v>
       </c>
       <c r="C76">
-        <v>890.6728393207511</v>
+        <v>975.8285754909457</v>
       </c>
       <c r="D76">
-        <v>1140.557297300123</v>
+        <v>1225.713033470318</v>
       </c>
       <c r="E76">
         <v>-80.94859334410364</v>
@@ -7510,37 +7510,37 @@
         <v>48.872</v>
       </c>
       <c r="M76">
-        <v>23.98628668058116</v>
+        <v>22.36561148690699</v>
       </c>
       <c r="N76">
-        <v>24.88571331941884</v>
+        <v>26.50638851309301</v>
       </c>
       <c r="O76">
-        <v>6.719142596243088</v>
+        <v>7.156724898535113</v>
       </c>
       <c r="P76">
-        <v>18.16657072317575</v>
+        <v>19.34966361455789</v>
       </c>
       <c r="Q76">
-        <v>65.02857072317575</v>
+        <v>66.21166361455789</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1715526841244867</v>
+        <v>0.1715011814137117</v>
       </c>
       <c r="T76">
         <v>2.302261282023653</v>
       </c>
       <c r="U76">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V76">
         <v>0.27</v>
       </c>
       <c r="W76">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.037497535605036</v>
+        <v>2.185140344971567</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,13 +7559,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.09346428293954134</v>
+        <v>0.09011118741707297</v>
       </c>
       <c r="C77">
-        <v>884.9113931421032</v>
+        <v>970.9589885133719</v>
       </c>
       <c r="D77">
-        <v>1138.38618163471</v>
+        <v>1224.433777005979</v>
       </c>
       <c r="E77">
         <v>-77.35826283086891</v>
@@ -7592,37 +7592,37 @@
         <v>48.872</v>
       </c>
       <c r="M77">
-        <v>24.3104256897782</v>
+        <v>22.6678494799733</v>
       </c>
       <c r="N77">
-        <v>24.5615743102218</v>
+        <v>26.2041505200267</v>
       </c>
       <c r="O77">
-        <v>6.631625063759886</v>
+        <v>7.075120640407209</v>
       </c>
       <c r="P77">
-        <v>17.92994924646191</v>
+        <v>19.12902987961949</v>
       </c>
       <c r="Q77">
-        <v>64.79194924646191</v>
+        <v>65.99102987961948</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1761415098885894</v>
+        <v>0.1760881277987159</v>
       </c>
       <c r="T77">
         <v>2.386272815934039</v>
       </c>
       <c r="U77">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V77">
         <v>0.27</v>
       </c>
       <c r="W77">
-        <v>0.06590520728985866</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.010330901796968</v>
+        <v>2.156005140371946</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,13 +7641,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1025982546122208</v>
+        <v>0.0901574342720855</v>
       </c>
       <c r="C78">
-        <v>698.2522833747979</v>
+        <v>966.0920690294969</v>
       </c>
       <c r="D78">
-        <v>955.3174023806394</v>
+        <v>1223.157188035338</v>
       </c>
       <c r="E78">
         <v>-73.76793231763412</v>
@@ -7674,45 +7674,45 @@
         <v>48.872</v>
       </c>
       <c r="M78">
-        <v>29.08226613877046</v>
+        <v>22.97008747303962</v>
       </c>
       <c r="N78">
-        <v>19.78973386122954</v>
+        <v>25.90191252696038</v>
       </c>
       <c r="O78">
-        <v>5.343228142531975</v>
+        <v>6.993516382279304</v>
       </c>
       <c r="P78">
-        <v>14.44650571869756</v>
+        <v>18.90839614468108</v>
       </c>
       <c r="Q78">
-        <v>61.30850571869755</v>
+        <v>65.77039614468107</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1811127377997008</v>
+        <v>0.1810573197158039</v>
       </c>
       <c r="T78">
         <v>2.477285311003624</v>
       </c>
       <c r="U78">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V78">
         <v>0.27</v>
       </c>
       <c r="W78">
-        <v>0.07780420728985867</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.680474271392738</v>
+        <v>2.127636651682842</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,13 +7723,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1028079762849002</v>
+        <v>0.09020368112709803</v>
       </c>
       <c r="C79">
-        <v>691.147518976632</v>
+        <v>961.2278087046618</v>
       </c>
       <c r="D79">
-        <v>951.8029684957082</v>
+        <v>1221.883258223738</v>
       </c>
       <c r="E79">
         <v>-70.17760180439939</v>
@@ -7756,45 +7756,45 @@
         <v>48.872</v>
       </c>
       <c r="M79">
-        <v>29.46492753533323</v>
+        <v>23.27232546610593</v>
       </c>
       <c r="N79">
-        <v>19.40707246466677</v>
+        <v>25.59967453389407</v>
       </c>
       <c r="O79">
-        <v>5.239909565460028</v>
+        <v>6.9119121241514</v>
       </c>
       <c r="P79">
-        <v>14.16716289920674</v>
+        <v>18.68776240974267</v>
       </c>
       <c r="Q79">
-        <v>61.02916289920674</v>
+        <v>65.54976240974267</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1865162463987348</v>
+        <v>0.1864586152778559</v>
       </c>
       <c r="T79">
         <v>2.576211936079259</v>
       </c>
       <c r="U79">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V79">
         <v>0.27</v>
       </c>
       <c r="W79">
-        <v>0.07780420728985867</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.65864993020582</v>
+        <v>2.100005006855792</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,13 +7805,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1030176979575796</v>
+        <v>0.09024992798211055</v>
       </c>
       <c r="C80">
-        <v>684.0685176895026</v>
+        <v>956.3661992388932</v>
       </c>
       <c r="D80">
-        <v>948.3142977218135</v>
+        <v>1220.611979271204</v>
       </c>
       <c r="E80">
         <v>-66.5872712911646</v>
@@ -7838,45 +7838,45 @@
         <v>48.872</v>
       </c>
       <c r="M80">
-        <v>29.84758893189601</v>
+        <v>23.57456345917224</v>
       </c>
       <c r="N80">
-        <v>19.02441106810399</v>
+        <v>25.29743654082776</v>
       </c>
       <c r="O80">
-        <v>5.136590988388079</v>
+        <v>6.830307866023496</v>
       </c>
       <c r="P80">
-        <v>13.88782007971592</v>
+        <v>18.46712867480426</v>
       </c>
       <c r="Q80">
-        <v>60.74982007971591</v>
+        <v>65.32912867480425</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1924109830522265</v>
+        <v>0.1923509377091855</v>
       </c>
       <c r="T80">
         <v>2.684131890707225</v>
       </c>
       <c r="U80">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V80">
         <v>0.27</v>
       </c>
       <c r="W80">
-        <v>0.07780420728985867</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.637385187510873</v>
+        <v>2.073081865742256</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,13 +7887,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.103227419630259</v>
+        <v>0.09029617483712307</v>
       </c>
       <c r="C81">
-        <v>677.0149972571579</v>
+        <v>951.5072323667235</v>
       </c>
       <c r="D81">
-        <v>944.8511078027036</v>
+        <v>1219.343342912269</v>
       </c>
       <c r="E81">
         <v>-62.99694077792986</v>
@@ -7920,45 +7920,45 @@
         <v>48.872</v>
       </c>
       <c r="M81">
-        <v>30.23025032845877</v>
+        <v>23.87680145223855</v>
       </c>
       <c r="N81">
-        <v>18.64174967154123</v>
+        <v>24.99519854776145</v>
       </c>
       <c r="O81">
-        <v>5.033272411316132</v>
+        <v>6.748703607895593</v>
       </c>
       <c r="P81">
-        <v>13.6084772602251</v>
+        <v>18.24649493986586</v>
       </c>
       <c r="Q81">
-        <v>60.4704772602251</v>
+        <v>65.10849493986586</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1988671231965268</v>
+        <v>0.1988044337054035</v>
       </c>
       <c r="T81">
         <v>2.80232993625214</v>
       </c>
       <c r="U81">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V81">
         <v>0.27</v>
       </c>
       <c r="W81">
-        <v>0.07780420728985867</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y81">
-        <v>1.616658792732255</v>
+        <v>2.046840323137924</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,13 +7969,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1034371413029384</v>
+        <v>0.0903424216921356</v>
       </c>
       <c r="C82">
-        <v>669.9866795314783</v>
+        <v>946.6508998570118</v>
       </c>
       <c r="D82">
-        <v>941.4131205902587</v>
+        <v>1218.077340915792</v>
       </c>
       <c r="E82">
         <v>-59.40661026469513</v>
@@ -8002,45 +8002,45 @@
         <v>48.872</v>
       </c>
       <c r="M82">
-        <v>30.61291172502154</v>
+        <v>24.17903944530486</v>
       </c>
       <c r="N82">
-        <v>18.25908827497846</v>
+        <v>24.69296055469514</v>
       </c>
       <c r="O82">
-        <v>4.929953834244185</v>
+        <v>6.66709934976769</v>
       </c>
       <c r="P82">
-        <v>13.32913444073428</v>
+        <v>18.02586120492746</v>
       </c>
       <c r="Q82">
-        <v>60.19113444073427</v>
+        <v>64.88786120492745</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2059688773552573</v>
+        <v>0.2059032793012434</v>
       </c>
       <c r="T82">
         <v>2.932347786351547</v>
       </c>
       <c r="U82">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V82">
         <v>0.27</v>
       </c>
       <c r="W82">
-        <v>0.07780420728985867</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.596450557823102</v>
+        <v>2.0212548190987</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,13 +8051,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1036468629756178</v>
+        <v>0.09878512854714813</v>
       </c>
       <c r="C83">
-        <v>662.983290398008</v>
+        <v>748.9708275979547</v>
       </c>
       <c r="D83">
-        <v>938.0000619700231</v>
+        <v>1023.98759916997</v>
       </c>
       <c r="E83">
         <v>-55.81627975146034</v>
@@ -8084,37 +8084,37 @@
         <v>48.872</v>
       </c>
       <c r="M83">
-        <v>30.99557312158431</v>
+        <v>28.61087559469379</v>
       </c>
       <c r="N83">
-        <v>17.87642687841569</v>
+        <v>20.26112440530621</v>
       </c>
       <c r="O83">
-        <v>4.826635257172236</v>
+        <v>5.470503589432678</v>
       </c>
       <c r="P83">
-        <v>13.04979162124345</v>
+        <v>14.79062081587353</v>
       </c>
       <c r="Q83">
-        <v>59.91179162124345</v>
+        <v>61.65262081587353</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2138181845833277</v>
+        <v>0.2137493718019085</v>
       </c>
       <c r="T83">
         <v>3.076051725935101</v>
       </c>
       <c r="U83">
-        <v>0.1065811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V83">
         <v>0.27</v>
       </c>
       <c r="W83">
-        <v>0.07780420728985867</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.576741291677137</v>
+        <v>1.708161633790189</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1038565846482972</v>
+        <v>0.09893503540216067</v>
       </c>
       <c r="C84">
-        <v>656.0045597030977</v>
+        <v>742.4915790779547</v>
       </c>
       <c r="D84">
-        <v>934.6116617883476</v>
+        <v>1021.098681163205</v>
       </c>
       <c r="E84">
         <v>-52.22594923822561</v>
@@ -8166,37 +8166,37 @@
         <v>48.872</v>
       </c>
       <c r="M84">
-        <v>31.37823451814708</v>
+        <v>28.96409628104803</v>
       </c>
       <c r="N84">
-        <v>17.49376548185292</v>
+        <v>19.90790371895197</v>
       </c>
       <c r="O84">
-        <v>4.723316680100289</v>
+        <v>5.375134004117032</v>
       </c>
       <c r="P84">
-        <v>12.77044880175263</v>
+        <v>14.53276971483494</v>
       </c>
       <c r="Q84">
-        <v>59.63244880175263</v>
+        <v>61.39476971483494</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2225396370589616</v>
+        <v>0.2224672523582031</v>
       </c>
       <c r="T84">
         <v>3.235722769916829</v>
       </c>
       <c r="U84">
-        <v>0.1065811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V84">
         <v>0.27</v>
       </c>
       <c r="W84">
-        <v>0.07780420728985867</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.557512739339611</v>
+        <v>1.687330394353724</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,13 +8215,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1040663063209766</v>
+        <v>0.09908494225717319</v>
       </c>
       <c r="C85">
-        <v>649.0502211826254</v>
+        <v>736.0285853794651</v>
       </c>
       <c r="D85">
-        <v>931.2476537811101</v>
+        <v>1018.22601797795</v>
       </c>
       <c r="E85">
         <v>-48.63561872499082</v>
@@ -8248,37 +8248,37 @@
         <v>48.872</v>
       </c>
       <c r="M85">
-        <v>31.76089591470985</v>
+        <v>29.31731696740228</v>
       </c>
       <c r="N85">
-        <v>17.11110408529015</v>
+        <v>19.55468303259772</v>
       </c>
       <c r="O85">
-        <v>4.619998103028341</v>
+        <v>5.279764418801386</v>
       </c>
       <c r="P85">
-        <v>12.49110598226181</v>
+        <v>14.27491861379634</v>
       </c>
       <c r="Q85">
-        <v>59.35310598226181</v>
+        <v>61.13691861379633</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.232287142767023</v>
+        <v>0.2322107659211206</v>
       </c>
       <c r="T85">
         <v>3.41417864260229</v>
       </c>
       <c r="U85">
-        <v>0.1065811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V85">
         <v>0.27</v>
       </c>
       <c r="W85">
-        <v>0.07780420728985867</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.538747525612628</v>
+        <v>1.66700111249404</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,13 +8297,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.104276027993656</v>
+        <v>0.09923484911218572</v>
       </c>
       <c r="C86">
-        <v>642.1200123922454</v>
+        <v>729.5817096979913</v>
       </c>
       <c r="D86">
-        <v>927.9077755039649</v>
+        <v>1015.369472809711</v>
       </c>
       <c r="E86">
         <v>-45.04528821175609</v>
@@ -8330,37 +8330,37 @@
         <v>48.872</v>
       </c>
       <c r="M86">
-        <v>32.14355731127262</v>
+        <v>29.67053765375652</v>
       </c>
       <c r="N86">
-        <v>16.72844268872738</v>
+        <v>19.20146234624348</v>
       </c>
       <c r="O86">
-        <v>4.516679525956394</v>
+        <v>5.18439483348574</v>
       </c>
       <c r="P86">
-        <v>12.21176316277099</v>
+        <v>14.01706751275774</v>
       </c>
       <c r="Q86">
-        <v>59.07376316277099</v>
+        <v>60.87906751275774</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.243253086688592</v>
+        <v>0.2431722186794027</v>
       </c>
       <c r="T86">
         <v>3.61494149937343</v>
       </c>
       <c r="U86">
-        <v>0.1065811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V86">
         <v>0.27</v>
       </c>
       <c r="W86">
-        <v>0.07780420728985867</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.520429102688668</v>
+        <v>1.647155861154826</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,13 +8379,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1044857496663354</v>
+        <v>0.09938475596719826</v>
       </c>
       <c r="C87">
-        <v>635.2136746391382</v>
+        <v>723.1508167599164</v>
       </c>
       <c r="D87">
-        <v>924.5917682640924</v>
+        <v>1012.528910384871</v>
       </c>
       <c r="E87">
         <v>-41.45495769852135</v>
@@ -8412,37 +8412,37 @@
         <v>48.872</v>
       </c>
       <c r="M87">
-        <v>32.52621870783538</v>
+        <v>30.02375834011076</v>
       </c>
       <c r="N87">
-        <v>16.34578129216462</v>
+        <v>18.84824165988924</v>
       </c>
       <c r="O87">
-        <v>4.413360948884447</v>
+        <v>5.089025248170095</v>
       </c>
       <c r="P87">
-        <v>11.93242034328017</v>
+        <v>13.75921641171914</v>
       </c>
       <c r="Q87">
-        <v>58.79442034328017</v>
+        <v>60.62121641171914</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2556811564663702</v>
+        <v>0.2555951984721225</v>
       </c>
       <c r="T87">
         <v>3.842472737047391</v>
       </c>
       <c r="U87">
-        <v>0.1065811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V87">
         <v>0.27</v>
       </c>
       <c r="W87">
-        <v>0.07780420728985867</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.502541701480566</v>
+        <v>1.627777556905945</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,13 +8461,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1496907023427542</v>
+        <v>0.09953466282221077</v>
       </c>
       <c r="C88">
-        <v>229.3147044991188</v>
+        <v>716.7357728011493</v>
       </c>
       <c r="D88">
-        <v>522.2831286373078</v>
+        <v>1009.704196939338</v>
       </c>
       <c r="E88">
         <v>-37.86462718528662</v>
@@ -8494,45 +8494,45 @@
         <v>48.872</v>
       </c>
       <c r="M88">
-        <v>53.10233504303571</v>
+        <v>30.376979026465</v>
       </c>
       <c r="N88">
-        <v>-4.230335043035709</v>
+        <v>18.495020973535</v>
       </c>
       <c r="O88">
-        <v>-1.142190461619641</v>
+        <v>4.99365566285445</v>
       </c>
       <c r="P88">
-        <v>-3.088144581416067</v>
+        <v>13.50136531068055</v>
       </c>
       <c r="Q88">
-        <v>43.77385541858393</v>
+        <v>60.36336531068054</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2752833423558707</v>
+        <v>0.2697928896638022</v>
       </c>
       <c r="T88">
-        <v>4.201346616604128</v>
+        <v>4.102508437246205</v>
       </c>
       <c r="U88">
-        <v>0.1719811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V88">
-        <v>0.2484907676716292</v>
+        <v>0.27</v>
       </c>
       <c r="W88">
-        <v>0.1292453888522468</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.9203361765615896</v>
+        <v>1.608849910895411</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,13 +8543,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1509525134015194</v>
+        <v>0.09968456967722331</v>
       </c>
       <c r="C89">
-        <v>219.457071320425</v>
+        <v>710.3364455461235</v>
       </c>
       <c r="D89">
-        <v>516.0158259718487</v>
+        <v>1006.895200197547</v>
       </c>
       <c r="E89">
         <v>-34.27429667205183</v>
@@ -8576,45 +8576,45 @@
         <v>48.872</v>
       </c>
       <c r="M89">
-        <v>53.71980405516404</v>
+        <v>30.73019971281925</v>
       </c>
       <c r="N89">
-        <v>-4.84780405516404</v>
+        <v>18.14180028718075</v>
       </c>
       <c r="O89">
-        <v>-1.308907094894291</v>
+        <v>4.898286077538803</v>
       </c>
       <c r="P89">
-        <v>-3.538896960269749</v>
+        <v>13.24351420964195</v>
       </c>
       <c r="Q89">
-        <v>43.32310303973024</v>
+        <v>60.10551420964194</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2929359071524761</v>
+        <v>0.2861748410388173</v>
       </c>
       <c r="T89">
-        <v>4.524527125573677</v>
+        <v>4.402549629783296</v>
       </c>
       <c r="U89">
-        <v>0.1719811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V89">
-        <v>0.2456345519512656</v>
+        <v>0.27</v>
       </c>
       <c r="W89">
-        <v>0.1297366039904569</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.9097575998195022</v>
+        <v>1.59035738318397</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,13 +8625,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1522143244602846</v>
+        <v>0.09983447653223583</v>
       </c>
       <c r="C90">
-        <v>209.7480676021357</v>
+        <v>703.9527041871528</v>
       </c>
       <c r="D90">
-        <v>509.8971527667941</v>
+        <v>1004.101789351811</v>
       </c>
       <c r="E90">
         <v>-30.6839661588171</v>
@@ -8658,45 +8658,45 @@
         <v>48.872</v>
       </c>
       <c r="M90">
-        <v>54.33727306729236</v>
+        <v>31.08342039917349</v>
       </c>
       <c r="N90">
-        <v>-5.465273067292358</v>
+        <v>17.78857960082651</v>
       </c>
       <c r="O90">
-        <v>-1.475623728168937</v>
+        <v>4.802916492223158</v>
       </c>
       <c r="P90">
-        <v>-3.989649339123421</v>
+        <v>12.98566310860335</v>
       </c>
       <c r="Q90">
-        <v>42.87235066087657</v>
+        <v>59.84766310860334</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3135305660818493</v>
+        <v>0.3052871176430016</v>
       </c>
       <c r="T90">
-        <v>4.901571052704818</v>
+        <v>4.752597687743238</v>
       </c>
       <c r="U90">
-        <v>0.1719811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V90">
-        <v>0.2428432502245467</v>
+        <v>0.27</v>
       </c>
       <c r="W90">
-        <v>0.130216655148253</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.8994194452760989</v>
+        <v>1.572285140193243</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,13 +8707,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1534761355190498</v>
+        <v>0.09998438338724835</v>
       </c>
       <c r="C91">
-        <v>200.1824681670311</v>
+        <v>697.5844193641232</v>
       </c>
       <c r="D91">
-        <v>503.9218838449243</v>
+        <v>1001.323835042016</v>
       </c>
       <c r="E91">
         <v>-27.09363564558231</v>
@@ -8740,45 +8740,45 @@
         <v>48.872</v>
       </c>
       <c r="M91">
-        <v>54.95474207942068</v>
+        <v>31.43664108552774</v>
       </c>
       <c r="N91">
-        <v>-6.082742079420683</v>
+        <v>17.43535891447226</v>
       </c>
       <c r="O91">
-        <v>-1.642340361443585</v>
+        <v>4.707546906907511</v>
       </c>
       <c r="P91">
-        <v>-4.440401717977099</v>
+        <v>12.72781200756475</v>
       </c>
       <c r="Q91">
-        <v>42.4215982820229</v>
+        <v>59.58981200756475</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3378697084529264</v>
+        <v>0.3278743536297649</v>
       </c>
       <c r="T91">
-        <v>5.347168421132528</v>
+        <v>5.166290847150441</v>
       </c>
       <c r="U91">
-        <v>0.1719811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V91">
-        <v>0.2401146743793271</v>
+        <v>0.27</v>
       </c>
       <c r="W91">
-        <v>0.1306859186395819</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.8893136088123225</v>
+        <v>1.554619015022532</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,13 +8789,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1547379465778149</v>
+        <v>0.1001342902422609</v>
       </c>
       <c r="C92">
-        <v>190.7552899275072</v>
+        <v>691.2314631445261</v>
       </c>
       <c r="D92">
-        <v>498.0850361186352</v>
+        <v>998.561209335654</v>
       </c>
       <c r="E92">
         <v>-23.50330513234758</v>
@@ -8822,45 +8822,45 @@
         <v>48.872</v>
       </c>
       <c r="M92">
-        <v>55.572211091549</v>
+        <v>31.78986177188198</v>
       </c>
       <c r="N92">
-        <v>-6.700211091549001</v>
+        <v>17.08213822811802</v>
       </c>
       <c r="O92">
-        <v>-1.80905699471823</v>
+        <v>4.612177321591865</v>
       </c>
       <c r="P92">
-        <v>-4.89115409683077</v>
+        <v>12.46996090652615</v>
       </c>
       <c r="Q92">
-        <v>41.97084590316923</v>
+        <v>59.33196090652615</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3670766792982191</v>
+        <v>0.3549790368138808</v>
       </c>
       <c r="T92">
-        <v>5.881885263245781</v>
+        <v>5.662722638439084</v>
       </c>
       <c r="U92">
-        <v>0.1719811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V92">
-        <v>0.2374467335528901</v>
+        <v>0.27</v>
       </c>
       <c r="W92">
-        <v>0.1311447540533256</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.8794323464921856</v>
+        <v>1.537345470411171</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,13 +8871,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1559997576365802</v>
+        <v>0.1002841970972734</v>
       </c>
       <c r="C93">
-        <v>181.4617780256835</v>
+        <v>684.8937090038171</v>
       </c>
       <c r="D93">
-        <v>492.3818547300462</v>
+        <v>995.8137857081798</v>
       </c>
       <c r="E93">
         <v>-19.91297461911279</v>
@@ -8904,45 +8904,45 @@
         <v>48.872</v>
       </c>
       <c r="M93">
-        <v>56.18968010367733</v>
+        <v>32.14308245823623</v>
       </c>
       <c r="N93">
-        <v>-7.317680103677333</v>
+        <v>16.72891754176377</v>
       </c>
       <c r="O93">
-        <v>-1.97577362799288</v>
+        <v>4.516807736276219</v>
       </c>
       <c r="P93">
-        <v>-5.341906475684453</v>
+        <v>12.21210980548755</v>
       </c>
       <c r="Q93">
-        <v>41.52009352431554</v>
+        <v>59.07410980548755</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4027740881091324</v>
+        <v>0.3881069829278002</v>
       </c>
       <c r="T93">
-        <v>6.535428070273091</v>
+        <v>6.269472605569649</v>
       </c>
       <c r="U93">
-        <v>0.1719811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V93">
-        <v>0.2348374287885726</v>
+        <v>0.27</v>
       </c>
       <c r="W93">
-        <v>0.1315935051722618</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.8697682547724911</v>
+        <v>1.520451564142916</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,13 +8953,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1572615686953453</v>
+        <v>0.1004341039522859</v>
       </c>
       <c r="C94">
-        <v>172.2973929149234</v>
+        <v>678.5710318061008</v>
       </c>
       <c r="D94">
-        <v>486.8078001325209</v>
+        <v>993.0814390236983</v>
       </c>
       <c r="E94">
         <v>-16.32264410587806</v>
@@ -8986,45 +8986,45 @@
         <v>48.872</v>
       </c>
       <c r="M94">
-        <v>56.80714911580565</v>
+        <v>32.49630314459047</v>
       </c>
       <c r="N94">
-        <v>-7.93514911580565</v>
+        <v>16.37569685540953</v>
       </c>
       <c r="O94">
-        <v>-2.142490261267526</v>
+        <v>4.421438150960573</v>
       </c>
       <c r="P94">
-        <v>-5.792658854538125</v>
+        <v>11.95425870444896</v>
       </c>
       <c r="Q94">
-        <v>41.06934114546187</v>
+        <v>58.81625870444896</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.447395849122774</v>
+        <v>0.4295169155701996</v>
       </c>
       <c r="T94">
-        <v>7.352356579057228</v>
+        <v>7.027910064482855</v>
       </c>
       <c r="U94">
-        <v>0.1719811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V94">
-        <v>0.2322848480408708</v>
+        <v>0.27</v>
       </c>
       <c r="W94">
-        <v>0.1320325008320907</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.860314252003225</v>
+        <v>1.50392491670658</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,13 +9035,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1585233797541105</v>
+        <v>0.1419413054589383</v>
       </c>
       <c r="C95">
-        <v>163.2577983090019</v>
+        <v>246.2364565033265</v>
       </c>
       <c r="D95">
-        <v>481.3585360398342</v>
+        <v>564.3371942341588</v>
       </c>
       <c r="E95">
         <v>-12.73231359264327</v>
@@ -9068,37 +9068,37 @@
         <v>48.872</v>
       </c>
       <c r="M95">
-        <v>57.42461812793398</v>
+        <v>51.81508573405599</v>
       </c>
       <c r="N95">
-        <v>-8.552618127933975</v>
+        <v>-2.943085734055991</v>
       </c>
       <c r="O95">
-        <v>-2.309206894542173</v>
+        <v>-0.7946331481951177</v>
       </c>
       <c r="P95">
-        <v>-6.243411233391802</v>
+        <v>-2.148452585860873</v>
       </c>
       <c r="Q95">
-        <v>40.61858876660819</v>
+        <v>44.71354741413912</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5047666847117418</v>
+        <v>0.4910799090664245</v>
       </c>
       <c r="T95">
-        <v>8.402693233208263</v>
+        <v>8.155457910396514</v>
       </c>
       <c r="U95">
-        <v>0.1719811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V95">
-        <v>0.2297871615027969</v>
+        <v>0.2546640580260039</v>
       </c>
       <c r="W95">
-        <v>0.1324620557250415</v>
+        <v>0.1156620557250415</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8510635611214699</v>
+        <v>0.9432002149111254</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,13 +9117,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1597851908128757</v>
+        <v>0.1430351165177035</v>
       </c>
       <c r="C96">
-        <v>154.3388499316868</v>
+        <v>236.2978200895844</v>
       </c>
       <c r="D96">
-        <v>476.0299181757538</v>
+        <v>557.9888883336514</v>
       </c>
       <c r="E96">
         <v>-9.141983079408533</v>
@@ -9150,37 +9150,37 @@
         <v>48.872</v>
       </c>
       <c r="M96">
-        <v>58.04208714006229</v>
+        <v>52.37223719356196</v>
       </c>
       <c r="N96">
-        <v>-9.170087140062293</v>
+        <v>-3.500237193561965</v>
       </c>
       <c r="O96">
-        <v>-2.475923527816819</v>
+        <v>-0.9450640422617306</v>
       </c>
       <c r="P96">
-        <v>-6.694163612245474</v>
+        <v>-2.555173151300234</v>
       </c>
       <c r="Q96">
-        <v>40.16783638775452</v>
+        <v>44.30682684869976</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5812611321636989</v>
+        <v>0.5652932272441621</v>
       </c>
       <c r="T96">
-        <v>9.803142105409643</v>
+        <v>9.514700895462603</v>
       </c>
       <c r="U96">
-        <v>0.1719811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V96">
-        <v>0.2273426172314905</v>
+        <v>0.2519548659193443</v>
       </c>
       <c r="W96">
-        <v>0.1328824711521849</v>
+        <v>0.1160824711521849</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8420096934499649</v>
+        <v>0.9331661700716455</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,13 +9199,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1610470018716409</v>
+        <v>0.1441289275764687</v>
       </c>
       <c r="C97">
-        <v>145.5365850053882</v>
+        <v>226.5004207943498</v>
       </c>
       <c r="D97">
-        <v>470.8179837626899</v>
+        <v>551.7818195516516</v>
       </c>
       <c r="E97">
         <v>-5.5516525661738</v>
@@ -9232,37 +9232,37 @@
         <v>48.872</v>
       </c>
       <c r="M97">
-        <v>58.65955615219061</v>
+        <v>52.92938865306794</v>
       </c>
       <c r="N97">
-        <v>-9.787556152190611</v>
+        <v>-4.057388653067939</v>
       </c>
       <c r="O97">
-        <v>-2.642640161091465</v>
+        <v>-1.095494936328343</v>
       </c>
       <c r="P97">
-        <v>-7.144915991099145</v>
+        <v>-2.961893716739596</v>
       </c>
       <c r="Q97">
-        <v>39.71708400890085</v>
+        <v>43.9001062832604</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.688353358596439</v>
+        <v>0.6691918726929947</v>
       </c>
       <c r="T97">
-        <v>11.76377052649158</v>
+        <v>11.41764107455513</v>
       </c>
       <c r="U97">
-        <v>0.1719811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V97">
-        <v>0.2249495370501065</v>
+        <v>0.2493027094359828</v>
       </c>
       <c r="W97">
-        <v>0.1332940357282305</v>
+        <v>0.1164940357282305</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8331464335189127</v>
+        <v>0.9233433682814177</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,13 +9281,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1623088129304061</v>
+        <v>0.1452227386352339</v>
       </c>
       <c r="C98">
-        <v>136.8472124228454</v>
+        <v>216.8395971068576</v>
       </c>
       <c r="D98">
-        <v>465.7189416933818</v>
+        <v>545.7113263773941</v>
       </c>
       <c r="E98">
         <v>-1.961322052939067</v>
@@ -9314,37 +9314,37 @@
         <v>48.872</v>
       </c>
       <c r="M98">
-        <v>59.27702516431894</v>
+        <v>53.48654011257392</v>
       </c>
       <c r="N98">
-        <v>-10.40502516431894</v>
+        <v>-4.61454011257392</v>
       </c>
       <c r="O98">
-        <v>-2.809356794366113</v>
+        <v>-1.245925830394959</v>
       </c>
       <c r="P98">
-        <v>-7.595668369952823</v>
+        <v>-3.368614282178961</v>
       </c>
       <c r="Q98">
-        <v>39.26633163004717</v>
+        <v>43.49338571782103</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8489916982455469</v>
+        <v>0.8250398408662417</v>
       </c>
       <c r="T98">
-        <v>14.70471315811444</v>
+        <v>14.27205134319388</v>
       </c>
       <c r="U98">
-        <v>0.1719811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V98">
-        <v>0.2226063127058345</v>
+        <v>0.2467058062126913</v>
       </c>
       <c r="W98">
-        <v>0.1336970260422752</v>
+        <v>0.1168970260422752</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.824467824836424</v>
+        <v>0.9137252081951529</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,13 +9363,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1635706239891713</v>
+        <v>0.146316549693999</v>
       </c>
       <c r="C99">
-        <v>128.2671035506273</v>
+        <v>207.3108904207223</v>
       </c>
       <c r="D99">
-        <v>460.7291633343985</v>
+        <v>539.7729502044936</v>
       </c>
       <c r="E99">
         <v>1.629008460295722</v>
@@ -9396,37 +9396,37 @@
         <v>48.872</v>
       </c>
       <c r="M99">
-        <v>59.89449417644726</v>
+        <v>54.0436915720799</v>
       </c>
       <c r="N99">
-        <v>-11.02249417644726</v>
+        <v>-5.171691572079901</v>
       </c>
       <c r="O99">
-        <v>-2.976073427640761</v>
+        <v>-1.396356724461573</v>
       </c>
       <c r="P99">
-        <v>-8.046420748806501</v>
+        <v>-3.775334847618327</v>
       </c>
       <c r="Q99">
-        <v>38.8155792511935</v>
+        <v>43.08666515238167</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.116722264327396</v>
+        <v>1.084786454488322</v>
       </c>
       <c r="T99">
-        <v>19.60628421081925</v>
+        <v>19.02940179092517</v>
       </c>
       <c r="U99">
-        <v>0.1719811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V99">
-        <v>0.2203114022655681</v>
+        <v>0.2441624473857563</v>
       </c>
       <c r="W99">
-        <v>0.1340917072776798</v>
+        <v>0.1172917072776797</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8159681565391412</v>
+        <v>0.9043053606879863</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,13 +9445,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1648324350479365</v>
+        <v>0.1474103607527642</v>
       </c>
       <c r="C100">
-        <v>119.7927836175604</v>
+        <v>197.9100341128537</v>
       </c>
       <c r="D100">
-        <v>455.8451739145663</v>
+        <v>533.9624244098598</v>
       </c>
       <c r="E100">
         <v>5.219338973530455</v>
@@ -9478,37 +9478,37 @@
         <v>48.872</v>
       </c>
       <c r="M100">
-        <v>60.51196318857558</v>
+        <v>54.60084303158587</v>
       </c>
       <c r="N100">
-        <v>-11.63996318857558</v>
+        <v>-5.728843031585875</v>
       </c>
       <c r="O100">
-        <v>-3.142790060915406</v>
+        <v>-1.546787618528186</v>
       </c>
       <c r="P100">
-        <v>-8.497173127660172</v>
+        <v>-4.182055413057689</v>
       </c>
       <c r="Q100">
-        <v>38.36482687233982</v>
+        <v>42.67994458694231</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.652183396491094</v>
+        <v>1.604279681732484</v>
       </c>
       <c r="T100">
-        <v>29.40942631622888</v>
+        <v>28.54410268638776</v>
       </c>
       <c r="U100">
-        <v>0.1719811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V100">
-        <v>0.218063326732246</v>
+        <v>0.2416709938410037</v>
       </c>
       <c r="W100">
-        <v>0.1344783337939944</v>
+        <v>0.1176783337939944</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8076419508601704</v>
+        <v>0.8950777549666804</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9527,13 +9527,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2198054094421459</v>
+        <v>0.1485041718115294</v>
       </c>
       <c r="C101">
-        <v>-27.81125976625725</v>
+        <v>188.6329433202375</v>
       </c>
       <c r="D101">
-        <v>311.8314610439835</v>
+        <v>528.2756641304783</v>
       </c>
       <c r="E101">
         <v>8.809669486765245</v>
@@ -9560,45 +9560,45 @@
         <v>48.872</v>
       </c>
       <c r="M101">
-        <v>79.68354222699847</v>
+        <v>55.15799449109186</v>
       </c>
       <c r="N101">
-        <v>-30.81154222699847</v>
+        <v>-6.285994491091856</v>
       </c>
       <c r="O101">
-        <v>-8.319116401289588</v>
+        <v>-1.697218512594801</v>
       </c>
       <c r="P101">
-        <v>-22.49242582570888</v>
+        <v>-4.588775978497054</v>
       </c>
       <c r="Q101">
-        <v>24.36957417429111</v>
+        <v>42.27322402150294</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.461883126526614</v>
+        <v>3.162759363464967</v>
       </c>
       <c r="T101">
-        <v>62.54113757596611</v>
+        <v>57.08820537277551</v>
       </c>
       <c r="U101">
-        <v>0.2241811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V101">
-        <v>0.1655980599156786</v>
+        <v>0.2392298726910946</v>
       </c>
       <c r="W101">
-        <v>0.1870571496736159</v>
+        <v>0.1180571496736159</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.6133261478358467</v>
+        <v>0.8860365655225725</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/chile/chile_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_hotel_gaming.xlsx
@@ -1269,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1406,22 +1406,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08664267329113351</v>
+        <v>0.08650277014614603</v>
       </c>
       <c r="C2">
-        <v>1344.217319453104</v>
+        <v>1345.193011355051</v>
       </c>
       <c r="D2">
-        <v>1328.417319453104</v>
+        <v>1332.983341868286</v>
       </c>
       <c r="E2">
-        <v>-346.6330513234755</v>
+        <v>-343.0427208102408</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.590330513234755</v>
       </c>
       <c r="G2">
         <v>15.8</v>
@@ -1442,28 +1442,28 @@
         <v>48.872</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2106845649788245</v>
       </c>
       <c r="N2">
-        <v>48.872</v>
+        <v>48.66131543502117</v>
       </c>
       <c r="O2">
-        <v>13.19544</v>
+        <v>13.13855516745572</v>
       </c>
       <c r="P2">
-        <v>35.67655999999999</v>
+        <v>35.52276026756546</v>
       </c>
       <c r="Q2">
-        <v>82.53855999999999</v>
+        <v>82.38476026756545</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08664267329113351</v>
+        <v>0.08694383643762368</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815169</v>
+        <v>0.753563813473613</v>
       </c>
       <c r="U2">
         <v>0.05868110587651873</v>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>231.967633722537</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1488,22 +1488,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08650277014614603</v>
+        <v>0.08636286700115858</v>
       </c>
       <c r="C3">
-        <v>1345.193011355051</v>
+        <v>1346.200200088617</v>
       </c>
       <c r="D3">
-        <v>1332.983341868286</v>
+        <v>1337.580861115087</v>
       </c>
       <c r="E3">
-        <v>-343.0427208102408</v>
+        <v>-339.452390297006</v>
       </c>
       <c r="F3">
-        <v>3.590330513234755</v>
+        <v>7.18066102646951</v>
       </c>
       <c r="G3">
         <v>15.8</v>
@@ -1524,28 +1524,28 @@
         <v>48.872</v>
       </c>
       <c r="M3">
-        <v>0.2106845649788245</v>
+        <v>0.421369129957649</v>
       </c>
       <c r="N3">
-        <v>48.66131543502117</v>
+        <v>48.45063087004235</v>
       </c>
       <c r="O3">
-        <v>13.13855516745572</v>
+        <v>13.08167033491144</v>
       </c>
       <c r="P3">
-        <v>35.52276026756546</v>
+        <v>35.36896053513092</v>
       </c>
       <c r="Q3">
-        <v>82.38476026756545</v>
+        <v>82.23096053513092</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08694383643762368</v>
+        <v>0.08725114577077694</v>
       </c>
       <c r="T3">
-        <v>0.753563813473613</v>
+        <v>0.7591922918328947</v>
       </c>
       <c r="U3">
         <v>0.05868110587651873</v>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>231.967633722537</v>
+        <v>115.9838168612685</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1570,22 +1570,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08636286700115858</v>
+        <v>0.08622296385617109</v>
       </c>
       <c r="C4">
-        <v>1346.200200088617</v>
+        <v>1347.239212683694</v>
       </c>
       <c r="D4">
-        <v>1337.580861115087</v>
+        <v>1342.210204223398</v>
       </c>
       <c r="E4">
-        <v>-339.452390297006</v>
+        <v>-335.8620597837713</v>
       </c>
       <c r="F4">
-        <v>7.18066102646951</v>
+        <v>10.77099153970426</v>
       </c>
       <c r="G4">
         <v>15.8</v>
@@ -1606,28 +1606,28 @@
         <v>48.872</v>
       </c>
       <c r="M4">
-        <v>0.421369129957649</v>
+        <v>0.6320536949364735</v>
       </c>
       <c r="N4">
-        <v>48.45063087004235</v>
+        <v>48.23994630506353</v>
       </c>
       <c r="O4">
-        <v>13.08167033491144</v>
+        <v>13.02478550236715</v>
       </c>
       <c r="P4">
-        <v>35.36896053513092</v>
+        <v>35.21516080269637</v>
       </c>
       <c r="Q4">
-        <v>82.23096053513092</v>
+        <v>82.07716080269637</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08725114577077694</v>
+        <v>0.08756479137884055</v>
       </c>
       <c r="T4">
-        <v>0.7591922918328947</v>
+        <v>0.7649368212923677</v>
       </c>
       <c r="U4">
         <v>0.05868110587651873</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>115.9838168612685</v>
+        <v>77.32254457417899</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1652,22 +1652,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08622296385617109</v>
+        <v>0.08608306071118363</v>
       </c>
       <c r="C5">
-        <v>1347.239212683694</v>
+        <v>1348.310380713269</v>
       </c>
       <c r="D5">
-        <v>1342.210204223398</v>
+        <v>1346.871702766208</v>
       </c>
       <c r="E5">
-        <v>-335.8620597837713</v>
+        <v>-332.2717292705365</v>
       </c>
       <c r="F5">
-        <v>10.77099153970426</v>
+        <v>14.36132205293902</v>
       </c>
       <c r="G5">
         <v>15.8</v>
@@ -1688,28 +1688,28 @@
         <v>48.872</v>
       </c>
       <c r="M5">
-        <v>0.6320536949364735</v>
+        <v>0.8427382599152979</v>
       </c>
       <c r="N5">
-        <v>48.23994630506353</v>
+        <v>48.0292617400847</v>
       </c>
       <c r="O5">
-        <v>13.02478550236715</v>
+        <v>12.96790066982287</v>
       </c>
       <c r="P5">
-        <v>35.21516080269637</v>
+        <v>35.06136107026183</v>
       </c>
       <c r="Q5">
-        <v>82.07716080269637</v>
+        <v>81.92336107026182</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08756479137884055</v>
+        <v>0.08788497127040551</v>
       </c>
       <c r="T5">
-        <v>0.7649368212923677</v>
+        <v>0.7708010284489132</v>
       </c>
       <c r="U5">
         <v>0.05868110587651873</v>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>77.32254457417899</v>
+        <v>57.99190843063424</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1734,22 +1734,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08608306071118363</v>
+        <v>0.08594315756619614</v>
       </c>
       <c r="C6">
-        <v>1348.310380713269</v>
+        <v>1349.414040372604</v>
       </c>
       <c r="D6">
-        <v>1346.871702766208</v>
+        <v>1351.565692938778</v>
       </c>
       <c r="E6">
-        <v>-332.2717292705365</v>
+        <v>-328.6813987573017</v>
       </c>
       <c r="F6">
-        <v>14.36132205293902</v>
+        <v>17.95165256617377</v>
       </c>
       <c r="G6">
         <v>15.8</v>
@@ -1770,28 +1770,28 @@
         <v>48.872</v>
       </c>
       <c r="M6">
-        <v>0.8427382599152979</v>
+        <v>1.053422824894122</v>
       </c>
       <c r="N6">
-        <v>48.0292617400847</v>
+        <v>47.81857717510588</v>
       </c>
       <c r="O6">
-        <v>12.96790066982287</v>
+        <v>12.91101583727859</v>
       </c>
       <c r="P6">
-        <v>35.06136107026183</v>
+        <v>34.90756133782729</v>
       </c>
       <c r="Q6">
-        <v>81.92336107026182</v>
+        <v>81.76956133782728</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08788497127040551</v>
+        <v>0.08821189179126654</v>
       </c>
       <c r="T6">
-        <v>0.7708010284489132</v>
+        <v>0.7767886925982278</v>
       </c>
       <c r="U6">
         <v>0.05868110587651873</v>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>57.99190843063424</v>
+        <v>46.3935267445074</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1816,22 +1816,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08594315756619614</v>
+        <v>0.08580325442120866</v>
       </c>
       <c r="C7">
-        <v>1349.414040372604</v>
+        <v>1350.550532560052</v>
       </c>
       <c r="D7">
-        <v>1351.565692938778</v>
+        <v>1356.29251563946</v>
       </c>
       <c r="E7">
-        <v>-328.6813987573017</v>
+        <v>-325.091068244067</v>
       </c>
       <c r="F7">
-        <v>17.95165256617377</v>
+        <v>21.54198307940853</v>
       </c>
       <c r="G7">
         <v>15.8</v>
@@ -1852,28 +1852,28 @@
         <v>48.872</v>
       </c>
       <c r="M7">
-        <v>1.053422824894122</v>
+        <v>1.264107389872947</v>
       </c>
       <c r="N7">
-        <v>47.81857717510588</v>
+        <v>47.60789261012705</v>
       </c>
       <c r="O7">
-        <v>12.91101583727859</v>
+        <v>12.8541310047343</v>
       </c>
       <c r="P7">
-        <v>34.90756133782729</v>
+        <v>34.75376160539275</v>
       </c>
       <c r="Q7">
-        <v>81.76956133782728</v>
+        <v>81.61576160539275</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08821189179126654</v>
+        <v>0.08854576806789058</v>
       </c>
       <c r="T7">
-        <v>0.7767886925982278</v>
+        <v>0.7829037538571025</v>
       </c>
       <c r="U7">
         <v>0.05868110587651873</v>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.3935267445074</v>
+        <v>38.6612722870895</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1898,22 +1898,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08580325442120866</v>
+        <v>0.08566335127622121</v>
       </c>
       <c r="C8">
-        <v>1350.550532560052</v>
+        <v>1351.720202959587</v>
       </c>
       <c r="D8">
-        <v>1356.29251563946</v>
+        <v>1361.05251655223</v>
       </c>
       <c r="E8">
-        <v>-325.091068244067</v>
+        <v>-321.5007377308322</v>
       </c>
       <c r="F8">
-        <v>21.54198307940853</v>
+        <v>25.13231359264328</v>
       </c>
       <c r="G8">
         <v>15.8</v>
@@ -1934,28 +1934,28 @@
         <v>48.872</v>
       </c>
       <c r="M8">
-        <v>1.264107389872947</v>
+        <v>1.474791954851771</v>
       </c>
       <c r="N8">
-        <v>47.60789261012705</v>
+        <v>47.39720804514823</v>
       </c>
       <c r="O8">
-        <v>12.8541310047343</v>
+        <v>12.79724617219002</v>
       </c>
       <c r="P8">
-        <v>34.75376160539275</v>
+        <v>34.5999618729582</v>
       </c>
       <c r="Q8">
-        <v>81.61576160539275</v>
+        <v>81.4619618729582</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08854576806789058</v>
+        <v>0.08888682447949581</v>
       </c>
       <c r="T8">
-        <v>0.7829037538571025</v>
+        <v>0.7891503218097164</v>
       </c>
       <c r="U8">
         <v>0.05868110587651873</v>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.6612722870895</v>
+        <v>33.13823338893386</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1980,22 +1980,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0856633512762212</v>
+        <v>0.08552344813123373</v>
       </c>
       <c r="C9">
-        <v>1351.720202959588</v>
+        <v>1352.923402125088</v>
       </c>
       <c r="D9">
-        <v>1361.052516552231</v>
+        <v>1365.846046230966</v>
       </c>
       <c r="E9">
-        <v>-321.5007377308322</v>
+        <v>-317.9104072175975</v>
       </c>
       <c r="F9">
-        <v>25.13231359264329</v>
+        <v>28.72264410587804</v>
       </c>
       <c r="G9">
         <v>15.8</v>
@@ -2016,28 +2016,28 @@
         <v>48.872</v>
       </c>
       <c r="M9">
-        <v>1.474791954851771</v>
+        <v>1.685476519830596</v>
       </c>
       <c r="N9">
-        <v>47.39720804514823</v>
+        <v>47.18652348016941</v>
       </c>
       <c r="O9">
-        <v>12.79724617219002</v>
+        <v>12.74036133964574</v>
       </c>
       <c r="P9">
-        <v>34.5999618729582</v>
+        <v>34.44616214052367</v>
       </c>
       <c r="Q9">
-        <v>81.4619618729582</v>
+        <v>81.30816214052366</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08888682447949581</v>
+        <v>0.08923529516091852</v>
       </c>
       <c r="T9">
-        <v>0.7891503218097164</v>
+        <v>0.7955326847178219</v>
       </c>
       <c r="U9">
         <v>0.05868110587651873</v>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.13823338893386</v>
+        <v>28.99595421531712</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2062,22 +2062,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08552344813123373</v>
+        <v>0.08538354498624626</v>
       </c>
       <c r="C10">
-        <v>1352.923402125088</v>
+        <v>1354.160485566385</v>
       </c>
       <c r="D10">
-        <v>1365.846046230966</v>
+        <v>1370.673460185497</v>
       </c>
       <c r="E10">
-        <v>-317.9104072175975</v>
+        <v>-314.3200767043627</v>
       </c>
       <c r="F10">
-        <v>28.72264410587804</v>
+        <v>32.31297461911279</v>
       </c>
       <c r="G10">
         <v>15.8</v>
@@ -2098,28 +2098,28 @@
         <v>48.872</v>
       </c>
       <c r="M10">
-        <v>1.685476519830596</v>
+        <v>1.89616108480942</v>
       </c>
       <c r="N10">
-        <v>47.18652348016941</v>
+        <v>46.97583891519058</v>
       </c>
       <c r="O10">
-        <v>12.74036133964574</v>
+        <v>12.68347650710146</v>
       </c>
       <c r="P10">
-        <v>34.44616214052367</v>
+        <v>34.29236240808912</v>
       </c>
       <c r="Q10">
-        <v>81.30816214052366</v>
+        <v>81.15436240808911</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08923529516091852</v>
+        <v>0.08959142453863624</v>
       </c>
       <c r="T10">
-        <v>0.7955326847178219</v>
+        <v>0.8020553193381935</v>
       </c>
       <c r="U10">
         <v>0.05868110587651873</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.99595421531712</v>
+        <v>25.77418152472633</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2144,22 +2144,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08538354498624626</v>
+        <v>0.08524364184125878</v>
       </c>
       <c r="C11">
-        <v>1354.160485566385</v>
+        <v>1355.431813837158</v>
       </c>
       <c r="D11">
-        <v>1370.673460185497</v>
+        <v>1375.535118969505</v>
       </c>
       <c r="E11">
-        <v>-314.3200767043627</v>
+        <v>-310.729746191128</v>
       </c>
       <c r="F11">
-        <v>32.31297461911279</v>
+        <v>35.90330513234755</v>
       </c>
       <c r="G11">
         <v>15.8</v>
@@ -2180,28 +2180,28 @@
         <v>48.872</v>
       </c>
       <c r="M11">
-        <v>1.89616108480942</v>
+        <v>2.106845649788245</v>
       </c>
       <c r="N11">
-        <v>46.97583891519058</v>
+        <v>46.76515435021175</v>
       </c>
       <c r="O11">
-        <v>12.68347650710146</v>
+        <v>12.62659167455717</v>
       </c>
       <c r="P11">
-        <v>34.29236240808912</v>
+        <v>34.13856267565458</v>
       </c>
       <c r="Q11">
-        <v>81.15436240808911</v>
+        <v>81.00056267565458</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08959142453863624</v>
+        <v>0.08995546790252545</v>
       </c>
       <c r="T11">
-        <v>0.8020553193381935</v>
+        <v>0.8087229013945734</v>
       </c>
       <c r="U11">
         <v>0.05868110587651873</v>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.77418152472633</v>
+        <v>23.1967633722537</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2226,22 +2226,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08524364184125878</v>
+        <v>0.0851037386962713</v>
       </c>
       <c r="C12">
-        <v>1355.431813837158</v>
+        <v>1356.737752624706</v>
       </c>
       <c r="D12">
-        <v>1375.535118969505</v>
+        <v>1380.431388270288</v>
       </c>
       <c r="E12">
-        <v>-310.729746191128</v>
+        <v>-307.1394156778932</v>
       </c>
       <c r="F12">
-        <v>35.90330513234755</v>
+        <v>39.4936356455823</v>
       </c>
       <c r="G12">
         <v>15.8</v>
@@ -2262,28 +2262,28 @@
         <v>48.872</v>
       </c>
       <c r="M12">
-        <v>2.106845649788245</v>
+        <v>2.317530214767069</v>
       </c>
       <c r="N12">
-        <v>46.76515435021175</v>
+        <v>46.55446978523293</v>
       </c>
       <c r="O12">
-        <v>12.62659167455717</v>
+        <v>12.56970684201289</v>
       </c>
       <c r="P12">
-        <v>34.13856267565458</v>
+        <v>33.98476294322004</v>
       </c>
       <c r="Q12">
-        <v>81.00056267565458</v>
+        <v>80.84676294322003</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08995546790252545</v>
+        <v>0.090327692016165</v>
       </c>
       <c r="T12">
-        <v>0.8087229013945734</v>
+        <v>0.8155403167555909</v>
       </c>
       <c r="U12">
         <v>0.05868110587651873</v>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.1967633722537</v>
+        <v>21.08796670204882</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2308,22 +2308,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0851037386962713</v>
+        <v>0.08496383555128383</v>
       </c>
       <c r="C13">
-        <v>1356.737752624706</v>
+        <v>1358.078672841639</v>
       </c>
       <c r="D13">
-        <v>1380.431388270288</v>
+        <v>1385.362639000456</v>
       </c>
       <c r="E13">
-        <v>-307.1394156778932</v>
+        <v>-303.5490851646584</v>
       </c>
       <c r="F13">
-        <v>39.4936356455823</v>
+        <v>43.08396615881706</v>
       </c>
       <c r="G13">
         <v>15.8</v>
@@ -2344,28 +2344,28 @@
         <v>48.872</v>
       </c>
       <c r="M13">
-        <v>2.317530214767069</v>
+        <v>2.528214779745894</v>
       </c>
       <c r="N13">
-        <v>46.55446978523293</v>
+        <v>46.34378522025411</v>
       </c>
       <c r="O13">
-        <v>12.56970684201289</v>
+        <v>12.51282200946861</v>
       </c>
       <c r="P13">
-        <v>33.98476294322004</v>
+        <v>33.8309632107855</v>
       </c>
       <c r="Q13">
-        <v>80.84676294322003</v>
+        <v>80.69296321078549</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.090327692016165</v>
+        <v>0.0907083757687509</v>
       </c>
       <c r="T13">
-        <v>0.8155403167555909</v>
+        <v>0.8225126733748135</v>
       </c>
       <c r="U13">
         <v>0.05868110587651873</v>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.08796670204882</v>
+        <v>19.33063614354475</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2390,22 +2390,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08496383555128383</v>
+        <v>0.08482393240629635</v>
       </c>
       <c r="C14">
-        <v>1358.078672841639</v>
+        <v>1359.454950719542</v>
       </c>
       <c r="D14">
-        <v>1385.362639000456</v>
+        <v>1390.329247391594</v>
       </c>
       <c r="E14">
-        <v>-303.5490851646584</v>
+        <v>-299.9587546514237</v>
       </c>
       <c r="F14">
-        <v>43.08396615881706</v>
+        <v>46.67429667205182</v>
       </c>
       <c r="G14">
         <v>15.8</v>
@@ -2426,28 +2426,28 @@
         <v>48.872</v>
       </c>
       <c r="M14">
-        <v>2.528214779745894</v>
+        <v>2.738899344724719</v>
       </c>
       <c r="N14">
-        <v>46.34378522025411</v>
+        <v>46.13310065527528</v>
       </c>
       <c r="O14">
-        <v>12.51282200946861</v>
+        <v>12.45593717692433</v>
       </c>
       <c r="P14">
-        <v>33.8309632107855</v>
+        <v>33.67716347835095</v>
       </c>
       <c r="Q14">
-        <v>80.69296321078549</v>
+        <v>80.53916347835094</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0907083757687509</v>
+        <v>0.09109781087197096</v>
       </c>
       <c r="T14">
-        <v>0.8225126733748135</v>
+        <v>0.8296453140542479</v>
       </c>
       <c r="U14">
         <v>0.05868110587651873</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.33063614354475</v>
+        <v>17.84366413250284</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2472,22 +2472,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08482393240629635</v>
+        <v>0.08468402926130889</v>
       </c>
       <c r="C15">
-        <v>1359.454950719542</v>
+        <v>1360.866967904664</v>
       </c>
       <c r="D15">
-        <v>1390.329247391594</v>
+        <v>1395.331595089951</v>
       </c>
       <c r="E15">
-        <v>-299.9587546514237</v>
+        <v>-296.368424138189</v>
       </c>
       <c r="F15">
-        <v>46.67429667205182</v>
+        <v>50.26462718528657</v>
       </c>
       <c r="G15">
         <v>15.8</v>
@@ -2508,28 +2508,28 @@
         <v>48.872</v>
       </c>
       <c r="M15">
-        <v>2.738899344724719</v>
+        <v>2.949583909703543</v>
       </c>
       <c r="N15">
-        <v>46.13310065527528</v>
+        <v>45.92241609029646</v>
       </c>
       <c r="O15">
-        <v>12.45593717692433</v>
+        <v>12.39905234438004</v>
       </c>
       <c r="P15">
-        <v>33.67716347835095</v>
+        <v>33.52336374591641</v>
       </c>
       <c r="Q15">
-        <v>80.53916347835094</v>
+        <v>80.38536374591641</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09109781087197096</v>
+        <v>0.09149630260549846</v>
       </c>
       <c r="T15">
-        <v>0.8296453140542479</v>
+        <v>0.8369438300983204</v>
       </c>
       <c r="U15">
         <v>0.05868110587651873</v>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.84366413250284</v>
+        <v>16.56911669446693</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2554,22 +2554,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08468402926130889</v>
+        <v>0.08454412611632142</v>
       </c>
       <c r="C16">
-        <v>1360.866967904664</v>
+        <v>1362.315111555678</v>
       </c>
       <c r="D16">
-        <v>1395.331595089951</v>
+        <v>1400.370069254199</v>
       </c>
       <c r="E16">
-        <v>-296.368424138189</v>
+        <v>-292.7780936249542</v>
       </c>
       <c r="F16">
-        <v>50.26462718528657</v>
+        <v>53.85495769852133</v>
       </c>
       <c r="G16">
         <v>15.8</v>
@@ -2590,28 +2590,28 @@
         <v>48.872</v>
       </c>
       <c r="M16">
-        <v>2.949583909703543</v>
+        <v>3.160268474682368</v>
       </c>
       <c r="N16">
-        <v>45.92241609029646</v>
+        <v>45.71173152531763</v>
       </c>
       <c r="O16">
-        <v>12.39905234438004</v>
+        <v>12.34216751183576</v>
       </c>
       <c r="P16">
-        <v>33.52336374591641</v>
+        <v>33.36956401348187</v>
       </c>
       <c r="Q16">
-        <v>80.38536374591641</v>
+        <v>80.23156401348186</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09149630260549846</v>
+        <v>0.09190417061510896</v>
       </c>
       <c r="T16">
-        <v>0.8369438300983204</v>
+        <v>0.8444140759316654</v>
       </c>
       <c r="U16">
         <v>0.05868110587651873</v>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.56911669446693</v>
+        <v>15.4645089148358</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2636,22 +2636,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08454412611632142</v>
+        <v>0.08440422297133393</v>
       </c>
       <c r="C17">
-        <v>1362.315111555678</v>
+        <v>1363.799774443566</v>
       </c>
       <c r="D17">
-        <v>1400.370069254199</v>
+        <v>1405.445062655322</v>
       </c>
       <c r="E17">
-        <v>-292.7780936249542</v>
+        <v>-289.1877631117194</v>
       </c>
       <c r="F17">
-        <v>53.85495769852132</v>
+        <v>57.44528821175608</v>
       </c>
       <c r="G17">
         <v>15.8</v>
@@ -2672,28 +2672,28 @@
         <v>48.872</v>
       </c>
       <c r="M17">
-        <v>3.160268474682367</v>
+        <v>3.370953039661192</v>
       </c>
       <c r="N17">
-        <v>45.71173152531763</v>
+        <v>45.50104696033881</v>
       </c>
       <c r="O17">
-        <v>12.34216751183576</v>
+        <v>12.28528267929148</v>
       </c>
       <c r="P17">
-        <v>33.36956401348187</v>
+        <v>33.21576428104733</v>
       </c>
       <c r="Q17">
-        <v>80.23156401348186</v>
+        <v>80.07776428104732</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09190417061510896</v>
+        <v>0.09232174976780541</v>
       </c>
       <c r="T17">
-        <v>0.8444140759316654</v>
+        <v>0.8520621847610422</v>
       </c>
       <c r="U17">
         <v>0.05868110587651873</v>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.4645089148358</v>
+        <v>14.49797710765856</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2718,22 +2718,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08440422297133393</v>
+        <v>0.08426431982634647</v>
       </c>
       <c r="C18">
-        <v>1363.799774443566</v>
+        <v>1365.321355053686</v>
       </c>
       <c r="D18">
-        <v>1405.445062655322</v>
+        <v>1410.556973778677</v>
       </c>
       <c r="E18">
-        <v>-289.1877631117194</v>
+        <v>-285.5974325984847</v>
       </c>
       <c r="F18">
-        <v>57.44528821175608</v>
+        <v>61.03561872499084</v>
       </c>
       <c r="G18">
         <v>15.8</v>
@@ -2754,28 +2754,28 @@
         <v>48.872</v>
       </c>
       <c r="M18">
-        <v>3.370953039661192</v>
+        <v>3.581637604640016</v>
       </c>
       <c r="N18">
-        <v>45.50104696033881</v>
+        <v>45.29036239535998</v>
       </c>
       <c r="O18">
-        <v>12.28528267929148</v>
+        <v>12.2283978467472</v>
       </c>
       <c r="P18">
-        <v>33.21576428104733</v>
+        <v>33.06196454861279</v>
       </c>
       <c r="Q18">
-        <v>80.07776428104732</v>
+        <v>79.92396454861279</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09232174976780541</v>
+        <v>0.09274939106875962</v>
       </c>
       <c r="T18">
-        <v>0.8520621847610422</v>
+        <v>0.8598945853694402</v>
       </c>
       <c r="U18">
         <v>0.05868110587651873</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.49797710765856</v>
+        <v>13.64515492485512</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2800,22 +2800,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08426431982634647</v>
+        <v>0.08412441668135899</v>
       </c>
       <c r="C19">
-        <v>1365.321355053686</v>
+        <v>1366.880257690076</v>
       </c>
       <c r="D19">
-        <v>1410.556973778677</v>
+        <v>1415.706206928301</v>
       </c>
       <c r="E19">
-        <v>-285.5974325984847</v>
+        <v>-282.0071020852499</v>
       </c>
       <c r="F19">
-        <v>61.03561872499084</v>
+        <v>64.6259492382256</v>
       </c>
       <c r="G19">
         <v>15.8</v>
@@ -2836,28 +2836,28 @@
         <v>48.872</v>
       </c>
       <c r="M19">
-        <v>3.581637604640016</v>
+        <v>3.792322169618842</v>
       </c>
       <c r="N19">
-        <v>45.29036239535998</v>
+        <v>45.07967783038116</v>
       </c>
       <c r="O19">
-        <v>12.2283978467472</v>
+        <v>12.17151301420291</v>
       </c>
       <c r="P19">
-        <v>33.06196454861279</v>
+        <v>32.90816481617824</v>
       </c>
       <c r="Q19">
-        <v>79.92396454861279</v>
+        <v>79.77016481617824</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09274939106875962</v>
+        <v>0.09318746264534686</v>
       </c>
       <c r="T19">
-        <v>0.8598945853694402</v>
+        <v>0.8679180201390185</v>
       </c>
       <c r="U19">
         <v>0.05868110587651873</v>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.64515492485512</v>
+        <v>12.88709076236316</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2882,22 +2882,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08412441668135899</v>
+        <v>0.0841925635363715</v>
       </c>
       <c r="C20">
-        <v>1366.880257690076</v>
+        <v>1360.777046641201</v>
       </c>
       <c r="D20">
-        <v>1415.706206928301</v>
+        <v>1413.193326392661</v>
       </c>
       <c r="E20">
-        <v>-282.0071020852499</v>
+        <v>-278.4167715720151</v>
       </c>
       <c r="F20">
-        <v>64.62594923822559</v>
+        <v>68.21627975146035</v>
       </c>
       <c r="G20">
         <v>15.8</v>
@@ -2918,45 +2918,45 @@
         <v>48.872</v>
       </c>
       <c r="M20">
-        <v>3.792322169618841</v>
+        <v>4.105331154224856</v>
       </c>
       <c r="N20">
-        <v>45.07967783038116</v>
+        <v>44.76666884577514</v>
       </c>
       <c r="O20">
-        <v>12.17151301420291</v>
+        <v>12.08700058835929</v>
       </c>
       <c r="P20">
-        <v>32.90816481617824</v>
+        <v>32.67966825741586</v>
       </c>
       <c r="Q20">
-        <v>79.77016481617824</v>
+        <v>79.54166825741585</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09318746264534686</v>
+        <v>0.09363635080407205</v>
       </c>
       <c r="T20">
-        <v>0.8679180201390185</v>
+        <v>0.8761395644090804</v>
       </c>
       <c r="U20">
-        <v>0.05868110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V20">
         <v>0.27</v>
       </c>
       <c r="W20">
-        <v>0.04283720728985867</v>
+        <v>0.04393220728985867</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>12.88709076236317</v>
+        <v>11.9045207716569</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2964,22 +2964,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0841925635363715</v>
+        <v>0.08406361039138405</v>
       </c>
       <c r="C21">
-        <v>1360.777046641201</v>
+        <v>1361.949354103045</v>
       </c>
       <c r="D21">
-        <v>1413.193326392661</v>
+        <v>1417.95596436774</v>
       </c>
       <c r="E21">
-        <v>-278.4167715720151</v>
+        <v>-274.8264410587804</v>
       </c>
       <c r="F21">
-        <v>68.21627975146035</v>
+        <v>71.8066102646951</v>
       </c>
       <c r="G21">
         <v>15.8</v>
@@ -3000,28 +3000,28 @@
         <v>48.872</v>
       </c>
       <c r="M21">
-        <v>4.105331154224856</v>
+        <v>4.321401214973532</v>
       </c>
       <c r="N21">
-        <v>44.76666884577514</v>
+        <v>44.55059878502647</v>
       </c>
       <c r="O21">
-        <v>12.08700058835929</v>
+        <v>12.02866167195715</v>
       </c>
       <c r="P21">
-        <v>32.67966825741586</v>
+        <v>32.52193711306932</v>
       </c>
       <c r="Q21">
-        <v>79.54166825741585</v>
+        <v>79.38393711306932</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09363635080407205</v>
+        <v>0.09409646116676539</v>
       </c>
       <c r="T21">
-        <v>0.8761395644090804</v>
+        <v>0.8845666472858938</v>
       </c>
       <c r="U21">
         <v>0.06018110587651872</v>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.9045207716569</v>
+        <v>11.30929473307406</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3046,22 +3046,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08406361039138405</v>
+        <v>0.08393465724639657</v>
       </c>
       <c r="C22">
-        <v>1361.949354103045</v>
+        <v>1363.153871485716</v>
       </c>
       <c r="D22">
-        <v>1417.95596436774</v>
+        <v>1422.750812263646</v>
       </c>
       <c r="E22">
-        <v>-274.8264410587804</v>
+        <v>-271.2361105455457</v>
       </c>
       <c r="F22">
-        <v>71.8066102646951</v>
+        <v>75.39694077792986</v>
       </c>
       <c r="G22">
         <v>15.8</v>
@@ -3082,28 +3082,28 @@
         <v>48.872</v>
       </c>
       <c r="M22">
-        <v>4.321401214973532</v>
+        <v>4.537471275722209</v>
       </c>
       <c r="N22">
-        <v>44.55059878502647</v>
+        <v>44.33452872427779</v>
       </c>
       <c r="O22">
-        <v>12.02866167195715</v>
+        <v>11.970322755555</v>
       </c>
       <c r="P22">
-        <v>32.52193711306932</v>
+        <v>32.36420596872279</v>
       </c>
       <c r="Q22">
-        <v>79.38393711306932</v>
+        <v>79.22620596872278</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09409646116676539</v>
+        <v>0.0945682198930712</v>
       </c>
       <c r="T22">
-        <v>0.8845666472858938</v>
+        <v>0.8932070740330063</v>
       </c>
       <c r="U22">
         <v>0.06018110587651872</v>
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.30929473307406</v>
+        <v>10.77075688864196</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3128,22 +3128,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08393465724639657</v>
+        <v>0.08380570410140908</v>
       </c>
       <c r="C23">
-        <v>1363.153871485716</v>
+        <v>1364.390926653466</v>
       </c>
       <c r="D23">
-        <v>1422.750812263646</v>
+        <v>1427.578197944631</v>
       </c>
       <c r="E23">
-        <v>-271.2361105455457</v>
+        <v>-267.6457800323109</v>
       </c>
       <c r="F23">
-        <v>75.39694077792986</v>
+        <v>78.9872712911646</v>
       </c>
       <c r="G23">
         <v>15.8</v>
@@ -3164,28 +3164,28 @@
         <v>48.872</v>
       </c>
       <c r="M23">
-        <v>4.537471275722209</v>
+        <v>4.753541336470885</v>
       </c>
       <c r="N23">
-        <v>44.33452872427779</v>
+        <v>44.11845866352911</v>
       </c>
       <c r="O23">
-        <v>11.970322755555</v>
+        <v>11.91198383915286</v>
       </c>
       <c r="P23">
-        <v>32.36420596872279</v>
+        <v>32.20647482437625</v>
       </c>
       <c r="Q23">
-        <v>79.22620596872278</v>
+        <v>79.06847482437624</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0945682198930712</v>
+        <v>0.0950520749969746</v>
       </c>
       <c r="T23">
-        <v>0.8932070740330063</v>
+        <v>0.9020690501838908</v>
       </c>
       <c r="U23">
         <v>0.06018110587651872</v>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.77075688864196</v>
+        <v>10.28117703006732</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3210,22 +3210,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08380570410140908</v>
+        <v>0.08367675095642163</v>
       </c>
       <c r="C24">
-        <v>1364.390926653466</v>
+        <v>1365.660851935463</v>
       </c>
       <c r="D24">
-        <v>1427.578197944631</v>
+        <v>1432.438453739862</v>
       </c>
       <c r="E24">
-        <v>-267.6457800323109</v>
+        <v>-264.0554495190761</v>
       </c>
       <c r="F24">
-        <v>78.9872712911646</v>
+        <v>82.57760180439936</v>
       </c>
       <c r="G24">
         <v>15.8</v>
@@ -3246,28 +3246,28 @@
         <v>48.872</v>
       </c>
       <c r="M24">
-        <v>4.753541336470885</v>
+        <v>4.969611397219562</v>
       </c>
       <c r="N24">
-        <v>44.11845866352911</v>
+        <v>43.90238860278044</v>
       </c>
       <c r="O24">
-        <v>11.91198383915286</v>
+        <v>11.85364492275072</v>
       </c>
       <c r="P24">
-        <v>32.20647482437625</v>
+        <v>32.04874368002972</v>
       </c>
       <c r="Q24">
-        <v>79.06847482437624</v>
+        <v>78.91074368002973</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0950520749969746</v>
+        <v>0.09554849776591445</v>
       </c>
       <c r="T24">
-        <v>0.9020690501838908</v>
+        <v>0.9111612075334996</v>
       </c>
       <c r="U24">
         <v>0.06018110587651872</v>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.28117703006732</v>
+        <v>9.834169333107877</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3292,22 +3292,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08367675095642163</v>
+        <v>0.08384563781143414</v>
       </c>
       <c r="C25">
-        <v>1365.660851935463</v>
+        <v>1355.711841705774</v>
       </c>
       <c r="D25">
-        <v>1432.438453739862</v>
+        <v>1426.079774023408</v>
       </c>
       <c r="E25">
-        <v>-264.0554495190761</v>
+        <v>-260.4651190058414</v>
       </c>
       <c r="F25">
-        <v>82.57760180439936</v>
+        <v>86.16793231763413</v>
       </c>
       <c r="G25">
         <v>15.8</v>
@@ -3328,45 +3328,45 @@
         <v>48.872</v>
       </c>
       <c r="M25">
-        <v>4.969611397219562</v>
+        <v>5.332166942908216</v>
       </c>
       <c r="N25">
-        <v>43.90238860278044</v>
+        <v>43.53983305709178</v>
       </c>
       <c r="O25">
-        <v>11.85364492275072</v>
+        <v>11.75575492541478</v>
       </c>
       <c r="P25">
-        <v>32.04874368002972</v>
+        <v>31.784078131677</v>
       </c>
       <c r="Q25">
-        <v>78.91074368002973</v>
+        <v>78.646078131677</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09554849776591445</v>
+        <v>0.09605798429193166</v>
       </c>
       <c r="T25">
-        <v>0.9111612075334996</v>
+        <v>0.9204926321817825</v>
       </c>
       <c r="U25">
-        <v>0.06018110587651872</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V25">
         <v>0.27</v>
       </c>
       <c r="W25">
-        <v>0.04393220728985867</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>9.834169333107877</v>
+        <v>9.165504479374896</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3374,22 +3374,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08384563781143414</v>
+        <v>0.08372909466644668</v>
       </c>
       <c r="C26">
-        <v>1355.711841705774</v>
+        <v>1356.503366950745</v>
       </c>
       <c r="D26">
-        <v>1426.079774023408</v>
+        <v>1430.461629781614</v>
       </c>
       <c r="E26">
-        <v>-260.4651190058414</v>
+        <v>-256.8747884926066</v>
       </c>
       <c r="F26">
-        <v>86.16793231763411</v>
+        <v>89.75826283086887</v>
       </c>
       <c r="G26">
         <v>15.8</v>
@@ -3410,28 +3410,28 @@
         <v>48.872</v>
       </c>
       <c r="M26">
-        <v>5.332166942908216</v>
+        <v>5.554340565529392</v>
       </c>
       <c r="N26">
-        <v>43.53983305709178</v>
+        <v>43.31765943447061</v>
       </c>
       <c r="O26">
-        <v>11.75575492541478</v>
+        <v>11.69576804730706</v>
       </c>
       <c r="P26">
-        <v>31.784078131677</v>
+        <v>31.62189138716354</v>
       </c>
       <c r="Q26">
-        <v>78.646078131677</v>
+        <v>78.48389138716354</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09605798429193166</v>
+        <v>0.09658105712530934</v>
       </c>
       <c r="T26">
-        <v>0.9204926321817825</v>
+        <v>0.9300728948206861</v>
       </c>
       <c r="U26">
         <v>0.06188110587651872</v>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.165504479374896</v>
+        <v>8.7988843001999</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3456,22 +3456,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08372909466644668</v>
+        <v>0.0836125515214592</v>
       </c>
       <c r="C27">
-        <v>1356.503366950745</v>
+        <v>1357.321903081277</v>
       </c>
       <c r="D27">
-        <v>1430.461629781614</v>
+        <v>1434.870496425381</v>
       </c>
       <c r="E27">
-        <v>-256.8747884926066</v>
+        <v>-253.2844579793719</v>
       </c>
       <c r="F27">
-        <v>89.75826283086887</v>
+        <v>93.34859334410363</v>
       </c>
       <c r="G27">
         <v>15.8</v>
@@ -3492,28 +3492,28 @@
         <v>48.872</v>
       </c>
       <c r="M27">
-        <v>5.554340565529392</v>
+        <v>5.776514188150568</v>
       </c>
       <c r="N27">
-        <v>43.31765943447061</v>
+        <v>43.09548581184943</v>
       </c>
       <c r="O27">
-        <v>11.69576804730706</v>
+        <v>11.63578116919935</v>
       </c>
       <c r="P27">
-        <v>31.62189138716354</v>
+        <v>31.45970464265008</v>
       </c>
       <c r="Q27">
-        <v>78.48389138716354</v>
+        <v>78.32170464265008</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09658105712530934</v>
+        <v>0.09711826706229182</v>
       </c>
       <c r="T27">
-        <v>0.9300728948206861</v>
+        <v>0.9399120834768573</v>
       </c>
       <c r="U27">
         <v>0.06188110587651872</v>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.7988843001999</v>
+        <v>8.460465673269134</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3538,22 +3538,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0836125515214592</v>
+        <v>0.08349600837647173</v>
       </c>
       <c r="C28">
-        <v>1357.321903081277</v>
+        <v>1358.167700622585</v>
       </c>
       <c r="D28">
-        <v>1434.870496425381</v>
+        <v>1439.306624479923</v>
       </c>
       <c r="E28">
-        <v>-253.2844579793719</v>
+        <v>-249.6941274661371</v>
       </c>
       <c r="F28">
-        <v>93.34859334410363</v>
+        <v>96.93892385733839</v>
       </c>
       <c r="G28">
         <v>15.8</v>
@@ -3574,28 +3574,28 @@
         <v>48.872</v>
       </c>
       <c r="M28">
-        <v>5.776514188150568</v>
+        <v>5.998687810771744</v>
       </c>
       <c r="N28">
-        <v>43.09548581184943</v>
+        <v>42.87331218922826</v>
       </c>
       <c r="O28">
-        <v>11.63578116919935</v>
+        <v>11.57579429109163</v>
       </c>
       <c r="P28">
-        <v>31.45970464265008</v>
+        <v>31.29751789813663</v>
       </c>
       <c r="Q28">
-        <v>78.32170464265008</v>
+        <v>78.15951789813661</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09711826706229182</v>
+        <v>0.09767019507973956</v>
       </c>
       <c r="T28">
-        <v>0.9399120834768573</v>
+        <v>0.9500208389455266</v>
       </c>
       <c r="U28">
         <v>0.06188110587651872</v>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.460465673269134</v>
+        <v>8.147115092777685</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3620,22 +3620,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08349600837647173</v>
+        <v>0.08337946523148426</v>
       </c>
       <c r="C29">
-        <v>1358.167700622585</v>
+        <v>1359.041013207647</v>
       </c>
       <c r="D29">
-        <v>1439.306624479923</v>
+        <v>1443.77026757822</v>
       </c>
       <c r="E29">
-        <v>-249.6941274661371</v>
+        <v>-246.1037969529024</v>
       </c>
       <c r="F29">
-        <v>96.93892385733839</v>
+        <v>100.5292543705731</v>
       </c>
       <c r="G29">
         <v>15.8</v>
@@ -3656,28 +3656,28 @@
         <v>48.872</v>
       </c>
       <c r="M29">
-        <v>5.998687810771744</v>
+        <v>6.220861433392919</v>
       </c>
       <c r="N29">
-        <v>42.87331218922826</v>
+        <v>42.65113856660708</v>
       </c>
       <c r="O29">
-        <v>11.57579429109163</v>
+        <v>11.51580741298391</v>
       </c>
       <c r="P29">
-        <v>31.29751789813663</v>
+        <v>31.13533115362317</v>
       </c>
       <c r="Q29">
-        <v>78.15951789813661</v>
+        <v>77.99733115362316</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09767019507973956</v>
+        <v>0.09823745443100532</v>
       </c>
       <c r="T29">
-        <v>0.9500208389455266</v>
+        <v>0.9604103931772142</v>
       </c>
       <c r="U29">
         <v>0.06188110587651872</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.147115092777685</v>
+        <v>7.856146696607054</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3702,22 +3702,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08337946523148426</v>
+        <v>0.08343228208649678</v>
       </c>
       <c r="C30">
-        <v>1359.041013207647</v>
+        <v>1353.424353153227</v>
       </c>
       <c r="D30">
-        <v>1443.77026757822</v>
+        <v>1441.743938037035</v>
       </c>
       <c r="E30">
-        <v>-246.1037969529024</v>
+        <v>-242.5134664396676</v>
       </c>
       <c r="F30">
-        <v>100.5292543705731</v>
+        <v>104.1195848838079</v>
       </c>
       <c r="G30">
         <v>15.8</v>
@@ -3738,45 +3738,45 @@
         <v>48.872</v>
       </c>
       <c r="M30">
-        <v>6.220861433392919</v>
+        <v>6.526330723921142</v>
       </c>
       <c r="N30">
-        <v>42.65113856660708</v>
+        <v>42.34566927607886</v>
       </c>
       <c r="O30">
-        <v>11.51580741298391</v>
+        <v>11.43333070454129</v>
       </c>
       <c r="P30">
-        <v>31.13533115362317</v>
+        <v>30.91233857153757</v>
       </c>
       <c r="Q30">
-        <v>77.99733115362316</v>
+        <v>77.77433857153756</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09823745443100532</v>
+        <v>0.09882069291892642</v>
       </c>
       <c r="T30">
-        <v>0.9604103931772142</v>
+        <v>0.9710926109083862</v>
       </c>
       <c r="U30">
-        <v>0.06188110587651872</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.04517320728985866</v>
+        <v>0.04575720728985867</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.856146696607054</v>
+        <v>7.48843447679844</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3784,22 +3784,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08343228208649676</v>
+        <v>0.08332157894150929</v>
       </c>
       <c r="C31">
-        <v>1353.424353153228</v>
+        <v>1354.087723915628</v>
       </c>
       <c r="D31">
-        <v>1441.743938037036</v>
+        <v>1445.99763931267</v>
       </c>
       <c r="E31">
-        <v>-242.5134664396676</v>
+        <v>-238.9231359264328</v>
       </c>
       <c r="F31">
-        <v>104.1195848838079</v>
+        <v>107.7099153970426</v>
       </c>
       <c r="G31">
         <v>15.8</v>
@@ -3820,28 +3820,28 @@
         <v>48.872</v>
       </c>
       <c r="M31">
-        <v>6.526330723921141</v>
+        <v>6.751376610952906</v>
       </c>
       <c r="N31">
-        <v>42.34566927607886</v>
+        <v>42.1206233890471</v>
       </c>
       <c r="O31">
-        <v>11.43333070454129</v>
+        <v>11.37256831504272</v>
       </c>
       <c r="P31">
-        <v>30.91233857153757</v>
+        <v>30.74805507400438</v>
       </c>
       <c r="Q31">
-        <v>77.77433857153756</v>
+        <v>77.61005507400438</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09882069291892642</v>
+        <v>0.09942059536364528</v>
       </c>
       <c r="T31">
-        <v>0.9710926109083862</v>
+        <v>0.9820800348604487</v>
       </c>
       <c r="U31">
         <v>0.06268110587651873</v>
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.488434476798441</v>
+        <v>7.238819994238492</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3866,22 +3866,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08332157894150929</v>
+        <v>0.08321087579652181</v>
       </c>
       <c r="C32">
-        <v>1354.087723915628</v>
+        <v>1354.776269074458</v>
       </c>
       <c r="D32">
-        <v>1445.99763931267</v>
+        <v>1450.276514984735</v>
       </c>
       <c r="E32">
-        <v>-238.9231359264328</v>
+        <v>-235.3328054131981</v>
       </c>
       <c r="F32">
-        <v>107.7099153970426</v>
+        <v>111.3002459102774</v>
       </c>
       <c r="G32">
         <v>15.8</v>
@@ -3902,28 +3902,28 @@
         <v>48.872</v>
       </c>
       <c r="M32">
-        <v>6.751376610952906</v>
+        <v>6.976422497984669</v>
       </c>
       <c r="N32">
-        <v>42.1206233890471</v>
+        <v>41.89557750201533</v>
       </c>
       <c r="O32">
-        <v>11.37256831504272</v>
+        <v>11.31180592554414</v>
       </c>
       <c r="P32">
-        <v>30.74805507400438</v>
+        <v>30.58377157647119</v>
       </c>
       <c r="Q32">
-        <v>77.61005507400438</v>
+        <v>77.44577157647119</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09942059536364528</v>
+        <v>0.1000378862850227</v>
       </c>
       <c r="T32">
-        <v>0.9820800348604487</v>
+        <v>0.9933859348690928</v>
       </c>
       <c r="U32">
         <v>0.06268110587651873</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.238819994238492</v>
+        <v>7.005309671843701</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3948,22 +3948,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08321087579652181</v>
+        <v>0.08310017265153435</v>
       </c>
       <c r="C33">
-        <v>1354.776269074458</v>
+        <v>1355.490212774915</v>
       </c>
       <c r="D33">
-        <v>1450.276514984735</v>
+        <v>1454.580789198428</v>
       </c>
       <c r="E33">
-        <v>-235.3328054131981</v>
+        <v>-231.7424748999634</v>
       </c>
       <c r="F33">
-        <v>111.3002459102774</v>
+        <v>114.8905764235122</v>
       </c>
       <c r="G33">
         <v>15.8</v>
@@ -3984,28 +3984,28 @@
         <v>48.872</v>
       </c>
       <c r="M33">
-        <v>6.976422497984669</v>
+        <v>7.201468385016432</v>
       </c>
       <c r="N33">
-        <v>41.89557750201533</v>
+        <v>41.67053161498357</v>
       </c>
       <c r="O33">
-        <v>11.31180592554414</v>
+        <v>11.25104353604556</v>
       </c>
       <c r="P33">
-        <v>30.58377157647119</v>
+        <v>30.419488078938</v>
       </c>
       <c r="Q33">
-        <v>77.44577157647119</v>
+        <v>77.281488078938</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1000378862850227</v>
+        <v>0.1006733328217347</v>
       </c>
       <c r="T33">
-        <v>0.9933859348690928</v>
+        <v>1.005024361348579</v>
       </c>
       <c r="U33">
         <v>0.06268110587651873</v>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.005309671843701</v>
+        <v>6.786393744598586</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4030,22 +4030,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08310017265153435</v>
+        <v>0.08298946950654687</v>
       </c>
       <c r="C34">
-        <v>1355.490212774915</v>
+        <v>1356.229781831081</v>
       </c>
       <c r="D34">
-        <v>1454.580789198428</v>
+        <v>1458.910688767828</v>
       </c>
       <c r="E34">
-        <v>-231.7424748999634</v>
+        <v>-228.1521443867286</v>
       </c>
       <c r="F34">
-        <v>114.8905764235122</v>
+        <v>118.4809069367469</v>
       </c>
       <c r="G34">
         <v>15.8</v>
@@ -4066,28 +4066,28 @@
         <v>48.872</v>
       </c>
       <c r="M34">
-        <v>7.201468385016432</v>
+        <v>7.426514272048196</v>
       </c>
       <c r="N34">
-        <v>41.67053161498357</v>
+        <v>41.44548572795181</v>
       </c>
       <c r="O34">
-        <v>11.25104353604556</v>
+        <v>11.19028114654699</v>
       </c>
       <c r="P34">
-        <v>30.419488078938</v>
+        <v>30.25520458140482</v>
       </c>
       <c r="Q34">
-        <v>77.281488078938</v>
+        <v>77.11720458140482</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1006733328217347</v>
+        <v>0.1013277479117814</v>
       </c>
       <c r="T34">
-        <v>1.005024361348579</v>
+        <v>1.017010203543871</v>
       </c>
       <c r="U34">
         <v>0.06268110587651873</v>
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.786393744598586</v>
+        <v>6.580745449307719</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4112,22 +4112,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08298946950654687</v>
+        <v>0.0828787663615594</v>
       </c>
       <c r="C35">
-        <v>1356.229781831081</v>
+        <v>1356.995205765758</v>
       </c>
       <c r="D35">
-        <v>1458.910688767828</v>
+        <v>1463.26644321574</v>
       </c>
       <c r="E35">
-        <v>-228.1521443867286</v>
+        <v>-224.5618138734938</v>
       </c>
       <c r="F35">
-        <v>118.4809069367469</v>
+        <v>122.0712374499817</v>
       </c>
       <c r="G35">
         <v>15.8</v>
@@ -4148,28 +4148,28 @@
         <v>48.872</v>
       </c>
       <c r="M35">
-        <v>7.426514272048196</v>
+        <v>7.651560159079961</v>
       </c>
       <c r="N35">
-        <v>41.44548572795181</v>
+        <v>41.22043984092004</v>
       </c>
       <c r="O35">
-        <v>11.19028114654699</v>
+        <v>11.12951875704841</v>
       </c>
       <c r="P35">
-        <v>30.25520458140482</v>
+        <v>30.09092108387163</v>
       </c>
       <c r="Q35">
-        <v>77.11720458140482</v>
+        <v>76.95292108387162</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1013277479117814</v>
+        <v>0.1020019937621325</v>
       </c>
       <c r="T35">
-        <v>1.017010203543871</v>
+        <v>1.029359253078415</v>
       </c>
       <c r="U35">
         <v>0.06268110587651873</v>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.580745449307719</v>
+        <v>6.387194112563374</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4194,22 +4194,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0828787663615594</v>
+        <v>0.08276806321657194</v>
       </c>
       <c r="C36">
-        <v>1356.995205765758</v>
+        <v>1357.78671685103</v>
       </c>
       <c r="D36">
-        <v>1463.26644321574</v>
+        <v>1467.648284814246</v>
       </c>
       <c r="E36">
-        <v>-224.5618138734938</v>
+        <v>-220.9714833602591</v>
       </c>
       <c r="F36">
-        <v>122.0712374499817</v>
+        <v>125.6615679632164</v>
       </c>
       <c r="G36">
         <v>15.8</v>
@@ -4230,28 +4230,28 @@
         <v>48.872</v>
       </c>
       <c r="M36">
-        <v>7.651560159079961</v>
+        <v>7.876606046111723</v>
       </c>
       <c r="N36">
-        <v>41.22043984092004</v>
+        <v>40.99539395388828</v>
       </c>
       <c r="O36">
-        <v>11.12951875704841</v>
+        <v>11.06875636754983</v>
       </c>
       <c r="P36">
-        <v>30.09092108387163</v>
+        <v>29.92663758633844</v>
       </c>
       <c r="Q36">
-        <v>76.95292108387162</v>
+        <v>76.78863758633844</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1020019937621325</v>
+        <v>0.1026969856386483</v>
       </c>
       <c r="T36">
-        <v>1.029359253078415</v>
+        <v>1.042088273367867</v>
       </c>
       <c r="U36">
         <v>0.06268110587651873</v>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.387194112563374</v>
+        <v>6.204702852204421</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4276,22 +4276,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08276806321657194</v>
+        <v>0.08292016007158445</v>
       </c>
       <c r="C37">
-        <v>1357.78671685103</v>
+        <v>1348.182816138898</v>
       </c>
       <c r="D37">
-        <v>1467.648284814246</v>
+        <v>1461.63471461535</v>
       </c>
       <c r="E37">
-        <v>-220.9714833602591</v>
+        <v>-217.3811528470243</v>
       </c>
       <c r="F37">
-        <v>125.6615679632164</v>
+        <v>129.2518984764512</v>
       </c>
       <c r="G37">
         <v>15.8</v>
@@ -4312,45 +4312,45 @@
         <v>48.872</v>
       </c>
       <c r="M37">
-        <v>7.876606046111723</v>
+        <v>8.230903831619939</v>
       </c>
       <c r="N37">
-        <v>40.99539395388828</v>
+        <v>40.64109616838006</v>
       </c>
       <c r="O37">
-        <v>11.06875636754983</v>
+        <v>10.97309596546262</v>
       </c>
       <c r="P37">
-        <v>29.92663758633844</v>
+        <v>29.66800020291744</v>
       </c>
       <c r="Q37">
-        <v>76.78863758633844</v>
+        <v>76.53000020291744</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1026969856386483</v>
+        <v>0.1034136960113052</v>
       </c>
       <c r="T37">
-        <v>1.042088273367867</v>
+        <v>1.055215075541365</v>
       </c>
       <c r="U37">
-        <v>0.06268110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.04575720728985867</v>
+        <v>0.04648720728985867</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>6.204702852204421</v>
+        <v>5.937622526004099</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4358,22 +4358,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08292016007158445</v>
+        <v>0.08281675692659698</v>
       </c>
       <c r="C38">
-        <v>1348.182816138898</v>
+        <v>1348.675437209288</v>
       </c>
       <c r="D38">
-        <v>1461.63471461535</v>
+        <v>1465.717666198974</v>
       </c>
       <c r="E38">
-        <v>-217.3811528470243</v>
+        <v>-213.7908223337896</v>
       </c>
       <c r="F38">
-        <v>129.2518984764512</v>
+        <v>132.8422289896859</v>
       </c>
       <c r="G38">
         <v>15.8</v>
@@ -4394,28 +4394,28 @@
         <v>48.872</v>
       </c>
       <c r="M38">
-        <v>8.230903831619937</v>
+        <v>8.459540049164936</v>
       </c>
       <c r="N38">
-        <v>40.64109616838006</v>
+        <v>40.41245995083506</v>
       </c>
       <c r="O38">
-        <v>10.97309596546262</v>
+        <v>10.91136418672547</v>
       </c>
       <c r="P38">
-        <v>29.66800020291744</v>
+        <v>29.5010957641096</v>
       </c>
       <c r="Q38">
-        <v>76.53000020291744</v>
+        <v>76.36309576410959</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1034136960113052</v>
+        <v>0.1041531590942052</v>
       </c>
       <c r="T38">
-        <v>1.055215075541365</v>
+        <v>1.068758601593386</v>
       </c>
       <c r="U38">
         <v>0.06368110587651873</v>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.9376225260041</v>
+        <v>5.777146241517503</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4440,22 +4440,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08281675692659698</v>
+        <v>0.08271335378160952</v>
       </c>
       <c r="C39">
-        <v>1348.675437209288</v>
+        <v>1349.190932930249</v>
       </c>
       <c r="D39">
-        <v>1465.717666198974</v>
+        <v>1469.823492433169</v>
       </c>
       <c r="E39">
-        <v>-213.7908223337896</v>
+        <v>-210.2004918205548</v>
       </c>
       <c r="F39">
-        <v>132.8422289896859</v>
+        <v>136.4325595029207</v>
       </c>
       <c r="G39">
         <v>15.8</v>
@@ -4476,28 +4476,28 @@
         <v>48.872</v>
       </c>
       <c r="M39">
-        <v>8.459540049164936</v>
+        <v>8.688176266709934</v>
       </c>
       <c r="N39">
-        <v>40.41245995083506</v>
+        <v>40.18382373329007</v>
       </c>
       <c r="O39">
-        <v>10.91136418672547</v>
+        <v>10.84963240798832</v>
       </c>
       <c r="P39">
-        <v>29.5010957641096</v>
+        <v>29.33419132530175</v>
       </c>
       <c r="Q39">
-        <v>76.36309576410959</v>
+        <v>76.19619132530174</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1041531590942052</v>
+        <v>0.1049164758249407</v>
       </c>
       <c r="T39">
-        <v>1.068758601593386</v>
+        <v>1.08273901558257</v>
       </c>
       <c r="U39">
         <v>0.06368110587651873</v>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.777146241517503</v>
+        <v>5.625116077267043</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4522,22 +4522,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08271335378160952</v>
+        <v>0.08260995063662205</v>
       </c>
       <c r="C40">
-        <v>1349.190932930249</v>
+        <v>1349.729496073906</v>
       </c>
       <c r="D40">
-        <v>1469.823492433169</v>
+        <v>1473.952386090062</v>
       </c>
       <c r="E40">
-        <v>-210.2004918205548</v>
+        <v>-206.6101613073201</v>
       </c>
       <c r="F40">
-        <v>136.4325595029207</v>
+        <v>140.0228900161555</v>
       </c>
       <c r="G40">
         <v>15.8</v>
@@ -4558,28 +4558,28 @@
         <v>48.872</v>
       </c>
       <c r="M40">
-        <v>8.688176266709934</v>
+        <v>8.916812484254933</v>
       </c>
       <c r="N40">
-        <v>40.18382373329007</v>
+        <v>39.95518751574507</v>
       </c>
       <c r="O40">
-        <v>10.84963240798832</v>
+        <v>10.78790062925117</v>
       </c>
       <c r="P40">
-        <v>29.33419132530175</v>
+        <v>29.1672868864939</v>
       </c>
       <c r="Q40">
-        <v>76.19619132530174</v>
+        <v>76.02928688649389</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1049164758249407</v>
+        <v>0.105704819333733</v>
       </c>
       <c r="T40">
-        <v>1.08273901558257</v>
+        <v>1.097177803800907</v>
       </c>
       <c r="U40">
         <v>0.06368110587651873</v>
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.625116077267043</v>
+        <v>5.480882331696092</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4604,22 +4604,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08260995063662205</v>
+        <v>0.08250654749163457</v>
       </c>
       <c r="C41">
-        <v>1349.729496073906</v>
+        <v>1350.291321584559</v>
       </c>
       <c r="D41">
-        <v>1473.952386090062</v>
+        <v>1478.104542113949</v>
       </c>
       <c r="E41">
-        <v>-206.6101613073201</v>
+        <v>-203.0198307940853</v>
       </c>
       <c r="F41">
-        <v>140.0228900161555</v>
+        <v>143.6132205293902</v>
       </c>
       <c r="G41">
         <v>15.8</v>
@@ -4640,28 +4640,28 @@
         <v>48.872</v>
       </c>
       <c r="M41">
-        <v>8.916812484254933</v>
+        <v>9.14544870179993</v>
       </c>
       <c r="N41">
-        <v>39.95518751574507</v>
+        <v>39.72655129820007</v>
       </c>
       <c r="O41">
-        <v>10.78790062925117</v>
+        <v>10.72616885051402</v>
       </c>
       <c r="P41">
-        <v>29.1672868864939</v>
+        <v>29.00038244768605</v>
       </c>
       <c r="Q41">
-        <v>76.02928688649389</v>
+        <v>75.86238244768604</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.105704819333733</v>
+        <v>0.1065194409594852</v>
       </c>
       <c r="T41">
-        <v>1.097177803800907</v>
+        <v>1.112097884959855</v>
       </c>
       <c r="U41">
         <v>0.06368110587651873</v>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.480882331696092</v>
+        <v>5.34386027340369</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4686,22 +4686,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08250654749163457</v>
+        <v>0.0824031443466471</v>
       </c>
       <c r="C42">
-        <v>1350.291321584559</v>
+        <v>1350.876606609361</v>
       </c>
       <c r="D42">
-        <v>1478.104542113949</v>
+        <v>1482.280157651986</v>
       </c>
       <c r="E42">
-        <v>-203.0198307940853</v>
+        <v>-199.4295002808506</v>
       </c>
       <c r="F42">
-        <v>143.6132205293902</v>
+        <v>147.203551042625</v>
       </c>
       <c r="G42">
         <v>15.8</v>
@@ -4722,28 +4722,28 @@
         <v>48.872</v>
       </c>
       <c r="M42">
-        <v>9.14544870179993</v>
+        <v>9.374084919344929</v>
       </c>
       <c r="N42">
-        <v>39.72655129820007</v>
+        <v>39.49791508065507</v>
       </c>
       <c r="O42">
-        <v>10.72616885051402</v>
+        <v>10.66443707177687</v>
       </c>
       <c r="P42">
-        <v>29.00038244768605</v>
+        <v>28.8334780088782</v>
       </c>
       <c r="Q42">
-        <v>75.86238244768604</v>
+        <v>75.6954780088782</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1065194409594852</v>
+        <v>0.1073616768776356</v>
       </c>
       <c r="T42">
-        <v>1.112097884959855</v>
+        <v>1.127523731581819</v>
       </c>
       <c r="U42">
         <v>0.06368110587651873</v>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.34386027340369</v>
+        <v>5.21352221795482</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4768,22 +4768,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0824031443466471</v>
+        <v>0.08229974120165962</v>
       </c>
       <c r="C43">
-        <v>1350.876606609361</v>
+        <v>1351.485550529523</v>
       </c>
       <c r="D43">
-        <v>1482.280157651986</v>
+        <v>1486.479432085383</v>
       </c>
       <c r="E43">
-        <v>-199.4295002808506</v>
+        <v>-195.8391697676158</v>
       </c>
       <c r="F43">
-        <v>147.203551042625</v>
+        <v>150.7938815558597</v>
       </c>
       <c r="G43">
         <v>15.8</v>
@@ -4804,28 +4804,28 @@
         <v>48.872</v>
       </c>
       <c r="M43">
-        <v>9.374084919344929</v>
+        <v>9.602721136889928</v>
       </c>
       <c r="N43">
-        <v>39.49791508065507</v>
+        <v>39.26927886311007</v>
       </c>
       <c r="O43">
-        <v>10.66443707177687</v>
+        <v>10.60270529303972</v>
       </c>
       <c r="P43">
-        <v>28.8334780088782</v>
+        <v>28.66657357007036</v>
       </c>
       <c r="Q43">
-        <v>75.6954780088782</v>
+        <v>75.52857357007035</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1073616768776356</v>
+        <v>0.1082329554136534</v>
       </c>
       <c r="T43">
-        <v>1.127523731581819</v>
+        <v>1.143481503949367</v>
       </c>
       <c r="U43">
         <v>0.06368110587651873</v>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.21352221795482</v>
+        <v>5.089390736574943</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4850,22 +4850,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08229974120165962</v>
+        <v>0.08219633805667215</v>
       </c>
       <c r="C44">
-        <v>1351.485550529523</v>
+        <v>1352.118354992051</v>
       </c>
       <c r="D44">
-        <v>1486.479432085383</v>
+        <v>1490.702567061146</v>
       </c>
       <c r="E44">
-        <v>-195.8391697676158</v>
+        <v>-192.2488392543811</v>
       </c>
       <c r="F44">
-        <v>150.7938815558597</v>
+        <v>154.3842120690944</v>
       </c>
       <c r="G44">
         <v>15.8</v>
@@ -4886,28 +4886,28 @@
         <v>48.872</v>
       </c>
       <c r="M44">
-        <v>9.602721136889928</v>
+        <v>9.831357354434925</v>
       </c>
       <c r="N44">
-        <v>39.26927886311007</v>
+        <v>39.04064264556507</v>
       </c>
       <c r="O44">
-        <v>10.60270529303972</v>
+        <v>10.54097351430257</v>
       </c>
       <c r="P44">
-        <v>28.66657357007036</v>
+        <v>28.4996691312625</v>
       </c>
       <c r="Q44">
-        <v>75.52857357007035</v>
+        <v>75.36166913126249</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1082329554136534</v>
+        <v>0.1091348051263735</v>
       </c>
       <c r="T44">
-        <v>1.143481503949367</v>
+        <v>1.159999198154373</v>
       </c>
       <c r="U44">
         <v>0.06368110587651873</v>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.089390736574943</v>
+        <v>4.971032812468549</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4932,22 +4932,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08219633805667215</v>
+        <v>0.08209293491168468</v>
       </c>
       <c r="C45">
-        <v>1352.118354992051</v>
+        <v>1352.775223942021</v>
       </c>
       <c r="D45">
-        <v>1490.702567061146</v>
+        <v>1494.94976652435</v>
       </c>
       <c r="E45">
-        <v>-192.2488392543811</v>
+        <v>-188.6585087411463</v>
       </c>
       <c r="F45">
-        <v>154.3842120690944</v>
+        <v>157.9745425823292</v>
       </c>
       <c r="G45">
         <v>15.8</v>
@@ -4968,28 +4968,28 @@
         <v>48.872</v>
       </c>
       <c r="M45">
-        <v>9.831357354434925</v>
+        <v>10.05999357197992</v>
       </c>
       <c r="N45">
-        <v>39.04064264556507</v>
+        <v>38.81200642802008</v>
       </c>
       <c r="O45">
-        <v>10.54097351430257</v>
+        <v>10.47924173556542</v>
       </c>
       <c r="P45">
-        <v>28.4996691312625</v>
+        <v>28.33276469245465</v>
       </c>
       <c r="Q45">
-        <v>75.36166913126249</v>
+        <v>75.19476469245464</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1091348051263735</v>
+        <v>0.1100688637574051</v>
       </c>
       <c r="T45">
-        <v>1.159999198154373</v>
+        <v>1.177106810009558</v>
       </c>
       <c r="U45">
         <v>0.06368110587651873</v>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.971032812468549</v>
+        <v>4.858054794003355</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5014,22 +5014,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08209293491168468</v>
+        <v>0.0819895317666972</v>
       </c>
       <c r="C46">
-        <v>1352.775223942021</v>
+        <v>1353.45636365541</v>
       </c>
       <c r="D46">
-        <v>1494.94976652435</v>
+        <v>1499.221236750974</v>
       </c>
       <c r="E46">
-        <v>-188.6585087411463</v>
+        <v>-185.0681782279115</v>
       </c>
       <c r="F46">
-        <v>157.9745425823292</v>
+        <v>161.564873095564</v>
       </c>
       <c r="G46">
         <v>15.8</v>
@@ -5050,28 +5050,28 @@
         <v>48.872</v>
       </c>
       <c r="M46">
-        <v>10.05999357197992</v>
+        <v>10.28862978952492</v>
       </c>
       <c r="N46">
-        <v>38.81200642802008</v>
+        <v>38.58337021047508</v>
       </c>
       <c r="O46">
-        <v>10.47924173556542</v>
+        <v>10.41750995682827</v>
       </c>
       <c r="P46">
-        <v>28.33276469245465</v>
+        <v>28.16586025364681</v>
       </c>
       <c r="Q46">
-        <v>75.19476469245464</v>
+        <v>75.02786025364681</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1100688637574051</v>
+        <v>0.1110368881568378</v>
       </c>
       <c r="T46">
-        <v>1.177106810009558</v>
+        <v>1.194836516841296</v>
       </c>
       <c r="U46">
         <v>0.06368110587651873</v>
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.858054794003355</v>
+        <v>4.75009802080328</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5096,22 +5096,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0819895317666972</v>
+        <v>0.08188612862170973</v>
       </c>
       <c r="C47">
-        <v>1353.45636365541</v>
+        <v>1354.161982772494</v>
       </c>
       <c r="D47">
-        <v>1499.221236750974</v>
+        <v>1503.517186381293</v>
       </c>
       <c r="E47">
-        <v>-185.0681782279115</v>
+        <v>-181.4778477146768</v>
       </c>
       <c r="F47">
-        <v>161.564873095564</v>
+        <v>165.1552036087987</v>
       </c>
       <c r="G47">
         <v>15.8</v>
@@ -5132,28 +5132,28 @@
         <v>48.872</v>
       </c>
       <c r="M47">
-        <v>10.28862978952492</v>
+        <v>10.51726600706992</v>
       </c>
       <c r="N47">
-        <v>38.58337021047508</v>
+        <v>38.35473399293008</v>
       </c>
       <c r="O47">
-        <v>10.41750995682827</v>
+        <v>10.35577817809112</v>
       </c>
       <c r="P47">
-        <v>28.16586025364681</v>
+        <v>27.99895581483896</v>
       </c>
       <c r="Q47">
-        <v>75.02786025364681</v>
+        <v>74.86095581483895</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1110368881568378</v>
+        <v>0.1120407653118051</v>
       </c>
       <c r="T47">
-        <v>1.194836516841296</v>
+        <v>1.213222879481616</v>
       </c>
       <c r="U47">
         <v>0.06368110587651873</v>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.75009802080328</v>
+        <v>4.646835020351034</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5178,22 +5178,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08188612862170973</v>
+        <v>0.08178272547672225</v>
       </c>
       <c r="C48">
-        <v>1354.161982772494</v>
+        <v>1354.892292331816</v>
       </c>
       <c r="D48">
-        <v>1503.517186381293</v>
+        <v>1507.83782645385</v>
       </c>
       <c r="E48">
-        <v>-181.4778477146768</v>
+        <v>-177.887517201442</v>
       </c>
       <c r="F48">
-        <v>165.1552036087987</v>
+        <v>168.7455341220335</v>
       </c>
       <c r="G48">
         <v>15.8</v>
@@ -5214,28 +5214,28 @@
         <v>48.872</v>
       </c>
       <c r="M48">
-        <v>10.51726600706992</v>
+        <v>10.74590222461492</v>
       </c>
       <c r="N48">
-        <v>38.35473399293008</v>
+        <v>38.12609777538508</v>
       </c>
       <c r="O48">
-        <v>10.35577817809112</v>
+        <v>10.29404639935397</v>
       </c>
       <c r="P48">
-        <v>27.99895581483896</v>
+        <v>27.8320513760311</v>
       </c>
       <c r="Q48">
-        <v>74.86095581483895</v>
+        <v>74.6940513760311</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1120407653118051</v>
+        <v>0.1130825246235635</v>
       </c>
       <c r="T48">
-        <v>1.213222879481616</v>
+        <v>1.232303067127231</v>
       </c>
       <c r="U48">
         <v>0.06368110587651873</v>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.646835020351034</v>
+        <v>4.547966190130799</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5260,22 +5260,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08178272547672225</v>
+        <v>0.08255532233173478</v>
       </c>
       <c r="C49">
-        <v>1354.892292331816</v>
+        <v>1319.607211543426</v>
       </c>
       <c r="D49">
-        <v>1507.83782645385</v>
+        <v>1476.143076178695</v>
       </c>
       <c r="E49">
-        <v>-177.887517201442</v>
+        <v>-174.2971866882073</v>
       </c>
       <c r="F49">
-        <v>168.7455341220335</v>
+        <v>172.3358646352683</v>
       </c>
       <c r="G49">
         <v>15.8</v>
@@ -5296,45 +5296,45 @@
         <v>48.872</v>
       </c>
       <c r="M49">
-        <v>10.74590222461492</v>
+        <v>11.40537810374809</v>
       </c>
       <c r="N49">
-        <v>38.12609777538508</v>
+        <v>37.46662189625192</v>
       </c>
       <c r="O49">
-        <v>10.29404639935397</v>
+        <v>10.11598791198802</v>
       </c>
       <c r="P49">
-        <v>27.8320513760311</v>
+        <v>27.3506339842639</v>
       </c>
       <c r="Q49">
-        <v>74.6940513760311</v>
+        <v>74.21263398426389</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1130825246235635</v>
+        <v>0.1141643516011589</v>
       </c>
       <c r="T49">
-        <v>1.232303067127231</v>
+        <v>1.252117108143831</v>
       </c>
       <c r="U49">
-        <v>0.06368110587651873</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V49">
         <v>0.27</v>
       </c>
       <c r="W49">
-        <v>0.04648720728985867</v>
+        <v>0.04831220728985867</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.547966190130799</v>
+        <v>4.284996039187817</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5342,22 +5342,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08255532233173477</v>
+        <v>0.08247016918674731</v>
       </c>
       <c r="C50">
-        <v>1319.607211543427</v>
+        <v>1319.444687014613</v>
       </c>
       <c r="D50">
-        <v>1476.143076178695</v>
+        <v>1479.570882163116</v>
       </c>
       <c r="E50">
-        <v>-174.2971866882073</v>
+        <v>-170.7068561749725</v>
       </c>
       <c r="F50">
-        <v>172.3358646352682</v>
+        <v>175.926195148503</v>
       </c>
       <c r="G50">
         <v>15.8</v>
@@ -5378,28 +5378,28 @@
         <v>48.872</v>
       </c>
       <c r="M50">
-        <v>11.40537810374808</v>
+        <v>11.64299014757617</v>
       </c>
       <c r="N50">
-        <v>37.46662189625192</v>
+        <v>37.22900985242383</v>
       </c>
       <c r="O50">
-        <v>10.11598791198802</v>
+        <v>10.05183266015444</v>
       </c>
       <c r="P50">
-        <v>27.3506339842639</v>
+        <v>27.17717719226939</v>
       </c>
       <c r="Q50">
-        <v>74.21263398426389</v>
+        <v>74.03917719226939</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1141643516011589</v>
+        <v>0.1152886031661109</v>
       </c>
       <c r="T50">
-        <v>1.252117108143831</v>
+        <v>1.272708170376769</v>
       </c>
       <c r="U50">
         <v>0.06618110587651872</v>
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.284996039187817</v>
+        <v>4.197547140428881</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5424,22 +5424,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08247016918674731</v>
+        <v>0.08238501604175982</v>
       </c>
       <c r="C51">
-        <v>1319.444687014613</v>
+        <v>1319.298119207517</v>
       </c>
       <c r="D51">
-        <v>1479.570882163116</v>
+        <v>1483.014644869255</v>
       </c>
       <c r="E51">
-        <v>-170.7068561749725</v>
+        <v>-167.1165256617378</v>
       </c>
       <c r="F51">
-        <v>175.926195148503</v>
+        <v>179.5165256617377</v>
       </c>
       <c r="G51">
         <v>15.8</v>
@@ -5460,28 +5460,28 @@
         <v>48.872</v>
       </c>
       <c r="M51">
-        <v>11.64299014757617</v>
+        <v>11.88060219140426</v>
       </c>
       <c r="N51">
-        <v>37.22900985242383</v>
+        <v>36.99139780859574</v>
       </c>
       <c r="O51">
-        <v>10.05183266015444</v>
+        <v>9.987677408320851</v>
       </c>
       <c r="P51">
-        <v>27.17717719226939</v>
+        <v>27.00372040027489</v>
       </c>
       <c r="Q51">
-        <v>74.03917719226939</v>
+        <v>73.86572040027488</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1152886031661109</v>
+        <v>0.116457824793661</v>
       </c>
       <c r="T51">
-        <v>1.272708170376769</v>
+        <v>1.294122875099024</v>
       </c>
       <c r="U51">
         <v>0.06618110587651872</v>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.197547140428881</v>
+        <v>4.113596197620303</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5506,22 +5506,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08238501604175982</v>
+        <v>0.08229986289677235</v>
       </c>
       <c r="C52">
-        <v>1319.298119207517</v>
+        <v>1319.167619801874</v>
       </c>
       <c r="D52">
-        <v>1483.014644869255</v>
+        <v>1486.474475976847</v>
       </c>
       <c r="E52">
-        <v>-167.1165256617378</v>
+        <v>-163.526195148503</v>
       </c>
       <c r="F52">
-        <v>179.5165256617377</v>
+        <v>183.1068561749725</v>
       </c>
       <c r="G52">
         <v>15.8</v>
@@ -5542,28 +5542,28 @@
         <v>48.872</v>
       </c>
       <c r="M52">
-        <v>11.88060219140426</v>
+        <v>12.11821423523234</v>
       </c>
       <c r="N52">
-        <v>36.99139780859574</v>
+        <v>36.75378576476766</v>
       </c>
       <c r="O52">
-        <v>9.987677408320851</v>
+        <v>9.923522156487268</v>
       </c>
       <c r="P52">
-        <v>27.00372040027489</v>
+        <v>26.83026360828039</v>
       </c>
       <c r="Q52">
-        <v>73.86572040027488</v>
+        <v>73.69226360828038</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.116457824793661</v>
+        <v>0.1176747697529478</v>
       </c>
       <c r="T52">
-        <v>1.294122875099024</v>
+        <v>1.31641164940178</v>
       </c>
       <c r="U52">
         <v>0.06618110587651872</v>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.113596197620303</v>
+        <v>4.032937448647356</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5588,22 +5588,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08229986289677235</v>
+        <v>0.08354330975178487</v>
       </c>
       <c r="C53">
-        <v>1319.167619801874</v>
+        <v>1266.605643071991</v>
       </c>
       <c r="D53">
-        <v>1486.474475976847</v>
+        <v>1437.502829760198</v>
       </c>
       <c r="E53">
-        <v>-163.526195148503</v>
+        <v>-159.9358646352682</v>
       </c>
       <c r="F53">
-        <v>183.1068561749725</v>
+        <v>186.6971866882073</v>
       </c>
       <c r="G53">
         <v>15.8</v>
@@ -5624,45 +5624,45 @@
         <v>48.872</v>
       </c>
       <c r="M53">
-        <v>12.11821423523234</v>
+        <v>13.00926643246915</v>
       </c>
       <c r="N53">
-        <v>36.75378576476766</v>
+        <v>35.86273356753085</v>
       </c>
       <c r="O53">
-        <v>9.923522156487268</v>
+        <v>9.68293806323333</v>
       </c>
       <c r="P53">
-        <v>26.83026360828039</v>
+        <v>26.17979550429752</v>
       </c>
       <c r="Q53">
-        <v>73.69226360828038</v>
+        <v>73.04179550429751</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1176747697529478</v>
+        <v>0.1189424207522049</v>
       </c>
       <c r="T53">
-        <v>1.31641164940178</v>
+        <v>1.339629122633817</v>
       </c>
       <c r="U53">
-        <v>0.06618110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V53">
         <v>0.27</v>
       </c>
       <c r="W53">
-        <v>0.04831220728985867</v>
+        <v>0.05086720728985867</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.032937448647356</v>
+        <v>3.756706825376634</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5670,22 +5670,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08354330975178487</v>
+        <v>0.08348370660679739</v>
       </c>
       <c r="C54">
-        <v>1266.605643071991</v>
+        <v>1265.288966009998</v>
       </c>
       <c r="D54">
-        <v>1437.502829760198</v>
+        <v>1439.77648321144</v>
       </c>
       <c r="E54">
-        <v>-159.9358646352682</v>
+        <v>-156.3455341220335</v>
       </c>
       <c r="F54">
-        <v>186.6971866882073</v>
+        <v>190.287517201442</v>
       </c>
       <c r="G54">
         <v>15.8</v>
@@ -5706,28 +5706,28 @@
         <v>48.872</v>
       </c>
       <c r="M54">
-        <v>13.00926643246915</v>
+        <v>13.25944463309356</v>
       </c>
       <c r="N54">
-        <v>35.86273356753085</v>
+        <v>35.61255536690644</v>
       </c>
       <c r="O54">
-        <v>9.68293806323333</v>
+        <v>9.61538994906474</v>
       </c>
       <c r="P54">
-        <v>26.17979550429752</v>
+        <v>25.9971654178417</v>
       </c>
       <c r="Q54">
-        <v>73.04179550429751</v>
+        <v>72.85916541784169</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1189424207522049</v>
+        <v>0.1202640143471751</v>
       </c>
       <c r="T54">
-        <v>1.339629122633817</v>
+        <v>1.363834573450196</v>
       </c>
       <c r="U54">
         <v>0.06968110587651873</v>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.756706825376634</v>
+        <v>3.685825564520471</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5752,22 +5752,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08348370660679739</v>
+        <v>0.08342410346180992</v>
       </c>
       <c r="C55">
-        <v>1265.288966009998</v>
+        <v>1263.979492675606</v>
       </c>
       <c r="D55">
-        <v>1439.77648321144</v>
+        <v>1442.057340390283</v>
       </c>
       <c r="E55">
-        <v>-156.3455341220335</v>
+        <v>-152.7552036087987</v>
       </c>
       <c r="F55">
-        <v>190.287517201442</v>
+        <v>193.8778477146768</v>
       </c>
       <c r="G55">
         <v>15.8</v>
@@ -5788,28 +5788,28 @@
         <v>48.872</v>
       </c>
       <c r="M55">
-        <v>13.25944463309356</v>
+        <v>13.50962283371797</v>
       </c>
       <c r="N55">
-        <v>35.61255536690644</v>
+        <v>35.36237716628203</v>
       </c>
       <c r="O55">
-        <v>9.61538994906474</v>
+        <v>9.547841834896149</v>
       </c>
       <c r="P55">
-        <v>25.9971654178417</v>
+        <v>25.81453533138588</v>
       </c>
       <c r="Q55">
-        <v>72.85916541784169</v>
+        <v>72.67653533138588</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1202640143471751</v>
+        <v>0.121643068533231</v>
       </c>
       <c r="T55">
-        <v>1.363834573450196</v>
+        <v>1.389092435171634</v>
       </c>
       <c r="U55">
         <v>0.06968110587651873</v>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.685825564520471</v>
+        <v>3.617569535547869</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5834,22 +5834,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08342410346180992</v>
+        <v>0.08336450031682247</v>
       </c>
       <c r="C56">
-        <v>1263.979492675606</v>
+        <v>1262.677257359022</v>
       </c>
       <c r="D56">
-        <v>1442.057340390283</v>
+        <v>1444.345435586934</v>
       </c>
       <c r="E56">
-        <v>-152.7552036087987</v>
+        <v>-149.164873095564</v>
       </c>
       <c r="F56">
-        <v>193.8778477146768</v>
+        <v>197.4681782279115</v>
       </c>
       <c r="G56">
         <v>15.8</v>
@@ -5870,28 +5870,28 @@
         <v>48.872</v>
       </c>
       <c r="M56">
-        <v>13.50962283371797</v>
+        <v>13.75980103434237</v>
       </c>
       <c r="N56">
-        <v>35.36237716628203</v>
+        <v>35.11219896565763</v>
       </c>
       <c r="O56">
-        <v>9.547841834896149</v>
+        <v>9.480293720727559</v>
       </c>
       <c r="P56">
-        <v>25.81453533138588</v>
+        <v>25.63190524493007</v>
       </c>
       <c r="Q56">
-        <v>72.67653533138588</v>
+        <v>72.49390524493006</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.121643068533231</v>
+        <v>0.1230834140164449</v>
       </c>
       <c r="T56">
-        <v>1.389092435171634</v>
+        <v>1.415472868525137</v>
       </c>
       <c r="U56">
         <v>0.06968110587651873</v>
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.617569535547869</v>
+        <v>3.551795543992454</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5916,22 +5916,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08336450031682247</v>
+        <v>0.08444953717183498</v>
       </c>
       <c r="C57">
-        <v>1262.677257359022</v>
+        <v>1218.538756190772</v>
       </c>
       <c r="D57">
-        <v>1444.345435586934</v>
+        <v>1403.797264931918</v>
       </c>
       <c r="E57">
-        <v>-149.164873095564</v>
+        <v>-145.5745425823292</v>
       </c>
       <c r="F57">
-        <v>197.4681782279115</v>
+        <v>201.0585087411463</v>
       </c>
       <c r="G57">
         <v>15.8</v>
@@ -5952,45 +5952,45 @@
         <v>48.872</v>
       </c>
       <c r="M57">
-        <v>13.75980103434237</v>
+        <v>14.57294305944199</v>
       </c>
       <c r="N57">
-        <v>35.11219896565763</v>
+        <v>34.29905694055801</v>
       </c>
       <c r="O57">
-        <v>9.480293720727559</v>
+        <v>9.260745373950664</v>
       </c>
       <c r="P57">
-        <v>25.63190524493007</v>
+        <v>25.03831156660735</v>
       </c>
       <c r="Q57">
-        <v>72.49390524493006</v>
+        <v>71.90031156660734</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1230834140164449</v>
+        <v>0.1245892297488957</v>
       </c>
       <c r="T57">
-        <v>1.415472868525137</v>
+        <v>1.443052412485617</v>
       </c>
       <c r="U57">
-        <v>0.06968110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V57">
         <v>0.27</v>
       </c>
       <c r="W57">
-        <v>0.05086720728985867</v>
+        <v>0.05291120728985867</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.551795543992454</v>
+        <v>3.353612225111607</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5998,22 +5998,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08444953717183498</v>
+        <v>0.08441037402684751</v>
       </c>
       <c r="C58">
-        <v>1218.538756190772</v>
+        <v>1216.372320607468</v>
       </c>
       <c r="D58">
-        <v>1403.797264931918</v>
+        <v>1405.221159861849</v>
       </c>
       <c r="E58">
-        <v>-145.5745425823292</v>
+        <v>-141.9842120690945</v>
       </c>
       <c r="F58">
-        <v>201.0585087411463</v>
+        <v>204.648839254381</v>
       </c>
       <c r="G58">
         <v>15.8</v>
@@ -6034,28 +6034,28 @@
         <v>48.872</v>
       </c>
       <c r="M58">
-        <v>14.57294305944199</v>
+        <v>14.83317418550345</v>
       </c>
       <c r="N58">
-        <v>34.29905694055801</v>
+        <v>34.03882581449655</v>
       </c>
       <c r="O58">
-        <v>9.260745373950664</v>
+        <v>9.190482969914068</v>
       </c>
       <c r="P58">
-        <v>25.03831156660735</v>
+        <v>24.84834284458248</v>
       </c>
       <c r="Q58">
-        <v>71.90031156660734</v>
+        <v>71.71034284458247</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1245892297488957</v>
+        <v>0.1261650834223909</v>
       </c>
       <c r="T58">
-        <v>1.443052412485617</v>
+        <v>1.471914725932632</v>
       </c>
       <c r="U58">
         <v>0.07248110587651872</v>
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.353612225111607</v>
+        <v>3.294776922916666</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6080,22 +6080,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08441037402684751</v>
+        <v>0.08437121088186003</v>
       </c>
       <c r="C59">
-        <v>1216.372320607468</v>
+        <v>1214.208776517705</v>
       </c>
       <c r="D59">
-        <v>1405.221159861849</v>
+        <v>1406.647946285321</v>
       </c>
       <c r="E59">
-        <v>-141.9842120690945</v>
+        <v>-138.3938815558597</v>
       </c>
       <c r="F59">
-        <v>204.648839254381</v>
+        <v>208.2391697676158</v>
       </c>
       <c r="G59">
         <v>15.8</v>
@@ -6116,28 +6116,28 @@
         <v>48.872</v>
       </c>
       <c r="M59">
-        <v>14.83317418550345</v>
+        <v>15.09340531156492</v>
       </c>
       <c r="N59">
-        <v>34.03882581449655</v>
+        <v>33.77859468843508</v>
       </c>
       <c r="O59">
-        <v>9.190482969914068</v>
+        <v>9.120220565877471</v>
       </c>
       <c r="P59">
-        <v>24.84834284458248</v>
+        <v>24.65837412255761</v>
       </c>
       <c r="Q59">
-        <v>71.71034284458247</v>
+        <v>71.5203741225576</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1261650834223909</v>
+        <v>0.1278159777470048</v>
       </c>
       <c r="T59">
-        <v>1.471914725932632</v>
+        <v>1.502151435258075</v>
       </c>
       <c r="U59">
         <v>0.07248110587651872</v>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.294776922916666</v>
+        <v>3.237970424245689</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6162,22 +6162,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08437121088186003</v>
+        <v>0.08433204773687256</v>
       </c>
       <c r="C60">
-        <v>1214.208776517705</v>
+        <v>1212.048132738041</v>
       </c>
       <c r="D60">
-        <v>1406.647946285321</v>
+        <v>1408.077633018891</v>
       </c>
       <c r="E60">
-        <v>-138.3938815558597</v>
+        <v>-134.803551042625</v>
       </c>
       <c r="F60">
-        <v>208.2391697676158</v>
+        <v>211.8295002808505</v>
       </c>
       <c r="G60">
         <v>15.8</v>
@@ -6198,28 +6198,28 @@
         <v>48.872</v>
       </c>
       <c r="M60">
-        <v>15.09340531156492</v>
+        <v>15.35363643762638</v>
       </c>
       <c r="N60">
-        <v>33.77859468843508</v>
+        <v>33.51836356237362</v>
       </c>
       <c r="O60">
-        <v>9.120220565877473</v>
+        <v>9.049958161840879</v>
       </c>
       <c r="P60">
-        <v>24.65837412255761</v>
+        <v>24.46840540053275</v>
       </c>
       <c r="Q60">
-        <v>71.5203741225576</v>
+        <v>71.33040540053274</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1278159777470048</v>
+        <v>0.1295474035020877</v>
       </c>
       <c r="T60">
-        <v>1.502151435258074</v>
+        <v>1.533863106014027</v>
       </c>
       <c r="U60">
         <v>0.07248110587651872</v>
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.23797042424569</v>
+        <v>3.183089569597458</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6244,22 +6244,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08433204773687256</v>
+        <v>0.08429288459188508</v>
       </c>
       <c r="C61">
-        <v>1212.048132738041</v>
+        <v>1209.89039812091</v>
       </c>
       <c r="D61">
-        <v>1408.077633018891</v>
+        <v>1409.510228914995</v>
       </c>
       <c r="E61">
-        <v>-134.803551042625</v>
+        <v>-131.2132205293902</v>
       </c>
       <c r="F61">
-        <v>211.8295002808505</v>
+        <v>215.4198307940853</v>
       </c>
       <c r="G61">
         <v>15.8</v>
@@ -6280,28 +6280,28 @@
         <v>48.872</v>
       </c>
       <c r="M61">
-        <v>15.35363643762638</v>
+        <v>15.61386756368785</v>
       </c>
       <c r="N61">
-        <v>33.51836356237362</v>
+        <v>33.25813243631215</v>
       </c>
       <c r="O61">
-        <v>9.049958161840879</v>
+        <v>8.979695757804281</v>
       </c>
       <c r="P61">
-        <v>24.46840540053275</v>
+        <v>24.27843667850787</v>
       </c>
       <c r="Q61">
-        <v>71.33040540053274</v>
+        <v>71.14043667850787</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1295474035020877</v>
+        <v>0.1313654005449247</v>
       </c>
       <c r="T61">
-        <v>1.533863106014027</v>
+        <v>1.567160360307778</v>
       </c>
       <c r="U61">
         <v>0.07248110587651872</v>
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.183089569597458</v>
+        <v>3.130038076770833</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6326,22 +6326,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08429288459188508</v>
+        <v>0.08425372144689761</v>
       </c>
       <c r="C62">
-        <v>1209.89039812091</v>
+        <v>1207.735581554812</v>
       </c>
       <c r="D62">
-        <v>1409.510228914995</v>
+        <v>1410.945742862132</v>
       </c>
       <c r="E62">
-        <v>-131.2132205293902</v>
+        <v>-127.6228900161555</v>
       </c>
       <c r="F62">
-        <v>215.4198307940853</v>
+        <v>219.01016130732</v>
       </c>
       <c r="G62">
         <v>15.8</v>
@@ -6362,28 +6362,28 @@
         <v>48.872</v>
       </c>
       <c r="M62">
-        <v>15.61386756368785</v>
+        <v>15.87409868974931</v>
       </c>
       <c r="N62">
-        <v>33.25813243631215</v>
+        <v>32.9979013102507</v>
       </c>
       <c r="O62">
-        <v>8.979695757804281</v>
+        <v>8.909433353767689</v>
       </c>
       <c r="P62">
-        <v>24.27843667850787</v>
+        <v>24.08846795648301</v>
       </c>
       <c r="Q62">
-        <v>71.14043667850787</v>
+        <v>70.95046795648301</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1313654005449247</v>
+        <v>0.1332766282053431</v>
       </c>
       <c r="T62">
-        <v>1.567160360307778</v>
+        <v>1.602165166103772</v>
       </c>
       <c r="U62">
         <v>0.07248110587651872</v>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.130038076770833</v>
+        <v>3.07872597715164</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6408,22 +6408,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08425372144689761</v>
+        <v>0.08421455830191013</v>
       </c>
       <c r="C63">
-        <v>1207.735581554812</v>
+        <v>1205.583691964492</v>
       </c>
       <c r="D63">
-        <v>1410.945742862132</v>
+        <v>1412.384183785047</v>
       </c>
       <c r="E63">
-        <v>-127.6228900161555</v>
+        <v>-124.0325595029207</v>
       </c>
       <c r="F63">
-        <v>219.01016130732</v>
+        <v>222.6004918205548</v>
       </c>
       <c r="G63">
         <v>15.8</v>
@@ -6444,28 +6444,28 @@
         <v>48.872</v>
       </c>
       <c r="M63">
-        <v>15.87409868974931</v>
+        <v>16.13432981581077</v>
       </c>
       <c r="N63">
-        <v>32.9979013102507</v>
+        <v>32.73767018418923</v>
       </c>
       <c r="O63">
-        <v>8.909433353767689</v>
+        <v>8.839170949731091</v>
       </c>
       <c r="P63">
-        <v>24.08846795648301</v>
+        <v>23.89849923445814</v>
       </c>
       <c r="Q63">
-        <v>70.95046795648301</v>
+        <v>70.76049923445814</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1332766282053431</v>
+        <v>0.1352884467952573</v>
       </c>
       <c r="T63">
-        <v>1.602165166103772</v>
+        <v>1.639012330099555</v>
       </c>
       <c r="U63">
         <v>0.07248110587651872</v>
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.07872597715164</v>
+        <v>3.02906910655242</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6490,22 +6490,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08421455830191013</v>
+        <v>0.08776261515692267</v>
       </c>
       <c r="C64">
-        <v>1205.583691964492</v>
+        <v>1082.572315683496</v>
       </c>
       <c r="D64">
-        <v>1412.384183785047</v>
+        <v>1292.963138017285</v>
       </c>
       <c r="E64">
-        <v>-124.0325595029207</v>
+        <v>-120.442228989686</v>
       </c>
       <c r="F64">
-        <v>222.6004918205548</v>
+        <v>226.1908223337896</v>
       </c>
       <c r="G64">
         <v>15.8</v>
@@ -6526,45 +6526,45 @@
         <v>48.872</v>
       </c>
       <c r="M64">
-        <v>16.13432981581077</v>
+        <v>18.1588493560758</v>
       </c>
       <c r="N64">
-        <v>32.73767018418923</v>
+        <v>30.7131506439242</v>
       </c>
       <c r="O64">
-        <v>8.839170949731091</v>
+        <v>8.292550673859536</v>
       </c>
       <c r="P64">
-        <v>23.89849923445814</v>
+        <v>22.42059997006466</v>
       </c>
       <c r="Q64">
-        <v>70.76049923445814</v>
+        <v>69.28259997006467</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1352884467952573</v>
+        <v>0.1374090123359776</v>
       </c>
       <c r="T64">
-        <v>1.639012330099555</v>
+        <v>1.677851232689705</v>
       </c>
       <c r="U64">
-        <v>0.07248110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V64">
         <v>0.27</v>
       </c>
       <c r="W64">
-        <v>0.05291120728985867</v>
+        <v>0.05860520728985868</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.02906910655242</v>
+        <v>2.69135995578089</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6572,22 +6572,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08776261515692267</v>
+        <v>0.0877803920119352</v>
       </c>
       <c r="C65">
-        <v>1082.572315683496</v>
+        <v>1078.434471982806</v>
       </c>
       <c r="D65">
-        <v>1292.963138017285</v>
+        <v>1292.41562482983</v>
       </c>
       <c r="E65">
-        <v>-120.442228989686</v>
+        <v>-116.8518984764512</v>
       </c>
       <c r="F65">
-        <v>226.1908223337896</v>
+        <v>229.7811528470243</v>
       </c>
       <c r="G65">
         <v>15.8</v>
@@ -6608,28 +6608,28 @@
         <v>48.872</v>
       </c>
       <c r="M65">
-        <v>18.1588493560758</v>
+        <v>18.44708506014049</v>
       </c>
       <c r="N65">
-        <v>30.7131506439242</v>
+        <v>30.42491493985951</v>
       </c>
       <c r="O65">
-        <v>8.292550673859536</v>
+        <v>8.214727033762067</v>
       </c>
       <c r="P65">
-        <v>22.42059997006466</v>
+        <v>22.21018790609744</v>
       </c>
       <c r="Q65">
-        <v>69.28259997006467</v>
+        <v>69.07218790609744</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1374090123359776</v>
+        <v>0.1396473870734046</v>
       </c>
       <c r="T65">
-        <v>1.677851232689705</v>
+        <v>1.718847852090419</v>
       </c>
       <c r="U65">
         <v>0.08028110587651874</v>
@@ -6646,7 +6646,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.69135995578089</v>
+        <v>2.649307456471814</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6654,22 +6654,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0877803920119352</v>
+        <v>0.08779816886694772</v>
       </c>
       <c r="C66">
-        <v>1078.434471982806</v>
+        <v>1074.297091781493</v>
       </c>
       <c r="D66">
-        <v>1292.41562482983</v>
+        <v>1291.868575141752</v>
       </c>
       <c r="E66">
-        <v>-116.8518984764512</v>
+        <v>-113.2615679632164</v>
       </c>
       <c r="F66">
-        <v>229.7811528470243</v>
+        <v>233.3714833602591</v>
       </c>
       <c r="G66">
         <v>15.8</v>
@@ -6690,28 +6690,28 @@
         <v>48.872</v>
       </c>
       <c r="M66">
-        <v>18.44708506014049</v>
+        <v>18.73532076420519</v>
       </c>
       <c r="N66">
-        <v>30.42491493985951</v>
+        <v>30.13667923579481</v>
       </c>
       <c r="O66">
-        <v>8.214727033762067</v>
+        <v>8.136903393664598</v>
       </c>
       <c r="P66">
-        <v>22.21018790609744</v>
+        <v>21.99977584213021</v>
       </c>
       <c r="Q66">
-        <v>69.07218790609744</v>
+        <v>68.86177584213021</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1396473870734046</v>
+        <v>0.1420136689386845</v>
       </c>
       <c r="T66">
-        <v>1.718847852090419</v>
+        <v>1.762187135456888</v>
       </c>
       <c r="U66">
         <v>0.08028110587651874</v>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.649307456471814</v>
+        <v>2.6085488802184</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6736,22 +6736,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08779816886694772</v>
+        <v>0.08781594572196025</v>
       </c>
       <c r="C67">
-        <v>1074.297091781493</v>
+        <v>1070.16017449124</v>
       </c>
       <c r="D67">
-        <v>1291.868575141752</v>
+        <v>1291.321988364734</v>
       </c>
       <c r="E67">
-        <v>-113.2615679632164</v>
+        <v>-109.6712374499817</v>
       </c>
       <c r="F67">
-        <v>233.3714833602591</v>
+        <v>236.9618138734938</v>
       </c>
       <c r="G67">
         <v>15.8</v>
@@ -6772,28 +6772,28 @@
         <v>48.872</v>
       </c>
       <c r="M67">
-        <v>18.73532076420519</v>
+        <v>19.02355646826988</v>
       </c>
       <c r="N67">
-        <v>30.13667923579481</v>
+        <v>29.84844353173012</v>
       </c>
       <c r="O67">
-        <v>8.136903393664598</v>
+        <v>8.059079753567131</v>
       </c>
       <c r="P67">
-        <v>21.99977584213021</v>
+        <v>21.78936377816299</v>
       </c>
       <c r="Q67">
-        <v>68.86177584213021</v>
+        <v>68.65136377816299</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1420136689386845</v>
+        <v>0.1445191438548633</v>
       </c>
       <c r="T67">
-        <v>1.762187135456888</v>
+        <v>1.808075788433149</v>
       </c>
       <c r="U67">
         <v>0.08028110587651874</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.6085488802184</v>
+        <v>2.569025412336304</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6818,22 +6818,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08781594572196025</v>
+        <v>0.08783372257697278</v>
       </c>
       <c r="C68">
-        <v>1070.16017449124</v>
+        <v>1066.023719524726</v>
       </c>
       <c r="D68">
-        <v>1291.321988364734</v>
+        <v>1290.775863911455</v>
       </c>
       <c r="E68">
-        <v>-109.6712374499817</v>
+        <v>-106.0809069367469</v>
       </c>
       <c r="F68">
-        <v>236.9618138734938</v>
+        <v>240.5521443867286</v>
       </c>
       <c r="G68">
         <v>15.8</v>
@@ -6854,28 +6854,28 @@
         <v>48.872</v>
       </c>
       <c r="M68">
-        <v>19.02355646826988</v>
+        <v>19.31179217233458</v>
       </c>
       <c r="N68">
-        <v>29.84844353173012</v>
+        <v>29.56020782766542</v>
       </c>
       <c r="O68">
-        <v>8.059079753567131</v>
+        <v>7.981256113469664</v>
       </c>
       <c r="P68">
-        <v>21.78936377816299</v>
+        <v>21.57895171419575</v>
       </c>
       <c r="Q68">
-        <v>68.65136377816299</v>
+        <v>68.44095171419575</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1445191438548633</v>
+        <v>0.147176465735659</v>
       </c>
       <c r="T68">
-        <v>1.808075788433149</v>
+        <v>1.85674557189282</v>
       </c>
       <c r="U68">
         <v>0.08028110587651874</v>
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.569025412336304</v>
+        <v>2.530681749465613</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6900,22 +6900,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08783372257697278</v>
+        <v>0.08978745943198529</v>
       </c>
       <c r="C69">
-        <v>1066.023719524726</v>
+        <v>1005.102585881481</v>
       </c>
       <c r="D69">
-        <v>1290.775863911455</v>
+        <v>1233.445060781445</v>
       </c>
       <c r="E69">
-        <v>-106.0809069367469</v>
+        <v>-102.4905764235122</v>
       </c>
       <c r="F69">
-        <v>240.5521443867286</v>
+        <v>244.1424748999634</v>
       </c>
       <c r="G69">
         <v>15.8</v>
@@ -6936,45 +6936,45 @@
         <v>48.872</v>
       </c>
       <c r="M69">
-        <v>19.31179217233458</v>
+        <v>20.55218352850913</v>
       </c>
       <c r="N69">
-        <v>29.56020782766542</v>
+        <v>28.31981647149087</v>
       </c>
       <c r="O69">
-        <v>7.981256113469664</v>
+        <v>7.646350447302535</v>
       </c>
       <c r="P69">
-        <v>21.57895171419575</v>
+        <v>20.67346602418834</v>
       </c>
       <c r="Q69">
-        <v>68.44095171419575</v>
+        <v>67.53546602418834</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.147176465735659</v>
+        <v>0.1499998702340044</v>
       </c>
       <c r="T69">
-        <v>1.85674557189282</v>
+        <v>1.90845721681872</v>
       </c>
       <c r="U69">
-        <v>0.08028110587651874</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V69">
         <v>0.27</v>
       </c>
       <c r="W69">
-        <v>0.05860520728985868</v>
+        <v>0.06145220728985867</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.530681749465613</v>
+        <v>2.377946845998471</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6982,22 +6982,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08978745943198529</v>
+        <v>0.08983370628699783</v>
       </c>
       <c r="C70">
-        <v>1005.102585881481</v>
+        <v>1000.216816948412</v>
       </c>
       <c r="D70">
-        <v>1233.445060781445</v>
+        <v>1232.14962236161</v>
       </c>
       <c r="E70">
-        <v>-102.4905764235122</v>
+        <v>-98.90024591027739</v>
       </c>
       <c r="F70">
-        <v>244.1424748999634</v>
+        <v>247.7328054131981</v>
       </c>
       <c r="G70">
         <v>15.8</v>
@@ -7018,28 +7018,28 @@
         <v>48.872</v>
       </c>
       <c r="M70">
-        <v>20.55218352850913</v>
+        <v>20.85442152157544</v>
       </c>
       <c r="N70">
-        <v>28.31981647149087</v>
+        <v>28.01757847842456</v>
       </c>
       <c r="O70">
-        <v>7.646350447302535</v>
+        <v>7.564746189174631</v>
       </c>
       <c r="P70">
-        <v>20.67346602418834</v>
+        <v>20.45283228924993</v>
       </c>
       <c r="Q70">
-        <v>67.53546602418834</v>
+        <v>67.31483228924992</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1499998702340044</v>
+        <v>0.1530054298612753</v>
       </c>
       <c r="T70">
-        <v>1.90845721681872</v>
+        <v>1.96350509690113</v>
       </c>
       <c r="U70">
         <v>0.08418110587651872</v>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.377946845998471</v>
+        <v>2.343483848230377</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7064,22 +7064,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08983370628699783</v>
+        <v>0.08987995314201036</v>
       </c>
       <c r="C71">
-        <v>1000.216816948412</v>
+        <v>995.3337662556545</v>
       </c>
       <c r="D71">
-        <v>1232.14962236161</v>
+        <v>1230.856902182087</v>
       </c>
       <c r="E71">
-        <v>-98.90024591027739</v>
+        <v>-95.30991539704266</v>
       </c>
       <c r="F71">
-        <v>247.7328054131981</v>
+        <v>251.3231359264329</v>
       </c>
       <c r="G71">
         <v>15.8</v>
@@ -7100,28 +7100,28 @@
         <v>48.872</v>
       </c>
       <c r="M71">
-        <v>20.85442152157544</v>
+        <v>21.15665951464175</v>
       </c>
       <c r="N71">
-        <v>28.01757847842456</v>
+        <v>27.71534048535825</v>
       </c>
       <c r="O71">
-        <v>7.564746189174631</v>
+        <v>7.483141931046728</v>
       </c>
       <c r="P71">
-        <v>20.45283228924993</v>
+        <v>20.23219855431152</v>
       </c>
       <c r="Q71">
-        <v>67.31483228924992</v>
+        <v>67.09419855431152</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1530054298612753</v>
+        <v>0.1562113601303643</v>
       </c>
       <c r="T71">
-        <v>1.96350509690113</v>
+        <v>2.022222835655701</v>
       </c>
       <c r="U71">
         <v>0.08418110587651872</v>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.343483848230377</v>
+        <v>2.310005507541371</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7146,22 +7146,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08987995314201036</v>
+        <v>0.08992619999702288</v>
       </c>
       <c r="C72">
-        <v>995.3337662556545</v>
+        <v>990.4534252565811</v>
       </c>
       <c r="D72">
-        <v>1230.856902182087</v>
+        <v>1229.566891696249</v>
       </c>
       <c r="E72">
-        <v>-95.30991539704266</v>
+        <v>-91.7195848838079</v>
       </c>
       <c r="F72">
-        <v>251.3231359264329</v>
+        <v>254.9134664396676</v>
       </c>
       <c r="G72">
         <v>15.8</v>
@@ -7182,28 +7182,28 @@
         <v>48.872</v>
       </c>
       <c r="M72">
-        <v>21.15665951464175</v>
+        <v>21.45889750770806</v>
       </c>
       <c r="N72">
-        <v>27.71534048535825</v>
+        <v>27.41310249229194</v>
       </c>
       <c r="O72">
-        <v>7.483141931046728</v>
+        <v>7.401537672918823</v>
       </c>
       <c r="P72">
-        <v>20.23219855431152</v>
+        <v>20.01156481937311</v>
       </c>
       <c r="Q72">
-        <v>67.09419855431152</v>
+        <v>66.87356481937312</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1562113601303643</v>
+        <v>0.1596383890387008</v>
       </c>
       <c r="T72">
-        <v>2.022222835655701</v>
+        <v>2.084990073634725</v>
       </c>
       <c r="U72">
         <v>0.08418110587651872</v>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.310005507541371</v>
+        <v>2.27747021870276</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7228,22 +7228,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08992619999702287</v>
+        <v>0.0899724468520354</v>
       </c>
       <c r="C73">
-        <v>990.4534252565815</v>
+        <v>985.5757854403562</v>
       </c>
       <c r="D73">
-        <v>1229.566891696249</v>
+        <v>1228.279582393259</v>
       </c>
       <c r="E73">
-        <v>-91.71958488380793</v>
+        <v>-88.12925437057316</v>
       </c>
       <c r="F73">
-        <v>254.9134664396676</v>
+        <v>258.5037969529023</v>
       </c>
       <c r="G73">
         <v>15.8</v>
@@ -7264,28 +7264,28 @@
         <v>48.872</v>
       </c>
       <c r="M73">
-        <v>21.45889750770806</v>
+        <v>21.76113550077437</v>
       </c>
       <c r="N73">
-        <v>27.41310249229194</v>
+        <v>27.11086449922563</v>
       </c>
       <c r="O73">
-        <v>7.401537672918825</v>
+        <v>7.31993341479092</v>
       </c>
       <c r="P73">
-        <v>20.01156481937312</v>
+        <v>19.79093108443471</v>
       </c>
       <c r="Q73">
-        <v>66.87356481937312</v>
+        <v>66.6529310844347</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1596383890387008</v>
+        <v>0.1633102057262041</v>
       </c>
       <c r="T73">
-        <v>2.084990073634724</v>
+        <v>2.152240685755107</v>
       </c>
       <c r="U73">
         <v>0.08418110587651872</v>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.277470218702761</v>
+        <v>2.245838687887444</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7310,22 +7310,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0899724468520354</v>
+        <v>0.09001869370704793</v>
       </c>
       <c r="C74">
-        <v>985.5757854403562</v>
+        <v>980.7008383317482</v>
       </c>
       <c r="D74">
-        <v>1228.279582393259</v>
+        <v>1226.994965797885</v>
       </c>
       <c r="E74">
-        <v>-88.12925437057316</v>
+        <v>-84.53892385733843</v>
       </c>
       <c r="F74">
-        <v>258.5037969529023</v>
+        <v>262.0941274661371</v>
       </c>
       <c r="G74">
         <v>15.8</v>
@@ -7346,28 +7346,28 @@
         <v>48.872</v>
       </c>
       <c r="M74">
-        <v>21.76113550077437</v>
+        <v>22.06337349384068</v>
       </c>
       <c r="N74">
-        <v>27.11086449922563</v>
+        <v>26.80862650615932</v>
       </c>
       <c r="O74">
-        <v>7.31993341479092</v>
+        <v>7.238329156663017</v>
       </c>
       <c r="P74">
-        <v>19.79093108443471</v>
+        <v>19.5702973494963</v>
       </c>
       <c r="Q74">
-        <v>66.6529310844347</v>
+        <v>66.4322973494963</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1633102057262041</v>
+        <v>0.167254008835004</v>
       </c>
       <c r="T74">
-        <v>2.152240685755107</v>
+        <v>2.224472824699222</v>
       </c>
       <c r="U74">
         <v>0.08418110587651872</v>
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.245838687887444</v>
+        <v>2.21507377435474</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7392,22 +7392,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09001869370704793</v>
+        <v>0.09006494056206046</v>
       </c>
       <c r="C75">
-        <v>980.7008383317482</v>
+        <v>975.8285754909457</v>
       </c>
       <c r="D75">
-        <v>1226.994965797885</v>
+        <v>1225.713033470318</v>
       </c>
       <c r="E75">
-        <v>-84.53892385733843</v>
+        <v>-80.94859334410364</v>
       </c>
       <c r="F75">
-        <v>262.0941274661371</v>
+        <v>265.6844579793719</v>
       </c>
       <c r="G75">
         <v>15.8</v>
@@ -7428,28 +7428,28 @@
         <v>48.872</v>
       </c>
       <c r="M75">
-        <v>22.06337349384068</v>
+        <v>22.36561148690699</v>
       </c>
       <c r="N75">
-        <v>26.80862650615932</v>
+        <v>26.50638851309301</v>
       </c>
       <c r="O75">
-        <v>7.238329156663017</v>
+        <v>7.156724898535113</v>
       </c>
       <c r="P75">
-        <v>19.5702973494963</v>
+        <v>19.34966361455789</v>
       </c>
       <c r="Q75">
-        <v>66.4322973494963</v>
+        <v>66.21166361455789</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.167254008835004</v>
+        <v>0.1715011814137117</v>
       </c>
       <c r="T75">
-        <v>2.224472824699222</v>
+        <v>2.302261282023653</v>
       </c>
       <c r="U75">
         <v>0.08418110587651872</v>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.21507377435474</v>
+        <v>2.185140344971567</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7474,22 +7474,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09006494056206046</v>
+        <v>0.09011118741707297</v>
       </c>
       <c r="C76">
-        <v>975.8285754909457</v>
+        <v>970.9589885133719</v>
       </c>
       <c r="D76">
-        <v>1225.713033470318</v>
+        <v>1224.433777005979</v>
       </c>
       <c r="E76">
-        <v>-80.94859334410364</v>
+        <v>-77.35826283086891</v>
       </c>
       <c r="F76">
-        <v>265.6844579793719</v>
+        <v>269.2747884926066</v>
       </c>
       <c r="G76">
         <v>15.8</v>
@@ -7510,28 +7510,28 @@
         <v>48.872</v>
       </c>
       <c r="M76">
-        <v>22.36561148690699</v>
+        <v>22.6678494799733</v>
       </c>
       <c r="N76">
-        <v>26.50638851309301</v>
+        <v>26.2041505200267</v>
       </c>
       <c r="O76">
-        <v>7.156724898535113</v>
+        <v>7.075120640407209</v>
       </c>
       <c r="P76">
-        <v>19.34966361455789</v>
+        <v>19.12902987961949</v>
       </c>
       <c r="Q76">
-        <v>66.21166361455789</v>
+        <v>65.99102987961948</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1715011814137117</v>
+        <v>0.1760881277987159</v>
       </c>
       <c r="T76">
-        <v>2.302261282023653</v>
+        <v>2.386272815934039</v>
       </c>
       <c r="U76">
         <v>0.08418110587651872</v>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.185140344971567</v>
+        <v>2.156005140371946</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7556,22 +7556,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09011118741707297</v>
+        <v>0.0901574342720855</v>
       </c>
       <c r="C77">
-        <v>970.9589885133719</v>
+        <v>966.0920690294969</v>
       </c>
       <c r="D77">
-        <v>1224.433777005979</v>
+        <v>1223.157188035338</v>
       </c>
       <c r="E77">
-        <v>-77.35826283086891</v>
+        <v>-73.76793231763412</v>
       </c>
       <c r="F77">
-        <v>269.2747884926066</v>
+        <v>272.8651190058414</v>
       </c>
       <c r="G77">
         <v>15.8</v>
@@ -7592,28 +7592,28 @@
         <v>48.872</v>
       </c>
       <c r="M77">
-        <v>22.6678494799733</v>
+        <v>22.97008747303962</v>
       </c>
       <c r="N77">
-        <v>26.2041505200267</v>
+        <v>25.90191252696038</v>
       </c>
       <c r="O77">
-        <v>7.075120640407209</v>
+        <v>6.993516382279304</v>
       </c>
       <c r="P77">
-        <v>19.12902987961949</v>
+        <v>18.90839614468108</v>
       </c>
       <c r="Q77">
-        <v>65.99102987961948</v>
+        <v>65.77039614468107</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1760881277987159</v>
+        <v>0.1810573197158039</v>
       </c>
       <c r="T77">
-        <v>2.386272815934039</v>
+        <v>2.477285311003624</v>
       </c>
       <c r="U77">
         <v>0.08418110587651872</v>
@@ -7630,7 +7630,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.156005140371946</v>
+        <v>2.127636651682842</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7638,22 +7638,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0901574342720855</v>
+        <v>0.09020368112709803</v>
       </c>
       <c r="C78">
-        <v>966.0920690294969</v>
+        <v>961.2278087046618</v>
       </c>
       <c r="D78">
-        <v>1223.157188035338</v>
+        <v>1221.883258223738</v>
       </c>
       <c r="E78">
-        <v>-73.76793231763412</v>
+        <v>-70.17760180439939</v>
       </c>
       <c r="F78">
-        <v>272.8651190058414</v>
+        <v>276.4554495190761</v>
       </c>
       <c r="G78">
         <v>15.8</v>
@@ -7674,28 +7674,28 @@
         <v>48.872</v>
       </c>
       <c r="M78">
-        <v>22.97008747303962</v>
+        <v>23.27232546610593</v>
       </c>
       <c r="N78">
-        <v>25.90191252696038</v>
+        <v>25.59967453389407</v>
       </c>
       <c r="O78">
-        <v>6.993516382279304</v>
+        <v>6.9119121241514</v>
       </c>
       <c r="P78">
-        <v>18.90839614468108</v>
+        <v>18.68776240974267</v>
       </c>
       <c r="Q78">
-        <v>65.77039614468107</v>
+        <v>65.54976240974267</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1810573197158039</v>
+        <v>0.1864586152778559</v>
       </c>
       <c r="T78">
-        <v>2.477285311003624</v>
+        <v>2.576211936079259</v>
       </c>
       <c r="U78">
         <v>0.08418110587651872</v>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.127636651682842</v>
+        <v>2.100005006855792</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7720,22 +7720,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09020368112709803</v>
+        <v>0.09024992798211055</v>
       </c>
       <c r="C79">
-        <v>961.2278087046618</v>
+        <v>956.3661992388932</v>
       </c>
       <c r="D79">
-        <v>1221.883258223738</v>
+        <v>1220.611979271204</v>
       </c>
       <c r="E79">
-        <v>-70.17760180439939</v>
+        <v>-66.5872712911646</v>
       </c>
       <c r="F79">
-        <v>276.4554495190761</v>
+        <v>280.0457800323109</v>
       </c>
       <c r="G79">
         <v>15.8</v>
@@ -7756,28 +7756,28 @@
         <v>48.872</v>
       </c>
       <c r="M79">
-        <v>23.27232546610593</v>
+        <v>23.57456345917224</v>
       </c>
       <c r="N79">
-        <v>25.59967453389407</v>
+        <v>25.29743654082776</v>
       </c>
       <c r="O79">
-        <v>6.9119121241514</v>
+        <v>6.830307866023496</v>
       </c>
       <c r="P79">
-        <v>18.68776240974267</v>
+        <v>18.46712867480426</v>
       </c>
       <c r="Q79">
-        <v>65.54976240974267</v>
+        <v>65.32912867480425</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1864586152778559</v>
+        <v>0.1923509377091855</v>
       </c>
       <c r="T79">
-        <v>2.576211936079259</v>
+        <v>2.684131890707225</v>
       </c>
       <c r="U79">
         <v>0.08418110587651872</v>
@@ -7794,7 +7794,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.100005006855792</v>
+        <v>2.073081865742256</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7802,22 +7802,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09024992798211055</v>
+        <v>0.09029617483712307</v>
       </c>
       <c r="C80">
-        <v>956.3661992388932</v>
+        <v>951.5072323667235</v>
       </c>
       <c r="D80">
-        <v>1220.611979271204</v>
+        <v>1219.343342912269</v>
       </c>
       <c r="E80">
-        <v>-66.5872712911646</v>
+        <v>-62.99694077792986</v>
       </c>
       <c r="F80">
-        <v>280.0457800323109</v>
+        <v>283.6361105455456</v>
       </c>
       <c r="G80">
         <v>15.8</v>
@@ -7838,28 +7838,28 @@
         <v>48.872</v>
       </c>
       <c r="M80">
-        <v>23.57456345917224</v>
+        <v>23.87680145223855</v>
       </c>
       <c r="N80">
-        <v>25.29743654082776</v>
+        <v>24.99519854776145</v>
       </c>
       <c r="O80">
-        <v>6.830307866023496</v>
+        <v>6.748703607895593</v>
       </c>
       <c r="P80">
-        <v>18.46712867480426</v>
+        <v>18.24649493986586</v>
       </c>
       <c r="Q80">
-        <v>65.32912867480425</v>
+        <v>65.10849493986586</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1923509377091855</v>
+        <v>0.1988044337054035</v>
       </c>
       <c r="T80">
-        <v>2.684131890707225</v>
+        <v>2.80232993625214</v>
       </c>
       <c r="U80">
         <v>0.08418110587651872</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.073081865742256</v>
+        <v>2.046840323137924</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7884,22 +7884,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09029617483712307</v>
+        <v>0.0903424216921356</v>
       </c>
       <c r="C81">
-        <v>951.5072323667235</v>
+        <v>946.6508998570118</v>
       </c>
       <c r="D81">
-        <v>1219.343342912269</v>
+        <v>1218.077340915792</v>
       </c>
       <c r="E81">
-        <v>-62.99694077792986</v>
+        <v>-59.40661026469513</v>
       </c>
       <c r="F81">
-        <v>283.6361105455456</v>
+        <v>287.2264410587804</v>
       </c>
       <c r="G81">
         <v>15.8</v>
@@ -7920,28 +7920,28 @@
         <v>48.872</v>
       </c>
       <c r="M81">
-        <v>23.87680145223855</v>
+        <v>24.17903944530486</v>
       </c>
       <c r="N81">
-        <v>24.99519854776145</v>
+        <v>24.69296055469514</v>
       </c>
       <c r="O81">
-        <v>6.748703607895593</v>
+        <v>6.66709934976769</v>
       </c>
       <c r="P81">
-        <v>18.24649493986586</v>
+        <v>18.02586120492746</v>
       </c>
       <c r="Q81">
-        <v>65.10849493986586</v>
+        <v>64.88786120492745</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1988044337054035</v>
+        <v>0.2059032793012434</v>
       </c>
       <c r="T81">
-        <v>2.80232993625214</v>
+        <v>2.932347786351547</v>
       </c>
       <c r="U81">
         <v>0.08418110587651872</v>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.046840323137924</v>
+        <v>2.0212548190987</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7966,22 +7966,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0903424216921356</v>
+        <v>0.09878512854714813</v>
       </c>
       <c r="C82">
-        <v>946.6508998570118</v>
+        <v>748.9708275979547</v>
       </c>
       <c r="D82">
-        <v>1218.077340915792</v>
+        <v>1023.98759916997</v>
       </c>
       <c r="E82">
-        <v>-59.40661026469513</v>
+        <v>-55.81627975146034</v>
       </c>
       <c r="F82">
-        <v>287.2264410587804</v>
+        <v>290.8167715720152</v>
       </c>
       <c r="G82">
         <v>15.8</v>
@@ -8002,45 +8002,45 @@
         <v>48.872</v>
       </c>
       <c r="M82">
-        <v>24.17903944530486</v>
+        <v>28.61087559469379</v>
       </c>
       <c r="N82">
-        <v>24.69296055469514</v>
+        <v>20.26112440530621</v>
       </c>
       <c r="O82">
-        <v>6.66709934976769</v>
+        <v>5.470503589432678</v>
       </c>
       <c r="P82">
-        <v>18.02586120492746</v>
+        <v>14.79062081587353</v>
       </c>
       <c r="Q82">
-        <v>64.88786120492745</v>
+        <v>61.65262081587353</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2059032793012434</v>
+        <v>0.2137493718019085</v>
       </c>
       <c r="T82">
-        <v>2.932347786351547</v>
+        <v>3.076051725935101</v>
       </c>
       <c r="U82">
-        <v>0.08418110587651872</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V82">
         <v>0.27</v>
       </c>
       <c r="W82">
-        <v>0.06145220728985867</v>
+        <v>0.07181820728985867</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.0212548190987</v>
+        <v>1.708161633790189</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8048,22 +8048,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09878512854714813</v>
+        <v>0.09893503540216067</v>
       </c>
       <c r="C83">
-        <v>748.9708275979547</v>
+        <v>742.4915790779547</v>
       </c>
       <c r="D83">
-        <v>1023.98759916997</v>
+        <v>1021.098681163205</v>
       </c>
       <c r="E83">
-        <v>-55.81627975146034</v>
+        <v>-52.22594923822561</v>
       </c>
       <c r="F83">
-        <v>290.8167715720152</v>
+        <v>294.4071020852499</v>
       </c>
       <c r="G83">
         <v>15.8</v>
@@ -8084,28 +8084,28 @@
         <v>48.872</v>
       </c>
       <c r="M83">
-        <v>28.61087559469379</v>
+        <v>28.96409628104803</v>
       </c>
       <c r="N83">
-        <v>20.26112440530621</v>
+        <v>19.90790371895197</v>
       </c>
       <c r="O83">
-        <v>5.470503589432678</v>
+        <v>5.375134004117032</v>
       </c>
       <c r="P83">
-        <v>14.79062081587353</v>
+        <v>14.53276971483494</v>
       </c>
       <c r="Q83">
-        <v>61.65262081587353</v>
+        <v>61.39476971483494</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2137493718019085</v>
+        <v>0.2224672523582031</v>
       </c>
       <c r="T83">
-        <v>3.076051725935101</v>
+        <v>3.235722769916829</v>
       </c>
       <c r="U83">
         <v>0.09838110587651873</v>
@@ -8122,7 +8122,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.708161633790189</v>
+        <v>1.687330394353724</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8130,22 +8130,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09893503540216067</v>
+        <v>0.09908494225717319</v>
       </c>
       <c r="C84">
-        <v>742.4915790779547</v>
+        <v>736.0285853794651</v>
       </c>
       <c r="D84">
-        <v>1021.098681163205</v>
+        <v>1018.22601797795</v>
       </c>
       <c r="E84">
-        <v>-52.22594923822561</v>
+        <v>-48.63561872499082</v>
       </c>
       <c r="F84">
-        <v>294.4071020852499</v>
+        <v>297.9974325984847</v>
       </c>
       <c r="G84">
         <v>15.8</v>
@@ -8166,28 +8166,28 @@
         <v>48.872</v>
       </c>
       <c r="M84">
-        <v>28.96409628104803</v>
+        <v>29.31731696740228</v>
       </c>
       <c r="N84">
-        <v>19.90790371895197</v>
+        <v>19.55468303259772</v>
       </c>
       <c r="O84">
-        <v>5.375134004117032</v>
+        <v>5.279764418801386</v>
       </c>
       <c r="P84">
-        <v>14.53276971483494</v>
+        <v>14.27491861379634</v>
       </c>
       <c r="Q84">
-        <v>61.39476971483494</v>
+        <v>61.13691861379633</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2224672523582031</v>
+        <v>0.2322107659211206</v>
       </c>
       <c r="T84">
-        <v>3.235722769916829</v>
+        <v>3.41417864260229</v>
       </c>
       <c r="U84">
         <v>0.09838110587651873</v>
@@ -8204,7 +8204,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.687330394353724</v>
+        <v>1.66700111249404</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8212,22 +8212,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09908494225717319</v>
+        <v>0.09923484911218572</v>
       </c>
       <c r="C85">
-        <v>736.0285853794651</v>
+        <v>729.5817096979913</v>
       </c>
       <c r="D85">
-        <v>1018.22601797795</v>
+        <v>1015.369472809711</v>
       </c>
       <c r="E85">
-        <v>-48.63561872499082</v>
+        <v>-45.04528821175609</v>
       </c>
       <c r="F85">
-        <v>297.9974325984847</v>
+        <v>301.5877631117194</v>
       </c>
       <c r="G85">
         <v>15.8</v>
@@ -8248,28 +8248,28 @@
         <v>48.872</v>
       </c>
       <c r="M85">
-        <v>29.31731696740228</v>
+        <v>29.67053765375652</v>
       </c>
       <c r="N85">
-        <v>19.55468303259772</v>
+        <v>19.20146234624348</v>
       </c>
       <c r="O85">
-        <v>5.279764418801386</v>
+        <v>5.18439483348574</v>
       </c>
       <c r="P85">
-        <v>14.27491861379634</v>
+        <v>14.01706751275774</v>
       </c>
       <c r="Q85">
-        <v>61.13691861379633</v>
+        <v>60.87906751275774</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2322107659211206</v>
+        <v>0.2431722186794028</v>
       </c>
       <c r="T85">
-        <v>3.41417864260229</v>
+        <v>3.614941499373433</v>
       </c>
       <c r="U85">
         <v>0.09838110587651873</v>
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.66700111249404</v>
+        <v>1.647155861154826</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8294,22 +8294,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09923484911218572</v>
+        <v>0.09938475596719826</v>
       </c>
       <c r="C86">
-        <v>729.5817096979913</v>
+        <v>723.1508167599164</v>
       </c>
       <c r="D86">
-        <v>1015.369472809711</v>
+        <v>1012.528910384871</v>
       </c>
       <c r="E86">
-        <v>-45.04528821175609</v>
+        <v>-41.45495769852135</v>
       </c>
       <c r="F86">
-        <v>301.5877631117194</v>
+        <v>305.1780936249542</v>
       </c>
       <c r="G86">
         <v>15.8</v>
@@ -8330,28 +8330,28 @@
         <v>48.872</v>
       </c>
       <c r="M86">
-        <v>29.67053765375652</v>
+        <v>30.02375834011076</v>
       </c>
       <c r="N86">
-        <v>19.20146234624348</v>
+        <v>18.84824165988924</v>
       </c>
       <c r="O86">
-        <v>5.18439483348574</v>
+        <v>5.089025248170095</v>
       </c>
       <c r="P86">
-        <v>14.01706751275774</v>
+        <v>13.75921641171914</v>
       </c>
       <c r="Q86">
-        <v>60.87906751275774</v>
+        <v>60.62121641171914</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2431722186794027</v>
+        <v>0.2555951984721225</v>
       </c>
       <c r="T86">
-        <v>3.61494149937343</v>
+        <v>3.842472737047391</v>
       </c>
       <c r="U86">
         <v>0.09838110587651873</v>
@@ -8368,7 +8368,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.647155861154826</v>
+        <v>1.627777556905945</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8376,22 +8376,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09938475596719826</v>
+        <v>0.09953466282221077</v>
       </c>
       <c r="C87">
-        <v>723.1508167599164</v>
+        <v>716.7357728011493</v>
       </c>
       <c r="D87">
-        <v>1012.528910384871</v>
+        <v>1009.704196939338</v>
       </c>
       <c r="E87">
-        <v>-41.45495769852135</v>
+        <v>-37.86462718528662</v>
       </c>
       <c r="F87">
-        <v>305.1780936249542</v>
+        <v>308.7684241381889</v>
       </c>
       <c r="G87">
         <v>15.8</v>
@@ -8412,28 +8412,28 @@
         <v>48.872</v>
       </c>
       <c r="M87">
-        <v>30.02375834011076</v>
+        <v>30.376979026465</v>
       </c>
       <c r="N87">
-        <v>18.84824165988924</v>
+        <v>18.495020973535</v>
       </c>
       <c r="O87">
-        <v>5.089025248170095</v>
+        <v>4.99365566285445</v>
       </c>
       <c r="P87">
-        <v>13.75921641171914</v>
+        <v>13.50136531068055</v>
       </c>
       <c r="Q87">
-        <v>60.62121641171914</v>
+        <v>60.36336531068054</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2555951984721225</v>
+        <v>0.2697928896638022</v>
       </c>
       <c r="T87">
-        <v>3.842472737047391</v>
+        <v>4.102508437246205</v>
       </c>
       <c r="U87">
         <v>0.09838110587651873</v>
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.627777556905945</v>
+        <v>1.608849910895411</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8458,22 +8458,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09953466282221077</v>
+        <v>0.09968456967722331</v>
       </c>
       <c r="C88">
-        <v>716.7357728011493</v>
+        <v>710.3364455461235</v>
       </c>
       <c r="D88">
-        <v>1009.704196939338</v>
+        <v>1006.895200197547</v>
       </c>
       <c r="E88">
-        <v>-37.86462718528662</v>
+        <v>-34.27429667205183</v>
       </c>
       <c r="F88">
-        <v>308.7684241381889</v>
+        <v>312.3587546514237</v>
       </c>
       <c r="G88">
         <v>15.8</v>
@@ -8494,28 +8494,28 @@
         <v>48.872</v>
       </c>
       <c r="M88">
-        <v>30.376979026465</v>
+        <v>30.73019971281925</v>
       </c>
       <c r="N88">
-        <v>18.495020973535</v>
+        <v>18.14180028718075</v>
       </c>
       <c r="O88">
-        <v>4.99365566285445</v>
+        <v>4.898286077538803</v>
       </c>
       <c r="P88">
-        <v>13.50136531068055</v>
+        <v>13.24351420964195</v>
       </c>
       <c r="Q88">
-        <v>60.36336531068054</v>
+        <v>60.10551420964194</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2697928896638022</v>
+        <v>0.2861748410388173</v>
       </c>
       <c r="T88">
-        <v>4.102508437246205</v>
+        <v>4.402549629783296</v>
       </c>
       <c r="U88">
         <v>0.09838110587651873</v>
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.608849910895411</v>
+        <v>1.59035738318397</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8540,22 +8540,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09968456967722331</v>
+        <v>0.09983447653223583</v>
       </c>
       <c r="C89">
-        <v>710.3364455461235</v>
+        <v>703.9527041871528</v>
       </c>
       <c r="D89">
-        <v>1006.895200197547</v>
+        <v>1004.101789351811</v>
       </c>
       <c r="E89">
-        <v>-34.27429667205183</v>
+        <v>-30.6839661588171</v>
       </c>
       <c r="F89">
-        <v>312.3587546514237</v>
+        <v>315.9490851646584</v>
       </c>
       <c r="G89">
         <v>15.8</v>
@@ -8576,28 +8576,28 @@
         <v>48.872</v>
       </c>
       <c r="M89">
-        <v>30.73019971281925</v>
+        <v>31.08342039917349</v>
       </c>
       <c r="N89">
-        <v>18.14180028718075</v>
+        <v>17.78857960082651</v>
       </c>
       <c r="O89">
-        <v>4.898286077538803</v>
+        <v>4.802916492223158</v>
       </c>
       <c r="P89">
-        <v>13.24351420964195</v>
+        <v>12.98566310860335</v>
       </c>
       <c r="Q89">
-        <v>60.10551420964194</v>
+        <v>59.84766310860334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2861748410388173</v>
+        <v>0.3052871176430016</v>
       </c>
       <c r="T89">
-        <v>4.402549629783296</v>
+        <v>4.752597687743238</v>
       </c>
       <c r="U89">
         <v>0.09838110587651873</v>
@@ -8614,7 +8614,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.59035738318397</v>
+        <v>1.572285140193243</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8622,22 +8622,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09983447653223583</v>
+        <v>0.09998438338724835</v>
       </c>
       <c r="C90">
-        <v>703.9527041871528</v>
+        <v>697.5844193641232</v>
       </c>
       <c r="D90">
-        <v>1004.101789351811</v>
+        <v>1001.323835042016</v>
       </c>
       <c r="E90">
-        <v>-30.6839661588171</v>
+        <v>-27.09363564558231</v>
       </c>
       <c r="F90">
-        <v>315.9490851646584</v>
+        <v>319.5394156778932</v>
       </c>
       <c r="G90">
         <v>15.8</v>
@@ -8658,28 +8658,28 @@
         <v>48.872</v>
       </c>
       <c r="M90">
-        <v>31.08342039917349</v>
+        <v>31.43664108552774</v>
       </c>
       <c r="N90">
-        <v>17.78857960082651</v>
+        <v>17.43535891447226</v>
       </c>
       <c r="O90">
-        <v>4.802916492223158</v>
+        <v>4.707546906907511</v>
       </c>
       <c r="P90">
-        <v>12.98566310860335</v>
+        <v>12.72781200756475</v>
       </c>
       <c r="Q90">
-        <v>59.84766310860334</v>
+        <v>59.58981200756475</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3052871176430016</v>
+        <v>0.3278743536297649</v>
       </c>
       <c r="T90">
-        <v>4.752597687743238</v>
+        <v>5.166290847150441</v>
       </c>
       <c r="U90">
         <v>0.09838110587651873</v>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.572285140193243</v>
+        <v>1.554619015022532</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8704,22 +8704,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09998438338724835</v>
+        <v>0.1001342902422609</v>
       </c>
       <c r="C91">
-        <v>697.5844193641232</v>
+        <v>691.2314631445261</v>
       </c>
       <c r="D91">
-        <v>1001.323835042016</v>
+        <v>998.561209335654</v>
       </c>
       <c r="E91">
-        <v>-27.09363564558231</v>
+        <v>-23.50330513234758</v>
       </c>
       <c r="F91">
-        <v>319.5394156778932</v>
+        <v>323.1297461911279</v>
       </c>
       <c r="G91">
         <v>15.8</v>
@@ -8740,28 +8740,28 @@
         <v>48.872</v>
       </c>
       <c r="M91">
-        <v>31.43664108552774</v>
+        <v>31.78986177188198</v>
       </c>
       <c r="N91">
-        <v>17.43535891447226</v>
+        <v>17.08213822811802</v>
       </c>
       <c r="O91">
-        <v>4.707546906907511</v>
+        <v>4.612177321591865</v>
       </c>
       <c r="P91">
-        <v>12.72781200756475</v>
+        <v>12.46996090652615</v>
       </c>
       <c r="Q91">
-        <v>59.58981200756475</v>
+        <v>59.33196090652615</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3278743536297649</v>
+        <v>0.3549790368138808</v>
       </c>
       <c r="T91">
-        <v>5.166290847150441</v>
+        <v>5.662722638439084</v>
       </c>
       <c r="U91">
         <v>0.09838110587651873</v>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.554619015022532</v>
+        <v>1.537345470411171</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8786,22 +8786,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1001342902422609</v>
+        <v>0.1002841970972734</v>
       </c>
       <c r="C92">
-        <v>691.2314631445261</v>
+        <v>684.8937090038171</v>
       </c>
       <c r="D92">
-        <v>998.561209335654</v>
+        <v>995.8137857081798</v>
       </c>
       <c r="E92">
-        <v>-23.50330513234758</v>
+        <v>-19.91297461911279</v>
       </c>
       <c r="F92">
-        <v>323.1297461911279</v>
+        <v>326.7200767043627</v>
       </c>
       <c r="G92">
         <v>15.8</v>
@@ -8822,28 +8822,28 @@
         <v>48.872</v>
       </c>
       <c r="M92">
-        <v>31.78986177188198</v>
+        <v>32.14308245823623</v>
       </c>
       <c r="N92">
-        <v>17.08213822811802</v>
+        <v>16.72891754176377</v>
       </c>
       <c r="O92">
-        <v>4.612177321591865</v>
+        <v>4.516807736276219</v>
       </c>
       <c r="P92">
-        <v>12.46996090652615</v>
+        <v>12.21210980548755</v>
       </c>
       <c r="Q92">
-        <v>59.33196090652615</v>
+        <v>59.07410980548755</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3549790368138808</v>
+        <v>0.3881069829278002</v>
       </c>
       <c r="T92">
-        <v>5.662722638439084</v>
+        <v>6.269472605569649</v>
       </c>
       <c r="U92">
         <v>0.09838110587651873</v>
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.537345470411171</v>
+        <v>1.520451564142916</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8868,22 +8868,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1002841970972734</v>
+        <v>0.1004341039522859</v>
       </c>
       <c r="C93">
-        <v>684.8937090038171</v>
+        <v>678.5710318061008</v>
       </c>
       <c r="D93">
-        <v>995.8137857081798</v>
+        <v>993.0814390236983</v>
       </c>
       <c r="E93">
-        <v>-19.91297461911279</v>
+        <v>-16.32264410587806</v>
       </c>
       <c r="F93">
-        <v>326.7200767043627</v>
+        <v>330.3104072175975</v>
       </c>
       <c r="G93">
         <v>15.8</v>
@@ -8904,28 +8904,28 @@
         <v>48.872</v>
       </c>
       <c r="M93">
-        <v>32.14308245823623</v>
+        <v>32.49630314459047</v>
       </c>
       <c r="N93">
-        <v>16.72891754176377</v>
+        <v>16.37569685540953</v>
       </c>
       <c r="O93">
-        <v>4.516807736276219</v>
+        <v>4.421438150960573</v>
       </c>
       <c r="P93">
-        <v>12.21210980548755</v>
+        <v>11.95425870444896</v>
       </c>
       <c r="Q93">
-        <v>59.07410980548755</v>
+        <v>58.81625870444896</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3881069829278002</v>
+        <v>0.4295169155701996</v>
       </c>
       <c r="T93">
-        <v>6.269472605569649</v>
+        <v>7.027910064482855</v>
       </c>
       <c r="U93">
         <v>0.09838110587651873</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.520451564142916</v>
+        <v>1.50392491670658</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8950,22 +8950,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1004341039522859</v>
+        <v>0.1419413054589383</v>
       </c>
       <c r="C94">
-        <v>678.5710318061008</v>
+        <v>246.2364565033265</v>
       </c>
       <c r="D94">
-        <v>993.0814390236983</v>
+        <v>564.3371942341588</v>
       </c>
       <c r="E94">
-        <v>-16.32264410587806</v>
+        <v>-12.73231359264327</v>
       </c>
       <c r="F94">
-        <v>330.3104072175975</v>
+        <v>333.9007377308322</v>
       </c>
       <c r="G94">
         <v>15.8</v>
@@ -8986,45 +8986,45 @@
         <v>48.872</v>
       </c>
       <c r="M94">
-        <v>32.49630314459047</v>
+        <v>51.81508573405599</v>
       </c>
       <c r="N94">
-        <v>16.37569685540953</v>
+        <v>-2.943085734055991</v>
       </c>
       <c r="O94">
-        <v>4.421438150960573</v>
+        <v>-0.7946331481951177</v>
       </c>
       <c r="P94">
-        <v>11.95425870444896</v>
+        <v>-2.148452585860873</v>
       </c>
       <c r="Q94">
-        <v>58.81625870444896</v>
+        <v>44.71354741413912</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4295169155701996</v>
+        <v>0.4910799090664245</v>
       </c>
       <c r="T94">
-        <v>7.027910064482855</v>
+        <v>8.155457910396514</v>
       </c>
       <c r="U94">
-        <v>0.09838110587651873</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V94">
-        <v>0.27</v>
+        <v>0.2546640580260039</v>
       </c>
       <c r="W94">
-        <v>0.07181820728985867</v>
+        <v>0.1156620557250415</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>1.50392491670658</v>
+        <v>0.9432002149111254</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9032,22 +9032,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1419413054589383</v>
+        <v>0.1430351165177035</v>
       </c>
       <c r="C95">
-        <v>246.2364565033265</v>
+        <v>236.2978200895844</v>
       </c>
       <c r="D95">
-        <v>564.3371942341588</v>
+        <v>557.9888883336514</v>
       </c>
       <c r="E95">
-        <v>-12.73231359264327</v>
+        <v>-9.141983079408533</v>
       </c>
       <c r="F95">
-        <v>333.9007377308322</v>
+        <v>337.491068244067</v>
       </c>
       <c r="G95">
         <v>15.8</v>
@@ -9068,37 +9068,37 @@
         <v>48.872</v>
       </c>
       <c r="M95">
-        <v>51.81508573405599</v>
+        <v>52.37223719356196</v>
       </c>
       <c r="N95">
-        <v>-2.943085734055991</v>
+        <v>-3.500237193561965</v>
       </c>
       <c r="O95">
-        <v>-0.7946331481951177</v>
+        <v>-0.9450640422617306</v>
       </c>
       <c r="P95">
-        <v>-2.148452585860873</v>
+        <v>-2.555173151300234</v>
       </c>
       <c r="Q95">
-        <v>44.71354741413912</v>
+        <v>44.30682684869976</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4910799090664245</v>
+        <v>0.5652932272441621</v>
       </c>
       <c r="T95">
-        <v>8.155457910396514</v>
+        <v>9.514700895462603</v>
       </c>
       <c r="U95">
         <v>0.1551811058765187</v>
       </c>
       <c r="V95">
-        <v>0.2546640580260039</v>
+        <v>0.2519548659193443</v>
       </c>
       <c r="W95">
-        <v>0.1156620557250415</v>
+        <v>0.1160824711521849</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9432002149111254</v>
+        <v>0.9331661700716455</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9114,22 +9114,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1430351165177035</v>
+        <v>0.1441289275764687</v>
       </c>
       <c r="C96">
-        <v>236.2978200895844</v>
+        <v>226.5004207943498</v>
       </c>
       <c r="D96">
-        <v>557.9888883336514</v>
+        <v>551.7818195516516</v>
       </c>
       <c r="E96">
-        <v>-9.141983079408533</v>
+        <v>-5.5516525661738</v>
       </c>
       <c r="F96">
-        <v>337.491068244067</v>
+        <v>341.0813987573017</v>
       </c>
       <c r="G96">
         <v>15.8</v>
@@ -9150,37 +9150,37 @@
         <v>48.872</v>
       </c>
       <c r="M96">
-        <v>52.37223719356196</v>
+        <v>52.92938865306794</v>
       </c>
       <c r="N96">
-        <v>-3.500237193561965</v>
+        <v>-4.057388653067939</v>
       </c>
       <c r="O96">
-        <v>-0.9450640422617306</v>
+        <v>-1.095494936328343</v>
       </c>
       <c r="P96">
-        <v>-2.555173151300234</v>
+        <v>-2.961893716739596</v>
       </c>
       <c r="Q96">
-        <v>44.30682684869976</v>
+        <v>43.9001062832604</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5652932272441621</v>
+        <v>0.6691918726929947</v>
       </c>
       <c r="T96">
-        <v>9.514700895462603</v>
+        <v>11.41764107455513</v>
       </c>
       <c r="U96">
         <v>0.1551811058765187</v>
       </c>
       <c r="V96">
-        <v>0.2519548659193443</v>
+        <v>0.2493027094359828</v>
       </c>
       <c r="W96">
-        <v>0.1160824711521849</v>
+        <v>0.1164940357282305</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9331661700716455</v>
+        <v>0.9233433682814177</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9196,22 +9196,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1441289275764687</v>
+        <v>0.1452227386352339</v>
       </c>
       <c r="C97">
-        <v>226.5004207943498</v>
+        <v>216.8395971068574</v>
       </c>
       <c r="D97">
-        <v>551.7818195516516</v>
+        <v>545.7113263773939</v>
       </c>
       <c r="E97">
-        <v>-5.5516525661738</v>
+        <v>-1.961322052939011</v>
       </c>
       <c r="F97">
-        <v>341.0813987573017</v>
+        <v>344.6717292705365</v>
       </c>
       <c r="G97">
         <v>15.8</v>
@@ -9232,37 +9232,37 @@
         <v>48.872</v>
       </c>
       <c r="M97">
-        <v>52.92938865306794</v>
+        <v>53.48654011257393</v>
       </c>
       <c r="N97">
-        <v>-4.057388653067939</v>
+        <v>-4.614540112573927</v>
       </c>
       <c r="O97">
-        <v>-1.095494936328343</v>
+        <v>-1.24592583039496</v>
       </c>
       <c r="P97">
-        <v>-2.961893716739596</v>
+        <v>-3.368614282178966</v>
       </c>
       <c r="Q97">
-        <v>43.9001062832604</v>
+        <v>43.49338571782103</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6691918726929947</v>
+        <v>0.8250398408662438</v>
       </c>
       <c r="T97">
-        <v>11.41764107455513</v>
+        <v>14.27205134319392</v>
       </c>
       <c r="U97">
         <v>0.1551811058765187</v>
       </c>
       <c r="V97">
-        <v>0.2493027094359828</v>
+        <v>0.2467058062126913</v>
       </c>
       <c r="W97">
-        <v>0.1164940357282305</v>
+        <v>0.1168970260422752</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9233433682814177</v>
+        <v>0.9137252081951528</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9278,22 +9278,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1452227386352339</v>
+        <v>0.146316549693999</v>
       </c>
       <c r="C98">
-        <v>216.8395971068576</v>
+        <v>207.3108904207223</v>
       </c>
       <c r="D98">
-        <v>545.7113263773941</v>
+        <v>539.7729502044936</v>
       </c>
       <c r="E98">
-        <v>-1.961322052939067</v>
+        <v>1.629008460295722</v>
       </c>
       <c r="F98">
-        <v>344.6717292705364</v>
+        <v>348.2620597837712</v>
       </c>
       <c r="G98">
         <v>15.8</v>
@@ -9314,37 +9314,37 @@
         <v>48.872</v>
       </c>
       <c r="M98">
-        <v>53.48654011257392</v>
+        <v>54.0436915720799</v>
       </c>
       <c r="N98">
-        <v>-4.61454011257392</v>
+        <v>-5.171691572079901</v>
       </c>
       <c r="O98">
-        <v>-1.245925830394959</v>
+        <v>-1.396356724461573</v>
       </c>
       <c r="P98">
-        <v>-3.368614282178961</v>
+        <v>-3.775334847618327</v>
       </c>
       <c r="Q98">
-        <v>43.49338571782103</v>
+        <v>43.08666515238167</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8250398408662417</v>
+        <v>1.084786454488322</v>
       </c>
       <c r="T98">
-        <v>14.27205134319388</v>
+        <v>19.02940179092517</v>
       </c>
       <c r="U98">
         <v>0.1551811058765187</v>
       </c>
       <c r="V98">
-        <v>0.2467058062126913</v>
+        <v>0.2441624473857563</v>
       </c>
       <c r="W98">
-        <v>0.1168970260422752</v>
+        <v>0.1172917072776797</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9137252081951529</v>
+        <v>0.9043053606879863</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9360,22 +9360,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.146316549693999</v>
+        <v>0.1474103607527642</v>
       </c>
       <c r="C99">
-        <v>207.3108904207223</v>
+        <v>197.9100341128537</v>
       </c>
       <c r="D99">
-        <v>539.7729502044936</v>
+        <v>533.9624244098598</v>
       </c>
       <c r="E99">
-        <v>1.629008460295722</v>
+        <v>5.219338973530455</v>
       </c>
       <c r="F99">
-        <v>348.2620597837712</v>
+        <v>351.852390297006</v>
       </c>
       <c r="G99">
         <v>15.8</v>
@@ -9396,37 +9396,37 @@
         <v>48.872</v>
       </c>
       <c r="M99">
-        <v>54.0436915720799</v>
+        <v>54.60084303158587</v>
       </c>
       <c r="N99">
-        <v>-5.171691572079901</v>
+        <v>-5.728843031585875</v>
       </c>
       <c r="O99">
-        <v>-1.396356724461573</v>
+        <v>-1.546787618528186</v>
       </c>
       <c r="P99">
-        <v>-3.775334847618327</v>
+        <v>-4.182055413057689</v>
       </c>
       <c r="Q99">
-        <v>43.08666515238167</v>
+        <v>42.67994458694231</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.084786454488322</v>
+        <v>1.604279681732484</v>
       </c>
       <c r="T99">
-        <v>19.02940179092517</v>
+        <v>28.54410268638776</v>
       </c>
       <c r="U99">
         <v>0.1551811058765187</v>
       </c>
       <c r="V99">
-        <v>0.2441624473857563</v>
+        <v>0.2416709938410037</v>
       </c>
       <c r="W99">
-        <v>0.1172917072776797</v>
+        <v>0.1176783337939944</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.9043053606879863</v>
+        <v>0.8950777549666804</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9442,22 +9442,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1474103607527642</v>
+        <v>0.1485041718115294</v>
       </c>
       <c r="C100">
-        <v>197.9100341128537</v>
+        <v>188.6329433202375</v>
       </c>
       <c r="D100">
-        <v>533.9624244098598</v>
+        <v>528.2756641304783</v>
       </c>
       <c r="E100">
-        <v>5.219338973530455</v>
+        <v>8.809669486765245</v>
       </c>
       <c r="F100">
-        <v>351.852390297006</v>
+        <v>355.4427208102408</v>
       </c>
       <c r="G100">
         <v>15.8</v>
@@ -9478,37 +9478,37 @@
         <v>48.872</v>
       </c>
       <c r="M100">
-        <v>54.60084303158587</v>
+        <v>55.15799449109186</v>
       </c>
       <c r="N100">
-        <v>-5.728843031585875</v>
+        <v>-6.285994491091856</v>
       </c>
       <c r="O100">
-        <v>-1.546787618528186</v>
+        <v>-1.697218512594801</v>
       </c>
       <c r="P100">
-        <v>-4.182055413057689</v>
+        <v>-4.588775978497054</v>
       </c>
       <c r="Q100">
-        <v>42.67994458694231</v>
+        <v>42.27322402150294</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.604279681732484</v>
+        <v>3.162759363464967</v>
       </c>
       <c r="T100">
-        <v>28.54410268638776</v>
+        <v>57.08820537277551</v>
       </c>
       <c r="U100">
         <v>0.1551811058765187</v>
       </c>
       <c r="V100">
-        <v>0.2416709938410037</v>
+        <v>0.2392298726910946</v>
       </c>
       <c r="W100">
-        <v>0.1176783337939944</v>
+        <v>0.1180571496736159</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9516,91 +9516,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8950777549666804</v>
+        <v>0.8860365655225725</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1485041718115294</v>
-      </c>
-      <c r="C101">
-        <v>188.6329433202375</v>
-      </c>
-      <c r="D101">
-        <v>528.2756641304783</v>
-      </c>
-      <c r="E101">
-        <v>8.809669486765245</v>
-      </c>
-      <c r="F101">
-        <v>355.4427208102408</v>
-      </c>
-      <c r="G101">
-        <v>15.8</v>
-      </c>
-      <c r="H101">
-        <v>12.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>95.73399999999999</v>
-      </c>
-      <c r="K101">
-        <v>46.86199999999999</v>
-      </c>
-      <c r="L101">
-        <v>48.872</v>
-      </c>
-      <c r="M101">
-        <v>55.15799449109186</v>
-      </c>
-      <c r="N101">
-        <v>-6.285994491091856</v>
-      </c>
-      <c r="O101">
-        <v>-1.697218512594801</v>
-      </c>
-      <c r="P101">
-        <v>-4.588775978497054</v>
-      </c>
-      <c r="Q101">
-        <v>42.27322402150294</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.162759363464967</v>
-      </c>
-      <c r="T101">
-        <v>57.08820537277551</v>
-      </c>
-      <c r="U101">
-        <v>0.1551811058765187</v>
-      </c>
-      <c r="V101">
-        <v>0.2392298726910946</v>
-      </c>
-      <c r="W101">
-        <v>0.1180571496736159</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8860365655225725</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
